--- a/01_Thermal/B_results/single_annular_var_params_pchip.xlsx
+++ b/01_Thermal/B_results/single_annular_var_params_pchip.xlsx
@@ -460,16 +460,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.001539755334519</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3642249850962551</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0899061960515843</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E2" t="n">
-        <v>9.999999999999948e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>0.01</v>
       </c>
       <c r="B3" t="n">
-        <v>5.970738189027601</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3580162252882962</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09302392710223431</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E3" t="n">
-        <v>9.999999999999948e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>0.02</v>
       </c>
       <c r="B4" t="n">
-        <v>5.936345027767276</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3522042745090387</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09643683302515241</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E4" t="n">
-        <v>9.999999999999948e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>0.03</v>
       </c>
       <c r="B5" t="n">
-        <v>5.898667385398209</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3467806539252937</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1001517323967928</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E5" t="n">
-        <v>9.999999999999949e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>0.04</v>
       </c>
       <c r="B6" t="n">
-        <v>5.858011884312136</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3417368847038723</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1041754251461358</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E6" t="n">
-        <v>9.999999999999949e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>0.05</v>
       </c>
       <c r="B7" t="n">
-        <v>5.814683190840776</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3370644880115858</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1085144114659292</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E7" t="n">
-        <v>9.99999999999995e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>0.06</v>
       </c>
       <c r="B8" t="n">
-        <v>5.768982691043611</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3327549850152455</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1131745854758975</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E8" t="n">
-        <v>9.999999999999952e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9" t="n">
-        <v>5.721207308513337</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3287998968816623</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1181609010261045</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E9" t="n">
-        <v>9.999999999999953e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>0.08</v>
       </c>
       <c r="B10" t="n">
-        <v>5.671648464227706</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3251907447776475</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1234770078432263</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E10" t="n">
-        <v>9.999999999999954e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>0.09</v>
       </c>
       <c r="B11" t="n">
-        <v>5.620591177056705</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3219190498700124</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1291248571944602</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E11" t="n">
-        <v>9.999999999999954e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>5.568313302292392</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C12" t="n">
-        <v>0.318976333325568</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1351042773991909</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E12" t="n">
-        <v>9.999999999999958e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>0.11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.515084904505744</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3163541163111256</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1414125208780398</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E13" t="n">
-        <v>9.99999999999996e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>0.12</v>
       </c>
       <c r="B14" t="n">
-        <v>5.46116776014776</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3140439199934963</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1480437860060592</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E14" t="n">
-        <v>9.999999999999961e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>0.13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.406814984596233</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3120372655394914</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1549887188356526</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E15" t="n">
-        <v>9.999999999999964e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>0.14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.352270777798034</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3103256741159219</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1622339017673958</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E16" t="n">
-        <v>9.999999999999965e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>0.15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.29777028226095</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3089006668895991</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1697613384507005</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E17" t="n">
-        <v>9.999999999999968e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>0.16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.243539546899721</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3077537650273342</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1775479465511496</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E18" t="n">
-        <v>9.999999999999971e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>0.17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.189795590127098</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3068764896959383</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1855650724673234</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E19" t="n">
-        <v>9.999999999999972e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>0.18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.136746555592141</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3062603620622226</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1937780445349008</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E20" t="n">
-        <v>9.999999999999975e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>0.19</v>
       </c>
       <c r="B21" t="n">
-        <v>5.084591954093222</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3058969032929984</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2021457836142272</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E21" t="n">
-        <v>9.999999999999976e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="22">
@@ -800,16 +800,16 @@
         <v>0.2</v>
       </c>
       <c r="B22" t="n">
-        <v>5.033522985421604</v>
+        <v>5.033052279130711</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3057776345550767</v>
+        <v>0.3056239944714074</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2106204920901815</v>
+        <v>0.210752420248507</v>
       </c>
       <c r="E22" t="n">
-        <v>9.999999999999979e-05</v>
+        <v>9.999999999996996e-05</v>
       </c>
     </row>
     <row r="23">
@@ -817,16 +817,16 @@
         <v>0.21</v>
       </c>
       <c r="B23" t="n">
-        <v>4.983722934212676</v>
+        <v>4.98159212569856</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3058940770152688</v>
+        <v>0.305740820929377</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2191474440684982</v>
+        <v>0.219370609957528</v>
       </c>
       <c r="E23" t="n">
-        <v>9.999999999999982e-05</v>
+        <v>9.999999999997297e-05</v>
       </c>
     </row>
     <row r="24">
@@ -834,16 +834,16 @@
         <v>0.22</v>
       </c>
       <c r="B24" t="n">
-        <v>4.935367634285881</v>
+        <v>4.931613575503428</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3062377518403858</v>
+        <v>0.3060856149727849</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2276649007598753</v>
+        <v>0.2279804537231699</v>
       </c>
       <c r="E24" t="n">
-        <v>9.999999999999983e-05</v>
+        <v>9.999999999997592e-05</v>
       </c>
     </row>
     <row r="25">
@@ -851,16 +851,16 @@
         <v>0.23</v>
       </c>
       <c r="B25" t="n">
-        <v>4.888625996432388</v>
+        <v>4.883310389204912</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3068001801972389</v>
+        <v>0.3066498486058792</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2361041755175586</v>
+        <v>0.2365124171442313</v>
       </c>
       <c r="E25" t="n">
-        <v>9.999999999999986e-05</v>
+        <v>9.999999999997885e-05</v>
       </c>
     </row>
     <row r="26">
@@ -868,16 +868,16 @@
         <v>0.24</v>
       </c>
       <c r="B26" t="n">
-        <v>4.843660595153216</v>
+        <v>4.83686877130233</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3075728832526394</v>
+        <v>0.3074249938329087</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2443898725448821</v>
+        <v>0.2448901430558438</v>
       </c>
       <c r="E26" t="n">
-        <v>9.999999999999987e-05</v>
+        <v>9.999999999998168e-05</v>
       </c>
     </row>
     <row r="27">
@@ -885,16 +885,16 @@
         <v>0.25</v>
       </c>
       <c r="B27" t="n">
-        <v>4.800628310453226</v>
+        <v>4.792468132012253</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3085473821733983</v>
+        <v>0.3084025226581215</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2524403217300981</v>
+        <v>0.2530308952085595</v>
       </c>
       <c r="E27" t="n">
-        <v>9.99999999999999e-05</v>
+        <v>9.999999999998442e-05</v>
       </c>
     </row>
     <row r="28">
@@ -902,16 +902,16 @@
         <v>0.26</v>
       </c>
       <c r="B28" t="n">
-        <v>4.759681021452161</v>
+        <v>4.750281917099877</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3097151981263269</v>
+        <v>0.3095739070857663</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2601682292277602</v>
+        <v>0.2608462221341931</v>
       </c>
       <c r="E28" t="n">
-        <v>9.999999999999992e-05</v>
+        <v>9.999999999998702e-05</v>
       </c>
     </row>
     <row r="29">
@@ -919,16 +919,16 @@
         <v>0.27</v>
       </c>
       <c r="B29" t="n">
-        <v>4.720966349278581</v>
+        <v>4.710478502122786</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3110678522782363</v>
+        <v>0.3109306191200913</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2674815591525552</v>
+        <v>0.2682428568235032</v>
       </c>
       <c r="E29" t="n">
-        <v>9.999999999999991e-05</v>
+        <v>9.999999999998945e-05</v>
       </c>
     </row>
     <row r="30">
@@ -936,16 +936,16 @@
         <v>0.28</v>
       </c>
       <c r="B30" t="n">
-        <v>4.684628447462891</v>
+        <v>4.673222148569235</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3125968657959378</v>
+        <v>0.3124641307653451</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2742846559960142</v>
+        <v>0.2751238619212177</v>
       </c>
       <c r="E30" t="n">
-        <v>9.999999999999994e-05</v>
+        <v>9.999999999999171e-05</v>
       </c>
     </row>
     <row r="31">
@@ -953,16 +953,16 @@
         <v>0.29</v>
       </c>
       <c r="B31" t="n">
-        <v>4.650808838840551</v>
+        <v>4.638674020462563</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3142937598462424</v>
+        <v>0.3141659140257759</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2804796100994949</v>
+        <v>0.2813900226657297</v>
       </c>
       <c r="E31" t="n">
-        <v>9.999999999999995e-05</v>
+        <v>9.999999999999374e-05</v>
       </c>
     </row>
     <row r="32">
@@ -970,16 +970,16 @@
         <v>0.3</v>
       </c>
       <c r="B32" t="n">
-        <v>4.619647298815762</v>
+        <v>4.606993261158708</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3161500555959615</v>
+        <v>0.3160274409056323</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2859678597833628</v>
+        <v>0.286941480833454</v>
       </c>
       <c r="E32" t="n">
-        <v>9.999999999999996e-05</v>
+        <v>9.999999999999555e-05</v>
       </c>
     </row>
     <row r="33">
@@ -987,16 +987,16 @@
         <v>0.31</v>
       </c>
       <c r="B33" t="n">
-        <v>4.591282785721559</v>
+        <v>4.578338131287263</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3181572742119061</v>
+        <v>0.3180401834091627</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2906520137075472</v>
+        <v>0.291679592663958</v>
       </c>
       <c r="E33" t="n">
-        <v>9.999999999999998e-05</v>
+        <v>9.999999999999708e-05</v>
       </c>
     </row>
     <row r="34">
@@ -1004,16 +1004,16 @@
         <v>0.32</v>
       </c>
       <c r="B34" t="n">
-        <v>4.565854419947729</v>
+        <v>4.5528672100836</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3203069368608874</v>
+        <v>0.3201956135406155</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2944378659993377</v>
+        <v>0.295508982429149</v>
       </c>
       <c r="E34" t="n">
-        <v>9.999999999999998e-05</v>
+        <v>9.999999999999831e-05</v>
       </c>
     </row>
     <row r="35">
@@ -1021,16 +1021,16 @@
         <v>0.33</v>
       </c>
       <c r="B35" t="n">
-        <v>4.543502514498726</v>
+        <v>4.530740663738229</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3225905647097167</v>
+        <v>0.3224852033042391</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2972365650246888</v>
+        <v>0.2983397513764138</v>
       </c>
       <c r="E35" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>9.999999999999923e-05</v>
       </c>
     </row>
     <row r="36">
@@ -1038,16 +1038,16 @@
         <v>0.34</v>
       </c>
       <c r="B36" t="n">
-        <v>4.524369660697492</v>
+        <v>4.512121585861386</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3249996789252051</v>
+        <v>0.3249004247042819</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2989668849095701</v>
+        <v>0.3000897897489179</v>
       </c>
       <c r="E36" t="n">
-        <v>9.999999999999998e-05</v>
+        <v>9.999999999999979e-05</v>
       </c>
     </row>
     <row r="37">
@@ -1055,13 +1055,13 @@
         <v>0.35</v>
       </c>
       <c r="B37" t="n">
-        <v>4.508601873877206</v>
+        <v>4.497177416740473</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3275258006741637</v>
+        <v>0.3274327497449923</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2995575376532067</v>
+        <v>0.300687128100693</v>
       </c>
       <c r="E37" t="n">
         <v>9.999999999999999e-05</v>
@@ -1072,13 +1072,13 @@
         <v>0.36</v>
       </c>
       <c r="B38" t="n">
-        <v>4.495618152223778</v>
+        <v>4.485128409563226</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3320247824102264</v>
+        <v>0.331935841590579</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2989647865748404</v>
+        <v>0.3000818264750856</v>
       </c>
       <c r="E38" t="n">
         <v>9.999999999999999e-05</v>
@@ -1089,13 +1089,13 @@
         <v>0.37</v>
       </c>
       <c r="B39" t="n">
-        <v>4.48453008202923</v>
+        <v>4.474884437025361</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3399854328684959</v>
+        <v>0.3398967091159713</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2973030990830512</v>
+        <v>0.2983850665946794</v>
       </c>
       <c r="E39" t="n">
         <v>9.999999999999999e-05</v>
@@ -1106,13 +1106,13 @@
         <v>0.38</v>
       </c>
       <c r="B40" t="n">
-        <v>4.475029837945911</v>
+        <v>4.46615507708476</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3508487076379868</v>
+        <v>0.3507568428914987</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2947531846832629</v>
+        <v>0.2957816528143613</v>
       </c>
       <c r="E40" t="n">
         <v>9.999999999999999e-05</v>
@@ -1123,16 +1123,16 @@
         <v>0.39</v>
       </c>
       <c r="B41" t="n">
-        <v>4.466814006792243</v>
+        <v>4.458653827763166</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3640555623077139</v>
+        <v>0.3639577334874904</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2914991598686126</v>
+        <v>0.2924599238524166</v>
       </c>
       <c r="E41" t="n">
-        <v>9.999999999999998e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="42">
@@ -1140,16 +1140,16 @@
         <v>0.4</v>
       </c>
       <c r="B42" t="n">
-        <v>4.459582629106349</v>
+        <v>4.45209724025482</v>
       </c>
       <c r="C42" t="n">
-        <v>0.379046952466692</v>
+        <v>0.3789408714742762</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2877238744104751</v>
+        <v>0.2886068955726969</v>
       </c>
       <c r="E42" t="n">
-        <v>9.999999999999998e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="43">
@@ -1157,16 +1157,16 @@
         <v>0.41</v>
       </c>
       <c r="B43" t="n">
-        <v>4.453038445653323</v>
+        <v>4.446204235261122</v>
       </c>
       <c r="C43" t="n">
-        <v>0.3952638337039355</v>
+        <v>0.3951477474221853</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2836053001452767</v>
+        <v>0.2844045102828656</v>
       </c>
       <c r="E43" t="n">
-        <v>9.999999999999998e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="44">
@@ -1174,16 +1174,16 @@
         <v>0.42</v>
       </c>
       <c r="B44" t="n">
-        <v>4.446886344299634</v>
+        <v>4.44069559868357</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4121471616084594</v>
+        <v>0.4120198519015472</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2793139949624759</v>
+        <v>0.2800270058833277</v>
       </c>
       <c r="E44" t="n">
-        <v>9.999999999999998e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="45">
@@ -1191,16 +1191,16 @@
         <v>0.43</v>
       </c>
       <c r="B45" t="n">
-        <v>4.440833003882729</v>
+        <v>4.43529365385362</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4291378917692784</v>
+        <v>0.4289986754826917</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2750116047113287</v>
+        <v>0.2756393653634587</v>
       </c>
       <c r="E45" t="n">
-        <v>9.999999999999996e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="46">
@@ -1208,16 +1208,16 @@
         <v>0.44</v>
       </c>
       <c r="B46" t="n">
-        <v>4.434586732545829</v>
+        <v>4.429722108208275</v>
       </c>
       <c r="C46" t="n">
-        <v>0.4456769797754071</v>
+        <v>0.4455257087359479</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2708503329578617</v>
+        <v>0.2713967725390189</v>
       </c>
       <c r="E46" t="n">
-        <v>9.999999999999996e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="47">
@@ -1225,16 +1225,16 @@
         <v>0.45</v>
       </c>
       <c r="B47" t="n">
-        <v>4.427857498486113</v>
+        <v>4.423706072741392</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4612053812158603</v>
+        <v>0.4610424422316454</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2669732921202659</v>
+        <v>0.2674449826749462</v>
       </c>
       <c r="E47" t="n">
-        <v>9.999999999999996e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="48">
@@ -1242,16 +1242,16 @@
         <v>0.46</v>
       </c>
       <c r="B48" t="n">
-        <v>4.420357151185529</v>
+        <v>4.416972252677958</v>
       </c>
       <c r="C48" t="n">
-        <v>0.4751640516796526</v>
+        <v>0.4749903665401136</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2635156478927249</v>
+        <v>0.263921515021868</v>
       </c>
       <c r="E48" t="n">
-        <v>9.999999999999995e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="49">
@@ -1259,16 +1259,16 @@
         <v>0.47</v>
       </c>
       <c r="B49" t="n">
-        <v>4.411799830962594</v>
+        <v>4.409249307635934</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4869939467557989</v>
+        <v>0.486810972231682</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2606064801488276</v>
+        <v>0.2609575862866443</v>
       </c>
       <c r="E49" t="n">
-        <v>9.999999999999995e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="50">
@@ -1276,16 +1276,16 @@
         <v>0.48</v>
       </c>
       <c r="B50" t="n">
-        <v>4.401902564106487</v>
+        <v>4.400268379062217</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4961360220333135</v>
+        <v>0.4959457498766801</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2583713059496377</v>
+        <v>0.2586807277830648</v>
       </c>
       <c r="E50" t="n">
-        <v>9.999999999999995e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="51">
@@ -1293,16 +1293,16 @@
         <v>0.49</v>
       </c>
       <c r="B51" t="n">
-        <v>4.390386039938517</v>
+        <v>4.389763781960907</v>
       </c>
       <c r="C51" t="n">
-        <v>0.5020312331012117</v>
+        <v>0.5018361900454374</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2569352426183922</v>
+        <v>0.2572180631295857</v>
       </c>
       <c r="E51" t="n">
-        <v>9.999999999999995e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="52">
@@ -1310,16 +1310,16 @@
         <v>0.5</v>
       </c>
       <c r="B52" t="n">
-        <v>4.376975564900279</v>
+        <v>4.377473856881211</v>
       </c>
       <c r="C52" t="n">
-        <v>0.5041205355485078</v>
+        <v>0.5039237833082832</v>
       </c>
       <c r="D52" t="n">
-        <v>0.2564268306340854</v>
+        <v>0.2567002673970867</v>
       </c>
       <c r="E52" t="n">
-        <v>9.999999999999995e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="53">
@@ -1327,16 +1327,16 @@
         <v>0.51</v>
       </c>
       <c r="B53" t="n">
-        <v>4.356931654090272</v>
+        <v>4.358519806625067</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5034466401915413</v>
+        <v>0.5032152083365818</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2571043358203341</v>
+        <v>0.2573796586254457</v>
       </c>
       <c r="E53" t="n">
-        <v>9.999999999999995e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="54">
@@ -1344,16 +1344,16 @@
         <v>0.52</v>
       </c>
       <c r="B54" t="n">
-        <v>4.326377008030371</v>
+        <v>4.328879518858309</v>
       </c>
       <c r="C54" t="n">
-        <v>0.5014988056666111</v>
+        <v>0.5011671354731709</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2590726853774803</v>
+        <v>0.2593535050559842</v>
       </c>
       <c r="E54" t="n">
-        <v>9.999999999999995e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="55">
@@ -1361,16 +1361,16 @@
         <v>0.53</v>
       </c>
       <c r="B55" t="n">
-        <v>4.286373198307668</v>
+        <v>4.289621086470994</v>
       </c>
       <c r="C55" t="n">
-        <v>0.4983878092926701</v>
+        <v>0.4978960427955905</v>
       </c>
       <c r="D55" t="n">
-        <v>0.262247749418312</v>
+        <v>0.2625374899477492</v>
       </c>
       <c r="E55" t="n">
-        <v>9.999999999999995e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="56">
@@ -1378,16 +1378,16 @@
         <v>0.54</v>
       </c>
       <c r="B56" t="n">
-        <v>4.238016259551657</v>
+        <v>4.24184962199841</v>
       </c>
       <c r="C56" t="n">
-        <v>0.494224428388672</v>
+        <v>0.4935184083813805</v>
       </c>
       <c r="D56" t="n">
-        <v>0.2665578377348803</v>
+        <v>0.2668597936860997</v>
       </c>
       <c r="E56" t="n">
-        <v>9.999999999999995e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="57">
@@ -1395,16 +1395,16 @@
         <v>0.55</v>
       </c>
       <c r="B57" t="n">
-        <v>4.18241660713036</v>
+        <v>4.186686624832443</v>
       </c>
       <c r="C57" t="n">
-        <v>0.4891194402735702</v>
+        <v>0.4881507103080809</v>
       </c>
       <c r="D57" t="n">
-        <v>0.2719395125501458</v>
+        <v>0.2722568888482048</v>
       </c>
       <c r="E57" t="n">
-        <v>9.999999999999995e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="58">
@@ -1412,16 +1412,16 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58" t="n">
-        <v>4.120681148960339</v>
+        <v>4.125251564768535</v>
       </c>
       <c r="C58" t="n">
-        <v>0.483183622266318</v>
+        <v>0.4819094266532316</v>
       </c>
       <c r="D58" t="n">
-        <v>0.2783338138360718</v>
+        <v>0.2786697496254322</v>
       </c>
       <c r="E58" t="n">
-        <v>9.999999999999996e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="59">
@@ -1429,16 +1429,16 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59" t="n">
-        <v>4.053897792700345</v>
+        <v>4.05864589818624</v>
       </c>
       <c r="C59" t="n">
-        <v>0.4765277516858688</v>
+        <v>0.4749110354943726</v>
       </c>
       <c r="D59" t="n">
-        <v>0.2856827719263129</v>
+        <v>0.2860403495528411</v>
       </c>
       <c r="E59" t="n">
-        <v>9.999999999999996e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="60">
@@ -1446,16 +1446,16 @@
         <v>0.58</v>
       </c>
       <c r="B60" t="n">
-        <v>3.983122448332542</v>
+        <v>3.987939627912844</v>
       </c>
       <c r="C60" t="n">
-        <v>0.469262605851176</v>
+        <v>0.4672720149090439</v>
       </c>
       <c r="D60" t="n">
-        <v>0.2939261211300479</v>
+        <v>0.2943083606981641</v>
       </c>
       <c r="E60" t="n">
-        <v>9.999999999999996e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="61">
@@ -1463,16 +1463,16 @@
         <v>0.59</v>
       </c>
       <c r="B61" t="n">
-        <v>3.90936853796565</v>
+        <v>3.914160425901702</v>
       </c>
       <c r="C61" t="n">
-        <v>0.4614989620811929</v>
+        <v>0.4591088429747854</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3029981622753387</v>
+        <v>0.3034080018791695</v>
       </c>
       <c r="E61" t="n">
-        <v>9.999999999999996e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="62">
@@ -1480,16 +1480,16 @@
         <v>0.6</v>
       </c>
       <c r="B62" t="n">
-        <v>3.833598951157075</v>
+        <v>3.838285260952537</v>
       </c>
       <c r="C62" t="n">
-        <v>0.453347597694873</v>
+        <v>0.450537997769137</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3128247536011571</v>
+        <v>0.313265015150729</v>
       </c>
       <c r="E62" t="n">
-        <v>9.999999999999996e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="63">
@@ -1497,16 +1497,16 @@
         <v>0.61</v>
       </c>
       <c r="B63" t="n">
-        <v>3.756720325730012</v>
+        <v>3.761234412489201</v>
       </c>
       <c r="C63" t="n">
-        <v>0.4449192900111696</v>
+        <v>0.4416759573696387</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3233204395064173</v>
+        <v>0.3237937800717226</v>
       </c>
       <c r="E63" t="n">
-        <v>9.999999999999996e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="64">
@@ -1514,16 +1514,16 @@
         <v>0.62</v>
       </c>
       <c r="B64" t="n">
-        <v>3.679579490750319</v>
+        <v>3.683867705735636</v>
       </c>
       <c r="C64" t="n">
-        <v>0.4363248163490361</v>
+        <v>0.4326391998538305</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3343857560633839</v>
+        <v>0.3348946048450526</v>
       </c>
       <c r="E64" t="n">
-        <v>9.999999999999996e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="65">
@@ -1531,16 +1531,16 @@
         <v>0.63</v>
       </c>
       <c r="B65" t="n">
-        <v>3.602961879206086</v>
+        <v>3.606982772683528</v>
       </c>
       <c r="C65" t="n">
-        <v>0.427674954027426</v>
+        <v>0.4235442032992522</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3459047810355294</v>
+        <v>0.3464512624474825</v>
       </c>
       <c r="E65" t="n">
-        <v>9.999999999999996e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="66">
@@ -1548,16 +1548,16 @@
         <v>0.64</v>
       </c>
       <c r="B66" t="n">
-        <v>3.527591701739889</v>
+        <v>3.531315125746909</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4190804803652926</v>
+        <v>0.414507445783444</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3577430239457811</v>
+        <v>0.3583288678668224</v>
       </c>
       <c r="E66" t="n">
-        <v>9.999999999999998e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="67">
@@ -1565,16 +1565,16 @@
         <v>0.65</v>
       </c>
       <c r="B67" t="n">
-        <v>3.454133667984227</v>
+        <v>3.45753982537296</v>
       </c>
       <c r="C67" t="n">
-        <v>0.4106521726815892</v>
+        <v>0.4056454053839457</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3697457774712266</v>
+        <v>0.3703722184859787</v>
       </c>
       <c r="E67" t="n">
-        <v>9.999999999999998e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="68">
@@ -1582,16 +1582,16 @@
         <v>0.66</v>
       </c>
       <c r="B68" t="n">
-        <v>3.383196046978922</v>
+        <v>3.386274527403975</v>
       </c>
       <c r="C68" t="n">
-        <v>0.4025008082952692</v>
+        <v>0.3970745601782973</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3817370734658045</v>
+        <v>0.3824047418552442</v>
       </c>
       <c r="E68" t="n">
-        <v>9.999999999999998e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="69">
@@ -1599,16 +1599,16 @@
         <v>0.67</v>
       </c>
       <c r="B69" t="n">
-        <v>3.31533487113406</v>
+        <v>3.318083708928796</v>
       </c>
       <c r="C69" t="n">
-        <v>0.3947371645252862</v>
+        <v>0.3889113882440388</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3935194030656716</v>
+        <v>0.3942282113908802</v>
       </c>
       <c r="E69" t="n">
-        <v>9.999999999999998e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="70">
@@ -1616,13 +1616,13 @@
         <v>0.68</v>
       </c>
       <c r="B70" t="n">
-        <v>3.251059107666428</v>
+        <v>3.253483891081982</v>
       </c>
       <c r="C70" t="n">
-        <v>0.3874720186905934</v>
+        <v>0.38127236765871</v>
       </c>
       <c r="D70" t="n">
-        <v>0.4048743680012277</v>
+        <v>0.4056233982960705</v>
       </c>
       <c r="E70" t="n">
         <v>9.999999999999999e-05</v>
@@ -1633,16 +1633,16 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71" t="n">
-        <v>3.190836645975776</v>
+        <v>3.192949702278973</v>
       </c>
       <c r="C71" t="n">
-        <v>0.3808161481101442</v>
+        <v>0.374273976499851</v>
       </c>
       <c r="D71" t="n">
-        <v>0.4155644265365022</v>
+        <v>0.4163518243059079</v>
       </c>
       <c r="E71" t="n">
-        <v>9.999999999999998e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="72">
@@ -1650,13 +1650,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72" t="n">
-        <v>3.135100977863209</v>
+        <v>3.136920654484479</v>
       </c>
       <c r="C72" t="n">
-        <v>0.374880330102892</v>
+        <v>0.3680326928450017</v>
       </c>
       <c r="D72" t="n">
-        <v>0.4253358794675929</v>
+        <v>0.4261587617718945</v>
       </c>
       <c r="E72" t="n">
         <v>9.999999999999999e-05</v>
@@ -1667,16 +1667,16 @@
         <v>0.71</v>
       </c>
       <c r="B73" t="n">
-        <v>3.084258478919025</v>
+        <v>3.085808537345953</v>
       </c>
       <c r="C73" t="n">
-        <v>0.3697753419877902</v>
+        <v>0.3626649947717021</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4339232067433947</v>
+        <v>0.4347775925057339</v>
       </c>
       <c r="E73" t="n">
-        <v>9.999999999999998e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="74">
@@ -1684,13 +1684,13 @@
         <v>0.72</v>
       </c>
       <c r="B74" t="n">
-        <v>3.038696233208869</v>
+        <v>3.04000536973716</v>
       </c>
       <c r="C74" t="n">
-        <v>0.3656119610837921</v>
+        <v>0.3582873603574921</v>
       </c>
       <c r="D74" t="n">
-        <v>0.4410548116773587</v>
+        <v>0.4419355828324205</v>
       </c>
       <c r="E74" t="n">
         <v>9.999999999999999e-05</v>
@@ -1701,13 +1701,13 @@
         <v>0.73</v>
       </c>
       <c r="B75" t="n">
-        <v>2.998790379266675</v>
+        <v>2.999891885128306</v>
       </c>
       <c r="C75" t="n">
-        <v>0.3625009647098513</v>
+        <v>0.3550162676799117</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4464601567856324</v>
+        <v>0.4473610588388774</v>
       </c>
       <c r="E75" t="n">
         <v>9.999999999999999e-05</v>
@@ -1718,13 +1718,13 @@
         <v>0.74</v>
       </c>
       <c r="B76" t="n">
-        <v>2.964914993392341</v>
+        <v>2.965846566251338</v>
       </c>
       <c r="C76" t="n">
-        <v>0.3605531301849209</v>
+        <v>0.3529681948165008</v>
       </c>
       <c r="D76" t="n">
-        <v>0.4498781841366243</v>
+        <v>0.4507918739773654</v>
       </c>
       <c r="E76" t="n">
         <v>9.999999999999999e-05</v>
@@ -1735,13 +1735,13 @@
         <v>0.75</v>
       </c>
       <c r="B77" t="n">
-        <v>2.937451566730601</v>
+        <v>2.938255286145861</v>
       </c>
       <c r="C77" t="n">
-        <v>0.3598792348279544</v>
+        <v>0.3522596198447994</v>
       </c>
       <c r="D77" t="n">
-        <v>0.451066807036104</v>
+        <v>0.4519849543278506</v>
       </c>
       <c r="E77" t="n">
         <v>9.999999999999999e-05</v>
@@ -1752,13 +1752,13 @@
         <v>0.76</v>
       </c>
       <c r="B78" t="n">
-        <v>2.913467181076602</v>
+        <v>2.91416439956993</v>
       </c>
       <c r="C78" t="n">
-        <v>0.3599472102823373</v>
+        <v>0.3523432809424807</v>
       </c>
       <c r="D78" t="n">
-        <v>0.4509915672480145</v>
+        <v>0.4519088330814388</v>
       </c>
       <c r="E78" t="n">
         <v>9.999999999999999e-05</v>
@@ -1769,13 +1769,13 @@
         <v>0.77</v>
       </c>
       <c r="B79" t="n">
-        <v>2.889787384061133</v>
+        <v>2.890376062641034</v>
       </c>
       <c r="C79" t="n">
-        <v>0.3601466839404109</v>
+        <v>0.3525886558347008</v>
       </c>
       <c r="D79" t="n">
-        <v>0.450771763671043</v>
+        <v>0.4516864551376762</v>
       </c>
       <c r="E79" t="n">
         <v>9.999999999999999e-05</v>
@@ -1786,13 +1786,13 @@
         <v>0.78</v>
       </c>
       <c r="B80" t="n">
-        <v>2.866442154026867</v>
+        <v>2.866920710922534</v>
       </c>
       <c r="C80" t="n">
-        <v>0.3604709767445621</v>
+        <v>0.3529873319202244</v>
       </c>
       <c r="D80" t="n">
-        <v>0.450416361483594</v>
+        <v>0.4513268926522145</v>
       </c>
       <c r="E80" t="n">
         <v>9.999999999999999e-05</v>
@@ -1803,13 +1803,13 @@
         <v>0.79</v>
       </c>
       <c r="B81" t="n">
-        <v>2.843460437397839</v>
+        <v>2.843827728340388</v>
       </c>
       <c r="C81" t="n">
-        <v>0.3609134096371782</v>
+        <v>0.3535308965978161</v>
       </c>
       <c r="D81" t="n">
-        <v>0.4499344260435619</v>
+        <v>0.4508393201089932</v>
       </c>
       <c r="E81" t="n">
         <v>9.999999999999999e-05</v>
@@ -1820,16 +1820,16 @@
         <v>0.8</v>
       </c>
       <c r="B82" t="n">
-        <v>2.820870188310109</v>
+        <v>2.821125487166179</v>
       </c>
       <c r="C82" t="n">
-        <v>0.3614673035606463</v>
+        <v>0.3542109372662403</v>
       </c>
       <c r="D82" t="n">
-        <v>0.4493350969735609</v>
+        <v>0.450232987845032</v>
       </c>
       <c r="E82" t="n">
-        <v>9.999999999999998e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="83">
@@ -1837,16 +1837,16 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83" t="n">
-        <v>2.798698411004478</v>
+        <v>2.798841390847312</v>
       </c>
       <c r="C83" t="n">
-        <v>0.3621259794573534</v>
+        <v>0.3550190413242619</v>
       </c>
       <c r="D83" t="n">
-        <v>0.4486275639322103</v>
+        <v>0.449517197297349</v>
       </c>
       <c r="E83" t="n">
-        <v>9.999999999999998e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="84">
@@ -1854,16 +1854,16 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84" t="n">
-        <v>2.776971204803064</v>
+        <v>2.777001919499885</v>
       </c>
       <c r="C84" t="n">
-        <v>0.3628827582696867</v>
+        <v>0.3559467961706452</v>
       </c>
       <c r="D84" t="n">
-        <v>0.4478210441274187</v>
+        <v>0.4487012780297069</v>
       </c>
       <c r="E84" t="n">
-        <v>9.999999999999998e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="85">
@@ -1871,16 +1871,16 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85" t="n">
-        <v>2.755713811505202</v>
+        <v>2.755632677893768</v>
       </c>
       <c r="C85" t="n">
-        <v>0.3637309609400333</v>
+        <v>0.3569857892041551</v>
       </c>
       <c r="D85" t="n">
-        <v>0.4469247616148308</v>
+        <v>0.4477945665837048</v>
       </c>
       <c r="E85" t="n">
-        <v>9.999999999999998e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="86">
@@ -1888,16 +1888,16 @@
         <v>0.84</v>
       </c>
       <c r="B86" t="n">
-        <v>2.73495066505244</v>
+        <v>2.734758445773983</v>
       </c>
       <c r="C86" t="n">
-        <v>0.3646639084107803</v>
+        <v>0.3581276078235559</v>
       </c>
       <c r="D86" t="n">
-        <v>0.4459479284127028</v>
+        <v>0.4468063871864569</v>
       </c>
       <c r="E86" t="n">
-        <v>9.999999999999996e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="87">
@@ -1905,16 +1905,16 @@
         <v>0.85</v>
       </c>
       <c r="B87" t="n">
-        <v>2.714705443327163</v>
+        <v>2.714403230377775</v>
       </c>
       <c r="C87" t="n">
-        <v>0.3656749216243149</v>
+        <v>0.3593638394276124</v>
       </c>
       <c r="D87" t="n">
-        <v>0.4448997274535134</v>
+        <v>0.4457460343357996</v>
       </c>
       <c r="E87" t="n">
-        <v>9.999999999999996e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="88">
@@ -1922,16 +1922,16 @@
         <v>0.86</v>
       </c>
       <c r="B88" t="n">
-        <v>2.69500112196478</v>
+        <v>2.694590321022424</v>
       </c>
       <c r="C88" t="n">
-        <v>0.366757321523024</v>
+        <v>0.360686071415089</v>
       </c>
       <c r="D88" t="n">
-        <v>0.4437892973826381</v>
+        <v>0.4446227572736684</v>
       </c>
       <c r="E88" t="n">
-        <v>9.999999999999996e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="89">
@@ -1939,16 +1939,16 @@
         <v>0.87</v>
       </c>
       <c r="B89" t="n">
-        <v>2.675860030075171</v>
+        <v>2.67534234565512</v>
       </c>
       <c r="C89" t="n">
-        <v>0.367904429049295</v>
+        <v>0.3620858911847504</v>
       </c>
       <c r="D89" t="n">
-        <v>0.4426257192054343</v>
+        <v>0.4434457463490243</v>
       </c>
       <c r="E89" t="n">
-        <v>9.999999999999995e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="90">
@@ -1956,16 +1956,16 @@
         <v>0.88</v>
       </c>
       <c r="B90" t="n">
-        <v>2.657303907785346</v>
+        <v>2.656681329272905</v>
       </c>
       <c r="C90" t="n">
-        <v>0.3691095651455149</v>
+        <v>0.3635548861353613</v>
       </c>
       <c r="D90" t="n">
-        <v>0.44141800477613</v>
+        <v>0.442224121263507</v>
       </c>
       <c r="E90" t="n">
-        <v>9.999999999999995e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="91">
@@ -1973,16 +1973,16 @@
         <v>0.89</v>
       </c>
       <c r="B91" t="n">
-        <v>2.639353965531885</v>
+        <v>2.638628754137736</v>
       </c>
       <c r="C91" t="n">
-        <v>0.3703660507540707</v>
+        <v>0.3650846436656861</v>
       </c>
       <c r="D91" t="n">
-        <v>0.4401750871149775</v>
+        <v>0.4409669211858396</v>
       </c>
       <c r="E91" t="n">
-        <v>9.999999999999995e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="92">
@@ -1990,16 +1990,16 @@
         <v>0.9</v>
       </c>
       <c r="B92" t="n">
-        <v>2.622030945048775</v>
+        <v>2.621205621729267</v>
       </c>
       <c r="C92" t="n">
-        <v>0.3716672068173497</v>
+        <v>0.3666667511744895</v>
       </c>
       <c r="D92" t="n">
-        <v>0.4389058125342378</v>
+        <v>0.4396830967149334</v>
       </c>
       <c r="E92" t="n">
-        <v>9.999999999999994e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="93">
@@ -2007,16 +2007,16 @@
         <v>0.91</v>
       </c>
       <c r="B93" t="n">
-        <v>2.60535518201365</v>
+        <v>2.604432516395834</v>
       </c>
       <c r="C93" t="n">
-        <v>0.3730063542777389</v>
+        <v>0.3682927960605361</v>
       </c>
       <c r="D93" t="n">
-        <v>0.4376189345486788</v>
+        <v>0.4383815036666061</v>
       </c>
       <c r="E93" t="n">
-        <v>9.999999999999994e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="94">
@@ -2024,16 +2024,16 @@
         <v>0.92</v>
       </c>
       <c r="B94" t="n">
-        <v>2.589346670333259</v>
+        <v>2.588329670682394</v>
       </c>
       <c r="C94" t="n">
-        <v>0.3743768140776254</v>
+        <v>0.3699543657225904</v>
       </c>
       <c r="D94" t="n">
-        <v>0.4363231095424021</v>
+        <v>0.4370708986548409</v>
       </c>
       <c r="E94" t="n">
-        <v>9.999999999999992e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="95">
@@ -2041,16 +2041,16 @@
         <v>0.93</v>
       </c>
       <c r="B95" t="n">
-        <v>2.57402512806716</v>
+        <v>2.572917032332926</v>
       </c>
       <c r="C95" t="n">
-        <v>0.3757719071593964</v>
+        <v>0.371643047559417</v>
       </c>
       <c r="D95" t="n">
-        <v>0.4350268941609287</v>
+        <v>0.4357599364355441</v>
       </c>
       <c r="E95" t="n">
-        <v>9.999999999999991e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="96">
@@ -2058,16 +2058,16 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96" t="n">
-        <v>2.559410065007293</v>
+        <v>2.558214332983911</v>
       </c>
       <c r="C96" t="n">
-        <v>0.3771849544654389</v>
+        <v>0.3733504289697806</v>
       </c>
       <c r="D96" t="n">
-        <v>0.4337387443955672</v>
+        <v>0.4344571689787919</v>
       </c>
       <c r="E96" t="n">
-        <v>9.999999999999992e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="97">
@@ -2075,16 +2075,16 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97" t="n">
-        <v>2.545520851950152</v>
+        <v>2.544241158585165</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3786092769381402</v>
+        <v>0.3750680973524457</v>
       </c>
       <c r="D97" t="n">
-        <v>0.4324670163261125</v>
+        <v>0.4331710462345615</v>
       </c>
       <c r="E97" t="n">
-        <v>9.999999999999991e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="98">
@@ -2092,16 +2092,16 @@
         <v>0.96</v>
       </c>
       <c r="B98" t="n">
-        <v>2.532376791717883</v>
+        <v>2.531017021604418</v>
       </c>
       <c r="C98" t="n">
-        <v>0.3800381955198873</v>
+        <v>0.376787640106177</v>
       </c>
       <c r="D98" t="n">
-        <v>0.4312199684878787</v>
+        <v>0.4319099185568924</v>
       </c>
       <c r="E98" t="n">
-        <v>9.99999999999999e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="99">
@@ -2109,16 +2109,16 @@
         <v>0.97</v>
       </c>
       <c r="B99" t="n">
-        <v>2.519997192004794</v>
+        <v>2.518561435092767</v>
       </c>
       <c r="C99" t="n">
-        <v>0.3814650311530673</v>
+        <v>0.3785006446297389</v>
       </c>
       <c r="D99" t="n">
-        <v>0.4300057658299082</v>
+        <v>0.4306820407522996</v>
       </c>
       <c r="E99" t="n">
-        <v>9.999999999999988e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="100">
@@ -2126,16 +2126,16 @@
         <v>0.98</v>
       </c>
       <c r="B100" t="n">
-        <v>2.508401440146549</v>
+        <v>2.506893988709524</v>
       </c>
       <c r="C100" t="n">
-        <v>0.3828831047800674</v>
+        <v>0.3801986983218962</v>
       </c>
       <c r="D100" t="n">
-        <v>0.4288324852329083</v>
+        <v>0.4294955777200199</v>
       </c>
       <c r="E100" t="n">
-        <v>9.999999999999988e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="101">
@@ -2143,16 +2143,16 @@
         <v>0.99</v>
       </c>
       <c r="B101" t="n">
-        <v>2.497609079930839</v>
+        <v>2.496034426827052</v>
       </c>
       <c r="C101" t="n">
-        <v>0.3842857373432746</v>
+        <v>0.3818733885814134</v>
       </c>
       <c r="D101" t="n">
-        <v>0.4277081225580176</v>
+        <v>0.4283586116543094</v>
       </c>
       <c r="E101" t="n">
-        <v>9.999999999999987e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="102">
@@ -2160,16 +2160,16 @@
         <v>1</v>
       </c>
       <c r="B102" t="n">
-        <v>2.487639890590641</v>
+        <v>2.486002728859157</v>
       </c>
       <c r="C102" t="n">
-        <v>0.385666249785076</v>
+        <v>0.3835163028070551</v>
       </c>
       <c r="D102" t="n">
-        <v>0.4266406012008694</v>
+        <v>0.4272791507824821</v>
       </c>
       <c r="E102" t="n">
-        <v>9.999999999999987e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="103">
@@ -2177,16 +2177,16 @@
         <v>1.01</v>
       </c>
       <c r="B103" t="n">
-        <v>2.478513968144383</v>
+        <v>2.476819191980464</v>
       </c>
       <c r="C103" t="n">
-        <v>0.387017963047859</v>
+        <v>0.3851190283975858</v>
       </c>
       <c r="D103" t="n">
-        <v>0.4256377821295942</v>
+        <v>0.4262651396166803</v>
       </c>
       <c r="E103" t="n">
-        <v>9.999999999999986e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="104">
@@ -2194,16 +2194,16 @@
         <v>1.02</v>
       </c>
       <c r="B104" t="n">
-        <v>2.470251809271653</v>
+        <v>2.468504516429154</v>
       </c>
       <c r="C104" t="n">
-        <v>0.3883341980740103</v>
+        <v>0.3866731527517702</v>
       </c>
       <c r="D104" t="n">
-        <v>0.4247074753903524</v>
+        <v>0.4253244707024775</v>
       </c>
       <c r="E104" t="n">
-        <v>9.999999999999984e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="105">
@@ -2211,16 +2211,16 @@
         <v>1.03</v>
       </c>
       <c r="B105" t="n">
-        <v>2.462874397938471</v>
+        <v>2.461079893611601</v>
       </c>
       <c r="C105" t="n">
-        <v>0.3896082758059173</v>
+        <v>0.3881702632683729</v>
       </c>
       <c r="D105" t="n">
-        <v>0.4238574530697189</v>
+        <v>0.4244649978533158</v>
       </c>
       <c r="E105" t="n">
-        <v>9.999999999999984e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="106">
@@ -2228,16 +2228,16 @@
         <v>1.04</v>
       </c>
       <c r="B106" t="n">
-        <v>2.456403295012974</v>
+        <v>2.454567097254944</v>
       </c>
       <c r="C106" t="n">
-        <v>0.3908335171859671</v>
+        <v>0.3896019473461584</v>
       </c>
       <c r="D106" t="n">
-        <v>0.4230954637097407</v>
+        <v>0.4236945508664809</v>
       </c>
       <c r="E106" t="n">
-        <v>9.999999999999984e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="107">
@@ -2245,16 +2245,16 @@
         <v>1.05</v>
       </c>
       <c r="B107" t="n">
-        <v>2.450860731140581</v>
+        <v>2.448988577882719</v>
       </c>
       <c r="C107" t="n">
-        <v>0.3920032431565467</v>
+        <v>0.3909597923838914</v>
       </c>
       <c r="D107" t="n">
-        <v>0.4224292481787562</v>
+        <v>0.4230209517238089</v>
       </c>
       <c r="E107" t="n">
-        <v>9.999999999999983e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="108">
@@ -2262,16 +2262,16 @@
         <v>1.06</v>
       </c>
       <c r="B108" t="n">
-        <v>2.446269703177701</v>
+        <v>2.444367560919439</v>
       </c>
       <c r="C108" t="n">
-        <v>0.3931107746600433</v>
+        <v>0.3922353857803365</v>
       </c>
       <c r="D108" t="n">
-        <v>0.4218665570091153</v>
+        <v>0.4224520322886104</v>
       </c>
       <c r="E108" t="n">
-        <v>9.999999999999983e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="109">
@@ -2279,16 +2279,16 @@
         <v>1.07</v>
       </c>
       <c r="B109" t="n">
-        <v>2.442654074514866</v>
+        <v>2.440728148762789</v>
       </c>
       <c r="C109" t="n">
-        <v>0.3941494326388439</v>
+        <v>0.3934203149342581</v>
       </c>
       <c r="D109" t="n">
-        <v>0.4214151692217859</v>
+        <v>0.4219956535194183</v>
       </c>
       <c r="E109" t="n">
-        <v>9.99999999999998e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="110">
@@ -2296,16 +2296,16 @@
         <v>1.08</v>
       </c>
       <c r="B110" t="n">
-        <v>2.440038679654183</v>
+        <v>2.438095427197044</v>
       </c>
       <c r="C110" t="n">
-        <v>0.3951125380353358</v>
+        <v>0.3945061672444209</v>
       </c>
       <c r="D110" t="n">
-        <v>0.4210829126675025</v>
+        <v>0.4216597262311244</v>
       </c>
       <c r="E110" t="n">
-        <v>9.99999999999998e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="111">
@@ -2313,16 +2313,16 @@
         <v>1.09</v>
       </c>
       <c r="B111" t="n">
-        <v>2.438449433442348</v>
+        <v>2.436495576558712</v>
       </c>
       <c r="C111" t="n">
-        <v>0.395993411791906</v>
+        <v>0.3954845301095897</v>
       </c>
       <c r="D111" t="n">
-        <v>0.4208776859246374</v>
+        <v>0.4214522334449192</v>
       </c>
       <c r="E111" t="n">
-        <v>9.99999999999998e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="112">
@@ -2330,16 +2330,16 @@
         <v>1.1</v>
       </c>
       <c r="B112" t="n">
-        <v>2.43791344539954</v>
+        <v>2.435955988105618</v>
       </c>
       <c r="C112" t="n">
-        <v>0.3967853748509416</v>
+        <v>0.3963469909285288</v>
       </c>
       <c r="D112" t="n">
-        <v>0.4208074818054103</v>
+        <v>0.4213812543802276</v>
       </c>
       <c r="E112" t="n">
-        <v>9.999999999999979e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="113">
@@ -2347,16 +2347,16 @@
         <v>1.11</v>
       </c>
       <c r="B113" t="n">
-        <v>2.4381465740115</v>
+        <v>2.436191399168916</v>
       </c>
       <c r="C113" t="n">
-        <v>0.3975343199210348</v>
+        <v>0.3971506334605505</v>
       </c>
       <c r="D113" t="n">
-        <v>0.420810369164909</v>
+        <v>0.4213838390650352</v>
       </c>
       <c r="E113" t="n">
-        <v>9.999999999999977e-05</v>
+        <v>9.999999999999999e-05</v>
       </c>
     </row>
     <row r="114">
@@ -2364,16 +2364,16 @@
         <v>1.12</v>
       </c>
       <c r="B114" t="n">
-        <v>2.438833487883098</v>
+        <v>2.436885039674825</v>
       </c>
       <c r="C114" t="n">
-        <v>0.3982899915225587</v>
+        <v>0.3979576118121385</v>
       </c>
       <c r="D114" t="n">
-        <v>0.4208189917706497</v>
+        <v>0.4213915596925535</v>
       </c>
       <c r="E114" t="n">
-        <v>9.999999999999977e-05</v>
+        <v>9.999999999999998e-05</v>
       </c>
     </row>
     <row r="115">
@@ -2381,16 +2381,16 @@
         <v>1.13</v>
       </c>
       <c r="B115" t="n">
-        <v>2.43995565323342</v>
+        <v>2.43801819833399</v>
       </c>
       <c r="C115" t="n">
-        <v>0.3990514883155724</v>
+        <v>0.3987671189028147</v>
       </c>
       <c r="D115" t="n">
-        <v>0.4208332905857296</v>
+        <v>0.4214043662605134</v>
       </c>
       <c r="E115" t="n">
-        <v>9.999999999999976e-05</v>
+        <v>9.999999999999996e-05</v>
       </c>
     </row>
     <row r="116">
@@ -2398,16 +2398,16 @@
         <v>1.14</v>
       </c>
       <c r="B116" t="n">
-        <v>2.441494741416656</v>
+        <v>2.439572373201446</v>
       </c>
       <c r="C116" t="n">
-        <v>0.3998179089601347</v>
+        <v>0.399578347652101</v>
       </c>
       <c r="D116" t="n">
-        <v>0.4208532067964756</v>
+        <v>0.421422208945906</v>
       </c>
       <c r="E116" t="n">
-        <v>9.999999999999975e-05</v>
+        <v>9.999999999999995e-05</v>
       </c>
     </row>
     <row r="117">
@@ -2415,16 +2415,16 @@
         <v>1.15</v>
       </c>
       <c r="B117" t="n">
-        <v>2.44343259639161</v>
+        <v>2.4415292384842</v>
       </c>
       <c r="C117" t="n">
-        <v>0.4005883521163047</v>
+        <v>0.4003904909795193</v>
       </c>
       <c r="D117" t="n">
-        <v>0.4208786818045145</v>
+        <v>0.4214450380989714</v>
       </c>
       <c r="E117" t="n">
-        <v>9.999999999999973e-05</v>
+        <v>9.999999999999994e-05</v>
       </c>
     </row>
     <row r="118">
@@ -2432,16 +2432,16 @@
         <v>1.16</v>
       </c>
       <c r="B118" t="n">
-        <v>2.445751203736328</v>
+        <v>2.443870612926461</v>
       </c>
       <c r="C118" t="n">
-        <v>0.4013619164441412</v>
+        <v>0.4012027418045913</v>
       </c>
       <c r="D118" t="n">
-        <v>0.4209096572189389</v>
+        <v>0.4214728042372564</v>
       </c>
       <c r="E118" t="n">
-        <v>9.999999999999973e-05</v>
+        <v>9.999999999999992e-05</v>
       </c>
     </row>
     <row r="119">
@@ -2449,16 +2449,16 @@
         <v>1.17</v>
       </c>
       <c r="B119" t="n">
-        <v>2.448432661159488</v>
+        <v>2.446578429722678</v>
       </c>
       <c r="C119" t="n">
-        <v>0.4021377006037032</v>
+        <v>0.4020142930468393</v>
       </c>
       <c r="D119" t="n">
-        <v>0.4209460748485698</v>
+        <v>0.4215054580397415</v>
       </c>
       <c r="E119" t="n">
-        <v>9.999999999999971e-05</v>
+        <v>9.999999999999988e-05</v>
       </c>
     </row>
     <row r="120">
@@ -2466,16 +2466,16 @@
         <v>1.18</v>
       </c>
       <c r="B120" t="n">
-        <v>2.451459150466783</v>
+        <v>2.449634707915295</v>
       </c>
       <c r="C120" t="n">
-        <v>0.4029148032550497</v>
+        <v>0.4028243376257848</v>
       </c>
       <c r="D120" t="n">
-        <v>0.4209878766943134</v>
+        <v>0.4215429503410357</v>
       </c>
       <c r="E120" t="n">
-        <v>9.999999999999969e-05</v>
+        <v>9.999999999999986e-05</v>
       </c>
     </row>
     <row r="121">
@@ -2483,16 +2483,16 @@
         <v>1.19</v>
       </c>
       <c r="B121" t="n">
-        <v>2.454812910946802</v>
+        <v>2.453021525240603</v>
       </c>
       <c r="C121" t="n">
-        <v>0.4036923230582396</v>
+        <v>0.4036320684609499</v>
       </c>
       <c r="D121" t="n">
-        <v>0.4210350049416119</v>
+        <v>0.4215852321256381</v>
       </c>
       <c r="E121" t="n">
-        <v>9.999999999999968e-05</v>
+        <v>9.999999999999983e-05</v>
       </c>
     </row>
     <row r="122">
@@ -2500,16 +2500,16 @@
         <v>1.2</v>
       </c>
       <c r="B122" t="n">
-        <v>2.458476214146732</v>
+        <v>2.45672099239212</v>
       </c>
       <c r="C122" t="n">
-        <v>0.4044693586733318</v>
+        <v>0.4044366784718565</v>
       </c>
       <c r="D122" t="n">
-        <v>0.4210874019529872</v>
+        <v>0.4216322545222673</v>
       </c>
       <c r="E122" t="n">
-        <v>9.999999999999968e-05</v>
+        <v>9.999999999999977e-05</v>
       </c>
     </row>
     <row r="123">
@@ -2517,16 +2517,16 @@
         <v>1.21</v>
       </c>
       <c r="B123" t="n">
-        <v>2.462431340013805</v>
+        <v>2.460715228676646</v>
       </c>
       <c r="C123" t="n">
-        <v>0.4052450087603853</v>
+        <v>0.4052373605780263</v>
       </c>
       <c r="D123" t="n">
-        <v>0.4211450102606766</v>
+        <v>0.4216839687982561</v>
       </c>
       <c r="E123" t="n">
-        <v>9.999999999999967e-05</v>
+        <v>9.999999999999975e-05</v>
       </c>
     </row>
     <row r="124">
@@ -2534,16 +2534,16 @@
         <v>1.22</v>
       </c>
       <c r="B124" t="n">
-        <v>2.466660554383622</v>
+        <v>2.464986339043525</v>
       </c>
       <c r="C124" t="n">
-        <v>0.4060183719794589</v>
+        <v>0.4060333076989815</v>
       </c>
       <c r="D124" t="n">
-        <v>0.4212077725593587</v>
+        <v>0.4217403263540117</v>
       </c>
       <c r="E124" t="n">
-        <v>9.999999999999964e-05</v>
+        <v>9.999999999999969e-05</v>
       </c>
     </row>
     <row r="125">
@@ -2551,16 +2551,16 @@
         <v>1.23</v>
       </c>
       <c r="B125" t="n">
-        <v>2.471146087801411</v>
+        <v>2.469516392472738</v>
       </c>
       <c r="C125" t="n">
-        <v>0.4067885469906117</v>
+        <v>0.4068237127542438</v>
       </c>
       <c r="D125" t="n">
-        <v>0.4212756316989708</v>
+        <v>0.4218012787175411</v>
       </c>
       <c r="E125" t="n">
-        <v>9.999999999999961e-05</v>
+        <v>9.999999999999965e-05</v>
       </c>
     </row>
     <row r="126">
@@ -2568,13 +2568,13 @@
         <v>1.24</v>
       </c>
       <c r="B126" t="n">
-        <v>2.475870115666897</v>
+        <v>2.474287401712214</v>
       </c>
       <c r="C126" t="n">
-        <v>0.4075546324539027</v>
+        <v>0.4076077686633351</v>
       </c>
       <c r="D126" t="n">
-        <v>0.421348530677614</v>
+        <v>0.4218667775390402</v>
       </c>
       <c r="E126" t="n">
         <v>9.99999999999996e-05</v>
@@ -2585,16 +2585,16 @@
         <v>1.25</v>
       </c>
       <c r="B127" t="n">
-        <v>2.480814739697801</v>
+        <v>2.479281304359199</v>
       </c>
       <c r="C127" t="n">
-        <v>0.4083157270293906</v>
+        <v>0.4083846683457774</v>
       </c>
       <c r="D127" t="n">
-        <v>0.4214264126345476</v>
+        <v>0.4219367745855471</v>
       </c>
       <c r="E127" t="n">
-        <v>9.999999999999958e-05</v>
+        <v>9.999999999999956e-05</v>
       </c>
     </row>
     <row r="128">
@@ -2602,16 +2602,16 @@
         <v>1.26</v>
       </c>
       <c r="B128" t="n">
-        <v>2.485961970711048</v>
+        <v>2.484479945284721</v>
       </c>
       <c r="C128" t="n">
-        <v>0.4090709293771345</v>
+        <v>0.4091536047210924</v>
       </c>
       <c r="D128" t="n">
-        <v>0.4215092208432709</v>
+        <v>0.4220112217356581</v>
       </c>
       <c r="E128" t="n">
-        <v>9.999999999999957e-05</v>
+        <v>9.999999999999952e-05</v>
       </c>
     </row>
     <row r="129">
@@ -2619,16 +2619,16 @@
         <v>1.27</v>
       </c>
       <c r="B129" t="n">
-        <v>2.491293712724501</v>
+        <v>2.489865060404071</v>
       </c>
       <c r="C129" t="n">
-        <v>0.4098193381571933</v>
+        <v>0.4099137707088021</v>
       </c>
       <c r="D129" t="n">
-        <v>0.4215968987046922</v>
+        <v>0.4220900709743067</v>
       </c>
       <c r="E129" t="n">
-        <v>9.999999999999956e-05</v>
+        <v>9.999999999999946e-05</v>
       </c>
     </row>
     <row r="130">
@@ -2636,16 +2636,16 @@
         <v>1.28</v>
       </c>
       <c r="B130" t="n">
-        <v>2.496791748385585</v>
+        <v>2.495418261799819</v>
       </c>
       <c r="C130" t="n">
-        <v>0.410560052029626</v>
+        <v>0.4106643592284284</v>
       </c>
       <c r="D130" t="n">
-        <v>0.421689389740383</v>
+        <v>0.422173274387604</v>
       </c>
       <c r="E130" t="n">
-        <v>9.999999999999954e-05</v>
+        <v>9.999999999999939e-05</v>
       </c>
     </row>
     <row r="131">
@@ -2653,16 +2653,16 @@
         <v>1.29</v>
       </c>
       <c r="B131" t="n">
-        <v>2.502437725736312</v>
+        <v>2.501121024207197</v>
       </c>
       <c r="C131" t="n">
-        <v>0.4112921696544915</v>
+        <v>0.4114045631994932</v>
       </c>
       <c r="D131" t="n">
-        <v>0.4217866375859183</v>
+        <v>0.4222607841577413</v>
       </c>
       <c r="E131" t="n">
-        <v>9.999999999999953e-05</v>
+        <v>9.999999999999934e-05</v>
       </c>
     </row>
     <row r="132">
@@ -2670,16 +2670,16 @@
         <v>1.3</v>
       </c>
       <c r="B132" t="n">
-        <v>2.508213146327236</v>
+        <v>2.506954672874741</v>
       </c>
       <c r="C132" t="n">
-        <v>0.4120147896918487</v>
+        <v>0.4121335755415184</v>
       </c>
       <c r="D132" t="n">
-        <v>0.4218885859843014</v>
+        <v>0.4223525525579535</v>
       </c>
       <c r="E132" t="n">
-        <v>9.999999999999949e-05</v>
+        <v>9.999999999999929e-05</v>
       </c>
     </row>
     <row r="133">
@@ -2687,16 +2687,16 @@
         <v>1.31</v>
       </c>
       <c r="B133" t="n">
-        <v>2.514099354695462</v>
+        <v>2.512900372815782</v>
       </c>
       <c r="C133" t="n">
-        <v>0.4127270108017566</v>
+        <v>0.4128505891740259</v>
       </c>
       <c r="D133" t="n">
-        <v>0.4219951787794731</v>
+        <v>0.4224485319475434</v>
       </c>
       <c r="E133" t="n">
-        <v>9.999999999999949e-05</v>
+        <v>9.999999999999923e-05</v>
       </c>
     </row>
     <row r="134">
@@ -2704,16 +2704,16 @@
         <v>1.32</v>
       </c>
       <c r="B134" t="n">
-        <v>2.520077529224239</v>
+        <v>2.518939119468876</v>
       </c>
       <c r="C134" t="n">
-        <v>0.4134279316442742</v>
+        <v>0.4135547970165376</v>
       </c>
       <c r="D134" t="n">
-        <v>0.4221063599099035</v>
+        <v>0.4225486747669658</v>
       </c>
       <c r="E134" t="n">
-        <v>9.999999999999946e-05</v>
+        <v>9.999999999999916e-05</v>
       </c>
     </row>
     <row r="135">
@@ -2721,16 +2721,16 @@
         <v>1.33</v>
       </c>
       <c r="B135" t="n">
-        <v>2.526128674403773</v>
+        <v>2.525051730787403</v>
       </c>
       <c r="C135" t="n">
-        <v>0.4141166508794602</v>
+        <v>0.4142453919885754</v>
       </c>
       <c r="D135" t="n">
-        <v>0.422222073402267</v>
+        <v>0.4226529335329711</v>
       </c>
       <c r="E135" t="n">
-        <v>9.999999999999946e-05</v>
+        <v>9.999999999999911e-05</v>
       </c>
     </row>
     <row r="136">
@@ -2738,16 +2738,16 @@
         <v>1.34</v>
       </c>
       <c r="B136" t="n">
-        <v>2.532233614514665</v>
+        <v>2.531218840780413</v>
       </c>
       <c r="C136" t="n">
-        <v>0.4147922671673738</v>
+        <v>0.414921567009661</v>
       </c>
       <c r="D136" t="n">
-        <v>0.4223422633652003</v>
+        <v>0.4227612608338092</v>
       </c>
       <c r="E136" t="n">
-        <v>9.999999999999942e-05</v>
+        <v>9.999999999999906e-05</v>
       </c>
     </row>
     <row r="137">
@@ -2755,16 +2755,16 @@
         <v>1.35</v>
       </c>
       <c r="B137" t="n">
-        <v>2.538372988756913</v>
+        <v>2.537420894528383</v>
       </c>
       <c r="C137" t="n">
-        <v>0.4154538791680739</v>
+        <v>0.4155825149993165</v>
       </c>
       <c r="D137" t="n">
-        <v>0.42246687398314</v>
+        <v>0.4228736093244917</v>
       </c>
       <c r="E137" t="n">
-        <v>9.999999999999941e-05</v>
+        <v>9.999999999999899e-05</v>
       </c>
     </row>
     <row r="138">
@@ -2772,16 +2772,16 @@
         <v>1.36</v>
       </c>
       <c r="B138" t="n">
-        <v>2.544527247848596</v>
+        <v>2.543638144698753</v>
       </c>
       <c r="C138" t="n">
-        <v>0.4161005855416193</v>
+        <v>0.4162274288770639</v>
       </c>
       <c r="D138" t="n">
-        <v>0.4225958495102436</v>
+        <v>0.4229899317221121</v>
       </c>
       <c r="E138" t="n">
-        <v>9.999999999999939e-05</v>
+        <v>9.999999999999893e-05</v>
       </c>
     </row>
     <row r="139">
@@ -2789,16 +2789,16 @@
         <v>1.37</v>
       </c>
       <c r="B139" t="n">
-        <v>2.550676652119269</v>
+        <v>2.549850649587071</v>
       </c>
       <c r="C139" t="n">
-        <v>0.4167314849480691</v>
+        <v>0.4168555015624248</v>
       </c>
       <c r="D139" t="n">
-        <v>0.4227291342643901</v>
+        <v>0.4231101808012256</v>
       </c>
       <c r="E139" t="n">
-        <v>9.999999999999938e-05</v>
+        <v>9.999999999999888e-05</v>
       </c>
     </row>
     <row r="140">
@@ -2806,16 +2806,16 @@
         <v>1.38</v>
       </c>
       <c r="B140" t="n">
-        <v>2.556801271123658</v>
+        <v>2.556038272710136</v>
       </c>
       <c r="C140" t="n">
-        <v>0.4173456760474821</v>
+        <v>0.4174659259749213</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4228666726212597</v>
+        <v>0.4232343093892851</v>
       </c>
       <c r="E140" t="n">
-        <v>9.999999999999937e-05</v>
+        <v>9.999999999999881e-05</v>
       </c>
     </row>
     <row r="141">
@@ -2823,16 +2823,16 @@
         <v>1.39</v>
       </c>
       <c r="B141" t="n">
-        <v>2.562880984801492</v>
+        <v>2.562180683977804</v>
       </c>
       <c r="C141" t="n">
-        <v>0.4179422574999173</v>
+        <v>0.4180578950340751</v>
       </c>
       <c r="D141" t="n">
-        <v>0.4230084090084952</v>
+        <v>0.423362270362136</v>
       </c>
       <c r="E141" t="n">
-        <v>9.999999999999934e-05</v>
+        <v>9.999999999999876e-05</v>
       </c>
     </row>
     <row r="142">
@@ -2840,16 +2840,16 @@
         <v>1.4</v>
       </c>
       <c r="B142" t="n">
-        <v>2.568895486209235</v>
+        <v>2.568257362470037</v>
       </c>
       <c r="C142" t="n">
-        <v>0.4185203279654336</v>
+        <v>0.4186306016594084</v>
       </c>
       <c r="D142" t="n">
-        <v>0.4231542878999409</v>
+        <v>0.4234940166395675</v>
       </c>
       <c r="E142" t="n">
-        <v>9.999999999999933e-05</v>
+        <v>9.999999999999869e-05</v>
       </c>
     </row>
     <row r="143">
@@ -2857,16 +2857,16 @@
         <v>1.41</v>
       </c>
       <c r="B143" t="n">
-        <v>2.574824285849043</v>
+        <v>2.57424760084534</v>
       </c>
       <c r="C143" t="n">
-        <v>0.4190789861040901</v>
+        <v>0.4191832387704428</v>
       </c>
       <c r="D143" t="n">
-        <v>0.423304253809961</v>
+        <v>0.4236295011809207</v>
       </c>
       <c r="E143" t="n">
-        <v>9.999999999999931e-05</v>
+        <v>9.999999999999864e-05</v>
       </c>
     </row>
     <row r="144">
@@ -2874,16 +2874,16 @@
         <v>1.42</v>
       </c>
       <c r="B144" t="n">
-        <v>2.580646717619496</v>
+        <v>2.580130511405912</v>
       </c>
       <c r="C144" t="n">
-        <v>0.4196173305759456</v>
+        <v>0.4197149992867004</v>
       </c>
       <c r="D144" t="n">
-        <v>0.4234582512878364</v>
+        <v>0.4237686769807541</v>
       </c>
       <c r="E144" t="n">
-        <v>9.99999999999993e-05</v>
+        <v>9.999999999999858e-05</v>
       </c>
     </row>
     <row r="145">
@@ -2891,16 +2891,16 @@
         <v>1.43</v>
       </c>
       <c r="B145" t="n">
-        <v>2.586341946411534</v>
+        <v>2.585885033843696</v>
       </c>
       <c r="C145" t="n">
-        <v>0.4201344600410591</v>
+        <v>0.420225076127703</v>
       </c>
       <c r="D145" t="n">
-        <v>0.4236162249122391</v>
+        <v>0.4239114970645639</v>
       </c>
       <c r="E145" t="n">
-        <v>9.999999999999929e-05</v>
+        <v>9.999999999999853e-05</v>
       </c>
     </row>
     <row r="146">
@@ -2908,16 +2908,16 @@
         <v>1.44</v>
       </c>
       <c r="B146" t="n">
-        <v>2.591888977371502</v>
+        <v>2.591489944689961</v>
       </c>
       <c r="C146" t="n">
-        <v>0.4206294731594895</v>
+        <v>0.4207126622129724</v>
       </c>
       <c r="D146" t="n">
-        <v>0.4237781192857848</v>
+        <v>0.4240579144845619</v>
       </c>
       <c r="E146" t="n">
-        <v>9.999999999999926e-05</v>
+        <v>9.999999999999847e-05</v>
       </c>
     </row>
     <row r="147">
@@ -2925,16 +2925,16 @@
         <v>1.45</v>
       </c>
       <c r="B147" t="n">
-        <v>2.597266666851388</v>
+        <v>2.59692386848911</v>
       </c>
       <c r="C147" t="n">
-        <v>0.4211014685912958</v>
+        <v>0.4211769504620307</v>
       </c>
       <c r="D147" t="n">
-        <v>0.4239438790296625</v>
+        <v>0.424207882315508</v>
       </c>
       <c r="E147" t="n">
-        <v>9.999999999999926e-05</v>
+        <v>9.999999999999842e-05</v>
       </c>
     </row>
     <row r="148">
@@ -2942,16 +2942,16 @@
         <v>1.46</v>
       </c>
       <c r="B148" t="n">
-        <v>2.60245373506402</v>
+        <v>2.602165290715118</v>
       </c>
       <c r="C148" t="n">
-        <v>0.4215495449965368</v>
+        <v>0.4216171337943996</v>
       </c>
       <c r="D148" t="n">
-        <v>0.4241134487783406</v>
+        <v>0.4243613536505992</v>
       </c>
       <c r="E148" t="n">
-        <v>9.999999999999923e-05</v>
+        <v>9.999999999999836e-05</v>
       </c>
     </row>
     <row r="149">
@@ -2959,16 +2959,16 @@
         <v>1.47</v>
       </c>
       <c r="B149" t="n">
-        <v>2.60742878045845</v>
+        <v>2.607192572446265</v>
       </c>
       <c r="C149" t="n">
-        <v>0.4219728010352716</v>
+        <v>0.4220324051296012</v>
       </c>
       <c r="D149" t="n">
-        <v>0.4242867731743511</v>
+        <v>0.4245182815974128</v>
       </c>
       <c r="E149" t="n">
-        <v>9.999999999999923e-05</v>
+        <v>9.999999999999832e-05</v>
       </c>
     </row>
     <row r="150">
@@ -2976,16 +2976,16 @@
         <v>1.48</v>
       </c>
       <c r="B150" t="n">
-        <v>2.612170295827667</v>
+        <v>2.611983966810751</v>
       </c>
       <c r="C150" t="n">
-        <v>0.422370335367559</v>
+        <v>0.4224219573871573</v>
       </c>
       <c r="D150" t="n">
-        <v>0.4244637968631484</v>
+        <v>0.4246786192739061</v>
       </c>
       <c r="E150" t="n">
-        <v>9.999999999999921e-05</v>
+        <v>9.999999999999828e-05</v>
       </c>
     </row>
     <row r="151">
@@ -2993,16 +2993,16 @@
         <v>1.49</v>
       </c>
       <c r="B151" t="n">
-        <v>2.616656686157421</v>
+        <v>2.616517637212249</v>
       </c>
       <c r="C151" t="n">
-        <v>0.4227412466534581</v>
+        <v>0.4227849834865896</v>
       </c>
       <c r="D151" t="n">
-        <v>0.4246444644880464</v>
+        <v>0.4248423198044696</v>
       </c>
       <c r="E151" t="n">
-        <v>9.999999999999921e-05</v>
+        <v>9.999999999999823e-05</v>
       </c>
     </row>
     <row r="152">
@@ -3010,16 +3010,16 @@
         <v>1.5</v>
       </c>
       <c r="B152" t="n">
-        <v>2.620866288221138</v>
+        <v>2.620771677340542</v>
       </c>
       <c r="C152" t="n">
-        <v>0.4230846335530278</v>
+        <v>0.4231206763474202</v>
       </c>
       <c r="D152" t="n">
-        <v>0.4248287206852291</v>
+        <v>0.4250093363160357</v>
       </c>
       <c r="E152" t="n">
-        <v>9.999999999999919e-05</v>
+        <v>9.99999999999982e-05</v>
       </c>
     </row>
     <row r="153">
@@ -3027,16 +3027,16 @@
         <v>1.51</v>
       </c>
       <c r="B153" t="n">
-        <v>2.624777391921715</v>
+        <v>2.624724132968097</v>
       </c>
       <c r="C153" t="n">
-        <v>0.4233995947263269</v>
+        <v>0.4234282288891711</v>
       </c>
       <c r="D153" t="n">
-        <v>0.4250165100788395</v>
+        <v>0.4251796219342422</v>
       </c>
       <c r="E153" t="n">
-        <v>9.999999999999918e-05</v>
+        <v>9.999999999999815e-05</v>
       </c>
     </row>
     <row r="154">
@@ -3044,16 +3044,16 @@
         <v>1.52</v>
       </c>
       <c r="B154" t="n">
-        <v>2.628368263376457</v>
+        <v>2.628353025528675</v>
       </c>
       <c r="C154" t="n">
-        <v>0.4236852288334145</v>
+        <v>0.4237068340313639</v>
       </c>
       <c r="D154" t="n">
-        <v>0.425207777276142</v>
+        <v>0.4253531297796496</v>
       </c>
       <c r="E154" t="n">
-        <v>9.999999999999918e-05</v>
+        <v>9.999999999999812e-05</v>
       </c>
     </row>
     <row r="155">
@@ -3061,16 +3061,16 @@
         <v>1.53</v>
       </c>
       <c r="B155" t="n">
-        <v>2.631617169736404</v>
+        <v>2.631636377469014</v>
       </c>
       <c r="C155" t="n">
-        <v>0.4239406345343495</v>
+        <v>0.4239556846935207</v>
       </c>
       <c r="D155" t="n">
-        <v>0.425402466862761</v>
+        <v>0.4255298129640127</v>
       </c>
       <c r="E155" t="n">
-        <v>9.999999999999916e-05</v>
+        <v>9.999999999999809e-05</v>
       </c>
     </row>
     <row r="156">
@@ -3078,16 +3078,16 @@
         <v>1.54</v>
       </c>
       <c r="B156" t="n">
-        <v>2.634502405726035</v>
+        <v>2.634552239359065</v>
       </c>
       <c r="C156" t="n">
-        <v>0.4241649104891908</v>
+        <v>0.4241739737951633</v>
       </c>
       <c r="D156" t="n">
-        <v>0.4256005233979954</v>
+        <v>0.4257096245866069</v>
       </c>
       <c r="E156" t="n">
-        <v>9.999999999999916e-05</v>
+        <v>9.999999999999807e-05</v>
       </c>
     </row>
     <row r="157">
@@ -3095,16 +3095,16 @@
         <v>1.55</v>
       </c>
       <c r="B157" t="n">
-        <v>2.637002321883581</v>
+        <v>2.637078718740433</v>
       </c>
       <c r="C157" t="n">
-        <v>0.4243571553579973</v>
+        <v>0.4243608942558137</v>
       </c>
       <c r="D157" t="n">
-        <v>0.4258018914102066</v>
+        <v>0.4258925177306082</v>
       </c>
       <c r="E157" t="n">
-        <v>9.999999999999915e-05</v>
+        <v>9.999999999999804e-05</v>
       </c>
     </row>
     <row r="158">
@@ -3112,16 +3112,16 @@
         <v>1.56</v>
       </c>
       <c r="B158" t="n">
-        <v>2.639095354476173</v>
+        <v>2.63919401068638</v>
       </c>
       <c r="C158" t="n">
-        <v>0.4245164678008281</v>
+        <v>0.4245156389949937</v>
       </c>
       <c r="D158" t="n">
-        <v>0.426006515392283</v>
+        <v>0.426078445459526</v>
       </c>
       <c r="E158" t="n">
-        <v>9.999999999999914e-05</v>
+        <v>9.999999999999801e-05</v>
       </c>
     </row>
     <row r="159">
@@ -3129,16 +3129,16 @@
         <v>1.57</v>
       </c>
       <c r="B159" t="n">
-        <v>2.640760057057601</v>
+        <v>2.640876430040163</v>
       </c>
       <c r="C159" t="n">
-        <v>0.4246419464777421</v>
+        <v>0.4246374009322252</v>
       </c>
       <c r="D159" t="n">
-        <v>0.4262143397971784</v>
+        <v>0.4262673608136925</v>
       </c>
       <c r="E159" t="n">
-        <v>9.999999999999915e-05</v>
+        <v>9.999999999999801e-05</v>
       </c>
     </row>
     <row r="160">
@@ -3146,16 +3146,16 @@
         <v>1.58</v>
       </c>
       <c r="B160" t="n">
-        <v>2.641975133629769</v>
+        <v>2.642104445291504</v>
       </c>
       <c r="C160" t="n">
-        <v>0.4247326900487981</v>
+        <v>0.4247253729870301</v>
       </c>
       <c r="D160" t="n">
-        <v>0.4264253090335254</v>
+        <v>0.4264592168068023</v>
       </c>
       <c r="E160" t="n">
-        <v>9.999999999999914e-05</v>
+        <v>9.9999999999998e-05</v>
       </c>
     </row>
     <row r="161">
@@ -3163,16 +3163,16 @@
         <v>1.59</v>
       </c>
       <c r="B161" t="n">
-        <v>2.642719473361864</v>
+        <v>2.642856714043754</v>
       </c>
       <c r="C161" t="n">
-        <v>0.4247877971740551</v>
+        <v>0.4247787480789303</v>
       </c>
       <c r="D161" t="n">
-        <v>0.4266393674613239</v>
+        <v>0.4266539664225082</v>
       </c>
       <c r="E161" t="n">
-        <v>9.999999999999914e-05</v>
+        <v>9.9999999999998e-05</v>
       </c>
     </row>
     <row r="162">
@@ -3180,16 +3180,16 @@
         <v>1.6</v>
       </c>
       <c r="B162" t="n">
-        <v>2.642972186813929</v>
+        <v>2.643112120016701</v>
       </c>
       <c r="C162" t="n">
-        <v>0.4248063665135722</v>
+        <v>0.4247967191274478</v>
       </c>
       <c r="D162" t="n">
-        <v>0.4268564593877036</v>
+        <v>0.4268515626110699</v>
       </c>
       <c r="E162" t="n">
-        <v>9.999999999999914e-05</v>
+        <v>9.999999999999799e-05</v>
       </c>
     </row>
     <row r="163">
@@ -3197,16 +3197,16 @@
         <v>1.61</v>
       </c>
       <c r="B163" t="n">
-        <v>2.642757060682768</v>
+        <v>2.642897350657758</v>
       </c>
       <c r="C163" t="n">
-        <v>0.4248036833882844</v>
+        <v>0.4247941142679862</v>
       </c>
       <c r="D163" t="n">
-        <v>0.4271026955875759</v>
+        <v>0.4270787633781793</v>
       </c>
       <c r="E163" t="n">
-        <v>9.999999999999914e-05</v>
+        <v>9.999999999999799e-05</v>
       </c>
     </row>
     <row r="164">
@@ -3214,16 +3214,16 @@
         <v>1.62</v>
       </c>
       <c r="B164" t="n">
-        <v>2.642114503836825</v>
+        <v>2.642255837260807</v>
       </c>
       <c r="C164" t="n">
-        <v>0.4247954554727067</v>
+        <v>0.4247861159193017</v>
       </c>
       <c r="D164" t="n">
-        <v>0.4274037536038841</v>
+        <v>0.4273618691158179</v>
       </c>
       <c r="E164" t="n">
-        <v>9.999999999999914e-05</v>
+        <v>9.999999999999799e-05</v>
       </c>
     </row>
     <row r="165">
@@ -3231,16 +3231,16 @@
         <v>1.63</v>
       </c>
       <c r="B165" t="n">
-        <v>2.641048901143932</v>
+        <v>2.641191923918608</v>
       </c>
       <c r="C165" t="n">
-        <v>0.4247814149572668</v>
+        <v>0.4247724484259444</v>
       </c>
       <c r="D165" t="n">
-        <v>0.4277589419930666</v>
+        <v>0.427700161155298</v>
       </c>
       <c r="E165" t="n">
-        <v>9.999999999999914e-05</v>
+        <v>9.999999999999799e-05</v>
       </c>
     </row>
     <row r="166">
@@ -3248,16 +3248,16 @@
         <v>1.64</v>
       </c>
       <c r="B166" t="n">
-        <v>2.639564835409551</v>
+        <v>2.639710152090641</v>
       </c>
       <c r="C166" t="n">
-        <v>0.4247612940323926</v>
+        <v>0.4247528361324644</v>
       </c>
       <c r="D166" t="n">
-        <v>0.42816758740331</v>
+        <v>0.4280929397979679</v>
       </c>
       <c r="E166" t="n">
-        <v>9.999999999999914e-05</v>
+        <v>9.9999999999998e-05</v>
       </c>
     </row>
     <row r="167">
@@ -3265,16 +3265,16 @@
         <v>1.65</v>
       </c>
       <c r="B167" t="n">
-        <v>2.637667080483277</v>
+        <v>2.637815253784695</v>
       </c>
       <c r="C167" t="n">
-        <v>0.4247348248885122</v>
+        <v>0.4247270033834121</v>
       </c>
       <c r="D167" t="n">
-        <v>0.4286290336430312</v>
+        <v>0.4285395233342196</v>
       </c>
       <c r="E167" t="n">
-        <v>9.999999999999914e-05</v>
+        <v>9.9999999999998e-05</v>
       </c>
     </row>
     <row r="168">
@@ -3282,16 +3282,16 @@
         <v>1.66</v>
       </c>
       <c r="B168" t="n">
-        <v>2.635360594289228</v>
+        <v>2.635512144661603</v>
       </c>
       <c r="C168" t="n">
-        <v>0.4247017397160534</v>
+        <v>0.4246946745233378</v>
       </c>
       <c r="D168" t="n">
-        <v>0.4291426407717408</v>
+        <v>0.4290392470864677</v>
       </c>
       <c r="E168" t="n">
-        <v>9.999999999999915e-05</v>
+        <v>9.9999999999998e-05</v>
       </c>
     </row>
     <row r="169">
@@ -3299,16 +3299,16 @@
         <v>1.67</v>
       </c>
       <c r="B169" t="n">
-        <v>2.632650511791326</v>
+        <v>2.63280591707396</v>
       </c>
       <c r="C169" t="n">
-        <v>0.4246617707054442</v>
+        <v>0.4246555738967915</v>
       </c>
       <c r="D169" t="n">
-        <v>0.429707784212166</v>
+        <v>0.4295914624748885</v>
       </c>
       <c r="E169" t="n">
-        <v>9.999999999999915e-05</v>
+        <v>9.999999999999801e-05</v>
       </c>
     </row>
     <row r="170">
@@ -3316,16 +3316,16 @@
         <v>1.68</v>
       </c>
       <c r="B170" t="n">
-        <v>2.629542137904274</v>
+        <v>2.629701833049514</v>
       </c>
       <c r="C170" t="n">
-        <v>0.4246146500471126</v>
+        <v>0.4246094258483236</v>
       </c>
       <c r="D170" t="n">
-        <v>0.4303238538825599</v>
+        <v>0.4301955361047671</v>
       </c>
       <c r="E170" t="n">
-        <v>9.999999999999915e-05</v>
+        <v>9.999999999999801e-05</v>
       </c>
     </row>
     <row r="171">
@@ -3333,16 +3333,16 @@
         <v>1.69</v>
       </c>
       <c r="B171" t="n">
-        <v>2.626040940360871</v>
+        <v>2.626205317229753</v>
       </c>
       <c r="C171" t="n">
-        <v>0.4245601099314864</v>
+        <v>0.4245559547224841</v>
       </c>
       <c r="D171" t="n">
-        <v>0.4309902533481774</v>
+        <v>0.4308508488743533</v>
       </c>
       <c r="E171" t="n">
-        <v>9.999999999999915e-05</v>
+        <v>9.999999999999803e-05</v>
       </c>
     </row>
     <row r="172">
@@ -3350,16 +3350,16 @@
         <v>1.7</v>
       </c>
       <c r="B172" t="n">
-        <v>2.622152542546114</v>
+        <v>2.622321949774017</v>
       </c>
       <c r="C172" t="n">
-        <v>0.4244978825489936</v>
+        <v>0.4244948848638235</v>
       </c>
       <c r="D172" t="n">
-        <v>0.4317063989909428</v>
+        <v>0.4315567951021835</v>
       </c>
       <c r="E172" t="n">
-        <v>9.999999999999916e-05</v>
+        <v>9.999999999999803e-05</v>
       </c>
     </row>
     <row r="173">
@@ -3367,16 +3367,16 @@
         <v>1.71</v>
       </c>
       <c r="B173" t="n">
-        <v>2.617882716308321</v>
+        <v>2.618057459239266</v>
       </c>
       <c r="C173" t="n">
-        <v>0.4244277000900621</v>
+        <v>0.4244259406168919</v>
       </c>
       <c r="D173" t="n">
-        <v>0.4324717191963864</v>
+        <v>0.4323127816728714</v>
       </c>
       <c r="E173" t="n">
-        <v>9.999999999999916e-05</v>
+        <v>9.999999999999804e-05</v>
       </c>
     </row>
     <row r="174">
@@ -3384,16 +3384,16 @@
         <v>1.72</v>
       </c>
       <c r="B174" t="n">
-        <v>2.613237374757302</v>
+        <v>2.613417715445419</v>
       </c>
       <c r="C174" t="n">
-        <v>0.42434929474512</v>
+        <v>0.4243488463262394</v>
       </c>
       <c r="D174" t="n">
-        <v>0.4332856535569679</v>
+        <v>0.4331182272004245</v>
       </c>
       <c r="E174" t="n">
-        <v>9.999999999999916e-05</v>
+        <v>9.999999999999805e-05</v>
       </c>
     </row>
     <row r="175">
@@ -3401,16 +3401,16 @@
         <v>1.73</v>
       </c>
       <c r="B175" t="n">
-        <v>2.608222565059357</v>
+        <v>2.608408722335944</v>
       </c>
       <c r="C175" t="n">
-        <v>0.424262398704595</v>
+        <v>0.4242633263364163</v>
       </c>
       <c r="D175" t="n">
-        <v>0.4341476520909485</v>
+        <v>0.4339725612081871</v>
       </c>
       <c r="E175" t="n">
-        <v>9.999999999999918e-05</v>
+        <v>9.999999999999807e-05</v>
       </c>
     </row>
     <row r="176">
@@ -3418,16 +3418,16 @@
         <v>1.74</v>
       </c>
       <c r="B176" t="n">
-        <v>2.60284446123864</v>
+        <v>2.603036610843168</v>
       </c>
       <c r="C176" t="n">
-        <v>0.4241667441589152</v>
+        <v>0.4241691049919729</v>
       </c>
       <c r="D176" t="n">
-        <v>0.4350571744760193</v>
+        <v>0.4348752233245564</v>
       </c>
       <c r="E176" t="n">
-        <v>9.999999999999918e-05</v>
+        <v>9.999999999999807e-05</v>
       </c>
     </row>
     <row r="177">
@@ -3435,16 +3435,16 @@
         <v>1.75</v>
       </c>
       <c r="B177" t="n">
-        <v>2.59710935699418</v>
+        <v>2.597307631767482</v>
       </c>
       <c r="C177" t="n">
-        <v>0.4240620632985084</v>
+        <v>0.4240659066374594</v>
       </c>
       <c r="D177" t="n">
-        <v>0.4360136892969291</v>
+        <v>0.4358256624936644</v>
       </c>
       <c r="E177" t="n">
-        <v>9.999999999999919e-05</v>
+        <v>9.999999999999808e-05</v>
       </c>
     </row>
     <row r="178">
@@ -3452,16 +3452,16 @@
         <v>1.76</v>
       </c>
       <c r="B178" t="n">
-        <v>2.591023658541574</v>
+        <v>2.591228148679404</v>
       </c>
       <c r="C178" t="n">
-        <v>0.4239480883138027</v>
+        <v>0.4239534556174259</v>
       </c>
       <c r="D178" t="n">
-        <v>0.4370166733063966</v>
+        <v>0.4368233362002565</v>
       </c>
       <c r="E178" t="n">
-        <v>9.999999999999919e-05</v>
+        <v>9.999999999999811e-05</v>
       </c>
     </row>
     <row r="179">
@@ -3469,16 +3469,16 @@
         <v>1.77</v>
       </c>
       <c r="B179" t="n">
-        <v>2.584593877488094</v>
+        <v>2.584804630853152</v>
       </c>
       <c r="C179" t="n">
-        <v>0.4238245513952259</v>
+        <v>0.4238314762764228</v>
       </c>
       <c r="D179" t="n">
-        <v>0.4380656106986308</v>
+        <v>0.4378677097080441</v>
       </c>
       <c r="E179" t="n">
-        <v>9.999999999999921e-05</v>
+        <v>9.999999999999813e-05</v>
       </c>
     </row>
     <row r="180">
@@ -3486,16 +3486,16 @@
         <v>1.78</v>
       </c>
       <c r="B180" t="n">
-        <v>2.577826623749676</v>
+        <v>2.578043646240141</v>
       </c>
       <c r="C180" t="n">
-        <v>0.423691184733206</v>
+        <v>0.4236996929590001</v>
       </c>
       <c r="D180" t="n">
-        <v>0.4391599923948168</v>
+        <v>0.4389582553108428</v>
       </c>
       <c r="E180" t="n">
-        <v>9.999999999999921e-05</v>
+        <v>9.999999999999815e-05</v>
       </c>
     </row>
     <row r="181">
@@ -3503,16 +3503,16 @@
         <v>1.79</v>
       </c>
       <c r="B181" t="n">
-        <v>2.57072859851796</v>
+        <v>2.570951854490499</v>
       </c>
       <c r="C181" t="n">
-        <v>0.423547720518171</v>
+        <v>0.4235578300097082</v>
       </c>
       <c r="D181" t="n">
-        <v>0.4402993153399637</v>
+        <v>0.4400944515958505</v>
       </c>
       <c r="E181" t="n">
-        <v>9.999999999999922e-05</v>
+        <v>9.999999999999816e-05</v>
       </c>
     </row>
     <row r="182">
@@ -3520,16 +3520,16 @@
         <v>1.8</v>
       </c>
       <c r="B182" t="n">
-        <v>2.563306587285251</v>
+        <v>2.563536000030446</v>
       </c>
       <c r="C182" t="n">
-        <v>0.4233938909405487</v>
+        <v>0.4234056117730973</v>
       </c>
       <c r="D182" t="n">
-        <v>0.4414830818105436</v>
+        <v>0.4412757827184555</v>
       </c>
       <c r="E182" t="n">
-        <v>9.999999999999923e-05</v>
+        <v>9.999999999999818e-05</v>
       </c>
     </row>
     <row r="183">
@@ -3537,16 +3537,16 @@
         <v>1.81</v>
       </c>
       <c r="B183" t="n">
-        <v>2.555567452934986</v>
+        <v>2.55580290520303</v>
       </c>
       <c r="C183" t="n">
-        <v>0.4232294281907671</v>
+        <v>0.4232427625937175</v>
       </c>
       <c r="D183" t="n">
-        <v>0.4427107987323837</v>
+        <v>0.4425017376879995</v>
       </c>
       <c r="E183" t="n">
-        <v>9.999999999999923e-05</v>
+        <v>9.99999999999982e-05</v>
       </c>
     </row>
     <row r="184">
@@ -3554,16 +3554,16 @@
         <v>1.82</v>
       </c>
       <c r="B184" t="n">
-        <v>2.547518128904964</v>
+        <v>2.547759463479478</v>
       </c>
       <c r="C184" t="n">
-        <v>0.4230540644592541</v>
+        <v>0.4230690068161191</v>
       </c>
       <c r="D184" t="n">
-        <v>0.4439819770083102</v>
+        <v>0.4437718096639605</v>
       </c>
       <c r="E184" t="n">
-        <v>9.999999999999925e-05</v>
+        <v>9.999999999999822e-05</v>
       </c>
     </row>
     <row r="185">
@@ -3571,16 +3571,16 @@
         <v>1.83</v>
       </c>
       <c r="B185" t="n">
-        <v>2.539165612430293</v>
+        <v>2.539412632748059</v>
       </c>
       <c r="C185" t="n">
-        <v>0.4228675319364377</v>
+        <v>0.4228840687848524</v>
       </c>
       <c r="D185" t="n">
-        <v>0.44529613085507</v>
+        <v>0.445085495262048</v>
       </c>
       <c r="E185" t="n">
-        <v>9.999999999999926e-05</v>
+        <v>9.999999999999824e-05</v>
       </c>
     </row>
     <row r="186">
@@ -3588,16 +3588,16 @@
         <v>1.84</v>
       </c>
       <c r="B186" t="n">
-        <v>2.530516957872709</v>
+        <v>2.530769428687081</v>
       </c>
       <c r="C186" t="n">
-        <v>0.4226695628127459</v>
+        <v>0.4226876728444675</v>
       </c>
       <c r="D186" t="n">
-        <v>0.4466527771490889</v>
+        <v>0.4464422938697441</v>
       </c>
       <c r="E186" t="n">
-        <v>9.999999999999927e-05</v>
+        <v>9.999999999999827e-05</v>
       </c>
     </row>
     <row r="187">
@@ -3605,16 +3605,16 @@
         <v>1.85</v>
       </c>
       <c r="B187" t="n">
-        <v>2.521579270142579</v>
+        <v>2.521836918228317</v>
       </c>
       <c r="C187" t="n">
-        <v>0.4224598892786065</v>
+        <v>0.4224795433395147</v>
       </c>
       <c r="D187" t="n">
-        <v>0.4480514347806591</v>
+        <v>0.4478417069708521</v>
       </c>
       <c r="E187" t="n">
-        <v>9.999999999999927e-05</v>
+        <v>9.99999999999983e-05</v>
       </c>
     </row>
     <row r="188">
@@ -3622,16 +3622,16 @@
         <v>1.86</v>
       </c>
       <c r="B188" t="n">
-        <v>2.512359698219595</v>
+        <v>2.512622213116861</v>
       </c>
       <c r="C188" t="n">
-        <v>0.4222382435244474</v>
+        <v>0.4222594046145441</v>
       </c>
       <c r="D188" t="n">
-        <v>0.4494916240161713</v>
+        <v>0.4492832374786463</v>
       </c>
       <c r="E188" t="n">
-        <v>9.999999999999929e-05</v>
+        <v>9.999999999999831e-05</v>
       </c>
     </row>
     <row r="189">
@@ -3639,16 +3639,16 @@
         <v>1.87</v>
       </c>
       <c r="B189" t="n">
-        <v>2.502865428777857</v>
+        <v>2.503132463573067</v>
       </c>
       <c r="C189" t="n">
-        <v>0.4220043577406967</v>
+        <v>0.4220269810141061</v>
       </c>
       <c r="D189" t="n">
-        <v>0.4509728658680442</v>
+        <v>0.4507663890772525</v>
       </c>
       <c r="E189" t="n">
-        <v>9.99999999999993e-05</v>
+        <v>9.999999999999835e-05</v>
       </c>
     </row>
     <row r="190">
@@ -3656,16 +3656,16 @@
         <v>1.88</v>
       </c>
       <c r="B190" t="n">
-        <v>2.493103679920706</v>
+        <v>2.493374852061952</v>
       </c>
       <c r="C190" t="n">
-        <v>0.4217579641177822</v>
+        <v>0.4217819968827508</v>
       </c>
       <c r="D190" t="n">
-        <v>0.4524946814720259</v>
+        <v>0.4522906655709136</v>
       </c>
       <c r="E190" t="n">
-        <v>9.999999999999931e-05</v>
+        <v>9.999999999999838e-05</v>
       </c>
     </row>
     <row r="191">
@@ -3673,16 +3673,16 @@
         <v>1.89</v>
       </c>
       <c r="B191" t="n">
-        <v>2.483081695030351</v>
+        <v>2.483356587175094</v>
       </c>
       <c r="C191" t="n">
-        <v>0.421498794846132</v>
+        <v>0.4215241765650284</v>
       </c>
       <c r="D191" t="n">
-        <v>0.4540565914715741</v>
+        <v>0.4538555702408301</v>
       </c>
       <c r="E191" t="n">
-        <v>9.999999999999933e-05</v>
+        <v>9.999999999999841e-05</v>
       </c>
     </row>
     <row r="192">
@@ -3690,16 +3690,16 @@
         <v>1.9</v>
       </c>
       <c r="B192" t="n">
-        <v>2.472806736737036</v>
+        <v>2.473084897629776</v>
       </c>
       <c r="C192" t="n">
-        <v>0.4212265821161738</v>
+        <v>0.4212532444054891</v>
       </c>
       <c r="D192" t="n">
-        <v>0.4556581154090477</v>
+        <v>0.4554606052092919</v>
       </c>
       <c r="E192" t="n">
-        <v>9.999999999999934e-05</v>
+        <v>9.999999999999845e-05</v>
       </c>
     </row>
     <row r="193">
@@ -3707,16 +3707,16 @@
         <v>1.91</v>
       </c>
       <c r="B193" t="n">
-        <v>2.462286081012142</v>
+        <v>2.462567026389766</v>
       </c>
       <c r="C193" t="n">
-        <v>0.4209410581183357</v>
+        <v>0.4209689247486832</v>
       </c>
       <c r="D193" t="n">
-        <v>0.4572987711234704</v>
+        <v>0.4571052708108482</v>
       </c>
       <c r="E193" t="n">
-        <v>9.999999999999935e-05</v>
+        <v>9.999999999999847e-05</v>
       </c>
     </row>
     <row r="194">
@@ -3724,16 +3724,16 @@
         <v>1.92</v>
       </c>
       <c r="B194" t="n">
-        <v>2.451527011389337</v>
+        <v>2.451810224911882</v>
       </c>
       <c r="C194" t="n">
-        <v>0.4206419550430455</v>
+        <v>0.420670941939161</v>
       </c>
       <c r="D194" t="n">
-        <v>0.4589780741546539</v>
+        <v>0.4587890649702912</v>
       </c>
       <c r="E194" t="n">
-        <v>9.999999999999937e-05</v>
+        <v>9.99999999999985e-05</v>
       </c>
     </row>
     <row r="195">
@@ -3741,16 +3741,16 @@
         <v>1.93</v>
       </c>
       <c r="B195" t="n">
-        <v>2.440536813317563</v>
+        <v>2.440821747522116</v>
       </c>
       <c r="C195" t="n">
-        <v>0.4203290050807314</v>
+        <v>0.4203590203214727</v>
       </c>
       <c r="D195" t="n">
-        <v>0.4606955371534924</v>
+        <v>0.460511482587257</v>
       </c>
       <c r="E195" t="n">
-        <v>9.999999999999938e-05</v>
+        <v>9.999999999999854e-05</v>
       </c>
     </row>
     <row r="196">
@@ -3758,16 +3758,16 @@
         <v>1.94</v>
       </c>
       <c r="B196" t="n">
-        <v>2.429322768649325</v>
+        <v>2.429608845924835</v>
       </c>
       <c r="C196" t="n">
-        <v>0.4200019404218211</v>
+        <v>0.4200328842401683</v>
       </c>
       <c r="D196" t="n">
-        <v>0.46245066929827</v>
+        <v>0.4622720149272763</v>
       </c>
       <c r="E196" t="n">
-        <v>9.999999999999941e-05</v>
+        <v>9.999999999999857e-05</v>
       </c>
     </row>
     <row r="197">
@@ -3775,16 +3775,16 @@
         <v>1.95</v>
       </c>
       <c r="B197" t="n">
-        <v>2.417892150267479</v>
+        <v>2.418178763848249</v>
       </c>
       <c r="C197" t="n">
-        <v>0.4196604932567426</v>
+        <v>0.4196922580397981</v>
       </c>
       <c r="D197" t="n">
-        <v>0.4642429757168448</v>
+        <v>0.4640701490191339</v>
       </c>
       <c r="E197" t="n">
-        <v>9.999999999999942e-05</v>
+        <v>9.999999999999861e-05</v>
       </c>
     </row>
     <row r="198">
@@ -3792,16 +3792,16 @@
         <v>1.96</v>
       </c>
       <c r="B198" t="n">
-        <v>2.406252216853376</v>
+        <v>2.406538731829055</v>
       </c>
       <c r="C198" t="n">
-        <v>0.4193043957759239</v>
+        <v>0.4193368660649125</v>
       </c>
       <c r="D198" t="n">
-        <v>0.4660719569146016</v>
+        <v>0.465905367058423</v>
       </c>
       <c r="E198" t="n">
-        <v>9.999999999999945e-05</v>
+        <v>9.999999999999865e-05</v>
       </c>
     </row>
     <row r="199">
@@ -3809,16 +3809,16 @@
         <v>1.97</v>
       </c>
       <c r="B199" t="n">
-        <v>2.394410207798953</v>
+        <v>2.394695962138862</v>
       </c>
       <c r="C199" t="n">
-        <v>0.4189333801697928</v>
+        <v>0.4189664326600616</v>
       </c>
       <c r="D199" t="n">
-        <v>0.4679371082080876</v>
+        <v>0.4677771458172101</v>
       </c>
       <c r="E199" t="n">
-        <v>9.999999999999946e-05</v>
+        <v>9.999999999999869e-05</v>
       </c>
     </row>
     <row r="200">
@@ -3826,16 +3826,16 @@
         <v>1.98</v>
       </c>
       <c r="B200" t="n">
-        <v>2.382373338265055</v>
+        <v>2.382657643854737</v>
       </c>
       <c r="C200" t="n">
-        <v>0.4185471786287773</v>
+        <v>0.4185806821697956</v>
       </c>
       <c r="D200" t="n">
-        <v>0.4698379191642726</v>
+        <v>0.4696849560597493</v>
       </c>
       <c r="E200" t="n">
-        <v>9.999999999999948e-05</v>
+        <v>9.999999999999873e-05</v>
       </c>
     </row>
     <row r="201">
@@ -3843,16 +3843,16 @@
         <v>1.99</v>
       </c>
       <c r="B201" t="n">
-        <v>2.370148794387998</v>
+        <v>2.37043093807589</v>
       </c>
       <c r="C201" t="n">
-        <v>0.4181455233433055</v>
+        <v>0.4181793389386647</v>
       </c>
       <c r="D201" t="n">
-        <v>0.4717738730453994</v>
+        <v>0.4716282619642142</v>
       </c>
       <c r="E201" t="n">
-        <v>9.999999999999949e-05</v>
+        <v>9.999999999999877e-05</v>
       </c>
     </row>
     <row r="202">
@@ -3860,16 +3860,16 @@
         <v>2</v>
       </c>
       <c r="B202" t="n">
-        <v>2.357743728636096</v>
+        <v>2.358022973288299</v>
       </c>
       <c r="C202" t="n">
-        <v>0.417728146503805</v>
+        <v>0.4177621273112193</v>
       </c>
       <c r="D202" t="n">
-        <v>0.4737444462594131</v>
+        <v>0.4736065205504393</v>
       </c>
       <c r="E202" t="n">
-        <v>9.999999999999952e-05</v>
+        <v>9.999999999999883e-05</v>
       </c>
     </row>
     <row r="203">
@@ -3877,16 +3877,16 @@
         <v>2.01</v>
       </c>
       <c r="B203" t="n">
-        <v>2.345165255317614</v>
+        <v>2.345440840878745</v>
       </c>
       <c r="C203" t="n">
-        <v>0.417294780300704</v>
+        <v>0.4173287716320093</v>
       </c>
       <c r="D203" t="n">
-        <v>0.4757491078159852</v>
+        <v>0.4756191811136922</v>
       </c>
       <c r="E203" t="n">
-        <v>9.999999999999953e-05</v>
+        <v>9.999999999999885e-05</v>
       </c>
     </row>
     <row r="204">
@@ -3894,16 +3894,16 @@
         <v>2.02</v>
       </c>
       <c r="B204" t="n">
-        <v>2.332420446241322</v>
+        <v>2.332691590799507</v>
       </c>
       <c r="C204" t="n">
-        <v>0.4168451569244304</v>
+        <v>0.4168789962455852</v>
       </c>
       <c r="D204" t="n">
-        <v>0.4777873187881674</v>
+        <v>0.4776656846645195</v>
       </c>
       <c r="E204" t="n">
-        <v>9.999999999999956e-05</v>
+        <v>9.999999999999891e-05</v>
       </c>
     </row>
     <row r="205">
@@ -3911,16 +3911,16 @@
         <v>2.03</v>
       </c>
       <c r="B205" t="n">
-        <v>2.319516326530595</v>
+        <v>2.319782227384694</v>
       </c>
       <c r="C205" t="n">
-        <v>0.4163790085654121</v>
+        <v>0.4164125254964971</v>
       </c>
       <c r="D205" t="n">
-        <v>0.4798585317797416</v>
+        <v>0.4797454633747401</v>
       </c>
       <c r="E205" t="n">
-        <v>9.999999999999957e-05</v>
+        <v>9.999999999999896e-05</v>
       </c>
     </row>
     <row r="206">
@@ -3928,16 +3928,16 @@
         <v>2.04</v>
       </c>
       <c r="B206" t="n">
-        <v>2.306459870591731</v>
+        <v>2.306719705318948</v>
       </c>
       <c r="C206" t="n">
-        <v>0.415896067414077</v>
+        <v>0.4159290837292953</v>
       </c>
       <c r="D206" t="n">
-        <v>0.4819621903983473</v>
+        <v>0.481857940029677</v>
       </c>
       <c r="E206" t="n">
-        <v>9.999999999999958e-05</v>
+        <v>9.999999999999902e-05</v>
       </c>
     </row>
     <row r="207">
@@ -3945,16 +3945,16 @@
         <v>2.05</v>
       </c>
       <c r="B207" t="n">
-        <v>2.293257998236927</v>
+        <v>2.293510925758998</v>
       </c>
       <c r="C207" t="n">
-        <v>0.4153960656608531</v>
+        <v>0.4154283952885299</v>
       </c>
       <c r="D207" t="n">
-        <v>0.4840977287344982</v>
+        <v>0.4840025274867557</v>
       </c>
       <c r="E207" t="n">
-        <v>9.999999999999961e-05</v>
+        <v>9.999999999999906e-05</v>
       </c>
     </row>
     <row r="208">
@@ -3962,16 +3962,16 @@
         <v>2.06</v>
       </c>
       <c r="B208" t="n">
-        <v>2.279917570962092</v>
+        <v>2.280162732608322</v>
       </c>
       <c r="C208" t="n">
-        <v>0.4148787354961683</v>
+        <v>0.4149101845187512</v>
       </c>
       <c r="D208" t="n">
-        <v>0.4862645708466206</v>
+        <v>0.4861786281406096</v>
       </c>
       <c r="E208" t="n">
-        <v>9.999999999999963e-05</v>
+        <v>9.999999999999911e-05</v>
       </c>
     </row>
     <row r="209">
@@ -3979,16 +3979,16 @@
         <v>2.07</v>
       </c>
       <c r="B209" t="n">
-        <v>2.266445388379506</v>
+        <v>2.266681908944949</v>
       </c>
       <c r="C209" t="n">
-        <v>0.4143438091104505</v>
+        <v>0.4143741757645094</v>
       </c>
       <c r="D209" t="n">
-        <v>0.4884621302522669</v>
+        <v>0.4883856333948666</v>
       </c>
       <c r="E209" t="n">
-        <v>9.999999999999965e-05</v>
+        <v>9.999999999999916e-05</v>
       </c>
     </row>
     <row r="210">
@@ -3996,16 +3996,16 @@
         <v>2.08</v>
       </c>
       <c r="B210" t="n">
-        <v>2.252848184805029</v>
+        <v>2.253075173602201</v>
       </c>
       <c r="C210" t="n">
-        <v>0.4137910186941277</v>
+        <v>0.4138200933703547</v>
       </c>
       <c r="D210" t="n">
-        <v>0.4906898094256875</v>
+        <v>0.4906229231408125</v>
       </c>
       <c r="E210" t="n">
-        <v>9.999999999999968e-05</v>
+        <v>9.999999999999922e-05</v>
       </c>
     </row>
     <row r="211">
@@ -4013,16 +4013,16 @@
         <v>2.09</v>
       </c>
       <c r="B211" t="n">
-        <v>2.23913262599943</v>
+        <v>2.239349177901977</v>
       </c>
       <c r="C211" t="n">
-        <v>0.4132200964376279</v>
+        <v>0.4132476616808374</v>
       </c>
       <c r="D211" t="n">
-        <v>0.492946999301957</v>
+        <v>0.492889865243151</v>
       </c>
       <c r="E211" t="n">
-        <v>9.999999999999971e-05</v>
+        <v>9.999999999999927e-05</v>
       </c>
     </row>
     <row r="212">
@@ -4030,16 +4030,16 @@
         <v>2.1</v>
       </c>
       <c r="B212" t="n">
-        <v>2.225305306063145</v>
+        <v>2.225510502539959</v>
       </c>
       <c r="C212" t="n">
-        <v>0.4126307745313789</v>
+        <v>0.4126566050405077</v>
       </c>
       <c r="D212" t="n">
-        <v>0.4952330787878848</v>
+        <v>0.4951858150331054</v>
       </c>
       <c r="E212" t="n">
-        <v>9.999999999999973e-05</v>
+        <v>9.999999999999933e-05</v>
       </c>
     </row>
     <row r="213">
@@ -4047,16 +4047,16 @@
         <v>2.11</v>
       </c>
       <c r="B213" t="n">
-        <v>2.21137274448363</v>
+        <v>2.211565654621959</v>
       </c>
       <c r="C213" t="n">
-        <v>0.4120227851658086</v>
+        <v>0.4120466477939157</v>
       </c>
       <c r="D213" t="n">
-        <v>0.4975474142799525</v>
+        <v>0.4975101148091303</v>
       </c>
       <c r="E213" t="n">
-        <v>9.999999999999976e-05</v>
+        <v>9.999999999999939e-05</v>
       </c>
     </row>
     <row r="214">
@@ -4064,16 +4064,16 @@
         <v>2.12</v>
       </c>
       <c r="B214" t="n">
-        <v>2.197341383334213</v>
+        <v>2.197521064850397</v>
       </c>
       <c r="C214" t="n">
-        <v>0.4113958605313451</v>
+        <v>0.4114175142856117</v>
       </c>
       <c r="D214" t="n">
-        <v>0.4998893591895511</v>
+        <v>0.499862093345527</v>
       </c>
       <c r="E214" t="n">
-        <v>9.999999999999977e-05</v>
+        <v>9.999999999999945e-05</v>
       </c>
     </row>
     <row r="215">
@@ -4081,16 +4081,16 @@
         <v>2.13</v>
       </c>
       <c r="B215" t="n">
-        <v>2.183217584623265</v>
+        <v>2.183383084859756</v>
       </c>
       <c r="C215" t="n">
-        <v>0.4107497328184163</v>
+        <v>0.4107689288601459</v>
       </c>
       <c r="D215" t="n">
-        <v>0.5022582534758051</v>
+        <v>0.5022410654092768</v>
       </c>
       <c r="E215" t="n">
-        <v>9.99999999999998e-05</v>
+        <v>9.99999999999995e-05</v>
       </c>
     </row>
     <row r="216">
@@ -4098,16 +4098,16 @@
         <v>2.14</v>
       </c>
       <c r="B216" t="n">
-        <v>2.169007627792244</v>
+        <v>2.169157984699665</v>
       </c>
       <c r="C216" t="n">
-        <v>0.4100841342174499</v>
+        <v>0.4101006158620686</v>
       </c>
       <c r="D216" t="n">
-        <v>0.5046534231863027</v>
+        <v>0.504646331285435</v>
       </c>
       <c r="E216" t="n">
-        <v>9.999999999999983e-05</v>
+        <v>9.999999999999958e-05</v>
       </c>
     </row>
     <row r="217">
@@ -4115,16 +4115,16 @@
         <v>2.15</v>
       </c>
       <c r="B217" t="n">
-        <v>2.154717707361081</v>
+        <v>2.154851950464115</v>
       </c>
       <c r="C217" t="n">
-        <v>0.4093987969188743</v>
+        <v>0.40941229963593</v>
       </c>
       <c r="D217" t="n">
-        <v>0.5070741800060611</v>
+        <v>0.5070771763114448</v>
       </c>
       <c r="E217" t="n">
-        <v>9.999999999999986e-05</v>
+        <v>9.999999999999964e-05</v>
       </c>
     </row>
     <row r="218">
@@ -4132,16 +4132,16 @@
         <v>2.16</v>
       </c>
       <c r="B218" t="n">
-        <v>2.14035393071917</v>
+        <v>2.140471082065161</v>
       </c>
       <c r="C218" t="n">
-        <v>0.408693453113117</v>
+        <v>0.4087037045262802</v>
       </c>
       <c r="D218" t="n">
-        <v>0.5095198208150873</v>
+        <v>0.5095328704207606</v>
       </c>
       <c r="E218" t="n">
-        <v>9.999999999999987e-05</v>
+        <v>9.999999999999972e-05</v>
       </c>
     </row>
     <row r="219">
@@ -4149,16 +4149,16 @@
         <v>2.17</v>
       </c>
       <c r="B219" t="n">
-        <v>2.125922316060114</v>
+        <v>2.12602139114929</v>
       </c>
       <c r="C219" t="n">
-        <v>0.4079678349906061</v>
+        <v>0.4079745548776696</v>
       </c>
       <c r="D219" t="n">
-        <v>0.5119896272549123</v>
+        <v>0.5120126676961854</v>
       </c>
       <c r="E219" t="n">
-        <v>9.99999999999999e-05</v>
+        <v>9.999999999999977e-05</v>
       </c>
     </row>
     <row r="220">
@@ -4166,16 +4166,16 @@
         <v>2.18</v>
       </c>
       <c r="B220" t="n">
-        <v>2.111428790458205</v>
+        <v>2.111508799154536</v>
       </c>
       <c r="C220" t="n">
-        <v>0.4072216747417696</v>
+        <v>0.4072245750346482</v>
       </c>
       <c r="D220" t="n">
-        <v>0.5144828653044947</v>
+        <v>0.5145158059333569</v>
       </c>
       <c r="E220" t="n">
-        <v>9.999999999999994e-05</v>
+        <v>9.999999999999986e-05</v>
       </c>
     </row>
     <row r="221">
@@ -4183,16 +4183,16 @@
         <v>2.19</v>
       </c>
       <c r="B221" t="n">
-        <v>2.096879188084543</v>
+        <v>2.096939135506279</v>
       </c>
       <c r="C221" t="n">
-        <v>0.4064547045570354</v>
+        <v>0.4064534893417664</v>
       </c>
       <c r="D221" t="n">
-        <v>0.5169987848659168</v>
+        <v>0.5170415062148308</v>
       </c>
       <c r="E221" t="n">
-        <v>9.999999999999996e-05</v>
+        <v>9.999999999999991e-05</v>
       </c>
     </row>
     <row r="222">
@@ -4200,13 +4200,13 @@
         <v>2.2</v>
       </c>
       <c r="B222" t="n">
-        <v>2.082279248560511</v>
+        <v>2.082318135949508</v>
       </c>
       <c r="C222" t="n">
-        <v>0.4056666566268314</v>
+        <v>0.4056610221435744</v>
       </c>
       <c r="D222" t="n">
-        <v>0.5195366193603094</v>
+        <v>0.5195889724952394</v>
       </c>
       <c r="E222" t="n">
         <v>9.999999999999999e-05</v>
@@ -4217,16 +4217,16 @@
         <v>2.21</v>
       </c>
       <c r="B223" t="n">
-        <v>2.067634615446266</v>
+        <v>2.0676514410153</v>
       </c>
       <c r="C223" t="n">
-        <v>0.4048572631415855</v>
+        <v>0.4048468977846224</v>
       </c>
       <c r="D223" t="n">
-        <v>0.5220955853344683</v>
+        <v>0.522157391198017</v>
       </c>
       <c r="E223" t="n">
-        <v>0.0001</v>
+        <v>0.0001000000000000001</v>
       </c>
     </row>
     <row r="224">
@@ -4234,16 +4234,16 @@
         <v>2.22</v>
       </c>
       <c r="B224" t="n">
-        <v>2.052950834861766</v>
+        <v>2.05294459461906</v>
       </c>
       <c r="C224" t="n">
-        <v>0.4040262562917257</v>
+        <v>0.4040108406094606</v>
       </c>
       <c r="D224" t="n">
-        <v>0.5246748820786397</v>
+        <v>0.5247459308242119</v>
       </c>
       <c r="E224" t="n">
-        <v>0.0001</v>
+        <v>0.0001000000000000002</v>
       </c>
     </row>
     <row r="225">
@@ -4251,16 +4251,16 @@
         <v>2.23</v>
       </c>
       <c r="B225" t="n">
-        <v>2.038233354237788</v>
+        <v>2.038203042788051</v>
       </c>
       <c r="C225" t="n">
-        <v>0.40317336826768</v>
+        <v>0.4031525749626391</v>
       </c>
       <c r="D225" t="n">
-        <v>0.5272736912559741</v>
+        <v>0.5273537415739187</v>
       </c>
       <c r="E225" t="n">
-        <v>0.0001000000000000001</v>
+        <v>0.0001000000000000002</v>
       </c>
     </row>
     <row r="226">
@@ -4268,16 +4268,16 @@
         <v>2.24</v>
       </c>
       <c r="B226" t="n">
-        <v>2.023487521194265</v>
+        <v>2.023432132515604</v>
       </c>
       <c r="C226" t="n">
-        <v>0.4022983312598762</v>
+        <v>0.4022718251887084</v>
       </c>
       <c r="D226" t="n">
-        <v>0.5298911765441655</v>
+        <v>0.5299799549808882</v>
       </c>
       <c r="E226" t="n">
-        <v>0.0001000000000000001</v>
+        <v>0.0001000000000000003</v>
       </c>
     </row>
     <row r="227">
@@ -4285,16 +4285,16 @@
         <v>2.25</v>
       </c>
       <c r="B227" t="n">
-        <v>2.008718582543227</v>
+        <v>2.008637110739356</v>
       </c>
       <c r="C227" t="n">
-        <v>0.4014008774587423</v>
+        <v>0.4013683156322185</v>
       </c>
       <c r="D227" t="n">
-        <v>0.5325264832898123</v>
+        <v>0.5326236835608905</v>
       </c>
       <c r="E227" t="n">
-        <v>0.0001000000000000002</v>
+        <v>0.0001000000000000004</v>
       </c>
     </row>
     <row r="228">
@@ -4302,16 +4302,16 @@
         <v>2.26</v>
       </c>
       <c r="B228" t="n">
-        <v>1.993931683413528</v>
+        <v>1.993823123440731</v>
       </c>
       <c r="C228" t="n">
-        <v>0.4004807390547062</v>
+        <v>0.4004417706377196</v>
       </c>
       <c r="D228" t="n">
-        <v>0.5351787381760527</v>
+        <v>0.535284020474425</v>
       </c>
       <c r="E228" t="n">
-        <v>0.0001000000000000002</v>
+        <v>0.0001000000000000005</v>
       </c>
     </row>
     <row r="229">
@@ -4319,16 +4319,16 @@
         <v>2.27</v>
       </c>
       <c r="B229" t="n">
-        <v>1.979131866494502</v>
+        <v>1.978995214862892</v>
       </c>
       <c r="C229" t="n">
-        <v>0.3995376482381959</v>
+        <v>0.3994919145497622</v>
       </c>
       <c r="D229" t="n">
-        <v>0.5378470489040446</v>
+        <v>0.5379600392043886</v>
       </c>
       <c r="E229" t="n">
-        <v>0.0001000000000000002</v>
+        <v>0.0001000000000000005</v>
       </c>
     </row>
     <row r="230">
@@ -4336,16 +4336,16 @@
         <v>2.28</v>
       </c>
       <c r="B230" t="n">
-        <v>1.964324071395595</v>
+        <v>1.964158326844242</v>
       </c>
       <c r="C230" t="n">
-        <v>0.3985713371996393</v>
+        <v>0.3985184717128962</v>
       </c>
       <c r="D230" t="n">
-        <v>0.5405305038888801</v>
+        <v>0.5406507932493345</v>
       </c>
       <c r="E230" t="n">
-        <v>0.0001000000000000002</v>
+        <v>0.0001000000000000006</v>
       </c>
     </row>
     <row r="231">
@@ -4353,16 +4353,16 @@
         <v>2.29</v>
       </c>
       <c r="B231" t="n">
-        <v>1.949513134119017</v>
+        <v>1.949317298264592</v>
       </c>
       <c r="C231" t="n">
-        <v>0.3975815381294644</v>
+        <v>0.397521166471672</v>
       </c>
       <c r="D231" t="n">
-        <v>0.5432281719705327</v>
+        <v>0.5433553158329631</v>
       </c>
       <c r="E231" t="n">
-        <v>0.0001000000000000003</v>
+        <v>0.0001000000000000007</v>
       </c>
     </row>
     <row r="232">
@@ -4370,16 +4370,16 @@
         <v>2.3</v>
       </c>
       <c r="B232" t="n">
-        <v>1.934703786642357</v>
+        <v>1.934476864600967</v>
       </c>
       <c r="C232" t="n">
-        <v>0.3965679832180989</v>
+        <v>0.3964997231706396</v>
       </c>
       <c r="D232" t="n">
-        <v>0.5459391021404632</v>
+        <v>0.5460726196305132</v>
       </c>
       <c r="E232" t="n">
-        <v>0.0001000000000000003</v>
+        <v>0.0001000000000000008</v>
       </c>
     </row>
     <row r="233">
@@ -4387,16 +4387,16 @@
         <v>2.31</v>
       </c>
       <c r="B233" t="n">
-        <v>1.919900656608124</v>
+        <v>1.919641657590087</v>
       </c>
       <c r="C233" t="n">
-        <v>0.3955304046559711</v>
+        <v>0.3954538661543496</v>
       </c>
       <c r="D233" t="n">
-        <v>0.548662323284508</v>
+        <v>0.5488016965127245</v>
       </c>
       <c r="E233" t="n">
-        <v>0.0001000000000000003</v>
+        <v>0.0001000000000000009</v>
       </c>
     </row>
     <row r="234">
@@ -4404,16 +4404,16 @@
         <v>2.32</v>
       </c>
       <c r="B234" t="n">
-        <v>1.905108267117089</v>
+        <v>1.90481620499442</v>
       </c>
       <c r="C234" t="n">
-        <v>0.3944685346335087</v>
+        <v>0.3943833197673519</v>
       </c>
       <c r="D234" t="n">
-        <v>0.5513968439427083</v>
+        <v>0.5515415173080672</v>
       </c>
       <c r="E234" t="n">
-        <v>0.0001000000000000004</v>
+        <v>0.000100000000000001</v>
       </c>
     </row>
     <row r="235">
@@ -4421,16 +4421,16 @@
         <v>2.33</v>
       </c>
       <c r="B235" t="n">
-        <v>1.890331036622313</v>
+        <v>1.890004930468777</v>
       </c>
       <c r="C235" t="n">
-        <v>0.3933821053411397</v>
+        <v>0.3932878083541968</v>
       </c>
       <c r="D235" t="n">
-        <v>0.5541416520867289</v>
+        <v>0.5542910315839435</v>
       </c>
       <c r="E235" t="n">
-        <v>0.0001000000000000004</v>
+        <v>0.0001000000000000011</v>
       </c>
     </row>
     <row r="236">
@@ -4438,16 +4438,16 @@
         <v>2.34</v>
       </c>
       <c r="B236" t="n">
-        <v>1.875573278920724</v>
+        <v>1.875212153524309</v>
       </c>
       <c r="C236" t="n">
-        <v>0.392270848969292</v>
+        <v>0.3921670562594347</v>
       </c>
       <c r="D236" t="n">
-        <v>0.5568957149155478</v>
+        <v>0.557049167447574</v>
       </c>
       <c r="E236" t="n">
-        <v>0.0001000000000000005</v>
+        <v>0.0001000000000000012</v>
       </c>
     </row>
     <row r="237">
@@ -4455,16 +4455,16 @@
         <v>2.35</v>
       </c>
       <c r="B237" t="n">
-        <v>1.860839203239068</v>
+        <v>1.860442089586817</v>
       </c>
       <c r="C237" t="n">
-        <v>0.3911344977083935</v>
+        <v>0.3910207878276154</v>
       </c>
       <c r="D237" t="n">
-        <v>0.5596579786700959</v>
+        <v>0.5598148313673043</v>
       </c>
       <c r="E237" t="n">
-        <v>0.0001000000000000005</v>
+        <v>0.0001000000000000013</v>
       </c>
     </row>
     <row r="238">
@@ -4472,16 +4472,16 @@
         <v>2.36</v>
       </c>
       <c r="B238" t="n">
-        <v>1.846132914411072</v>
+        <v>1.845698850146237</v>
       </c>
       <c r="C238" t="n">
-        <v>0.3899727837488723</v>
+        <v>0.3898487274032896</v>
       </c>
       <c r="D238" t="n">
-        <v>0.5624273684675414</v>
+        <v>0.5625869080150641</v>
       </c>
       <c r="E238" t="n">
-        <v>0.0001000000000000005</v>
+        <v>0.0001000000000000014</v>
       </c>
     </row>
     <row r="239">
@@ -4489,16 +4489,16 @@
         <v>2.37</v>
       </c>
       <c r="B239" t="n">
-        <v>1.831458413142652</v>
+        <v>1.830986442994163</v>
       </c>
       <c r="C239" t="n">
-        <v>0.3887854392811561</v>
+        <v>0.3886505993310072</v>
       </c>
       <c r="D239" t="n">
-        <v>0.5652027881559233</v>
+        <v>0.5653642601307327</v>
       </c>
       <c r="E239" t="n">
-        <v>0.0001000000000000006</v>
+        <v>0.0001000000000000015</v>
       </c>
     </row>
     <row r="240">
@@ -4506,16 +4506,16 @@
         <v>2.38</v>
       </c>
       <c r="B240" t="n">
-        <v>1.816819596361991</v>
+        <v>1.816308772546299</v>
       </c>
       <c r="C240" t="n">
-        <v>0.3875721964956731</v>
+        <v>0.3874261279553186</v>
       </c>
       <c r="D240" t="n">
-        <v>0.5679831201898442</v>
+        <v>0.5681457284091628</v>
       </c>
       <c r="E240" t="n">
-        <v>0.0001000000000000006</v>
+        <v>0.0001000000000000016</v>
       </c>
     </row>
     <row r="241">
@@ -4523,16 +4523,16 @@
         <v>2.39</v>
       </c>
       <c r="B241" t="n">
-        <v>1.802220257651316</v>
+        <v>1.801669640246678</v>
       </c>
       <c r="C241" t="n">
-        <v>0.386332787582851</v>
+        <v>0.3861750376207739</v>
       </c>
       <c r="D241" t="n">
-        <v>0.5707672255279432</v>
+        <v>0.570930131410628</v>
       </c>
       <c r="E241" t="n">
-        <v>0.0001000000000000006</v>
+        <v>0.0001000000000000017</v>
       </c>
     </row>
     <row r="242">
@@ -4540,16 +4540,16 @@
         <v>2.4</v>
       </c>
       <c r="B242" t="n">
-        <v>1.787664087757244</v>
+        <v>1.787072745050574</v>
       </c>
       <c r="C242" t="n">
-        <v>0.385066944733118</v>
+        <v>0.3848970526719234</v>
       </c>
       <c r="D242" t="n">
-        <v>0.5735539435528701</v>
+        <v>0.5737162654954608</v>
       </c>
       <c r="E242" t="n">
-        <v>0.0001000000000000007</v>
+        <v>0.0001000000000000018</v>
       </c>
     </row>
     <row r="243">
@@ -4557,16 +4557,16 @@
         <v>2.41</v>
       </c>
       <c r="B243" t="n">
-        <v>1.773154675176533</v>
+        <v>1.772521683982959</v>
       </c>
       <c r="C243" t="n">
-        <v>0.3837744001369017</v>
+        <v>0.3835918974533173</v>
       </c>
       <c r="D243" t="n">
-        <v>0.5763420920144959</v>
+        <v>0.5765029047836564</v>
       </c>
       <c r="E243" t="n">
-        <v>0.0001000000000000007</v>
+        <v>0.0001000000000000019</v>
       </c>
     </row>
     <row r="244">
@@ -4574,16 +4574,16 @@
         <v>2.42</v>
       </c>
       <c r="B244" t="n">
-        <v>1.758695506814145</v>
+        <v>1.758019952769464</v>
       </c>
       <c r="C244" t="n">
-        <v>0.3824548859846303</v>
+        <v>0.3822592963095058</v>
       </c>
       <c r="D244" t="n">
-        <v>0.5791304669970848</v>
+        <v>0.5792888011402118</v>
       </c>
       <c r="E244" t="n">
-        <v>0.0001000000000000008</v>
+        <v>0.000100000000000002</v>
       </c>
     </row>
     <row r="245">
@@ -4591,16 +4591,16 @@
         <v>2.43</v>
       </c>
       <c r="B245" t="n">
-        <v>1.744289968710515</v>
+        <v>1.743570946536746</v>
       </c>
       <c r="C245" t="n">
-        <v>0.3811081344667315</v>
+        <v>0.380898973585039</v>
       </c>
       <c r="D245" t="n">
-        <v>0.581917842911172</v>
+        <v>0.5820726841869832</v>
       </c>
       <c r="E245" t="n">
-        <v>0.0001000000000000008</v>
+        <v>0.0001000000000000021</v>
       </c>
     </row>
     <row r="246">
@@ -4608,16 +4608,16 @@
         <v>2.44</v>
       </c>
       <c r="B246" t="n">
-        <v>1.72994134683497</v>
+        <v>1.729177960579249</v>
       </c>
       <c r="C246" t="n">
-        <v>0.3797338777736336</v>
+        <v>0.3795106536244674</v>
       </c>
       <c r="D246" t="n">
-        <v>0.5847029725108741</v>
+        <v>0.584853261341833</v>
       </c>
       <c r="E246" t="n">
-        <v>0.0001000000000000008</v>
+        <v>0.0001000000000000022</v>
       </c>
     </row>
     <row r="247">
@@ -4625,16 +4625,16 @@
         <v>2.45</v>
       </c>
       <c r="B247" t="n">
-        <v>1.715652827942263</v>
+        <v>1.714844191189341</v>
       </c>
       <c r="C247" t="n">
-        <v>0.3783318480957642</v>
+        <v>0.378094060772341</v>
       </c>
       <c r="D247" t="n">
-        <v>0.5874845869373749</v>
+        <v>0.5876292178858415</v>
       </c>
       <c r="E247" t="n">
-        <v>0.0001000000000000009</v>
+        <v>0.0001000000000000023</v>
       </c>
     </row>
     <row r="248">
@@ -4642,16 +4642,16 @@
         <v>2.46</v>
       </c>
       <c r="B248" t="n">
-        <v>1.701427500489228</v>
+        <v>1.700572736547869</v>
       </c>
       <c r="C248" t="n">
-        <v>0.3769017776235514</v>
+        <v>0.3766489193732101</v>
       </c>
       <c r="D248" t="n">
-        <v>0.5902613957893125</v>
+        <v>0.5903992170593532</v>
       </c>
       <c r="E248" t="n">
-        <v>0.0001000000000000009</v>
+        <v>0.0001000000000000025</v>
       </c>
     </row>
     <row r="249">
@@ -4659,16 +4659,16 @@
         <v>2.47</v>
       </c>
       <c r="B249" t="n">
-        <v>1.687268355608585</v>
+        <v>1.686366597672169</v>
       </c>
       <c r="C249" t="n">
-        <v>0.375443398547423</v>
+        <v>0.3751749537716249</v>
       </c>
       <c r="D249" t="n">
-        <v>0.5930320872208027</v>
+        <v>0.5931619001876238</v>
       </c>
       <c r="E249" t="n">
-        <v>0.000100000000000001</v>
+        <v>0.0001000000000000026</v>
       </c>
     </row>
     <row r="250">
@@ -4676,16 +4676,16 @@
         <v>2.48</v>
       </c>
       <c r="B250" t="n">
-        <v>1.673178288137007</v>
+        <v>1.672228679418675</v>
       </c>
       <c r="C250" t="n">
-        <v>0.3739564430578072</v>
+        <v>0.3736718883121357</v>
       </c>
       <c r="D250" t="n">
-        <v>0.5957953280678188</v>
+        <v>0.5959158868368232</v>
       </c>
       <c r="E250" t="n">
-        <v>0.000100000000000001</v>
+        <v>0.0001000000000000027</v>
       </c>
     </row>
     <row r="251">
@@ -4693,16 +4693,16 @@
         <v>2.49</v>
       </c>
       <c r="B251" t="n">
-        <v>1.659160097694539</v>
+        <v>1.658161791537234</v>
       </c>
       <c r="C251" t="n">
-        <v>0.3724406433451317</v>
+        <v>0.3721394473392925</v>
       </c>
       <c r="D251" t="n">
-        <v>0.5985497640036446</v>
+        <v>0.5986597750011454</v>
       </c>
       <c r="E251" t="n">
-        <v>0.000100000000000001</v>
+        <v>0.0001000000000000028</v>
       </c>
     </row>
     <row r="252">
@@ -4710,16 +4710,16 @@
         <v>2.5</v>
       </c>
       <c r="B252" t="n">
-        <v>1.645216489812572</v>
+        <v>1.644168649774348</v>
       </c>
       <c r="C252" t="n">
-        <v>0.3708957315998244</v>
+        <v>0.3705773551976458</v>
       </c>
       <c r="D252" t="n">
-        <v>0.6012940197241092</v>
+        <v>0.6013921413217596</v>
       </c>
       <c r="E252" t="n">
-        <v>0.0001000000000000011</v>
+        <v>0.0001000000000000029</v>
       </c>
     </row>
     <row r="253">
@@ -4727,16 +4727,16 @@
         <v>2.51</v>
       </c>
       <c r="B253" t="n">
-        <v>1.63135007710758</v>
+        <v>1.630251877022562</v>
       </c>
       <c r="C253" t="n">
-        <v>0.3693214400123134</v>
+        <v>0.3689853362317456</v>
       </c>
       <c r="D253" t="n">
-        <v>0.604026699163301</v>
+        <v>0.6041115413383311</v>
       </c>
       <c r="E253" t="n">
-        <v>0.0001000000000000012</v>
+        <v>0.0001000000000000031</v>
       </c>
     </row>
     <row r="254">
@@ -4744,16 +4744,16 @@
         <v>2.52</v>
       </c>
       <c r="B254" t="n">
-        <v>1.617563380497908</v>
+        <v>1.616414004513313</v>
       </c>
       <c r="C254" t="n">
-        <v>0.3677175007730267</v>
+        <v>0.3673631147861423</v>
       </c>
       <c r="D254" t="n">
-        <v>0.6067463857404423</v>
+        <v>0.6068165097738165</v>
       </c>
       <c r="E254" t="n">
-        <v>0.0001000000000000012</v>
+        <v>0.0001000000000000032</v>
       </c>
     </row>
     <row r="255">
@@ -4761,16 +4761,16 @@
         <v>2.53</v>
       </c>
       <c r="B255" t="n">
-        <v>1.603858830460918</v>
+        <v>1.602657473050543</v>
       </c>
       <c r="C255" t="n">
-        <v>0.3660836460723919</v>
+        <v>0.3657104152053859</v>
       </c>
       <c r="D255" t="n">
-        <v>0.6094516426385997</v>
+        <v>0.6095055608532319</v>
       </c>
       <c r="E255" t="n">
-        <v>0.0001000000000000012</v>
+        <v>0.0001000000000000033</v>
       </c>
     </row>
     <row r="256">
@@ -4778,16 +4778,16 @@
         <v>2.54</v>
       </c>
       <c r="B256" t="n">
-        <v>1.590238768327901</v>
+        <v>1.588984634282518</v>
       </c>
       <c r="C256" t="n">
-        <v>0.3644196081008373</v>
+        <v>0.3640269618340268</v>
       </c>
       <c r="D256" t="n">
-        <v>0.6121410131158795</v>
+        <v>0.6121771886570595</v>
       </c>
       <c r="E256" t="n">
-        <v>0.0001000000000000013</v>
+        <v>0.0001000000000000035</v>
       </c>
     </row>
     <row r="257">
@@ -4795,16 +4795,16 @@
         <v>2.55</v>
       </c>
       <c r="B257" t="n">
-        <v>1.576705447614181</v>
+        <v>1.575397752009261</v>
       </c>
       <c r="C257" t="n">
-        <v>0.3627251190487906</v>
+        <v>0.3623124790166151</v>
       </c>
       <c r="D257" t="n">
-        <v>0.6148130208497457</v>
+        <v>0.6148298675099529</v>
       </c>
       <c r="E257" t="n">
-        <v>0.0001000000000000013</v>
+        <v>0.0001000000000000036</v>
       </c>
     </row>
     <row r="258">
@@ -4812,16 +4812,16 @@
         <v>2.56</v>
       </c>
       <c r="B258" t="n">
-        <v>1.563261035381915</v>
+        <v>1.561899003523138</v>
       </c>
       <c r="C258" t="n">
-        <v>0.3609999111066799</v>
+        <v>0.3605666910977013</v>
       </c>
       <c r="D258" t="n">
-        <v>0.6174661703150758</v>
+        <v>0.6174620524053609</v>
       </c>
       <c r="E258" t="n">
-        <v>0.0001000000000000014</v>
+        <v>0.0001000000000000037</v>
       </c>
     </row>
     <row r="259">
@@ -4829,16 +4829,16 @@
         <v>2.57</v>
       </c>
       <c r="B259" t="n">
-        <v>1.54990761363315</v>
+        <v>1.548490480980149</v>
       </c>
       <c r="C259" t="n">
-        <v>0.359243716464933</v>
+        <v>0.3587893224218353</v>
       </c>
       <c r="D259" t="n">
-        <v>0.6200989471965477</v>
+        <v>0.6200721794666797</v>
       </c>
       <c r="E259" t="n">
-        <v>0.0001000000000000014</v>
+        <v>0.0001000000000000039</v>
       </c>
     </row>
     <row r="260">
@@ -4846,16 +4846,16 @@
         <v>2.58</v>
       </c>
       <c r="B260" t="n">
-        <v>1.536647180730752</v>
+        <v>1.53517419279955</v>
       </c>
       <c r="C260" t="n">
-        <v>0.3574562673139779</v>
+        <v>0.3569800973335674</v>
       </c>
       <c r="D260" t="n">
-        <v>0.6227098188359231</v>
+        <v>0.6226586664455019</v>
       </c>
       <c r="E260" t="n">
-        <v>0.0001000000000000015</v>
+        <v>0.000100000000000004</v>
       </c>
     </row>
     <row r="261">
@@ -4863,16 +4863,16 @@
         <v>2.59</v>
       </c>
       <c r="B261" t="n">
-        <v>1.523481652844904</v>
+        <v>1.521952065089511</v>
       </c>
       <c r="C261" t="n">
-        <v>0.3556372958442426</v>
+        <v>0.3551387401774478</v>
       </c>
       <c r="D261" t="n">
-        <v>0.6252972347147727</v>
+        <v>0.6252199132575074</v>
       </c>
       <c r="E261" t="n">
-        <v>0.0001000000000000015</v>
+        <v>0.0001000000000000042</v>
       </c>
     </row>
     <row r="262">
@@ -4880,16 +4880,16 @@
         <v>2.6</v>
       </c>
       <c r="B262" t="n">
-        <v>1.510412865422903</v>
+        <v>1.50882594309653</v>
       </c>
       <c r="C262" t="n">
-        <v>0.3537865342461548</v>
+        <v>0.3532649752980268</v>
       </c>
       <c r="D262" t="n">
-        <v>0.6278596269731533</v>
+        <v>0.6277543025565089</v>
       </c>
       <c r="E262" t="n">
-        <v>0.0001000000000000016</v>
+        <v>0.0001000000000000043</v>
       </c>
     </row>
     <row r="263">
@@ -4897,16 +4897,16 @@
         <v>2.61</v>
       </c>
       <c r="B263" t="n">
-        <v>1.497442574680079</v>
+        <v>1.495797592676447</v>
       </c>
       <c r="C263" t="n">
-        <v>0.3519037147101428</v>
+        <v>0.3513585270398547</v>
       </c>
       <c r="D263" t="n">
-        <v>0.6303954109647185</v>
+        <v>0.6302602003471226</v>
       </c>
       <c r="E263" t="n">
-        <v>0.0001000000000000016</v>
+        <v>0.0001000000000000044</v>
       </c>
     </row>
     <row r="264">
@@ -4914,16 +4914,16 @@
         <v>2.62</v>
       </c>
       <c r="B264" t="n">
-        <v>1.484572459109707</v>
+        <v>1.48286870178491</v>
       </c>
       <c r="C264" t="n">
-        <v>0.3499885694266341</v>
+        <v>0.3494191197474814</v>
       </c>
       <c r="D264" t="n">
-        <v>0.6329029858487126</v>
+        <v>0.6327359566365064</v>
       </c>
       <c r="E264" t="n">
-        <v>0.0001000000000000017</v>
+        <v>0.0001000000000000046</v>
       </c>
     </row>
     <row r="265">
@@ -4931,16 +4931,16 @@
         <v>2.63</v>
       </c>
       <c r="B265" t="n">
-        <v>1.471804121009851</v>
+        <v>1.470040881985249</v>
       </c>
       <c r="C265" t="n">
-        <v>0.3480408305860571</v>
+        <v>0.3474464777654575</v>
       </c>
       <c r="D265" t="n">
-        <v>0.6353807352192579</v>
+        <v>0.6351799061255567</v>
       </c>
       <c r="E265" t="n">
-        <v>0.0001000000000000017</v>
+        <v>0.0001000000000000047</v>
       </c>
     </row>
     <row r="266">
@@ -4948,16 +4948,16 @@
         <v>2.64</v>
       </c>
       <c r="B266" t="n">
-        <v>1.459139088025148</v>
+        <v>1.457315669971751</v>
       </c>
       <c r="C266" t="n">
-        <v>0.3460602303788394</v>
+        <v>0.345440325438333</v>
       </c>
       <c r="D266" t="n">
-        <v>0.6378270277723119</v>
+        <v>0.637590368939924</v>
       </c>
       <c r="E266" t="n">
-        <v>0.0001000000000000018</v>
+        <v>0.0001000000000000049</v>
       </c>
     </row>
     <row r="267">
@@ -4965,16 +4965,16 @@
         <v>2.65</v>
       </c>
       <c r="B267" t="n">
-        <v>1.446578814701612</v>
+        <v>1.444694529106415</v>
       </c>
       <c r="C267" t="n">
-        <v>0.3440465009954091</v>
+        <v>0.3434003871106581</v>
       </c>
       <c r="D267" t="n">
-        <v>0.6402402180106265</v>
+        <v>0.6399656514011489</v>
       </c>
       <c r="E267" t="n">
-        <v>0.0001000000000000018</v>
+        <v>0.0001000000000000051</v>
       </c>
     </row>
     <row r="268">
@@ -4982,16 +4982,16 @@
         <v>2.66</v>
       </c>
       <c r="B268" t="n">
-        <v>1.434124684052573</v>
+        <v>1.432178850967307</v>
       </c>
       <c r="C268" t="n">
-        <v>0.341999374626194</v>
+        <v>0.3413263871269831</v>
       </c>
       <c r="D268" t="n">
-        <v>0.6426186469870038</v>
+        <v>0.6423040468381873</v>
       </c>
       <c r="E268" t="n">
-        <v>0.0001000000000000019</v>
+        <v>0.0001000000000000052</v>
       </c>
     </row>
     <row r="269">
@@ -4999,16 +4999,16 @@
         <v>2.67</v>
       </c>
       <c r="B269" t="n">
-        <v>1.421778009133987</v>
+        <v>1.419769956906736</v>
       </c>
       <c r="C269" t="n">
-        <v>0.3399185834616222</v>
+        <v>0.3392180498318583</v>
       </c>
       <c r="D269" t="n">
-        <v>0.6449606430860907</v>
+        <v>0.6446038364395263</v>
       </c>
       <c r="E269" t="n">
-        <v>0.000100000000000002</v>
+        <v>0.0001000000000000054</v>
       </c>
     </row>
     <row r="270">
@@ -5016,16 +5016,16 @@
         <v>2.68</v>
       </c>
       <c r="B270" t="n">
-        <v>1.409540034627354</v>
+        <v>1.407469099617482</v>
       </c>
       <c r="C270" t="n">
-        <v>0.3378038596921215</v>
+        <v>0.3370750995698338</v>
       </c>
       <c r="D270" t="n">
-        <v>0.6472645228449163</v>
+        <v>0.6468632901460577</v>
       </c>
       <c r="E270" t="n">
-        <v>0.000100000000000002</v>
+        <v>0.0001000000000000055</v>
       </c>
     </row>
     <row r="271">
@@ -5033,16 +5033,16 @@
         <v>2.69</v>
       </c>
       <c r="B271" t="n">
-        <v>1.397411938428609</v>
+        <v>1.395277464705447</v>
       </c>
       <c r="C271" t="n">
-        <v>0.3356549355081199</v>
+        <v>0.3348972606854598</v>
       </c>
       <c r="D271" t="n">
-        <v>0.6495285918123184</v>
+        <v>0.6490806675848021</v>
       </c>
       <c r="E271" t="n">
-        <v>0.0001000000000000021</v>
+        <v>0.0001000000000000057</v>
       </c>
     </row>
     <row r="272">
@@ -5050,16 +5050,16 @@
         <v>2.7</v>
       </c>
       <c r="B272" t="n">
-        <v>1.385394833241366</v>
+        <v>1.383196172267076</v>
       </c>
       <c r="C272" t="n">
-        <v>0.3334715431000453</v>
+        <v>0.3326842575232866</v>
       </c>
       <c r="D272" t="n">
-        <v>0.6517511454473583</v>
+        <v>0.6512542190435355</v>
       </c>
       <c r="E272" t="n">
-        <v>0.0001000000000000021</v>
+        <v>0.0001000000000000058</v>
       </c>
     </row>
     <row r="273">
@@ -5067,16 +5067,16 @@
         <v>2.71</v>
       </c>
       <c r="B273" t="n">
-        <v>1.373489768172988</v>
+        <v>1.371226278470042</v>
       </c>
       <c r="C273" t="n">
-        <v>0.3312534146583258</v>
+        <v>0.3304358144278644</v>
       </c>
       <c r="D273" t="n">
-        <v>0.6539304700567681</v>
+        <v>0.6533821864862978</v>
       </c>
       <c r="E273" t="n">
-        <v>0.0001000000000000022</v>
+        <v>0.000100000000000006</v>
       </c>
     </row>
     <row r="274">
@@ -5084,16 +5084,16 @@
         <v>2.72</v>
       </c>
       <c r="B274" t="n">
-        <v>1.361697730332018</v>
+        <v>1.359368777135697</v>
       </c>
       <c r="C274" t="n">
-        <v>0.329000282373389</v>
+        <v>0.3281516557437433</v>
       </c>
       <c r="D274" t="n">
-        <v>0.6560648437714147</v>
+        <v>0.655462804609706</v>
       </c>
       <c r="E274" t="n">
-        <v>0.0001000000000000022</v>
+        <v>0.0001000000000000062</v>
       </c>
     </row>
     <row r="275">
@@ -5101,16 +5101,16 @@
         <v>2.73</v>
       </c>
       <c r="B275" t="n">
-        <v>1.350019646425562</v>
+        <v>1.347624601321876</v>
       </c>
       <c r="C275" t="n">
-        <v>0.3267118784356632</v>
+        <v>0.3258315058154738</v>
       </c>
       <c r="D275" t="n">
-        <v>0.6581525375617132</v>
+        <v>0.6574943019399279</v>
       </c>
       <c r="E275" t="n">
-        <v>0.0001000000000000023</v>
+        <v>0.0001000000000000064</v>
       </c>
     </row>
     <row r="276">
@@ -5118,16 +5118,16 @@
         <v>2.74</v>
       </c>
       <c r="B276" t="n">
-        <v>1.338456384355278</v>
+        <v>1.335994624904707</v>
       </c>
       <c r="C276" t="n">
-        <v>0.3243879350355761</v>
+        <v>0.3234750889876059</v>
       </c>
       <c r="D276" t="n">
-        <v>0.6601918162918529</v>
+        <v>0.6594749019701059</v>
       </c>
       <c r="E276" t="n">
-        <v>0.0001000000000000023</v>
+        <v>0.0001000000000000065</v>
       </c>
     </row>
     <row r="277">
@@ -5135,16 +5135,16 @@
         <v>2.75</v>
       </c>
       <c r="B277" t="n">
-        <v>1.327008754810707</v>
+        <v>1.324479664158128</v>
       </c>
       <c r="C277" t="n">
-        <v>0.3220281843635557</v>
+        <v>0.3210821296046898</v>
       </c>
       <c r="D277" t="n">
-        <v>0.6621809398126413</v>
+        <v>0.6614028243379482</v>
       </c>
       <c r="E277" t="n">
-        <v>0.0001000000000000024</v>
+        <v>0.0001000000000000067</v>
       </c>
     </row>
     <row r="278">
@@ -5152,16 +5152,16 @@
         <v>2.76</v>
       </c>
       <c r="B278" t="n">
-        <v>1.315677512858707</v>
+        <v>1.313080479329892</v>
       </c>
       <c r="C278" t="n">
-        <v>0.31963235861003</v>
+        <v>0.3186523520112758</v>
       </c>
       <c r="D278" t="n">
-        <v>0.6641181640927064</v>
+        <v>0.6632762860431359</v>
       </c>
       <c r="E278" t="n">
-        <v>0.0001000000000000025</v>
+        <v>0.0001000000000000069</v>
       </c>
     </row>
     <row r="279">
@@ -5169,16 +5169,16 @@
         <v>2.77</v>
       </c>
       <c r="B279" t="n">
-        <v>1.304463359527863</v>
+        <v>1.301797776212877</v>
       </c>
       <c r="C279" t="n">
-        <v>0.3172001899654269</v>
+        <v>0.3161854805519142</v>
       </c>
       <c r="D279" t="n">
-        <v>0.6660017423877265</v>
+        <v>0.6650935027041175</v>
       </c>
       <c r="E279" t="n">
-        <v>0.0001000000000000025</v>
+        <v>0.0001000000000000071</v>
       </c>
     </row>
     <row r="280">
@@ -5186,16 +5186,16 @@
         <v>2.78</v>
       </c>
       <c r="B280" t="n">
-        <v>1.293366943386748</v>
+        <v>1.29063220771061</v>
       </c>
       <c r="C280" t="n">
-        <v>0.3147314106201742</v>
+        <v>0.313681239571155</v>
       </c>
       <c r="D280" t="n">
-        <v>0.6678299264472907</v>
+        <v>0.6668526898537892</v>
       </c>
       <c r="E280" t="n">
-        <v>0.0001000000000000026</v>
+        <v>0.0001000000000000072</v>
       </c>
     </row>
     <row r="281">
@@ -5203,16 +5203,16 @@
         <v>2.79</v>
       </c>
       <c r="B281" t="n">
-        <v>1.282388862115033</v>
+        <v>1.27958437539594</v>
       </c>
       <c r="C281" t="n">
-        <v>0.3122257527647</v>
+        <v>0.3111393534135486</v>
       </c>
       <c r="D281" t="n">
-        <v>0.6696009677589201</v>
+        <v>0.6685520642734762</v>
       </c>
       <c r="E281" t="n">
-        <v>0.0001000000000000026</v>
+        <v>0.0001000000000000074</v>
       </c>
     </row>
     <row r="282">
@@ -5220,16 +5220,16 @@
         <v>2.8</v>
       </c>
       <c r="B282" t="n">
-        <v>1.271529664066441</v>
+        <v>1.268654831061879</v>
       </c>
       <c r="C282" t="n">
-        <v>0.3096829485894322</v>
+        <v>0.3085595464236452</v>
       </c>
       <c r="D282" t="n">
-        <v>0.671313118828709</v>
+        <v>0.6701898453645579</v>
       </c>
       <c r="E282" t="n">
-        <v>0.0001000000000000027</v>
+        <v>0.0001000000000000076</v>
       </c>
     </row>
     <row r="283">
@@ -5237,16 +5237,16 @@
         <v>2.81</v>
       </c>
       <c r="B283" t="n">
-        <v>1.260789849822644</v>
+        <v>1.257844078263674</v>
       </c>
       <c r="C283" t="n">
-        <v>0.3071027302847988</v>
+        <v>0.305941542945995</v>
       </c>
       <c r="D283" t="n">
-        <v>0.672964634497966</v>
+        <v>0.6717642565569893</v>
       </c>
       <c r="E283" t="n">
-        <v>0.0001000000000000028</v>
+        <v>0.0001000000000000078</v>
       </c>
     </row>
     <row r="284">
@@ -5254,16 +5254,16 @@
         <v>2.82</v>
       </c>
       <c r="B284" t="n">
-        <v>1.250169873737241</v>
+        <v>1.247152573851227</v>
       </c>
       <c r="C284" t="n">
-        <v>0.3044848300412277</v>
+        <v>0.3032850673251483</v>
       </c>
       <c r="D284" t="n">
-        <v>0.6745537732951633</v>
+        <v>0.6732735267538931</v>
       </c>
       <c r="E284" t="n">
-        <v>0.0001000000000000028</v>
+        <v>0.000100000000000008</v>
       </c>
     </row>
     <row r="285">
@@ -5271,16 +5271,16 @@
         <v>2.83</v>
       </c>
       <c r="B285" t="n">
-        <v>1.239670145469003</v>
+        <v>1.236580729491051</v>
       </c>
       <c r="C285" t="n">
-        <v>0.3018289800491467</v>
+        <v>0.300589843905655</v>
       </c>
       <c r="D285" t="n">
-        <v>0.6760787988224208</v>
+        <v>0.6747158918113114</v>
       </c>
       <c r="E285" t="n">
-        <v>0.0001000000000000029</v>
+        <v>0.0001000000000000082</v>
       </c>
     </row>
     <row r="286">
@@ -5288,16 +5288,16 @@
         <v>2.84</v>
       </c>
       <c r="B286" t="n">
-        <v>1.229291031503648</v>
+        <v>1.226128913176991</v>
       </c>
       <c r="C286" t="n">
-        <v>0.2991349124989838</v>
+        <v>0.2978555970320657</v>
       </c>
       <c r="D286" t="n">
-        <v>0.6775379811756741</v>
+        <v>0.6760895960521164</v>
       </c>
       <c r="E286" t="n">
-        <v>0.000100000000000003</v>
+        <v>0.0001000000000000084</v>
       </c>
     </row>
     <row r="287">
@@ -5305,16 +5305,16 @@
         <v>2.85</v>
       </c>
       <c r="B287" t="n">
-        <v>1.219032856663431</v>
+        <v>1.215797450728982</v>
       </c>
       <c r="C287" t="n">
-        <v>0.296402359581167</v>
+        <v>0.2950820510489304</v>
       </c>
       <c r="D287" t="n">
-        <v>0.6789295983975927</v>
+        <v>0.6773928938129946</v>
       </c>
       <c r="E287" t="n">
-        <v>0.000100000000000003</v>
+        <v>0.0001000000000000086</v>
       </c>
     </row>
     <row r="288">
@@ -5322,16 +5322,16 @@
         <v>2.86</v>
       </c>
       <c r="B288" t="n">
-        <v>1.208895905603933</v>
+        <v>1.205586627279206</v>
       </c>
       <c r="C288" t="n">
-        <v>0.2936310534861243</v>
+        <v>0.2922689303007995</v>
       </c>
       <c r="D288" t="n">
-        <v>0.6802519379622342</v>
+        <v>0.6786240510233292</v>
       </c>
       <c r="E288" t="n">
-        <v>0.0001000000000000031</v>
+        <v>0.0001000000000000088</v>
       </c>
     </row>
     <row r="289">
@@ -5339,16 +5339,16 @@
         <v>2.87</v>
       </c>
       <c r="B289" t="n">
-        <v>1.198880424297416</v>
+        <v>1.195496688745013</v>
       </c>
       <c r="C289" t="n">
-        <v>0.2908207264042834</v>
+        <v>0.2894159591322228</v>
       </c>
       <c r="D289" t="n">
-        <v>0.6815032982903353</v>
+        <v>0.6797813468147136</v>
       </c>
       <c r="E289" t="n">
-        <v>0.0001000000000000031</v>
+        <v>0.000100000000000009</v>
       </c>
     </row>
     <row r="290">
@@ -5356,16 +5356,16 @@
         <v>2.88</v>
       </c>
       <c r="B290" t="n">
-        <v>1.188986621502249</v>
+        <v>1.185527843288062</v>
       </c>
       <c r="C290" t="n">
-        <v>0.2879711105260725</v>
+        <v>0.2865228618877512</v>
       </c>
       <c r="D290" t="n">
-        <v>0.6826819902940606</v>
+        <v>0.6808630751597446</v>
       </c>
       <c r="E290" t="n">
-        <v>0.0001000000000000032</v>
+        <v>0.0001000000000000092</v>
       </c>
     </row>
     <row r="291">
@@ -5373,16 +5373,16 @@
         <v>2.89</v>
       </c>
       <c r="B291" t="n">
-        <v>1.179214670217872</v>
+        <v>1.175680262759158</v>
       </c>
       <c r="C291" t="n">
-        <v>0.2850819380419192</v>
+        <v>0.2835893629119344</v>
       </c>
       <c r="D291" t="n">
-        <v>0.683786338949936</v>
+        <v>0.681867546538641</v>
       </c>
       <c r="E291" t="n">
-        <v>0.0001000000000000033</v>
+        <v>0.0001000000000000094</v>
       </c>
     </row>
     <row r="292">
@@ -5390,16 +5390,16 @@
         <v>2.9</v>
       </c>
       <c r="B292" t="n">
-        <v>1.169564709124881</v>
+        <v>1.165954084128323</v>
       </c>
       <c r="C292" t="n">
-        <v>0.2821529411422519</v>
+        <v>0.2806151865493228</v>
       </c>
       <c r="D292" t="n">
-        <v>0.68481468489862</v>
+        <v>0.6827930896321549</v>
       </c>
       <c r="E292" t="n">
-        <v>0.0001000000000000034</v>
+        <v>0.0001000000000000096</v>
       </c>
     </row>
     <row r="293">
@@ -5407,16 +5407,16 @@
         <v>2.91</v>
       </c>
       <c r="B293" t="n">
-        <v>1.160036844009815</v>
+        <v>1.156349410899688</v>
       </c>
       <c r="C293" t="n">
-        <v>0.2791838520174982</v>
+        <v>0.2776000571444664</v>
       </c>
       <c r="D293" t="n">
-        <v>0.6857653860700712</v>
+        <v>0.6836380530391418</v>
       </c>
       <c r="E293" t="n">
-        <v>0.0001000000000000034</v>
+        <v>0.0001000000000000098</v>
       </c>
     </row>
     <row r="294">
@@ -5424,16 +5424,16 @@
         <v>2.92</v>
       </c>
       <c r="B294" t="n">
-        <v>1.150631149174314</v>
+        <v>1.146866314510831</v>
       </c>
       <c r="C294" t="n">
-        <v>0.2761744028580861</v>
+        <v>0.2745436990419159</v>
       </c>
       <c r="D294" t="n">
-        <v>0.686636819332587</v>
+        <v>0.6844008070170664</v>
       </c>
       <c r="E294" t="n">
-        <v>0.0001000000000000035</v>
+        <v>0.00010000000000001</v>
       </c>
     </row>
     <row r="295">
@@ -5441,16 +5441,16 @@
         <v>2.93</v>
       </c>
       <c r="B295" t="n">
-        <v>1.141347668828322</v>
+        <v>1.13750483571622</v>
       </c>
       <c r="C295" t="n">
-        <v>0.2731243258544436</v>
+        <v>0.2714458365862211</v>
       </c>
       <c r="D295" t="n">
-        <v>0.6874273821641036</v>
+        <v>0.685079745243629</v>
       </c>
       <c r="E295" t="n">
-        <v>0.0001000000000000036</v>
+        <v>0.0001000000000000102</v>
       </c>
     </row>
     <row r="296">
@@ -5458,16 +5458,16 @@
         <v>2.94</v>
       </c>
       <c r="B296" t="n">
-        <v>1.132186418467085</v>
+        <v>1.128264985954499</v>
       </c>
       <c r="C296" t="n">
-        <v>0.2700333531969986</v>
+        <v>0.2683061941219324</v>
       </c>
       <c r="D296" t="n">
-        <v>0.6881354943440587</v>
+        <v>0.6856732865976096</v>
       </c>
       <c r="E296" t="n">
-        <v>0.0001000000000000036</v>
+        <v>0.0001000000000000105</v>
       </c>
     </row>
     <row r="297">
@@ -5475,16 +5475,16 @@
         <v>2.95</v>
       </c>
       <c r="B297" t="n">
-        <v>1.123147386231712</v>
+        <v>1.119146748699354</v>
       </c>
       <c r="C297" t="n">
-        <v>0.266901217076179</v>
+        <v>0.2651244959935998</v>
       </c>
       <c r="D297" t="n">
-        <v>0.6887595996640359</v>
+        <v>0.6861798769569274</v>
       </c>
       <c r="E297" t="n">
-        <v>0.0001000000000000037</v>
+        <v>0.0001000000000000107</v>
       </c>
     </row>
     <row r="298">
@@ -5492,16 +5492,16 @@
         <v>2.96</v>
       </c>
       <c r="B298" t="n">
-        <v>1.114230534253136</v>
+        <v>1.110150080793768</v>
       </c>
       <c r="C298" t="n">
-        <v>0.2637276496824129</v>
+        <v>0.2619004665457739</v>
       </c>
       <c r="D298" t="n">
-        <v>0.6892981676553187</v>
+        <v>0.6865979910118322</v>
       </c>
       <c r="E298" t="n">
-        <v>0.0001000000000000038</v>
+        <v>0.0001000000000000109</v>
       </c>
     </row>
     <row r="299">
@@ -5509,16 +5509,16 @@
         <v>2.97</v>
       </c>
       <c r="B299" t="n">
-        <v>1.105435799979308</v>
+        <v>1.101274913767498</v>
       </c>
       <c r="C299" t="n">
-        <v>0.2605123832061279</v>
+        <v>0.2586338301230046</v>
       </c>
       <c r="D299" t="n">
-        <v>0.689749695331406</v>
+        <v>0.6869261340910531</v>
       </c>
       <c r="E299" t="n">
-        <v>0.0001000000000000038</v>
+        <v>0.0001000000000000111</v>
       </c>
     </row>
     <row r="300">
@@ -5526,16 +5526,16 @@
         <v>2.98</v>
       </c>
       <c r="B300" t="n">
-        <v>1.096763097485554</v>
+        <v>1.092521155137647</v>
       </c>
       <c r="C300" t="n">
-        <v>0.2572551498377523</v>
+        <v>0.2553243110698423</v>
       </c>
       <c r="D300" t="n">
-        <v>0.6901127089434473</v>
+        <v>0.6871628439986361</v>
       </c>
       <c r="E300" t="n">
-        <v>0.0001000000000000039</v>
+        <v>0.0001000000000000113</v>
       </c>
     </row>
     <row r="301">
@@ -5543,16 +5543,16 @@
         <v>2.99</v>
       </c>
       <c r="B301" t="n">
-        <v>1.088212318768012</v>
+        <v>1.083888689692258</v>
       </c>
       <c r="C301" t="n">
-        <v>0.2539556817677138</v>
+        <v>0.251971633730837</v>
       </c>
       <c r="D301" t="n">
-        <v>0.6903857657464856</v>
+        <v>0.6873066928591287</v>
       </c>
       <c r="E301" t="n">
-        <v>0.000100000000000004</v>
+        <v>0.0001000000000000116</v>
       </c>
     </row>
     <row r="302">
@@ -5560,16 +5560,16 @@
         <v>3</v>
       </c>
       <c r="B302" t="n">
-        <v>1.079783335020131</v>
+        <v>1.075377380756869</v>
       </c>
       <c r="C302" t="n">
-        <v>0.2506137111864404</v>
+        <v>0.2485755224505393</v>
       </c>
       <c r="D302" t="n">
-        <v>0.6905674557742995</v>
+        <v>0.6873562889686722</v>
       </c>
       <c r="E302" t="n">
-        <v>0.0001000000000000041</v>
+        <v>0.0001000000000000118</v>
       </c>
     </row>
     <row r="303">
@@ -5577,16 +5577,16 @@
         <v>3.01</v>
       </c>
       <c r="B303" t="n">
-        <v>1.071475997892241</v>
+        <v>1.066987071444016</v>
       </c>
       <c r="C303" t="n">
-        <v>0.2472289702843601</v>
+        <v>0.2451357015734989</v>
       </c>
       <c r="D303" t="n">
-        <v>0.6906564036205757</v>
+        <v>0.6873102786494907</v>
       </c>
       <c r="E303" t="n">
-        <v>0.0001000000000000041</v>
+        <v>0.0001000000000000121</v>
       </c>
     </row>
     <row r="304">
@@ -5594,16 +5594,16 @@
         <v>3.02</v>
       </c>
       <c r="B304" t="n">
-        <v>1.063290140734243</v>
+        <v>1.058717585885712</v>
       </c>
       <c r="C304" t="n">
-        <v>0.2438011912519008</v>
+        <v>0.2416518954442666</v>
       </c>
       <c r="D304" t="n">
-        <v>0.6906512702240472</v>
+        <v>0.6871673481051831</v>
       </c>
       <c r="E304" t="n">
-        <v>0.0001000000000000042</v>
+        <v>0.0001000000000000123</v>
       </c>
     </row>
     <row r="305">
@@ -5611,16 +5611,16 @@
         <v>3.03</v>
       </c>
       <c r="B305" t="n">
-        <v>1.055225579821493</v>
+        <v>1.050568730448955</v>
       </c>
       <c r="C305" t="n">
-        <v>0.2403301062794903</v>
+        <v>0.2381238284073921</v>
       </c>
       <c r="D305" t="n">
-        <v>0.6905507546551709</v>
+        <v>0.6869262252741438</v>
       </c>
       <c r="E305" t="n">
-        <v>0.0001000000000000043</v>
+        <v>0.0001000000000000125</v>
       </c>
     </row>
     <row r="306">
@@ -5628,16 +5628,16 @@
         <v>3.04</v>
       </c>
       <c r="B306" t="n">
-        <v>1.047282115563996</v>
+        <v>1.042540294934344</v>
       </c>
       <c r="C306" t="n">
-        <v>0.2368154475575569</v>
+        <v>0.2345512248074261</v>
       </c>
       <c r="D306" t="n">
-        <v>0.6903535959018395</v>
+        <v>0.6865856816783728</v>
       </c>
       <c r="E306" t="n">
-        <v>0.0001000000000000044</v>
+        <v>0.0001000000000000128</v>
       </c>
     </row>
     <row r="307">
@@ -5645,16 +5645,16 @@
         <v>3.05</v>
       </c>
       <c r="B307" t="n">
-        <v>1.039459533699058</v>
+        <v>1.03463205375794</v>
       </c>
       <c r="C307" t="n">
-        <v>0.2332569472765281</v>
+        <v>0.2309338089889183</v>
       </c>
       <c r="D307" t="n">
-        <v>0.6900585746515527</v>
+        <v>0.6861445342648542</v>
       </c>
       <c r="E307" t="n">
-        <v>0.0001000000000000044</v>
+        <v>0.000100000000000013</v>
       </c>
     </row>
     <row r="308">
@@ -5662,16 +5662,16 @@
         <v>3.06</v>
       </c>
       <c r="B308" t="n">
-        <v>1.031757606467562</v>
+        <v>1.026843767116498</v>
       </c>
       <c r="C308" t="n">
-        <v>0.2296543376268322</v>
+        <v>0.2272713052964195</v>
       </c>
       <c r="D308" t="n">
-        <v>0.6896645150674106</v>
+        <v>0.685601647236629</v>
       </c>
       <c r="E308" t="n">
-        <v>0.0001000000000000045</v>
+        <v>0.0001000000000000133</v>
       </c>
     </row>
     <row r="309">
@@ -5679,16 +5679,16 @@
         <v>3.07</v>
       </c>
       <c r="B309" t="n">
-        <v>1.024176093774089</v>
+        <v>1.019175182136272</v>
       </c>
       <c r="C309" t="n">
-        <v>0.2260073507988968</v>
+        <v>0.2235634380744793</v>
       </c>
       <c r="D309" t="n">
-        <v>0.6891702865552169</v>
+        <v>0.6849559338706093</v>
       </c>
       <c r="E309" t="n">
-        <v>0.0001000000000000046</v>
+        <v>0.0001000000000000135</v>
       </c>
     </row>
     <row r="310">
@@ -5696,16 +5696,16 @@
         <v>3.08</v>
       </c>
       <c r="B310" t="n">
-        <v>1.016714744331102</v>
+        <v>1.011626034005591</v>
       </c>
       <c r="C310" t="n">
-        <v>0.2223157189831501</v>
+        <v>0.2198099316676484</v>
       </c>
       <c r="D310" t="n">
-        <v>0.6885748055189381</v>
+        <v>0.6842063583191369</v>
       </c>
       <c r="E310" t="n">
-        <v>0.0001000000000000047</v>
+        <v>0.0001000000000000138</v>
       </c>
     </row>
     <row r="311">
@@ -5713,16 +5713,16 @@
         <v>3.09</v>
       </c>
       <c r="B311" t="n">
-        <v>1.009373296787476</v>
+        <v>1.004196047091442</v>
       </c>
       <c r="C311" t="n">
-        <v>0.21857917437002</v>
+        <v>0.2160105104204769</v>
       </c>
       <c r="D311" t="n">
-        <v>0.6878770371016851</v>
+        <v>0.6833519373922242</v>
       </c>
       <c r="E311" t="n">
-        <v>0.0001000000000000047</v>
+        <v>0.000100000000000014</v>
       </c>
     </row>
     <row r="312">
@@ -5730,16 +5730,16 @@
         <v>3.1</v>
       </c>
       <c r="B312" t="n">
-        <v>1.002151480841651</v>
+        <v>0.9968849360403325</v>
       </c>
       <c r="C312" t="n">
-        <v>0.2147974491499342</v>
+        <v>0.2121648986775148</v>
       </c>
       <c r="D312" t="n">
-        <v>0.6870759969093527</v>
+        <v>0.6823917423173697</v>
       </c>
       <c r="E312" t="n">
-        <v>0.0001000000000000048</v>
+        <v>0.0001000000000000143</v>
       </c>
     </row>
     <row r="313">
@@ -5747,16 +5747,16 @@
         <v>3.11</v>
       </c>
       <c r="B313" t="n">
-        <v>0.9950490183397427</v>
+        <v>0.9896924068637172</v>
       </c>
       <c r="C313" t="n">
-        <v>0.210970275513321</v>
+        <v>0.2082728207833126</v>
       </c>
       <c r="D313" t="n">
-        <v>0.6861707527139871</v>
+        <v>0.6813249004737957</v>
       </c>
       <c r="E313" t="n">
-        <v>0.0001000000000000049</v>
+        <v>0.0001000000000000145</v>
       </c>
     </row>
     <row r="314">
@@ -5764,16 +5764,16 @@
         <v>3.12</v>
       </c>
       <c r="B314" t="n">
-        <v>0.9880656243589376</v>
+        <v>0.9826181580083067</v>
       </c>
       <c r="C314" t="n">
-        <v>0.207097385650608</v>
+        <v>0.2043340010824204</v>
       </c>
       <c r="D314" t="n">
-        <v>0.6851604261339191</v>
+        <v>0.6801505970979156</v>
       </c>
       <c r="E314" t="n">
-        <v>0.000100000000000005</v>
+        <v>0.0001000000000000148</v>
       </c>
     </row>
     <row r="315">
@@ -5781,16 +5781,16 @@
         <v>3.13</v>
       </c>
       <c r="B315" t="n">
-        <v>0.9812010082765674</v>
+        <v>0.975661881411607</v>
       </c>
       <c r="C315" t="n">
-        <v>0.2031785117522234</v>
+        <v>0.2003481639193885</v>
       </c>
       <c r="D315" t="n">
-        <v>0.6840441942876563</v>
+        <v>0.6788680769568025</v>
       </c>
       <c r="E315" t="n">
-        <v>0.0001000000000000051</v>
+        <v>0.0001000000000000151</v>
       </c>
     </row>
     <row r="316">
@@ -5798,16 +5798,16 @@
         <v>3.14</v>
       </c>
       <c r="B316" t="n">
-        <v>0.9744548748252436</v>
+        <v>0.968823263543049</v>
       </c>
       <c r="C316" t="n">
-        <v>0.199213386008595</v>
+        <v>0.1963150336387669</v>
       </c>
       <c r="D316" t="n">
-        <v>0.6828212914184921</v>
+        <v>0.677476645986404</v>
       </c>
       <c r="E316" t="n">
-        <v>0.0001000000000000052</v>
+        <v>0.0001000000000000153</v>
       </c>
     </row>
     <row r="317">
@@ -5815,16 +5815,16 @@
         <v>3.15</v>
       </c>
       <c r="B317" t="n">
-        <v>0.9678269251344803</v>
+        <v>0.9621019864311076</v>
       </c>
       <c r="C317" t="n">
-        <v>0.1952017406101507</v>
+        <v>0.1922343345851061</v>
       </c>
       <c r="D317" t="n">
-        <v>0.6814910104867674</v>
+        <v>0.6759756728912255</v>
       </c>
       <c r="E317" t="n">
-        <v>0.0001000000000000052</v>
+        <v>0.0001000000000000156</v>
       </c>
     </row>
     <row r="318">
@@ -5832,16 +5832,16 @@
         <v>3.16</v>
       </c>
       <c r="B318" t="n">
-        <v>0.9613168577592526</v>
+        <v>0.9554977286768171</v>
       </c>
       <c r="C318" t="n">
-        <v>0.1911433077473185</v>
+        <v>0.188105791102956</v>
       </c>
       <c r="D318" t="n">
-        <v>0.6800527047266862</v>
+        <v>0.6743645907021864</v>
       </c>
       <c r="E318" t="n">
-        <v>0.0001000000000000053</v>
+        <v>0.0001000000000000159</v>
       </c>
     </row>
     <row r="319">
@@ -5849,16 +5849,16 @@
         <v>3.17</v>
       </c>
       <c r="B319" t="n">
-        <v>0.9549243696959595</v>
+        <v>0.9490101664541309</v>
       </c>
       <c r="C319" t="n">
-        <v>0.1870378196105264</v>
+        <v>0.1839291275368672</v>
       </c>
       <c r="D319" t="n">
-        <v>0.6785057891645833</v>
+        <v>0.672642898289348</v>
       </c>
       <c r="E319" t="n">
-        <v>0.0001000000000000054</v>
+        <v>0.0001000000000000162</v>
       </c>
     </row>
     <row r="320">
@@ -5866,16 +5866,16 @@
         <v>3.18</v>
       </c>
       <c r="B320" t="n">
-        <v>0.9486491573862842</v>
+        <v>0.9426389744975743</v>
       </c>
       <c r="C320" t="n">
-        <v>0.1828850083902022</v>
+        <v>0.1797040682313897</v>
       </c>
       <c r="D320" t="n">
-        <v>0.6768497420955146</v>
+        <v>0.6708101618262041</v>
       </c>
       <c r="E320" t="n">
-        <v>0.0001000000000000055</v>
+        <v>0.0001000000000000164</v>
       </c>
     </row>
     <row r="321">
@@ -5883,16 +5883,16 @@
         <v>3.19</v>
       </c>
       <c r="B321" t="n">
-        <v>0.942490917709468</v>
+        <v>0.9363838270776844</v>
       </c>
       <c r="C321" t="n">
-        <v>0.178684606276774</v>
+        <v>0.1754303375310738</v>
       </c>
       <c r="D321" t="n">
-        <v>0.6750841065150509</v>
+        <v>0.6688660162022307</v>
       </c>
       <c r="E321" t="n">
-        <v>0.0001000000000000056</v>
+        <v>0.0001000000000000167</v>
       </c>
     </row>
     <row r="322">
@@ -5900,16 +5900,16 @@
         <v>3.2</v>
       </c>
       <c r="B322" t="n">
-        <v>0.936449348963539</v>
+        <v>0.9302443989647331</v>
       </c>
       <c r="C322" t="n">
-        <v>0.1744363454606695</v>
+        <v>0.1711076597804694</v>
       </c>
       <c r="D322" t="n">
-        <v>0.6732084915031409</v>
+        <v>0.6668101663804055</v>
       </c>
       <c r="E322" t="n">
-        <v>0.0001000000000000057</v>
+        <v>0.000100000000000017</v>
       </c>
     </row>
     <row r="323">
@@ -5917,16 +5917,16 @@
         <v>3.21</v>
       </c>
       <c r="B323" t="n">
-        <v>0.9305241518360543</v>
+        <v>0.9242203663812647</v>
       </c>
       <c r="C323" t="n">
-        <v>0.1701399581323169</v>
+        <v>0.1667357593241274</v>
       </c>
       <c r="D323" t="n">
-        <v>0.671222573556932</v>
+        <v>0.6646423886964239</v>
       </c>
       <c r="E323" t="n">
-        <v>0.0001000000000000058</v>
+        <v>0.0001000000000000173</v>
       </c>
     </row>
     <row r="324">
@@ -5934,16 +5934,16 @@
         <v>3.22</v>
       </c>
       <c r="B324" t="n">
-        <v>0.9247150303649379</v>
+        <v>0.918311407943986</v>
       </c>
       <c r="C324" t="n">
-        <v>0.1657951764821438</v>
+        <v>0.1623143605065972</v>
       </c>
       <c r="D324" t="n">
-        <v>0.6691260978694406</v>
+        <v>0.6623625320963619</v>
       </c>
       <c r="E324" t="n">
-        <v>0.0001000000000000058</v>
+        <v>0.0001000000000000176</v>
       </c>
     </row>
     <row r="325">
@@ -5951,16 +5951,16 @@
         <v>3.23</v>
       </c>
       <c r="B325" t="n">
-        <v>0.9190216928900213</v>
+        <v>0.9125172055955918</v>
       </c>
       <c r="C325" t="n">
-        <v>0.1614017327005787</v>
+        <v>0.1578431876724298</v>
       </c>
       <c r="D325" t="n">
-        <v>0.6669188795509881</v>
+        <v>0.6599705193095763</v>
       </c>
       <c r="E325" t="n">
-        <v>0.0001000000000000059</v>
+        <v>0.0001000000000000179</v>
       </c>
     </row>
     <row r="326">
@@ -5968,16 +5968,16 @@
         <v>3.24</v>
       </c>
       <c r="B326" t="n">
-        <v>0.913443852995914</v>
+        <v>0.9068374455270947</v>
       </c>
       <c r="C326" t="n">
-        <v>0.156959358978049</v>
+        <v>0.1533219651661748</v>
       </c>
       <c r="D326" t="n">
-        <v>0.6646008047903501</v>
+        <v>0.6574663479536681</v>
       </c>
       <c r="E326" t="n">
-        <v>0.000100000000000006</v>
+        <v>0.0001000000000000182</v>
       </c>
     </row>
     <row r="327">
@@ -5985,16 +5985,16 @@
         <v>3.25</v>
       </c>
       <c r="B327" t="n">
-        <v>0.907981230446848</v>
+        <v>0.901271819091283</v>
       </c>
       <c r="C327" t="n">
-        <v>0.1524677875049828</v>
+        <v>0.1487504173323828</v>
       </c>
       <c r="D327" t="n">
-        <v>0.662171831952597</v>
+        <v>0.6548500915683888</v>
       </c>
       <c r="E327" t="n">
-        <v>0.0001000000000000061</v>
+        <v>0.0001000000000000185</v>
       </c>
     </row>
     <row r="328">
@@ -6002,16 +6002,16 @@
         <v>3.26</v>
       </c>
       <c r="B328" t="n">
-        <v>0.9026335521141645</v>
+        <v>0.8958200237079258</v>
       </c>
       <c r="C328" t="n">
-        <v>0.147926750471808</v>
+        <v>0.1441282685156038</v>
       </c>
       <c r="D328" t="n">
-        <v>0.6596319926106518</v>
+        <v>0.6521219005754261</v>
       </c>
       <c r="E328" t="n">
-        <v>0.0001000000000000062</v>
+        <v>0.0001000000000000188</v>
       </c>
     </row>
     <row r="329">
@@ -6019,16 +6019,16 @@
         <v>3.27</v>
       </c>
       <c r="B329" t="n">
-        <v>0.8974005528971475</v>
+        <v>0.890481763761379</v>
       </c>
       <c r="C329" t="n">
-        <v>0.1433359800689528</v>
+        <v>0.1394552430603883</v>
       </c>
       <c r="D329" t="n">
-        <v>0.6569813925076338</v>
+        <v>0.6492820031610677</v>
       </c>
       <c r="E329" t="n">
-        <v>0.0001000000000000063</v>
+        <v>0.0001000000000000191</v>
       </c>
     </row>
     <row r="330">
@@ -6036,16 +6036,16 @@
         <v>3.28</v>
       </c>
       <c r="B330" t="n">
-        <v>0.8922819766378917</v>
+        <v>0.8852567514912597</v>
       </c>
       <c r="C330" t="n">
-        <v>0.1386952084868448</v>
+        <v>0.1347310653112861</v>
       </c>
       <c r="D330" t="n">
-        <v>0.6542202124471242</v>
+        <v>0.6463307060788244</v>
       </c>
       <c r="E330" t="n">
-        <v>0.0001000000000000064</v>
+        <v>0.0001000000000000194</v>
       </c>
     </row>
     <row r="331">
@@ -6053,16 +6053,16 @@
         <v>3.29</v>
       </c>
       <c r="B331" t="n">
-        <v>0.8872775770309658</v>
+        <v>0.8801447078768763</v>
       </c>
       <c r="C331" t="n">
-        <v>0.1340041679159122</v>
+        <v>0.1299554596128479</v>
       </c>
       <c r="D331" t="n">
-        <v>0.6513487091085511</v>
+        <v>0.6432683953691672</v>
       </c>
       <c r="E331" t="n">
-        <v>0.0001000000000000065</v>
+        <v>0.0001000000000000197</v>
       </c>
     </row>
     <row r="332">
@@ -6070,16 +6070,16 @@
         <v>3.3</v>
       </c>
       <c r="B332" t="n">
-        <v>0.8823871185286031</v>
+        <v>0.8751453635161263</v>
       </c>
       <c r="C332" t="n">
-        <v>0.1292625905465825</v>
+        <v>0.1251281503096234</v>
       </c>
       <c r="D332" t="n">
-        <v>0.6483672157849578</v>
+        <v>0.6400955369936304</v>
       </c>
       <c r="E332" t="n">
-        <v>0.0001000000000000065</v>
+        <v>0.00010000000000002</v>
       </c>
     </row>
     <row r="333">
@@ -6087,16 +6087,16 @@
         <v>3.31</v>
       </c>
       <c r="B333" t="n">
-        <v>0.8776103772422175</v>
+        <v>0.8702584594995924</v>
       </c>
       <c r="C333" t="n">
-        <v>0.1244702085692843</v>
+        <v>0.1202488617461633</v>
       </c>
       <c r="D333" t="n">
-        <v>0.6452761430405138</v>
+        <v>0.6368126773806289</v>
       </c>
       <c r="E333" t="n">
-        <v>0.0001000000000000066</v>
+        <v>0.0001000000000000203</v>
       </c>
     </row>
     <row r="334">
@@ -6104,16 +6104,16 @@
         <v>3.32</v>
       </c>
       <c r="B334" t="n">
-        <v>0.8729471418410276</v>
+        <v>0.8654837482805818</v>
       </c>
       <c r="C334" t="n">
-        <v>0.1196267541744448</v>
+        <v>0.1153173182670174</v>
       </c>
       <c r="D334" t="n">
-        <v>0.6420759792852014</v>
+        <v>0.6334204438804443</v>
       </c>
       <c r="E334" t="n">
-        <v>0.0001000000000000067</v>
+        <v>0.0001000000000000206</v>
       </c>
     </row>
     <row r="335">
@@ -6121,16 +6121,16 @@
         <v>3.33</v>
       </c>
       <c r="B335" t="n">
-        <v>0.8683972144486269</v>
+        <v>0.8608209945418894</v>
       </c>
       <c r="C335" t="n">
-        <v>0.1147319595524926</v>
+        <v>0.1103332442167363</v>
       </c>
       <c r="D335" t="n">
-        <v>0.6387672912642189</v>
+        <v>0.6299195451269579</v>
       </c>
       <c r="E335" t="n">
-        <v>0.0001000000000000068</v>
+        <v>0.0001000000000000209</v>
       </c>
     </row>
     <row r="336">
@@ -6138,16 +6138,16 @@
         <v>3.34</v>
       </c>
       <c r="B336" t="n">
-        <v>0.8639604115383314</v>
+        <v>0.8562699760600667</v>
       </c>
       <c r="C336" t="n">
-        <v>0.1097855568938554</v>
+        <v>0.1052963639398702</v>
       </c>
       <c r="D336" t="n">
-        <v>0.6353507244597396</v>
+        <v>0.6263107713038194</v>
       </c>
       <c r="E336" t="n">
-        <v>0.0001000000000000069</v>
+        <v>0.0001000000000000213</v>
       </c>
     </row>
     <row r="337">
@@ -6155,16 +6155,16 @@
         <v>3.35</v>
       </c>
       <c r="B337" t="n">
-        <v>0.8596365648281865</v>
+        <v>0.8518304845680198</v>
       </c>
       <c r="C337" t="n">
-        <v>0.1047872783889609</v>
+        <v>0.1002064017809689</v>
       </c>
       <c r="D337" t="n">
-        <v>0.6318270034027756</v>
+        <v>0.6225949943128856</v>
       </c>
       <c r="E337" t="n">
-        <v>0.000100000000000007</v>
+        <v>0.0001000000000000216</v>
       </c>
     </row>
     <row r="338">
@@ -6172,16 +6172,16 @@
         <v>3.36</v>
       </c>
       <c r="B338" t="n">
-        <v>0.8554255221765207</v>
+        <v>0.8475023266167699</v>
       </c>
       <c r="C338" t="n">
-        <v>0.09973685622823736</v>
+        <v>0.09506308208458303</v>
       </c>
       <c r="D338" t="n">
-        <v>0.6281969318930286</v>
+        <v>0.618773167842897</v>
       </c>
       <c r="E338" t="n">
-        <v>0.0001000000000000071</v>
+        <v>0.0001000000000000219</v>
       </c>
     </row>
     <row r="339">
@@ -6189,16 +6189,16 @@
         <v>3.37</v>
       </c>
       <c r="B339" t="n">
-        <v>0.8513271484789637</v>
+        <v>0.843285324437231</v>
       </c>
       <c r="C339" t="n">
-        <v>0.09463402260211237</v>
+        <v>0.08986612919526249</v>
       </c>
       <c r="D339" t="n">
-        <v>0.6244613931247098</v>
+        <v>0.6148463273365066</v>
       </c>
       <c r="E339" t="n">
-        <v>0.0001000000000000072</v>
+        <v>0.0001000000000000222</v>
       </c>
     </row>
     <row r="340">
@@ -6206,16 +6206,16 @@
         <v>3.38</v>
       </c>
       <c r="B340" t="n">
-        <v>0.8473413265678742</v>
+        <v>0.8391793168028934</v>
       </c>
       <c r="C340" t="n">
-        <v>0.08947850970101429</v>
+        <v>0.08461526745755804</v>
       </c>
       <c r="D340" t="n">
-        <v>0.6206213497164819</v>
+        <v>0.6108155898539368</v>
       </c>
       <c r="E340" t="n">
-        <v>0.0001000000000000073</v>
+        <v>0.0001000000000000226</v>
       </c>
     </row>
     <row r="341">
@@ -6223,16 +6223,16 @@
         <v>3.39</v>
       </c>
       <c r="B341" t="n">
-        <v>0.8434679581151466</v>
+        <v>0.8351841598943142</v>
       </c>
       <c r="C341" t="n">
-        <v>0.08427004971537072</v>
+        <v>0.07931022121601922</v>
       </c>
       <c r="D341" t="n">
-        <v>0.6166778436437799</v>
+        <v>0.6066821538316977</v>
       </c>
       <c r="E341" t="n">
-        <v>0.0001000000000000074</v>
+        <v>0.0001000000000000229</v>
       </c>
     </row>
     <row r="342">
@@ -6240,16 +6240,16 @@
         <v>3.4</v>
       </c>
       <c r="B342" t="n">
-        <v>0.8397069645393979</v>
+        <v>0.8312997281663455</v>
       </c>
       <c r="C342" t="n">
-        <v>0.0790083748356098</v>
+        <v>0.07395071481519677</v>
       </c>
       <c r="D342" t="n">
-        <v>0.6126319960719477</v>
+        <v>0.6024472987349754</v>
       </c>
       <c r="E342" t="n">
-        <v>0.0001000000000000075</v>
+        <v>0.0001000000000000233</v>
       </c>
     </row>
     <row r="343">
@@ -6257,16 +6257,16 @@
         <v>3.41</v>
       </c>
       <c r="B343" t="n">
-        <v>0.8360582879185475</v>
+        <v>0.8275259152190571</v>
       </c>
       <c r="C343" t="n">
-        <v>0.07369321725215922</v>
+        <v>0.06853647259964052</v>
       </c>
       <c r="D343" t="n">
-        <v>0.6084850070887622</v>
+        <v>0.5981123846024718</v>
       </c>
       <c r="E343" t="n">
-        <v>0.0001000000000000076</v>
+        <v>0.0001000000000000236</v>
       </c>
     </row>
     <row r="344">
@@ -6274,16 +6274,16 @@
         <v>3.42</v>
       </c>
       <c r="B344" t="n">
-        <v>0.8325218919088587</v>
+        <v>0.8238626346733341</v>
       </c>
       <c r="C344" t="n">
-        <v>0.06832430915544729</v>
+        <v>0.0630672189139011</v>
       </c>
       <c r="D344" t="n">
-        <v>0.6042381553350861</v>
+        <v>0.5936788514826623</v>
       </c>
       <c r="E344" t="n">
-        <v>0.0001000000000000077</v>
+        <v>0.0001000000000000239</v>
       </c>
     </row>
     <row r="345">
@@ -6291,16 +6291,16 @@
         <v>3.43</v>
       </c>
       <c r="B345" t="n">
-        <v>0.8290977626715129</v>
+        <v>0.8203098210521557</v>
       </c>
       <c r="C345" t="n">
-        <v>0.06290138273590151</v>
+        <v>0.05754267810252822</v>
       </c>
       <c r="D345" t="n">
-        <v>0.5998927975325631</v>
+        <v>0.5891482187606355</v>
       </c>
       <c r="E345" t="n">
-        <v>0.0001000000000000078</v>
+        <v>0.0001000000000000243</v>
       </c>
     </row>
     <row r="346">
@@ -6308,16 +6308,16 @@
         <v>3.44</v>
       </c>
       <c r="B346" t="n">
-        <v>0.8257859098078388</v>
+        <v>0.8168674306685971</v>
       </c>
       <c r="C346" t="n">
-        <v>0.0574241701839503</v>
+        <v>0.05196257451007269</v>
       </c>
       <c r="D346" t="n">
-        <v>0.5954503679074367</v>
+        <v>0.5845220843748622</v>
       </c>
       <c r="E346" t="n">
-        <v>0.0001000000000000079</v>
+        <v>0.0001000000000000246</v>
       </c>
     </row>
     <row r="347">
@@ -6325,16 +6325,16 @@
         <v>3.45</v>
       </c>
       <c r="B347" t="n">
-        <v>0.8225863673043361</v>
+        <v>0.813535442521608</v>
       </c>
       <c r="C347" t="n">
-        <v>0.05189240369002102</v>
+        <v>0.04632663248108421</v>
       </c>
       <c r="D347" t="n">
-        <v>0.5909123775097552</v>
+        <v>0.5798021239234531</v>
       </c>
       <c r="E347" t="n">
-        <v>0.000100000000000008</v>
+        <v>0.000100000000000025</v>
       </c>
     </row>
     <row r="348">
@@ -6342,16 +6342,16 @@
         <v>3.46</v>
       </c>
       <c r="B348" t="n">
-        <v>0.8194991944886877</v>
+        <v>0.8103138592006807</v>
       </c>
       <c r="C348" t="n">
-        <v>0.04630581544454221</v>
+        <v>0.04063457636011342</v>
       </c>
       <c r="D348" t="n">
-        <v>0.5862804134274162</v>
+        <v>0.5749900896596708</v>
       </c>
       <c r="E348" t="n">
-        <v>0.0001000000000000081</v>
+        <v>0.0001000000000000254</v>
       </c>
     </row>
     <row r="349">
@@ -6359,16 +6359,16 @@
         <v>3.47</v>
       </c>
       <c r="B349" t="n">
-        <v>0.8165244769979548</v>
+        <v>0.8072027078005147</v>
       </c>
       <c r="C349" t="n">
-        <v>0.0406641376379413</v>
+        <v>0.03488613049171013</v>
       </c>
       <c r="D349" t="n">
-        <v>0.5815561378946925</v>
+        <v>0.5700878093766677</v>
       </c>
       <c r="E349" t="n">
-        <v>0.0001000000000000082</v>
+        <v>0.0001000000000000257</v>
       </c>
     </row>
     <row r="350">
@@ -6376,16 +6376,16 @@
         <v>3.48</v>
       </c>
       <c r="B350" t="n">
-        <v>0.8136623277602288</v>
+        <v>0.8042020408468542</v>
       </c>
       <c r="C350" t="n">
-        <v>0.03496710246064672</v>
+        <v>0.029081019220425</v>
       </c>
       <c r="D350" t="n">
-        <v>0.5767412872950735</v>
+        <v>0.5650971851816492</v>
       </c>
       <c r="E350" t="n">
-        <v>0.0001000000000000083</v>
+        <v>0.0001000000000000261</v>
       </c>
     </row>
     <row r="351">
@@ -6393,16 +6393,16 @@
         <v>3.49</v>
       </c>
       <c r="B351" t="n">
-        <v>0.8109128879910168</v>
+        <v>0.801311937234679</v>
       </c>
       <c r="C351" t="n">
-        <v>0.02921444210308588</v>
+        <v>0.02321896689080788</v>
       </c>
       <c r="D351" t="n">
-        <v>0.5718376710584586</v>
+        <v>0.560020192159864</v>
       </c>
       <c r="E351" t="n">
-        <v>0.0001000000000000084</v>
+        <v>0.0001000000000000264</v>
       </c>
     </row>
     <row r="352">
@@ -6410,16 +6410,16 @@
         <v>3.5</v>
       </c>
       <c r="B352" t="n">
-        <v>0.8082763282056938</v>
+        <v>0.7985325031799861</v>
       </c>
       <c r="C352" t="n">
-        <v>0.02340588875568717</v>
+        <v>0.01729969784740926</v>
       </c>
       <c r="D352" t="n">
-        <v>0.5668471704529486</v>
+        <v>0.5548588769290708</v>
       </c>
       <c r="E352" t="n">
-        <v>0.0001000000000000085</v>
+        <v>0.0001000000000000268</v>
       </c>
     </row>
   </sheetData>

--- a/01_Thermal/B_results/single_annular_var_params_pchip.xlsx
+++ b/01_Thermal/B_results/single_annular_var_params_pchip.xlsx
@@ -460,16 +460,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D2" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E2" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>0.01</v>
       </c>
       <c r="B3" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D3" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E3" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>0.02</v>
       </c>
       <c r="B4" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D4" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E4" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>0.03</v>
       </c>
       <c r="B5" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D5" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E5" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>0.04</v>
       </c>
       <c r="B6" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D6" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E6" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>0.05</v>
       </c>
       <c r="B7" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D7" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E7" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>0.06</v>
       </c>
       <c r="B8" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D8" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E8" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D9" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E9" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>0.08</v>
       </c>
       <c r="B10" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D10" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E10" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>0.09</v>
       </c>
       <c r="B11" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D11" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E11" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D12" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E12" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>0.11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D13" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E13" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>0.12</v>
       </c>
       <c r="B14" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D14" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E14" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>0.13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D15" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E15" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>0.14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D16" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E16" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>0.15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D17" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E17" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>0.16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D18" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E18" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>0.17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D19" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E19" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>0.18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D20" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E20" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>0.19</v>
       </c>
       <c r="B21" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828834</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D21" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E21" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="22">
@@ -800,16 +800,16 @@
         <v>0.2</v>
       </c>
       <c r="B22" t="n">
-        <v>5.033052279130711</v>
+        <v>4.916295944828835</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3056239944714074</v>
+        <v>0.3066769217402805</v>
       </c>
       <c r="D22" t="n">
-        <v>0.210752420248507</v>
+        <v>0.2018969531010486</v>
       </c>
       <c r="E22" t="n">
-        <v>9.999999999996996e-05</v>
+        <v>0.1193549673528184</v>
       </c>
     </row>
     <row r="23">
@@ -817,16 +817,16 @@
         <v>0.21</v>
       </c>
       <c r="B23" t="n">
-        <v>4.98159212569856</v>
+        <v>4.878661060304989</v>
       </c>
       <c r="C23" t="n">
-        <v>0.305740820929377</v>
+        <v>0.3067913214307943</v>
       </c>
       <c r="D23" t="n">
-        <v>0.219370609957528</v>
+        <v>0.2107387131634375</v>
       </c>
       <c r="E23" t="n">
-        <v>9.999999999997297e-05</v>
+        <v>0.1081366855896947</v>
       </c>
     </row>
     <row r="24">
@@ -834,16 +834,16 @@
         <v>0.22</v>
       </c>
       <c r="B24" t="n">
-        <v>4.931613575503428</v>
+        <v>4.842067008035257</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3060856149727849</v>
+        <v>0.3071290049324162</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2279804537231699</v>
+        <v>0.2196210284283484</v>
       </c>
       <c r="E24" t="n">
-        <v>9.999999999997592e-05</v>
+        <v>0.09710616519411353</v>
       </c>
     </row>
     <row r="25">
@@ -851,16 +851,16 @@
         <v>0.23</v>
       </c>
       <c r="B25" t="n">
-        <v>4.883310389204912</v>
+        <v>4.806615897947761</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3066498486058792</v>
+        <v>0.3076816988902676</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2365124171442313</v>
+        <v>0.2284703290732541</v>
       </c>
       <c r="E25" t="n">
-        <v>9.999999999997885e-05</v>
+        <v>0.08635024509555114</v>
       </c>
     </row>
     <row r="26">
@@ -868,16 +868,16 @@
         <v>0.24</v>
       </c>
       <c r="B26" t="n">
-        <v>4.83686877130233</v>
+        <v>4.772406986792324</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3074249938329087</v>
+        <v>0.3084411299494694</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2448901430558438</v>
+        <v>0.2372046692948225</v>
       </c>
       <c r="E26" t="n">
-        <v>9.999999999998168e-05</v>
+        <v>0.0759557642234838</v>
       </c>
     </row>
     <row r="27">
@@ -885,16 +885,16 @@
         <v>0.25</v>
       </c>
       <c r="B27" t="n">
-        <v>4.792468132012253</v>
+        <v>4.739536955272539</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3084025226581215</v>
+        <v>0.3093990247551426</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2530308952085595</v>
+        <v>0.2457341139056164</v>
       </c>
       <c r="E27" t="n">
-        <v>9.999999999998442e-05</v>
+        <v>0.06600956150738763</v>
       </c>
     </row>
     <row r="28">
@@ -902,16 +902,16 @@
         <v>0.26</v>
       </c>
       <c r="B28" t="n">
-        <v>4.750281917099877</v>
+        <v>4.708100205181494</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3095739070857663</v>
+        <v>0.3105471099524084</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2608462221341931</v>
+        <v>0.2539613991834851</v>
       </c>
       <c r="E28" t="n">
-        <v>9.999999999998702e-05</v>
+        <v>0.05659847587673891</v>
       </c>
     </row>
     <row r="29">
@@ -919,16 +919,16 @@
         <v>0.27</v>
       </c>
       <c r="B29" t="n">
-        <v>4.710478502122786</v>
+        <v>4.678189175873423</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3109306191200913</v>
+        <v>0.3118771121863879</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2682428568235032</v>
+        <v>0.2617828936830937</v>
       </c>
       <c r="E29" t="n">
-        <v>9.999999999998945e-05</v>
+        <v>0.04780934626101385</v>
       </c>
     </row>
     <row r="30">
@@ -936,16 +936,16 @@
         <v>0.28</v>
       </c>
       <c r="B30" t="n">
-        <v>4.673222148569235</v>
+        <v>4.649894679601542</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3124641307653451</v>
+        <v>0.3133807581022022</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2751238619212177</v>
+        <v>0.269089877449682</v>
       </c>
       <c r="E30" t="n">
-        <v>9.999999999999171e-05</v>
+        <v>0.03972901158968865</v>
       </c>
     </row>
     <row r="31">
@@ -953,16 +953,16 @@
         <v>0.29</v>
       </c>
       <c r="B31" t="n">
-        <v>4.638674020462563</v>
+        <v>4.623306255461236</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3141659140257759</v>
+        <v>0.3150497743449722</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2813900226657297</v>
+        <v>0.2757701484183793</v>
       </c>
       <c r="E31" t="n">
-        <v>9.999999999999374e-05</v>
+        <v>0.03244431079223957</v>
       </c>
     </row>
     <row r="32">
@@ -970,16 +970,16 @@
         <v>0.3</v>
       </c>
       <c r="B32" t="n">
-        <v>4.606993261158708</v>
+        <v>4.598512541898093</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3160274409056323</v>
+        <v>0.3168758875598192</v>
       </c>
       <c r="D32" t="n">
-        <v>0.286941480833454</v>
+        <v>0.2817099527684763</v>
       </c>
       <c r="E32" t="n">
-        <v>9.999999999999555e-05</v>
+        <v>0.02604208279814274</v>
       </c>
     </row>
     <row r="33">
@@ -987,16 +987,16 @@
         <v>0.31</v>
       </c>
       <c r="B33" t="n">
-        <v>4.578338131287263</v>
+        <v>4.575601667972243</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3180401834091627</v>
+        <v>0.3188508243918641</v>
       </c>
       <c r="D33" t="n">
-        <v>0.291679592663958</v>
+        <v>0.2867962218223767</v>
       </c>
       <c r="E33" t="n">
-        <v>9.999999999999708e-05</v>
+        <v>0.02060916653687445</v>
       </c>
     </row>
     <row r="34">
@@ -1004,16 +1004,16 @@
         <v>0.32</v>
       </c>
       <c r="B34" t="n">
-        <v>4.5528672100836</v>
+        <v>4.554661663814586</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3201956135406155</v>
+        <v>0.3209663114862282</v>
       </c>
       <c r="D34" t="n">
-        <v>0.295508982429149</v>
+        <v>0.2909190821109755</v>
       </c>
       <c r="E34" t="n">
-        <v>9.999999999999831e-05</v>
+        <v>0.01623240093791087</v>
       </c>
     </row>
     <row r="35">
@@ -1021,16 +1021,16 @@
         <v>0.33</v>
       </c>
       <c r="B35" t="n">
-        <v>4.530740663738229</v>
+        <v>4.535780890968005</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3224852033042391</v>
+        <v>0.3232140754880323</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2983397513764138</v>
+        <v>0.29397458805018</v>
       </c>
       <c r="E35" t="n">
-        <v>9.999999999999923e-05</v>
+        <v>0.01299862493072824</v>
       </c>
     </row>
     <row r="36">
@@ -1038,16 +1038,16 @@
         <v>0.34</v>
       </c>
       <c r="B36" t="n">
-        <v>4.512121585861386</v>
+        <v>4.519048493578473</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3249004247042819</v>
+        <v>0.3255858430423978</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3000897897489179</v>
+        <v>0.2958676090706954</v>
       </c>
       <c r="E36" t="n">
-        <v>9.999999999999979e-05</v>
+        <v>0.01099467744480279</v>
       </c>
     </row>
     <row r="37">
@@ -1055,16 +1055,16 @@
         <v>0.35</v>
       </c>
       <c r="B37" t="n">
-        <v>4.497177416740473</v>
+        <v>4.504554871688979</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3274327497449923</v>
+        <v>0.3280733407944455</v>
       </c>
       <c r="D37" t="n">
-        <v>0.300687128100693</v>
+        <v>0.2965147859884885</v>
       </c>
       <c r="E37" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01030739740961069</v>
       </c>
     </row>
     <row r="38">
@@ -1072,16 +1072,16 @@
         <v>0.36</v>
       </c>
       <c r="B38" t="n">
-        <v>4.485128409563226</v>
+        <v>4.492162571721678</v>
       </c>
       <c r="C38" t="n">
-        <v>0.331935841590579</v>
+        <v>0.3325223279547383</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3000818264750856</v>
+        <v>0.2959319004499767</v>
       </c>
       <c r="E38" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01045205290417247</v>
       </c>
     </row>
     <row r="39">
@@ -1089,16 +1089,16 @@
         <v>0.37</v>
       </c>
       <c r="B39" t="n">
-        <v>4.474884437025361</v>
+        <v>4.48148090417604</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3398967091159713</v>
+        <v>0.3404136354718398</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2983850665946794</v>
+        <v>0.2942978290389194</v>
       </c>
       <c r="E39" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01085910673770678</v>
       </c>
     </row>
     <row r="40">
@@ -1106,16 +1106,16 @@
         <v>0.38</v>
       </c>
       <c r="B40" t="n">
-        <v>4.46615507708476</v>
+        <v>4.472225077870323</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3507568428914987</v>
+        <v>0.3511915975978725</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2957816528143613</v>
+        <v>0.2917901758112764</v>
       </c>
       <c r="E40" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01148818993498708</v>
       </c>
     </row>
     <row r="41">
@@ -1123,16 +1123,16 @@
         <v>0.39</v>
       </c>
       <c r="B41" t="n">
-        <v>4.458653827763166</v>
+        <v>4.464114112018759</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3639577334874904</v>
+        <v>0.3643005485849587</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2924599238524166</v>
+        <v>0.2885898749584488</v>
       </c>
       <c r="E41" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01229893352078683</v>
       </c>
     </row>
     <row r="42">
@@ -1140,16 +1140,16 @@
         <v>0.4</v>
       </c>
       <c r="B42" t="n">
-        <v>4.45209724025482</v>
+        <v>4.45687004061754</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3789408714742762</v>
+        <v>0.3791848226852212</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2886068955726969</v>
+        <v>0.2848766256438352</v>
       </c>
       <c r="E42" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01325096851987948</v>
       </c>
     </row>
     <row r="43">
@@ -1157,16 +1157,16 @@
         <v>0.41</v>
       </c>
       <c r="B43" t="n">
-        <v>4.446204235261122</v>
+        <v>4.450217292589179</v>
       </c>
       <c r="C43" t="n">
-        <v>0.3951477474221853</v>
+        <v>0.3952887541507821</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2844045102828656</v>
+        <v>0.2808253638416682</v>
       </c>
       <c r="E43" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01430392595703849</v>
       </c>
     </row>
     <row r="44">
@@ -1174,16 +1174,16 @@
         <v>0.42</v>
       </c>
       <c r="B44" t="n">
-        <v>4.44069559868357</v>
+        <v>4.443882244030197</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4120198519015472</v>
+        <v>0.412056677233764</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2800270058833277</v>
+        <v>0.2766037835406489</v>
       </c>
       <c r="E44" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.0154174368570373</v>
       </c>
     </row>
     <row r="45">
@@ -1191,16 +1191,16 @@
         <v>0.43</v>
       </c>
       <c r="B45" t="n">
-        <v>4.43529365385362</v>
+        <v>4.437592939827695</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4289986754826917</v>
+        <v>0.4289329261862896</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2756393653634587</v>
+        <v>0.2723708711641611</v>
       </c>
       <c r="E45" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01655113224464939</v>
       </c>
     </row>
     <row r="46">
@@ -1208,16 +1208,16 @@
         <v>0.44</v>
       </c>
       <c r="B46" t="n">
-        <v>4.429722108208275</v>
+        <v>4.431078982534226</v>
       </c>
       <c r="C46" t="n">
-        <v>0.4455257087359479</v>
+        <v>0.445361835260481</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2713967725390189</v>
+        <v>0.2682763852226191</v>
       </c>
       <c r="E46" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01766464314464822</v>
       </c>
     </row>
     <row r="47">
@@ -1225,16 +1225,16 @@
         <v>0.45</v>
       </c>
       <c r="B47" t="n">
-        <v>4.423706072741392</v>
+        <v>4.424071586724375</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4610424422316454</v>
+        <v>0.4607877387084607</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2674449826749462</v>
+        <v>0.2644611972639037</v>
       </c>
       <c r="E47" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01871760058180722</v>
       </c>
     </row>
     <row r="48">
@@ -1242,16 +1242,16 @@
         <v>0.46</v>
       </c>
       <c r="B48" t="n">
-        <v>4.416972252677958</v>
+        <v>4.416303797105303</v>
       </c>
       <c r="C48" t="n">
-        <v>0.4749903665401136</v>
+        <v>0.4746549707823515</v>
       </c>
       <c r="D48" t="n">
-        <v>0.263921515021868</v>
+        <v>0.2610584085845591</v>
       </c>
       <c r="E48" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01966963558089987</v>
       </c>
     </row>
     <row r="49">
@@ -1259,16 +1259,16 @@
         <v>0.47</v>
       </c>
       <c r="B49" t="n">
-        <v>4.409249307635934</v>
+        <v>4.407510868421785</v>
       </c>
       <c r="C49" t="n">
-        <v>0.486810972231682</v>
+        <v>0.4864078657342754</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2609575862866443</v>
+        <v>0.2581951680888568</v>
       </c>
       <c r="E49" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.02048037916669961</v>
       </c>
     </row>
     <row r="50">
@@ -1276,16 +1276,16 @@
         <v>0.48</v>
       </c>
       <c r="B50" t="n">
-        <v>4.400268379062217</v>
+        <v>4.397430804688746</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4959457498766801</v>
+        <v>0.4954907578163553</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2586807277830648</v>
+        <v>0.2559951384497179</v>
       </c>
       <c r="E50" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.02110946236397991</v>
       </c>
     </row>
     <row r="51">
@@ -1293,16 +1293,16 @@
         <v>0.49</v>
       </c>
       <c r="B51" t="n">
-        <v>4.389763781960907</v>
+        <v>4.385805054506567</v>
       </c>
       <c r="C51" t="n">
-        <v>0.5018361900454374</v>
+        <v>0.5013479812807133</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2572180631295857</v>
+        <v>0.2545815891281534</v>
       </c>
       <c r="E51" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.02151651619751422</v>
       </c>
     </row>
     <row r="52">
@@ -1310,16 +1310,16 @@
         <v>0.5</v>
       </c>
       <c r="B52" t="n">
-        <v>4.377473856881211</v>
+        <v>4.372379358174996</v>
       </c>
       <c r="C52" t="n">
-        <v>0.5039237833082832</v>
+        <v>0.5034238703794722</v>
       </c>
       <c r="D52" t="n">
-        <v>0.2567002673970867</v>
+        <v>0.2540811354115556</v>
       </c>
       <c r="E52" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.02166117169207601</v>
       </c>
     </row>
     <row r="53">
@@ -1327,16 +1327,16 @@
         <v>0.51</v>
       </c>
       <c r="B53" t="n">
-        <v>4.358519806625067</v>
+        <v>4.352971136117175</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5032152083365818</v>
+        <v>0.5028084141744932</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2573796586254457</v>
+        <v>0.2546875768097981</v>
       </c>
       <c r="E53" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.02164937158111585</v>
       </c>
     </row>
     <row r="54">
@@ -1344,16 +1344,16 @@
         <v>0.52</v>
       </c>
       <c r="B54" t="n">
-        <v>4.328879518858309</v>
+        <v>4.324160039111483</v>
       </c>
       <c r="C54" t="n">
-        <v>0.5011671354731709</v>
+        <v>0.5010294928148962</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2593535050559842</v>
+        <v>0.2564485921568287</v>
       </c>
       <c r="E54" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.02161484361923466</v>
       </c>
     </row>
     <row r="55">
@@ -1361,16 +1361,16 @@
         <v>0.53</v>
       </c>
       <c r="B55" t="n">
-        <v>4.289621086470994</v>
+        <v>4.286869636350116</v>
       </c>
       <c r="C55" t="n">
-        <v>0.4978960427955905</v>
+        <v>0.4981882771836914</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2625374899477492</v>
+        <v>0.2592864980460822</v>
       </c>
       <c r="E55" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.02155889636293135</v>
       </c>
     </row>
     <row r="56">
@@ -1378,16 +1378,16 @@
         <v>0.54</v>
       </c>
       <c r="B56" t="n">
-        <v>4.24184962199841</v>
+        <v>4.242050824730428</v>
       </c>
       <c r="C56" t="n">
-        <v>0.4935184083813805</v>
+        <v>0.4943859381638893</v>
       </c>
       <c r="D56" t="n">
-        <v>0.2668597936860997</v>
+        <v>0.2631336059083221</v>
       </c>
       <c r="E56" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.02148283836870486</v>
       </c>
     </row>
     <row r="57">
@@ -1395,16 +1395,16 @@
         <v>0.55</v>
       </c>
       <c r="B57" t="n">
-        <v>4.186686624832443</v>
+        <v>4.190666090973953</v>
       </c>
       <c r="C57" t="n">
-        <v>0.4881507103080809</v>
+        <v>0.4897236466384999</v>
       </c>
       <c r="D57" t="n">
-        <v>0.2722568888482048</v>
+        <v>0.2679287831387771</v>
       </c>
       <c r="E57" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.02138797819305412</v>
       </c>
     </row>
     <row r="58">
@@ -1412,16 +1412,16 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58" t="n">
-        <v>4.125251564768535</v>
+        <v>4.133675441894602</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4819094266532316</v>
+        <v>0.4843025734905336</v>
       </c>
       <c r="D58" t="n">
-        <v>0.2786697496254322</v>
+        <v>0.2736143511629143</v>
       </c>
       <c r="E58" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.02127562439247804</v>
       </c>
     </row>
     <row r="59">
@@ -1429,16 +1429,16 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59" t="n">
-        <v>4.05864589818624</v>
+        <v>4.072024145871232</v>
       </c>
       <c r="C59" t="n">
-        <v>0.4749110354943726</v>
+        <v>0.4782238896030007</v>
       </c>
       <c r="D59" t="n">
-        <v>0.2860403495528411</v>
+        <v>0.2801332288520516</v>
       </c>
       <c r="E59" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.02114708552347555</v>
       </c>
     </row>
     <row r="60">
@@ -1446,16 +1446,16 @@
         <v>0.58</v>
       </c>
       <c r="B60" t="n">
-        <v>3.987939627912844</v>
+        <v>4.00663235889122</v>
       </c>
       <c r="C60" t="n">
-        <v>0.4672720149090439</v>
+        <v>0.4715887658589115</v>
       </c>
       <c r="D60" t="n">
-        <v>0.2943083606981641</v>
+        <v>0.287426258950021</v>
       </c>
       <c r="E60" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.02100367014254559</v>
       </c>
     </row>
     <row r="61">
@@ -1463,16 +1463,16 @@
         <v>0.59</v>
       </c>
       <c r="B61" t="n">
-        <v>3.914160425901702</v>
+        <v>3.938386647495419</v>
       </c>
       <c r="C61" t="n">
-        <v>0.4591088429747854</v>
+        <v>0.4644983731412759</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3034080018791695</v>
+        <v>0.2954296809190959</v>
       </c>
       <c r="E61" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.02084668680618706</v>
       </c>
     </row>
     <row r="62">
@@ -1480,16 +1480,16 @@
         <v>0.6</v>
       </c>
       <c r="B62" t="n">
-        <v>3.838285260952537</v>
+        <v>3.868133369553209</v>
       </c>
       <c r="C62" t="n">
-        <v>0.450537997769137</v>
+        <v>0.4570538823331045</v>
       </c>
       <c r="D62" t="n">
-        <v>0.313265015150729</v>
+        <v>0.3040727371965491</v>
       </c>
       <c r="E62" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.02067744407089891</v>
       </c>
     </row>
     <row r="63">
@@ -1497,16 +1497,16 @@
         <v>0.61</v>
       </c>
       <c r="B63" t="n">
-        <v>3.761234412489201</v>
+        <v>3.796673832434567</v>
       </c>
       <c r="C63" t="n">
-        <v>0.4416759573696387</v>
+        <v>0.4493564643174074</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3237937800717226</v>
+        <v>0.3132754221339709</v>
       </c>
       <c r="E63" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.02049725049318005</v>
       </c>
     </row>
     <row r="64">
@@ -1514,16 +1514,16 @@
         <v>0.62</v>
       </c>
       <c r="B64" t="n">
-        <v>3.683867705735636</v>
+        <v>3.724761116744197</v>
       </c>
       <c r="C64" t="n">
-        <v>0.4326391998538305</v>
+        <v>0.441507289977195</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3348946048450526</v>
+        <v>0.322946404307271</v>
       </c>
       <c r="E64" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.02030741462952941</v>
       </c>
     </row>
     <row r="65">
@@ -1531,16 +1531,16 @@
         <v>0.63</v>
       </c>
       <c r="B65" t="n">
-        <v>3.606982772683528</v>
+        <v>3.653098431878174</v>
       </c>
       <c r="C65" t="n">
-        <v>0.4235442032992522</v>
+        <v>0.4336075301954774</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3464512624474825</v>
+        <v>0.3329811734751759</v>
       </c>
       <c r="E65" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.02010924503644593</v>
       </c>
     </row>
     <row r="66">
@@ -1548,16 +1548,16 @@
         <v>0.64</v>
       </c>
       <c r="B66" t="n">
-        <v>3.531315125746909</v>
+        <v>3.582338856511157</v>
       </c>
       <c r="C66" t="n">
-        <v>0.414507445783444</v>
+        <v>0.425758355855265</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3583288678668224</v>
+        <v>0.3432604828789818</v>
       </c>
       <c r="E66" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01990405027042851</v>
       </c>
     </row>
     <row r="67">
@@ -1565,16 +1565,16 @@
         <v>0.65</v>
       </c>
       <c r="B67" t="n">
-        <v>3.45753982537296</v>
+        <v>3.513086311791973</v>
       </c>
       <c r="C67" t="n">
-        <v>0.4056454053839457</v>
+        <v>0.4180609378395679</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3703722184859787</v>
+        <v>0.3536491750864014</v>
       </c>
       <c r="E67" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01969313888797609</v>
       </c>
     </row>
     <row r="68">
@@ -1582,16 +1582,16 @@
         <v>0.66</v>
       </c>
       <c r="B68" t="n">
-        <v>3.386274527403975</v>
+        <v>3.445897616488558</v>
       </c>
       <c r="C68" t="n">
-        <v>0.3970745601782973</v>
+        <v>0.4106164470313965</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3824047418552442</v>
+        <v>0.363995494092797</v>
       </c>
       <c r="E68" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01947781944558759</v>
       </c>
     </row>
     <row r="69">
@@ -1599,16 +1599,16 @@
         <v>0.67</v>
       </c>
       <c r="B69" t="n">
-        <v>3.318083708928796</v>
+        <v>3.381285480527907</v>
       </c>
       <c r="C69" t="n">
-        <v>0.3889113882440388</v>
+        <v>0.403526054313761</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3942282113908802</v>
+        <v>0.3741309964811614</v>
       </c>
       <c r="E69" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01925940049976195</v>
       </c>
     </row>
     <row r="70">
@@ -1616,16 +1616,16 @@
         <v>0.68</v>
       </c>
       <c r="B70" t="n">
-        <v>3.253483891081982</v>
+        <v>3.319722305310512</v>
       </c>
       <c r="C70" t="n">
-        <v>0.38127236765871</v>
+        <v>0.3968909305696717</v>
       </c>
       <c r="D70" t="n">
-        <v>0.4056233982960705</v>
+        <v>0.3838711784263797</v>
       </c>
       <c r="E70" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01903919060699808</v>
       </c>
     </row>
     <row r="71">
@@ -1633,16 +1633,16 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71" t="n">
-        <v>3.192949702278973</v>
+        <v>3.261644674918248</v>
       </c>
       <c r="C71" t="n">
-        <v>0.374273976499851</v>
+        <v>0.3908122466821388</v>
       </c>
       <c r="D71" t="n">
-        <v>0.4163518243059079</v>
+        <v>0.3930169313808969</v>
       </c>
       <c r="E71" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01881849832379491</v>
       </c>
     </row>
     <row r="72">
@@ -1650,16 +1650,16 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72" t="n">
-        <v>3.136920654484479</v>
+        <v>3.207458441083491</v>
       </c>
       <c r="C72" t="n">
-        <v>0.3680326928450017</v>
+        <v>0.3853911735341725</v>
       </c>
       <c r="D72" t="n">
-        <v>0.4261587617718945</v>
+        <v>0.401356925583186</v>
       </c>
       <c r="E72" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01859863220665136</v>
       </c>
     </row>
     <row r="73">
@@ -1667,16 +1667,16 @@
         <v>0.71</v>
       </c>
       <c r="B73" t="n">
-        <v>3.085808537345953</v>
+        <v>3.157544325903925</v>
       </c>
       <c r="C73" t="n">
-        <v>0.3626649947717021</v>
+        <v>0.3807288820087832</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4347775925057339</v>
+        <v>0.4086709954991071</v>
       </c>
       <c r="E73" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01838090081206637</v>
       </c>
     </row>
     <row r="74">
@@ -1684,16 +1684,16 @@
         <v>0.72</v>
       </c>
       <c r="B74" t="n">
-        <v>3.04000536973716</v>
+        <v>3.112263989305328</v>
       </c>
       <c r="C74" t="n">
-        <v>0.3582873603574921</v>
+        <v>0.376926542988981</v>
       </c>
       <c r="D74" t="n">
-        <v>0.4419355828324205</v>
+        <v>0.414734563836455</v>
       </c>
       <c r="E74" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01816661269653886</v>
       </c>
     </row>
     <row r="75">
@@ -1701,16 +1701,16 @@
         <v>0.73</v>
       </c>
       <c r="B75" t="n">
-        <v>2.999891885128306</v>
+        <v>3.071966532895868</v>
       </c>
       <c r="C75" t="n">
-        <v>0.3550162676799117</v>
+        <v>0.3740853273577763</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4473610588388774</v>
+        <v>0.4193240905376529</v>
       </c>
       <c r="E75" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01795707641656775</v>
       </c>
     </row>
     <row r="76">
@@ -1718,16 +1718,16 @@
         <v>0.74</v>
       </c>
       <c r="B76" t="n">
-        <v>2.965846566251338</v>
+        <v>3.036995438042817</v>
       </c>
       <c r="C76" t="n">
-        <v>0.3529681948165008</v>
+        <v>0.3723064059981793</v>
       </c>
       <c r="D76" t="n">
-        <v>0.4507918739773654</v>
+        <v>0.4222234709003157</v>
       </c>
       <c r="E76" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01775360052865197</v>
       </c>
     </row>
     <row r="77">
@@ -1735,16 +1735,16 @@
         <v>0.75</v>
       </c>
       <c r="B77" t="n">
-        <v>2.938255286145861</v>
+        <v>3.007695963869996</v>
       </c>
       <c r="C77" t="n">
-        <v>0.3522596198447994</v>
+        <v>0.3716909497932002</v>
       </c>
       <c r="D77" t="n">
-        <v>0.4519849543278506</v>
+        <v>0.4232312347850639</v>
       </c>
       <c r="E77" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01755749358929044</v>
       </c>
     </row>
     <row r="78">
@@ -1752,16 +1752,16 @@
         <v>0.76</v>
       </c>
       <c r="B78" t="n">
-        <v>2.91416439956993</v>
+        <v>2.981434996191224</v>
       </c>
       <c r="C78" t="n">
-        <v>0.3523432809424807</v>
+        <v>0.3717383879665199</v>
       </c>
       <c r="D78" t="n">
-        <v>0.4519088330814388</v>
+        <v>0.4232147535870053</v>
       </c>
       <c r="E78" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01736086895025232</v>
       </c>
     </row>
     <row r="79">
@@ -1769,16 +1769,16 @@
         <v>0.77</v>
       </c>
       <c r="B79" t="n">
-        <v>2.890376062641034</v>
+        <v>2.955375914873581</v>
       </c>
       <c r="C79" t="n">
-        <v>0.3525886558347008</v>
+        <v>0.3718777227798674</v>
       </c>
       <c r="D79" t="n">
-        <v>0.4516864551376762</v>
+        <v>0.4231665937640576</v>
       </c>
       <c r="E79" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01715536234827001</v>
       </c>
     </row>
     <row r="80">
@@ -1786,16 +1786,16 @@
         <v>0.78</v>
       </c>
       <c r="B80" t="n">
-        <v>2.866920710922534</v>
+        <v>2.929563519162011</v>
       </c>
       <c r="C80" t="n">
-        <v>0.3529873319202244</v>
+        <v>0.372104484673326</v>
       </c>
       <c r="D80" t="n">
-        <v>0.4513268926522145</v>
+        <v>0.4230886856567425</v>
       </c>
       <c r="E80" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01694156591728729</v>
       </c>
     </row>
     <row r="81">
@@ -1803,16 +1803,16 @@
         <v>0.79</v>
       </c>
       <c r="B81" t="n">
-        <v>2.843827728340388</v>
+        <v>2.904041003759251</v>
       </c>
       <c r="C81" t="n">
-        <v>0.3535308965978161</v>
+        <v>0.3724142040869786</v>
       </c>
       <c r="D81" t="n">
-        <v>0.4508393201089932</v>
+        <v>0.4229829647441813</v>
       </c>
       <c r="E81" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01672007179124794</v>
       </c>
     </row>
     <row r="82">
@@ -1820,16 +1820,16 @@
         <v>0.8</v>
       </c>
       <c r="B82" t="n">
-        <v>2.821125487166179</v>
+        <v>2.87885000047398</v>
       </c>
       <c r="C82" t="n">
-        <v>0.3542109372662403</v>
+        <v>0.3728024114609083</v>
       </c>
       <c r="D82" t="n">
-        <v>0.450232987845032</v>
+        <v>0.4228513703330513</v>
       </c>
       <c r="E82" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01649147210409573</v>
       </c>
     </row>
     <row r="83">
@@ -1837,16 +1837,16 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83" t="n">
-        <v>2.798841390847312</v>
+        <v>2.854030625977317</v>
       </c>
       <c r="C83" t="n">
-        <v>0.3550190413242619</v>
+        <v>0.373264637235198</v>
       </c>
       <c r="D83" t="n">
-        <v>0.449517197297349</v>
+        <v>0.4226958443334353</v>
       </c>
       <c r="E83" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01625635898977445</v>
       </c>
     </row>
     <row r="84">
@@ -1854,16 +1854,16 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84" t="n">
-        <v>2.777001919499885</v>
+        <v>2.829621535261811</v>
       </c>
       <c r="C84" t="n">
-        <v>0.3559467961706452</v>
+        <v>0.373796411849931</v>
       </c>
       <c r="D84" t="n">
-        <v>0.4487012780297069</v>
+        <v>0.4225183301222321</v>
       </c>
       <c r="E84" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01601532458222789</v>
       </c>
     </row>
     <row r="85">
@@ -1871,16 +1871,16 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85" t="n">
-        <v>2.755632677893768</v>
+        <v>2.80565998041874</v>
       </c>
       <c r="C85" t="n">
-        <v>0.3569857892041551</v>
+        <v>0.3743932657451902</v>
       </c>
       <c r="D85" t="n">
-        <v>0.4477945665837048</v>
+        <v>0.4223207714946398</v>
       </c>
       <c r="E85" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01576896101539981</v>
       </c>
     </row>
     <row r="86">
@@ -1888,16 +1888,16 @@
         <v>0.84</v>
       </c>
       <c r="B86" t="n">
-        <v>2.734758445773983</v>
+        <v>2.782181874373239</v>
       </c>
       <c r="C86" t="n">
-        <v>0.3581276078235559</v>
+        <v>0.3750507293610588</v>
       </c>
       <c r="D86" t="n">
-        <v>0.4468063871864569</v>
+        <v>0.42210511170409</v>
       </c>
       <c r="E86" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01551786042323402</v>
       </c>
     </row>
     <row r="87">
@@ -1905,16 +1905,16 @@
         <v>0.85</v>
       </c>
       <c r="B87" t="n">
-        <v>2.714403230377775</v>
+        <v>2.759221859242452</v>
       </c>
       <c r="C87" t="n">
-        <v>0.3593638394276124</v>
+        <v>0.3757643331376195</v>
       </c>
       <c r="D87" t="n">
-        <v>0.4457460343357996</v>
+        <v>0.4218732925908795</v>
       </c>
       <c r="E87" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01526261493967427</v>
       </c>
     </row>
     <row r="88">
@@ -1922,16 +1922,16 @@
         <v>0.86</v>
       </c>
       <c r="B88" t="n">
-        <v>2.694590321022424</v>
+        <v>2.736813379009143</v>
       </c>
       <c r="C88" t="n">
-        <v>0.360686071415089</v>
+        <v>0.3765296075149557</v>
       </c>
       <c r="D88" t="n">
-        <v>0.4446227572736684</v>
+        <v>0.4216272537996294</v>
       </c>
       <c r="E88" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01500381669866436</v>
       </c>
     </row>
     <row r="89">
@@ -1939,16 +1939,16 @@
         <v>0.87</v>
       </c>
       <c r="B89" t="n">
-        <v>2.67534234565512</v>
+        <v>2.714988756232037</v>
       </c>
       <c r="C89" t="n">
-        <v>0.3620858911847504</v>
+        <v>0.3773420829331504</v>
       </c>
       <c r="D89" t="n">
-        <v>0.4434457463490243</v>
+        <v>0.4213689320855987</v>
       </c>
       <c r="E89" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01474205783414806</v>
       </c>
     </row>
     <row r="90">
@@ -1956,16 +1956,16 @@
         <v>0.88</v>
       </c>
       <c r="B90" t="n">
-        <v>2.656681329272905</v>
+        <v>2.693779272544309</v>
       </c>
       <c r="C90" t="n">
-        <v>0.3635548861353613</v>
+        <v>0.3781972898322865</v>
       </c>
       <c r="D90" t="n">
-        <v>0.442224121263507</v>
+        <v>0.4211002607097808</v>
       </c>
       <c r="E90" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01447793048006917</v>
       </c>
     </row>
     <row r="91">
@@ -1973,16 +1973,16 @@
         <v>0.89</v>
       </c>
       <c r="B91" t="n">
-        <v>2.638628754137736</v>
+        <v>2.673215252723002</v>
       </c>
       <c r="C91" t="n">
-        <v>0.3650846436656861</v>
+        <v>0.3790907586524471</v>
       </c>
       <c r="D91" t="n">
-        <v>0.4409669211858396</v>
+        <v>0.4208231689226325</v>
       </c>
       <c r="E91" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01421202677037145</v>
       </c>
     </row>
     <row r="92">
@@ -1990,16 +1990,16 @@
         <v>0.9</v>
       </c>
       <c r="B92" t="n">
-        <v>2.621205621729267</v>
+        <v>2.653326152144673</v>
       </c>
       <c r="C92" t="n">
-        <v>0.3666667511744895</v>
+        <v>0.3800180198337153</v>
       </c>
       <c r="D92" t="n">
-        <v>0.4396830967149334</v>
+        <v>0.4205395815362105</v>
       </c>
       <c r="E92" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01394493883899869</v>
       </c>
     </row>
     <row r="93">
@@ -2007,16 +2007,16 @@
         <v>0.91</v>
       </c>
       <c r="B93" t="n">
-        <v>2.604432516395834</v>
+        <v>2.634140647476084</v>
       </c>
       <c r="C93" t="n">
-        <v>0.3682927960605361</v>
+        <v>0.380974603816174</v>
       </c>
       <c r="D93" t="n">
-        <v>0.4383815036666061</v>
+        <v>0.4202514185844325</v>
       </c>
       <c r="E93" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01367725881989468</v>
       </c>
     </row>
     <row r="94">
@@ -2024,16 +2024,16 @@
         <v>0.92</v>
       </c>
       <c r="B94" t="n">
-        <v>2.588329670682394</v>
+        <v>2.615686730483291</v>
       </c>
       <c r="C94" t="n">
-        <v>0.3699543657225904</v>
+        <v>0.3819560410399065</v>
       </c>
       <c r="D94" t="n">
-        <v>0.4370708986548409</v>
+        <v>0.4199605950711288</v>
       </c>
       <c r="E94" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01340957884700318</v>
       </c>
     </row>
     <row r="95">
@@ -2041,16 +2041,16 @@
         <v>0.93</v>
       </c>
       <c r="B95" t="n">
-        <v>2.572917032332926</v>
+        <v>2.597991804877974</v>
       </c>
       <c r="C95" t="n">
-        <v>0.371643047559417</v>
+        <v>0.3829578619449957</v>
       </c>
       <c r="D95" t="n">
-        <v>0.4357599364355441</v>
+        <v>0.4196690208055141</v>
       </c>
       <c r="E95" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01314249105426799</v>
       </c>
     </row>
     <row r="96">
@@ -2058,16 +2058,16 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96" t="n">
-        <v>2.558214332983911</v>
+        <v>2.581082786156277</v>
       </c>
       <c r="C96" t="n">
-        <v>0.3733504289697806</v>
+        <v>0.3839755969715247</v>
       </c>
       <c r="D96" t="n">
-        <v>0.4344571689787919</v>
+        <v>0.4193786003246827</v>
       </c>
       <c r="E96" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01287658757563288</v>
       </c>
     </row>
     <row r="97">
@@ -2075,16 +2075,16 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97" t="n">
-        <v>2.544241158585165</v>
+        <v>2.564986204422877</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3750680973524457</v>
+        <v>0.3850047765595764</v>
       </c>
       <c r="D97" t="n">
-        <v>0.4331710462345615</v>
+        <v>0.4190912329027134</v>
       </c>
       <c r="E97" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01261246054504164</v>
       </c>
     </row>
     <row r="98">
@@ -2092,16 +2092,16 @@
         <v>0.96</v>
       </c>
       <c r="B98" t="n">
-        <v>2.531017021604418</v>
+        <v>2.549728310231456</v>
       </c>
       <c r="C98" t="n">
-        <v>0.376787640106177</v>
+        <v>0.3860409311492339</v>
       </c>
       <c r="D98" t="n">
-        <v>0.4319099185568924</v>
+        <v>0.4188088126459688</v>
       </c>
       <c r="E98" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01235070209643804</v>
       </c>
     </row>
     <row r="99">
@@ -2109,16 +2109,16 @@
         <v>0.97</v>
       </c>
       <c r="B99" t="n">
-        <v>2.518561435092767</v>
+        <v>2.535335183512356</v>
       </c>
       <c r="C99" t="n">
-        <v>0.3785006446297389</v>
+        <v>0.3870795911805804</v>
       </c>
       <c r="D99" t="n">
-        <v>0.4306820407522996</v>
+        <v>0.4185332286741756</v>
       </c>
       <c r="E99" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01209190436376588</v>
       </c>
     </row>
     <row r="100">
@@ -2126,16 +2126,16 @@
         <v>0.98</v>
       </c>
       <c r="B100" t="n">
-        <v>2.506893988709524</v>
+        <v>2.521832845699004</v>
       </c>
       <c r="C100" t="n">
-        <v>0.3801986983218962</v>
+        <v>0.3881162870936989</v>
       </c>
       <c r="D100" t="n">
-        <v>0.4294955777200199</v>
+        <v>0.4182663653868972</v>
       </c>
       <c r="E100" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01183665948096892</v>
       </c>
     </row>
     <row r="101">
@@ -2143,16 +2143,16 @@
         <v>0.99</v>
       </c>
       <c r="B101" t="n">
-        <v>2.496034426827052</v>
+        <v>2.509247375206948</v>
       </c>
       <c r="C101" t="n">
-        <v>0.3818733885814134</v>
+        <v>0.3891465493286724</v>
       </c>
       <c r="D101" t="n">
-        <v>0.4283586116543094</v>
+        <v>0.4180101028150296</v>
       </c>
       <c r="E101" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01158555958199094</v>
       </c>
     </row>
     <row r="102">
@@ -2160,16 +2160,16 @@
         <v>1</v>
       </c>
       <c r="B102" t="n">
-        <v>2.486002728859157</v>
+        <v>2.497605026463053</v>
       </c>
       <c r="C102" t="n">
-        <v>0.3835163028070551</v>
+        <v>0.3901659083255839</v>
       </c>
       <c r="D102" t="n">
-        <v>0.4272791507824821</v>
+        <v>0.4177663170569995</v>
       </c>
       <c r="E102" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01133919680077574</v>
       </c>
     </row>
     <row r="103">
@@ -2177,16 +2177,16 @@
         <v>1.01</v>
       </c>
       <c r="B103" t="n">
-        <v>2.476819191980464</v>
+        <v>2.486932352728006</v>
       </c>
       <c r="C103" t="n">
-        <v>0.3851190283975858</v>
+        <v>0.3911698945245164</v>
       </c>
       <c r="D103" t="n">
-        <v>0.4262651396166803</v>
+        <v>0.4175368807993848</v>
       </c>
       <c r="E103" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01109816327126709</v>
       </c>
     </row>
     <row r="104">
@@ -2194,16 +2194,16 @@
         <v>1.02</v>
       </c>
       <c r="B104" t="n">
-        <v>2.468504516429154</v>
+        <v>2.477256333002776</v>
       </c>
       <c r="C104" t="n">
-        <v>0.3866731527517702</v>
+        <v>0.3921540383655532</v>
       </c>
       <c r="D104" t="n">
-        <v>0.4253244707024775</v>
+        <v>0.4173236639217463</v>
       </c>
       <c r="E104" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01086305112740877</v>
       </c>
     </row>
     <row r="105">
@@ -2211,16 +2211,16 @@
         <v>1.03</v>
       </c>
       <c r="B105" t="n">
-        <v>2.461079893611601</v>
+        <v>2.468604503359561</v>
       </c>
       <c r="C105" t="n">
-        <v>0.3881702632683729</v>
+        <v>0.3931138702887772</v>
       </c>
       <c r="D105" t="n">
-        <v>0.4244649978533158</v>
+        <v>0.4171285341855232</v>
       </c>
       <c r="E105" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01063445250314458</v>
       </c>
     </row>
     <row r="106">
@@ -2228,16 +2228,16 @@
         <v>1.04</v>
       </c>
       <c r="B106" t="n">
-        <v>2.454567097254944</v>
+        <v>2.461005093090202</v>
       </c>
       <c r="C106" t="n">
-        <v>0.3896019473461584</v>
+        <v>0.3940449207342714</v>
       </c>
       <c r="D106" t="n">
-        <v>0.4236945508664809</v>
+        <v>0.416953358006933</v>
       </c>
       <c r="E106" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01041295953241827</v>
       </c>
     </row>
     <row r="107">
@@ -2245,16 +2245,16 @@
         <v>1.05</v>
       </c>
       <c r="B107" t="n">
-        <v>2.448988577882719</v>
+        <v>2.454487166120529</v>
       </c>
       <c r="C107" t="n">
-        <v>0.3909597923838914</v>
+        <v>0.3949427201421188</v>
       </c>
       <c r="D107" t="n">
-        <v>0.4230209517238089</v>
+        <v>0.4168000013139035</v>
       </c>
       <c r="E107" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.01019916434917363</v>
       </c>
     </row>
     <row r="108">
@@ -2262,16 +2262,16 @@
         <v>1.06</v>
       </c>
       <c r="B108" t="n">
-        <v>2.444367560919439</v>
+        <v>2.449080768197968</v>
       </c>
       <c r="C108" t="n">
-        <v>0.3922353857803365</v>
+        <v>0.3958027989524027</v>
       </c>
       <c r="D108" t="n">
-        <v>0.4224520322886104</v>
+        <v>0.4166703304871716</v>
       </c>
       <c r="E108" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.009993659087354461</v>
       </c>
     </row>
     <row r="109">
@@ -2279,16 +2279,16 @@
         <v>1.07</v>
       </c>
       <c r="B109" t="n">
-        <v>2.440728148762789</v>
+        <v>2.444817080422512</v>
       </c>
       <c r="C109" t="n">
-        <v>0.3934203149342581</v>
+        <v>0.3966206876052059</v>
       </c>
       <c r="D109" t="n">
-        <v>0.4219956535194183</v>
+        <v>0.4165662133857939</v>
       </c>
       <c r="E109" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.009797035880904522</v>
       </c>
     </row>
     <row r="110">
@@ -2296,16 +2296,16 @@
         <v>1.08</v>
       </c>
       <c r="B110" t="n">
-        <v>2.438095427197044</v>
+        <v>2.441728579758304</v>
       </c>
       <c r="C110" t="n">
-        <v>0.3945061672444209</v>
+        <v>0.3973919165406115</v>
       </c>
       <c r="D110" t="n">
-        <v>0.4216597262311244</v>
+        <v>0.4164895204574424</v>
       </c>
       <c r="E110" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.009609886863767606</v>
       </c>
     </row>
     <row r="111">
@@ -2313,16 +2313,16 @@
         <v>1.09</v>
       </c>
       <c r="B111" t="n">
-        <v>2.436495576558712</v>
+        <v>2.439849207235275</v>
       </c>
       <c r="C111" t="n">
-        <v>0.3954845301095897</v>
+        <v>0.3981120161987026</v>
       </c>
       <c r="D111" t="n">
-        <v>0.4214522334449192</v>
+        <v>0.4164421259339888</v>
       </c>
       <c r="E111" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.009432804169887489</v>
       </c>
     </row>
     <row r="112">
@@ -2330,16 +2330,16 @@
         <v>1.1</v>
       </c>
       <c r="B112" t="n">
-        <v>2.435955988105618</v>
+        <v>2.439214544628072</v>
       </c>
       <c r="C112" t="n">
-        <v>0.3963469909285288</v>
+        <v>0.3987765170195623</v>
       </c>
       <c r="D112" t="n">
-        <v>0.4213812543802276</v>
+        <v>0.4164259091130328</v>
       </c>
       <c r="E112" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.009266379933207952</v>
       </c>
     </row>
     <row r="113">
@@ -2347,16 +2347,16 @@
         <v>1.11</v>
       </c>
       <c r="B113" t="n">
-        <v>2.436191399168916</v>
+        <v>2.439447143223756</v>
       </c>
       <c r="C113" t="n">
-        <v>0.3971506334605505</v>
+        <v>0.3994178701843819</v>
       </c>
       <c r="D113" t="n">
-        <v>0.4213838390650352</v>
+        <v>0.4164301412721976</v>
       </c>
       <c r="E113" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.009104854637196456</v>
       </c>
     </row>
     <row r="114">
@@ -2364,16 +2364,16 @@
         <v>1.12</v>
       </c>
       <c r="B114" t="n">
-        <v>2.436885039674825</v>
+        <v>2.440132495038688</v>
       </c>
       <c r="C114" t="n">
-        <v>0.3979576118121385</v>
+        <v>0.4000708312441332</v>
       </c>
       <c r="D114" t="n">
-        <v>0.4213915596925535</v>
+        <v>0.4164427666543455</v>
       </c>
       <c r="E114" t="n">
-        <v>9.999999999999998e-05</v>
+        <v>0.008942194908937101</v>
       </c>
     </row>
     <row r="115">
@@ -2381,16 +2381,16 @@
         <v>1.13</v>
       </c>
       <c r="B115" t="n">
-        <v>2.43801819833399</v>
+        <v>2.44125210739633</v>
       </c>
       <c r="C115" t="n">
-        <v>0.3987671189028147</v>
+        <v>0.40073438719357</v>
       </c>
       <c r="D115" t="n">
-        <v>0.4214043662605134</v>
+        <v>0.4164636789873694</v>
       </c>
       <c r="E115" t="n">
-        <v>9.999999999999996e-05</v>
+        <v>0.008778582097798629</v>
       </c>
     </row>
     <row r="116">
@@ -2398,16 +2398,16 @@
         <v>1.14</v>
       </c>
       <c r="B116" t="n">
-        <v>2.439572373201446</v>
+        <v>2.442787691713411</v>
       </c>
       <c r="C116" t="n">
-        <v>0.399578347652101</v>
+        <v>0.401407525027446</v>
       </c>
       <c r="D116" t="n">
-        <v>0.421422208945906</v>
+        <v>0.416492772476669</v>
       </c>
       <c r="E116" t="n">
-        <v>9.999999999999995e-05</v>
+        <v>0.008614197553149782</v>
       </c>
     </row>
     <row r="117">
@@ -2415,16 +2415,16 @@
         <v>1.15</v>
       </c>
       <c r="B117" t="n">
-        <v>2.4415292384842</v>
+        <v>2.444721131133204</v>
       </c>
       <c r="C117" t="n">
-        <v>0.4003904909795193</v>
+        <v>0.4020892317405149</v>
       </c>
       <c r="D117" t="n">
-        <v>0.4214450380989714</v>
+        <v>0.4165299417841107</v>
       </c>
       <c r="E117" t="n">
-        <v>9.999999999999994e-05</v>
+        <v>0.008449222624359305</v>
       </c>
     </row>
     <row r="118">
@@ -2432,16 +2432,16 @@
         <v>1.16</v>
       </c>
       <c r="B118" t="n">
-        <v>2.443870612926461</v>
+        <v>2.447034449695871</v>
       </c>
       <c r="C118" t="n">
-        <v>0.4012027418045913</v>
+        <v>0.4027784943275304</v>
       </c>
       <c r="D118" t="n">
-        <v>0.4214728042372564</v>
+        <v>0.4165750820073011</v>
       </c>
       <c r="E118" t="n">
-        <v>9.999999999999992e-05</v>
+        <v>0.008283838660795939</v>
       </c>
     </row>
     <row r="119">
@@ -2449,16 +2449,16 @@
         <v>1.17</v>
       </c>
       <c r="B119" t="n">
-        <v>2.446578429722678</v>
+        <v>2.449709782997879</v>
       </c>
       <c r="C119" t="n">
-        <v>0.4020142930468393</v>
+        <v>0.4034742997832464</v>
       </c>
       <c r="D119" t="n">
-        <v>0.4215054580397415</v>
+        <v>0.4166280886591731</v>
       </c>
       <c r="E119" t="n">
-        <v>9.999999999999988e-05</v>
+        <v>0.008118227011828424</v>
       </c>
     </row>
     <row r="120">
@@ -2466,16 +2466,16 @@
         <v>1.18</v>
       </c>
       <c r="B120" t="n">
-        <v>2.449634707915295</v>
+        <v>2.452729350299067</v>
       </c>
       <c r="C120" t="n">
-        <v>0.4028243376257848</v>
+        <v>0.4041756351024165</v>
       </c>
       <c r="D120" t="n">
-        <v>0.4215429503410357</v>
+        <v>0.4166888576478776</v>
       </c>
       <c r="E120" t="n">
-        <v>9.999999999999986e-05</v>
+        <v>0.007952569026825503</v>
       </c>
     </row>
     <row r="121">
@@ -2483,16 +2483,16 @@
         <v>1.19</v>
       </c>
       <c r="B121" t="n">
-        <v>2.453021525240603</v>
+        <v>2.45607542804211</v>
       </c>
       <c r="C121" t="n">
-        <v>0.4036320684609499</v>
+        <v>0.4048814872797944</v>
       </c>
       <c r="D121" t="n">
-        <v>0.4215852321256381</v>
+        <v>0.4167572852569792</v>
       </c>
       <c r="E121" t="n">
-        <v>9.999999999999983e-05</v>
+        <v>0.007787046055155921</v>
       </c>
     </row>
     <row r="122">
@@ -2500,16 +2500,16 @@
         <v>1.2</v>
       </c>
       <c r="B122" t="n">
-        <v>2.45672099239212</v>
+        <v>2.459730324754979</v>
       </c>
       <c r="C122" t="n">
-        <v>0.4044366784718565</v>
+        <v>0.4055908433101339</v>
       </c>
       <c r="D122" t="n">
-        <v>0.4216322545222673</v>
+        <v>0.4168332681259499</v>
       </c>
       <c r="E122" t="n">
-        <v>9.999999999999977e-05</v>
+        <v>0.007621839446188417</v>
       </c>
     </row>
     <row r="123">
@@ -2517,16 +2517,16 @@
         <v>1.21</v>
       </c>
       <c r="B123" t="n">
-        <v>2.460715228676646</v>
+        <v>2.463676357312488</v>
       </c>
       <c r="C123" t="n">
-        <v>0.4052373605780263</v>
+        <v>0.4063026901881888</v>
       </c>
       <c r="D123" t="n">
-        <v>0.4216839687982561</v>
+        <v>0.4169167032309599</v>
       </c>
       <c r="E123" t="n">
-        <v>9.999999999999975e-05</v>
+        <v>0.007457130549291736</v>
       </c>
     </row>
     <row r="124">
@@ -2534,16 +2534,16 @@
         <v>1.22</v>
       </c>
       <c r="B124" t="n">
-        <v>2.464986339043525</v>
+        <v>2.467895828538206</v>
       </c>
       <c r="C124" t="n">
-        <v>0.4060333076989815</v>
+        <v>0.4070160149087126</v>
       </c>
       <c r="D124" t="n">
-        <v>0.4217403263540117</v>
+        <v>0.4170074878659596</v>
       </c>
       <c r="E124" t="n">
-        <v>9.999999999999969e-05</v>
+        <v>0.007293100713834622</v>
       </c>
     </row>
     <row r="125">
@@ -2551,16 +2551,16 @@
         <v>1.23</v>
       </c>
       <c r="B125" t="n">
-        <v>2.469516392472738</v>
+        <v>2.47237100613291</v>
       </c>
       <c r="C125" t="n">
-        <v>0.4068237127542438</v>
+        <v>0.4077298044664592</v>
       </c>
       <c r="D125" t="n">
-        <v>0.4218012787175411</v>
+        <v>0.417105519624052</v>
       </c>
       <c r="E125" t="n">
-        <v>9.999999999999965e-05</v>
+        <v>0.007129931289185815</v>
       </c>
     </row>
     <row r="126">
@@ -2568,16 +2568,16 @@
         <v>1.24</v>
       </c>
       <c r="B126" t="n">
-        <v>2.474287401712214</v>
+        <v>2.477084102920341</v>
       </c>
       <c r="C126" t="n">
-        <v>0.4076077686633351</v>
+        <v>0.4084430458561823</v>
       </c>
       <c r="D126" t="n">
-        <v>0.4218667775390402</v>
+        <v>0.4172106963791502</v>
       </c>
       <c r="E126" t="n">
-        <v>9.99999999999996e-05</v>
+        <v>0.006967803624714058</v>
       </c>
     </row>
     <row r="127">
@@ -2585,16 +2585,16 @@
         <v>1.25</v>
       </c>
       <c r="B127" t="n">
-        <v>2.479281304359199</v>
+        <v>2.482017258405299</v>
       </c>
       <c r="C127" t="n">
-        <v>0.4083846683457774</v>
+        <v>0.4091547260726356</v>
       </c>
       <c r="D127" t="n">
-        <v>0.4219367745855471</v>
+        <v>0.4173229162679182</v>
       </c>
       <c r="E127" t="n">
-        <v>9.999999999999956e-05</v>
+        <v>0.006806899069788093</v>
       </c>
     </row>
     <row r="128">
@@ -2602,16 +2602,16 @@
         <v>1.26</v>
       </c>
       <c r="B128" t="n">
-        <v>2.484479945284721</v>
+        <v>2.487152521643182</v>
       </c>
       <c r="C128" t="n">
-        <v>0.4091536047210924</v>
+        <v>0.4098638321105729</v>
       </c>
       <c r="D128" t="n">
-        <v>0.4220112217356581</v>
+        <v>0.417442077671992</v>
       </c>
       <c r="E128" t="n">
-        <v>9.999999999999952e-05</v>
+        <v>0.006647398973776663</v>
       </c>
     </row>
     <row r="129">
@@ -2619,16 +2619,16 @@
         <v>1.27</v>
       </c>
       <c r="B129" t="n">
-        <v>2.489865060404071</v>
+        <v>2.492471835423771</v>
       </c>
       <c r="C129" t="n">
-        <v>0.4099137707088021</v>
+        <v>0.4105693509647479</v>
       </c>
       <c r="D129" t="n">
-        <v>0.4220900709743067</v>
+        <v>0.4175680792004783</v>
       </c>
       <c r="E129" t="n">
-        <v>9.999999999999946e-05</v>
+        <v>0.00648948468604851</v>
       </c>
     </row>
     <row r="130">
@@ -2636,16 +2636,16 @@
         <v>1.28</v>
       </c>
       <c r="B130" t="n">
-        <v>2.495418261799819</v>
+        <v>2.497957021775549</v>
       </c>
       <c r="C130" t="n">
-        <v>0.4106643592284284</v>
+        <v>0.4112702696299142</v>
       </c>
       <c r="D130" t="n">
-        <v>0.422173274387604</v>
+        <v>0.4177008196727281</v>
       </c>
       <c r="E130" t="n">
-        <v>9.999999999999939e-05</v>
+        <v>0.006333337555972377</v>
       </c>
     </row>
     <row r="131">
@@ -2653,16 +2653,16 @@
         <v>1.29</v>
       </c>
       <c r="B131" t="n">
-        <v>2.501121024207197</v>
+        <v>2.503589768800044</v>
       </c>
       <c r="C131" t="n">
-        <v>0.4114045631994932</v>
+        <v>0.4119655751008257</v>
       </c>
       <c r="D131" t="n">
-        <v>0.4222607841577413</v>
+        <v>0.417840198101382</v>
       </c>
       <c r="E131" t="n">
-        <v>9.999999999999934e-05</v>
+        <v>0.006179138932917007</v>
       </c>
     </row>
     <row r="132">
@@ -2670,16 +2670,16 @@
         <v>1.3</v>
       </c>
       <c r="B132" t="n">
-        <v>2.506954672874741</v>
+        <v>2.50935161884857</v>
       </c>
       <c r="C132" t="n">
-        <v>0.4121335755415184</v>
+        <v>0.4126542543722361</v>
       </c>
       <c r="D132" t="n">
-        <v>0.4223525525579535</v>
+        <v>0.4179861136756869</v>
       </c>
       <c r="E132" t="n">
-        <v>9.999999999999929e-05</v>
+        <v>0.006027070166251142</v>
       </c>
     </row>
     <row r="133">
@@ -2687,16 +2687,16 @@
         <v>1.31</v>
       </c>
       <c r="B133" t="n">
-        <v>2.512900372815782</v>
+        <v>2.515223958056407</v>
       </c>
       <c r="C133" t="n">
-        <v>0.4128505891740259</v>
+        <v>0.413335294438899</v>
       </c>
       <c r="D133" t="n">
-        <v>0.4224485319475434</v>
+        <v>0.4181384657450798</v>
       </c>
       <c r="E133" t="n">
-        <v>9.999999999999923e-05</v>
+        <v>0.005877312605343525</v>
       </c>
     </row>
     <row r="134">
@@ -2704,16 +2704,16 @@
         <v>1.32</v>
       </c>
       <c r="B134" t="n">
-        <v>2.518939119468876</v>
+        <v>2.521188007251826</v>
       </c>
       <c r="C134" t="n">
-        <v>0.4135547970165376</v>
+        <v>0.4140076822955682</v>
       </c>
       <c r="D134" t="n">
-        <v>0.4225486747669658</v>
+        <v>0.4182971538030372</v>
       </c>
       <c r="E134" t="n">
-        <v>9.999999999999916e-05</v>
+        <v>0.005730047599562896</v>
       </c>
     </row>
     <row r="135">
@@ -2721,16 +2721,16 @@
         <v>1.33</v>
       </c>
       <c r="B135" t="n">
-        <v>2.525051730787403</v>
+        <v>2.527224814259395</v>
       </c>
       <c r="C135" t="n">
-        <v>0.4142453919885754</v>
+        <v>0.4146704049369976</v>
       </c>
       <c r="D135" t="n">
-        <v>0.4226529335329711</v>
+        <v>0.4184620774711889</v>
       </c>
       <c r="E135" t="n">
-        <v>9.999999999999911e-05</v>
+        <v>0.005585456498278</v>
       </c>
     </row>
     <row r="136">
@@ -2738,16 +2738,16 @@
         <v>1.34</v>
       </c>
       <c r="B136" t="n">
-        <v>2.531218840780413</v>
+        <v>2.533315247618854</v>
       </c>
       <c r="C136" t="n">
-        <v>0.414921567009661</v>
+        <v>0.4153224493579407</v>
       </c>
       <c r="D136" t="n">
-        <v>0.4227612608338092</v>
+        <v>0.4186331364836932</v>
       </c>
       <c r="E136" t="n">
-        <v>9.999999999999906e-05</v>
+        <v>0.005443720650857579</v>
       </c>
     </row>
     <row r="137">
@@ -2755,16 +2755,16 @@
         <v>1.35</v>
       </c>
       <c r="B137" t="n">
-        <v>2.537420894528383</v>
+        <v>2.539439991742278</v>
       </c>
       <c r="C137" t="n">
-        <v>0.4155825149993165</v>
+        <v>0.4159628025531513</v>
       </c>
       <c r="D137" t="n">
-        <v>0.4228736093244917</v>
+        <v>0.4188102306718727</v>
       </c>
       <c r="E137" t="n">
-        <v>9.999999999999899e-05</v>
+        <v>0.005305021406670376</v>
       </c>
     </row>
     <row r="138">
@@ -2772,16 +2772,16 @@
         <v>1.36</v>
       </c>
       <c r="B138" t="n">
-        <v>2.543638144698753</v>
+        <v>2.545579543533486</v>
       </c>
       <c r="C138" t="n">
-        <v>0.4162274288770639</v>
+        <v>0.4165904515173831</v>
       </c>
       <c r="D138" t="n">
-        <v>0.4229899317221121</v>
+        <v>0.4189932599491082</v>
       </c>
       <c r="E138" t="n">
-        <v>9.999999999999893e-05</v>
+        <v>0.005169540115085132</v>
       </c>
     </row>
     <row r="139">
@@ -2789,16 +2789,16 @@
         <v>1.37</v>
       </c>
       <c r="B139" t="n">
-        <v>2.549850649587071</v>
+        <v>2.551714210494501</v>
       </c>
       <c r="C139" t="n">
-        <v>0.4168555015624248</v>
+        <v>0.4172043832453899</v>
       </c>
       <c r="D139" t="n">
-        <v>0.4231101808012256</v>
+        <v>0.4191821242959897</v>
       </c>
       <c r="E139" t="n">
-        <v>9.999999999999888e-05</v>
+        <v>0.005037458125470589</v>
       </c>
     </row>
     <row r="140">
@@ -2806,16 +2806,16 @@
         <v>1.38</v>
       </c>
       <c r="B140" t="n">
-        <v>2.556038272710136</v>
+        <v>2.55782411034446</v>
       </c>
       <c r="C140" t="n">
-        <v>0.4174659259749213</v>
+        <v>0.4178035847319254</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4232343093892851</v>
+        <v>0.4193767237457235</v>
       </c>
       <c r="E140" t="n">
-        <v>9.999999999999881e-05</v>
+        <v>0.004908956787195492</v>
       </c>
     </row>
     <row r="141">
@@ -2823,16 +2823,16 @@
         <v>1.39</v>
       </c>
       <c r="B141" t="n">
-        <v>2.562180683977804</v>
+        <v>2.563889172176612</v>
       </c>
       <c r="C141" t="n">
-        <v>0.4180578950340751</v>
+        <v>0.4183870429717432</v>
       </c>
       <c r="D141" t="n">
-        <v>0.423362270362136</v>
+        <v>0.4195769583697921</v>
       </c>
       <c r="E141" t="n">
-        <v>9.999999999999876e-05</v>
+        <v>0.004784217449628582</v>
       </c>
     </row>
     <row r="142">
@@ -2840,16 +2840,16 @@
         <v>1.4</v>
       </c>
       <c r="B142" t="n">
-        <v>2.568257362470037</v>
+        <v>2.569889139178938</v>
       </c>
       <c r="C142" t="n">
-        <v>0.4186306016594084</v>
+        <v>0.4189537449595973</v>
       </c>
       <c r="D142" t="n">
-        <v>0.4234940166395675</v>
+        <v>0.4197827282638689</v>
       </c>
       <c r="E142" t="n">
-        <v>9.999999999999869e-05</v>
+        <v>0.004663421462138601</v>
       </c>
     </row>
     <row r="143">
@@ -2857,16 +2857,16 @@
         <v>1.41</v>
       </c>
       <c r="B143" t="n">
-        <v>2.57424760084534</v>
+        <v>2.575803572943531</v>
       </c>
       <c r="C143" t="n">
-        <v>0.4191832387704428</v>
+        <v>0.4195026776902412</v>
       </c>
       <c r="D143" t="n">
-        <v>0.4236295011809207</v>
+        <v>0.419993933533983</v>
       </c>
       <c r="E143" t="n">
-        <v>9.999999999999864e-05</v>
+        <v>0.004546750174094295</v>
       </c>
     </row>
     <row r="144">
@@ -2874,16 +2874,16 @@
         <v>1.42</v>
       </c>
       <c r="B144" t="n">
-        <v>2.580130511405912</v>
+        <v>2.581611859389096</v>
       </c>
       <c r="C144" t="n">
-        <v>0.4197149992867004</v>
+        <v>0.4200328281584288</v>
       </c>
       <c r="D144" t="n">
-        <v>0.4237686769807541</v>
+        <v>0.4202104742829361</v>
       </c>
       <c r="E144" t="n">
-        <v>9.999999999999858e-05</v>
+        <v>0.004434384934864401</v>
       </c>
     </row>
     <row r="145">
@@ -2891,16 +2891,16 @@
         <v>1.43</v>
       </c>
       <c r="B145" t="n">
-        <v>2.585885033843696</v>
+        <v>2.587293216319776</v>
       </c>
       <c r="C145" t="n">
-        <v>0.420225076127703</v>
+        <v>0.4205431833589136</v>
       </c>
       <c r="D145" t="n">
-        <v>0.4239114970645639</v>
+        <v>0.4204322505969686</v>
       </c>
       <c r="E145" t="n">
-        <v>9.999999999999853e-05</v>
+        <v>0.004326507093817664</v>
       </c>
     </row>
     <row r="146">
@@ -2908,16 +2908,16 @@
         <v>1.44</v>
       </c>
       <c r="B146" t="n">
-        <v>2.591489944689961</v>
+        <v>2.592826702642079</v>
       </c>
       <c r="C146" t="n">
-        <v>0.4207126622129724</v>
+        <v>0.4210327302864496</v>
       </c>
       <c r="D146" t="n">
-        <v>0.4240579144845619</v>
+        <v>0.4206591625326749</v>
       </c>
       <c r="E146" t="n">
-        <v>9.999999999999847e-05</v>
+        <v>0.004223298000322825</v>
       </c>
     </row>
     <row r="147">
@@ -2925,16 +2925,16 @@
         <v>1.45</v>
       </c>
       <c r="B147" t="n">
-        <v>2.59692386848911</v>
+        <v>2.598191229259768</v>
       </c>
       <c r="C147" t="n">
-        <v>0.4211769504620307</v>
+        <v>0.4215004559357903</v>
       </c>
       <c r="D147" t="n">
-        <v>0.424207882315508</v>
+        <v>0.4208911101041667</v>
       </c>
       <c r="E147" t="n">
-        <v>9.999999999999842e-05</v>
+        <v>0.00412493900374863</v>
       </c>
     </row>
     <row r="148">
@@ -2942,16 +2942,16 @@
         <v>1.46</v>
       </c>
       <c r="B148" t="n">
-        <v>2.602165290715118</v>
+        <v>2.603365571664405</v>
       </c>
       <c r="C148" t="n">
-        <v>0.4216171337943996</v>
+        <v>0.4219453473016896</v>
       </c>
       <c r="D148" t="n">
-        <v>0.4243613536505992</v>
+        <v>0.4211279932704846</v>
       </c>
       <c r="E148" t="n">
-        <v>9.999999999999836e-05</v>
+        <v>0.004031611453463819</v>
       </c>
     </row>
     <row r="149">
@@ -2959,16 +2959,16 @@
         <v>1.47</v>
       </c>
       <c r="B149" t="n">
-        <v>2.607192572446265</v>
+        <v>2.608328384236581</v>
       </c>
       <c r="C149" t="n">
-        <v>0.4220324051296012</v>
+        <v>0.4223663913789011</v>
       </c>
       <c r="D149" t="n">
-        <v>0.4245182815974128</v>
+        <v>0.4213697119232559</v>
       </c>
       <c r="E149" t="n">
-        <v>9.999999999999832e-05</v>
+        <v>0.003943496698837133</v>
       </c>
     </row>
     <row r="150">
@@ -2976,16 +2976,16 @@
         <v>1.48</v>
       </c>
       <c r="B150" t="n">
-        <v>2.611983966810751</v>
+        <v>2.613058216269922</v>
       </c>
       <c r="C150" t="n">
-        <v>0.4224219573871573</v>
+        <v>0.4227625751621785</v>
       </c>
       <c r="D150" t="n">
-        <v>0.4246786192739061</v>
+        <v>0.4216161658745995</v>
       </c>
       <c r="E150" t="n">
-        <v>9.999999999999828e-05</v>
+        <v>0.003860776089237319</v>
       </c>
     </row>
     <row r="151">
@@ -2993,16 +2993,16 @@
         <v>1.49</v>
       </c>
       <c r="B151" t="n">
-        <v>2.616517637212249</v>
+        <v>2.617533529726557</v>
       </c>
       <c r="C151" t="n">
-        <v>0.4227849834865896</v>
+        <v>0.4231328856462757</v>
       </c>
       <c r="D151" t="n">
-        <v>0.4248423198044696</v>
+        <v>0.4218672548452772</v>
       </c>
       <c r="E151" t="n">
-        <v>9.999999999999823e-05</v>
+        <v>0.003783630974033116</v>
       </c>
     </row>
     <row r="152">
@@ -3010,16 +3010,16 @@
         <v>1.5</v>
       </c>
       <c r="B152" t="n">
-        <v>2.620771677340542</v>
+        <v>2.621732718728994</v>
       </c>
       <c r="C152" t="n">
-        <v>0.4231206763474202</v>
+        <v>0.4234763098259464</v>
       </c>
       <c r="D152" t="n">
-        <v>0.4250093363160357</v>
+        <v>0.4221228784530897</v>
       </c>
       <c r="E152" t="n">
-        <v>9.99999999999982e-05</v>
+        <v>0.003712242702593266</v>
       </c>
     </row>
     <row r="153">
@@ -3027,16 +3027,16 @@
         <v>1.51</v>
       </c>
       <c r="B153" t="n">
-        <v>2.624724132968097</v>
+        <v>2.625634130789186</v>
       </c>
       <c r="C153" t="n">
-        <v>0.4234282288891711</v>
+        <v>0.4237918346959442</v>
       </c>
       <c r="D153" t="n">
-        <v>0.4251796219342422</v>
+        <v>0.4223829362015197</v>
       </c>
       <c r="E153" t="n">
-        <v>9.999999999999815e-05</v>
+        <v>0.003646792624286514</v>
       </c>
     </row>
     <row r="154">
@@ -3044,16 +3044,16 @@
         <v>1.52</v>
       </c>
       <c r="B154" t="n">
-        <v>2.628353025528675</v>
+        <v>2.629216089771059</v>
       </c>
       <c r="C154" t="n">
-        <v>0.4237068340313639</v>
+        <v>0.4240784472510228</v>
       </c>
       <c r="D154" t="n">
-        <v>0.4253531297796496</v>
+        <v>0.4226473274686193</v>
       </c>
       <c r="E154" t="n">
-        <v>9.999999999999812e-05</v>
+        <v>0.003587462088481601</v>
       </c>
     </row>
     <row r="155">
@@ -3061,16 +3061,16 @@
         <v>1.53</v>
       </c>
       <c r="B155" t="n">
-        <v>2.631636377469014</v>
+        <v>2.632456920577848</v>
       </c>
       <c r="C155" t="n">
-        <v>0.4239556846935207</v>
+        <v>0.4243351344859361</v>
       </c>
       <c r="D155" t="n">
-        <v>0.4255298129640127</v>
+        <v>0.4229159514961437</v>
       </c>
       <c r="E155" t="n">
-        <v>9.999999999999809e-05</v>
+        <v>0.003534432444547269</v>
       </c>
     </row>
     <row r="156">
@@ -3078,16 +3078,16 @@
         <v>1.54</v>
       </c>
       <c r="B156" t="n">
-        <v>2.634552239359065</v>
+        <v>2.635334975550306</v>
       </c>
       <c r="C156" t="n">
-        <v>0.4241739737951633</v>
+        <v>0.4245608833954378</v>
       </c>
       <c r="D156" t="n">
-        <v>0.4257096245866069</v>
+        <v>0.4231887073789292</v>
       </c>
       <c r="E156" t="n">
-        <v>9.999999999999807e-05</v>
+        <v>0.003487885041852262</v>
       </c>
     </row>
     <row r="157">
@@ -3095,16 +3095,16 @@
         <v>1.55</v>
       </c>
       <c r="B157" t="n">
-        <v>2.637078718740433</v>
+        <v>2.637828662556218</v>
       </c>
       <c r="C157" t="n">
-        <v>0.4243608942558137</v>
+        <v>0.4247546809742815</v>
       </c>
       <c r="D157" t="n">
-        <v>0.4258925177306082</v>
+        <v>0.423465494054518</v>
       </c>
       <c r="E157" t="n">
-        <v>9.999999999999804e-05</v>
+        <v>0.003448001229765322</v>
       </c>
     </row>
     <row r="158">
@@ -3112,16 +3112,16 @@
         <v>1.56</v>
       </c>
       <c r="B158" t="n">
-        <v>2.63919401068638</v>
+        <v>2.639916474745605</v>
       </c>
       <c r="C158" t="n">
-        <v>0.4245156389949937</v>
+        <v>0.4249155142172211</v>
       </c>
       <c r="D158" t="n">
-        <v>0.426078445459526</v>
+        <v>0.4237462102930274</v>
       </c>
       <c r="E158" t="n">
-        <v>9.999999999999801e-05</v>
+        <v>0.00341496235765519</v>
       </c>
     </row>
     <row r="159">
@@ -3129,16 +3129,16 @@
         <v>1.57</v>
       </c>
       <c r="B159" t="n">
-        <v>2.640876430040163</v>
+        <v>2.641577021939703</v>
       </c>
       <c r="C159" t="n">
-        <v>0.4246374009322252</v>
+        <v>0.4250423701190101</v>
       </c>
       <c r="D159" t="n">
-        <v>0.4262673608136925</v>
+        <v>0.4240307546872658</v>
       </c>
       <c r="E159" t="n">
-        <v>9.999999999999801e-05</v>
+        <v>0.00338894977489061</v>
       </c>
     </row>
     <row r="160">
@@ -3146,16 +3146,16 @@
         <v>1.58</v>
       </c>
       <c r="B160" t="n">
-        <v>2.642104445291504</v>
+        <v>2.64278906361508</v>
       </c>
       <c r="C160" t="n">
-        <v>0.4247253729870301</v>
+        <v>0.4251342356744025</v>
       </c>
       <c r="D160" t="n">
-        <v>0.4264592168068023</v>
+        <v>0.4243190256430938</v>
       </c>
       <c r="E160" t="n">
-        <v>9.9999999999998e-05</v>
+        <v>0.003370144830840325</v>
       </c>
     </row>
     <row r="161">
@@ -3163,16 +3163,16 @@
         <v>1.59</v>
       </c>
       <c r="B161" t="n">
-        <v>2.642856714043754</v>
+        <v>2.643531543437306</v>
       </c>
       <c r="C161" t="n">
-        <v>0.4247787480789303</v>
+        <v>0.4251900978781518</v>
       </c>
       <c r="D161" t="n">
-        <v>0.4266539664225082</v>
+        <v>0.4246109213700334</v>
       </c>
       <c r="E161" t="n">
-        <v>9.9999999999998e-05</v>
+        <v>0.003358728874873075</v>
       </c>
     </row>
     <row r="162">
@@ -3180,16 +3180,16 @@
         <v>1.6</v>
       </c>
       <c r="B162" t="n">
-        <v>2.643112120016701</v>
+        <v>2.64378362529128</v>
       </c>
       <c r="C162" t="n">
-        <v>0.4247967191274478</v>
+        <v>0.4252089437250119</v>
       </c>
       <c r="D162" t="n">
-        <v>0.4268515626110699</v>
+        <v>0.4249063398721223</v>
       </c>
       <c r="E162" t="n">
-        <v>9.999999999999799e-05</v>
+        <v>0.003354883256357605</v>
       </c>
     </row>
     <row r="163">
@@ -3197,16 +3197,16 @@
         <v>1.61</v>
       </c>
       <c r="B163" t="n">
-        <v>2.642897350657758</v>
+        <v>2.643566973760238</v>
       </c>
       <c r="C163" t="n">
-        <v>0.4247941142679862</v>
+        <v>0.4252064365620241</v>
       </c>
       <c r="D163" t="n">
-        <v>0.4270787633781793</v>
+        <v>0.4252279351674651</v>
       </c>
       <c r="E163" t="n">
-        <v>9.999999999999799e-05</v>
+        <v>0.003355261329972068</v>
       </c>
     </row>
     <row r="164">
@@ -3214,16 +3214,16 @@
         <v>1.62</v>
       </c>
       <c r="B164" t="n">
-        <v>2.642255837260807</v>
+        <v>2.64291987857634</v>
       </c>
       <c r="C164" t="n">
-        <v>0.4247861159193017</v>
+        <v>0.425198746155622</v>
       </c>
       <c r="D164" t="n">
-        <v>0.4273618691158179</v>
+        <v>0.4255980484429554</v>
       </c>
       <c r="E164" t="n">
-        <v>9.999999999999799e-05</v>
+        <v>0.003356437153434438</v>
       </c>
     </row>
     <row r="165">
@@ -3231,16 +3231,16 @@
         <v>1.63</v>
       </c>
       <c r="B165" t="n">
-        <v>2.641191923918608</v>
+        <v>2.641846783491508</v>
       </c>
       <c r="C165" t="n">
-        <v>0.4247724484259444</v>
+        <v>0.4251856191296476</v>
       </c>
       <c r="D165" t="n">
-        <v>0.427700161155298</v>
+        <v>0.4260161189718851</v>
       </c>
       <c r="E165" t="n">
-        <v>9.999999999999799e-05</v>
+        <v>0.003358473130673182</v>
       </c>
     </row>
     <row r="166">
@@ -3248,16 +3248,16 @@
         <v>1.64</v>
       </c>
       <c r="B166" t="n">
-        <v>2.639710152090641</v>
+        <v>2.64035233287378</v>
       </c>
       <c r="C166" t="n">
-        <v>0.4247528361324644</v>
+        <v>0.4251668021079432</v>
       </c>
       <c r="D166" t="n">
-        <v>0.4280929397979679</v>
+        <v>0.4264815996980305</v>
       </c>
       <c r="E166" t="n">
-        <v>9.9999999999998e-05</v>
+        <v>0.003361431665616772</v>
       </c>
     </row>
     <row r="167">
@@ -3265,16 +3265,16 @@
         <v>1.65</v>
       </c>
       <c r="B167" t="n">
-        <v>2.637815253784695</v>
+        <v>2.638441364674925</v>
       </c>
       <c r="C167" t="n">
-        <v>0.4247270033834121</v>
+        <v>0.4251420417143507</v>
       </c>
       <c r="D167" t="n">
-        <v>0.4285395233342196</v>
+        <v>0.4269939565443627</v>
       </c>
       <c r="E167" t="n">
-        <v>9.9999999999998e-05</v>
+        <v>0.003365375162193676</v>
       </c>
     </row>
     <row r="168">
@@ -3282,16 +3282,16 @@
         <v>1.66</v>
       </c>
       <c r="B168" t="n">
-        <v>2.635512144661603</v>
+        <v>2.636118903320932</v>
       </c>
       <c r="C168" t="n">
-        <v>0.4246946745233378</v>
+        <v>0.4251110845727122</v>
       </c>
       <c r="D168" t="n">
-        <v>0.4290392470864677</v>
+        <v>0.4275526677369206</v>
       </c>
       <c r="E168" t="n">
-        <v>9.9999999999998e-05</v>
+        <v>0.003370366024332364</v>
       </c>
     </row>
     <row r="169">
@@ -3299,16 +3299,16 @@
         <v>1.67</v>
       </c>
       <c r="B169" t="n">
-        <v>2.63280591707396</v>
+        <v>2.633390152536667</v>
       </c>
       <c r="C169" t="n">
-        <v>0.4246555738967915</v>
+        <v>0.4250736773068696</v>
       </c>
       <c r="D169" t="n">
-        <v>0.4295914624748885</v>
+        <v>0.4281572231431161</v>
       </c>
       <c r="E169" t="n">
-        <v>9.999999999999801e-05</v>
+        <v>0.003376466655961305</v>
       </c>
     </row>
     <row r="170">
@@ -3316,16 +3316,16 @@
         <v>1.68</v>
       </c>
       <c r="B170" t="n">
-        <v>2.629701833049514</v>
+        <v>2.630260488115788</v>
       </c>
       <c r="C170" t="n">
-        <v>0.4246094258483236</v>
+        <v>0.4250295665406653</v>
       </c>
       <c r="D170" t="n">
-        <v>0.4301955361047671</v>
+        <v>0.4288071236237685</v>
       </c>
       <c r="E170" t="n">
-        <v>9.999999999999801e-05</v>
+        <v>0.003383739461008969</v>
       </c>
     </row>
     <row r="171">
@@ -3333,16 +3333,16 @@
         <v>1.69</v>
       </c>
       <c r="B171" t="n">
-        <v>2.626205317229753</v>
+        <v>2.626735450646832</v>
       </c>
       <c r="C171" t="n">
-        <v>0.4245559547224841</v>
+        <v>0.424978498897941</v>
       </c>
       <c r="D171" t="n">
-        <v>0.4308508488743533</v>
+        <v>0.4295018803982003</v>
       </c>
       <c r="E171" t="n">
-        <v>9.999999999999803e-05</v>
+        <v>0.003392246843403824</v>
       </c>
     </row>
     <row r="172">
@@ -3350,16 +3350,16 @@
         <v>1.7</v>
       </c>
       <c r="B172" t="n">
-        <v>2.622321949774017</v>
+        <v>2.622820738206213</v>
       </c>
       <c r="C172" t="n">
-        <v>0.4244948848638235</v>
+        <v>0.424920221002539</v>
       </c>
       <c r="D172" t="n">
-        <v>0.4315567951021835</v>
+        <v>0.4302410144217546</v>
       </c>
       <c r="E172" t="n">
-        <v>9.999999999999803e-05</v>
+        <v>0.003402051207074341</v>
       </c>
     </row>
     <row r="173">
@@ -3367,16 +3367,16 @@
         <v>1.71</v>
       </c>
       <c r="B173" t="n">
-        <v>2.618057459239266</v>
+        <v>2.618522199028608</v>
       </c>
       <c r="C173" t="n">
-        <v>0.4244259406168919</v>
+        <v>0.4248544794783013</v>
       </c>
       <c r="D173" t="n">
-        <v>0.4323127816728714</v>
+        <v>0.4310240557751259</v>
       </c>
       <c r="E173" t="n">
-        <v>9.999999999999804e-05</v>
+        <v>0.00341321495594899</v>
       </c>
     </row>
     <row r="174">
@@ -3384,16 +3384,16 @@
         <v>1.72</v>
       </c>
       <c r="B174" t="n">
-        <v>2.613417715445419</v>
+        <v>2.613845824165028</v>
       </c>
       <c r="C174" t="n">
-        <v>0.4243488463262394</v>
+        <v>0.4247810209490699</v>
       </c>
       <c r="D174" t="n">
-        <v>0.4331182272004245</v>
+        <v>0.4318505430649216</v>
       </c>
       <c r="E174" t="n">
-        <v>9.999999999999805e-05</v>
+        <v>0.003425800493956238</v>
       </c>
     </row>
     <row r="175">
@@ -3401,16 +3401,16 @@
         <v>1.73</v>
       </c>
       <c r="B175" t="n">
-        <v>2.608408722335944</v>
+        <v>2.608797740138579</v>
       </c>
       <c r="C175" t="n">
-        <v>0.4242633263364163</v>
+        <v>0.424699592038687</v>
       </c>
       <c r="D175" t="n">
-        <v>0.4339725612081871</v>
+        <v>0.4327200228349037</v>
       </c>
       <c r="E175" t="n">
-        <v>9.999999999999807e-05</v>
+        <v>0.003439870225024557</v>
       </c>
     </row>
     <row r="176">
@@ -3418,16 +3418,16 @@
         <v>1.74</v>
       </c>
       <c r="B176" t="n">
-        <v>2.603036610843168</v>
+        <v>2.603384201607726</v>
       </c>
       <c r="C176" t="n">
-        <v>0.4241691049919729</v>
+        <v>0.4246099393709944</v>
       </c>
       <c r="D176" t="n">
-        <v>0.4348752233245564</v>
+        <v>0.4336320489873808</v>
       </c>
       <c r="E176" t="n">
-        <v>9.999999999999807e-05</v>
+        <v>0.003455486553082415</v>
       </c>
     </row>
     <row r="177">
@@ -3435,16 +3435,16 @@
         <v>1.75</v>
       </c>
       <c r="B177" t="n">
-        <v>2.597307631767482</v>
+        <v>2.597611584046532</v>
       </c>
       <c r="C177" t="n">
-        <v>0.4240659066374594</v>
+        <v>0.4245118095698345</v>
       </c>
       <c r="D177" t="n">
-        <v>0.4358256624936644</v>
+        <v>0.4345861822142507</v>
       </c>
       <c r="E177" t="n">
-        <v>9.999999999999808e-05</v>
+        <v>0.003472711882058281</v>
       </c>
     </row>
     <row r="178">
@@ -3452,16 +3452,16 @@
         <v>1.76</v>
       </c>
       <c r="B178" t="n">
-        <v>2.591228148679404</v>
+        <v>2.591486376451147</v>
       </c>
       <c r="C178" t="n">
-        <v>0.4239534556174259</v>
+        <v>0.4244049492590492</v>
       </c>
       <c r="D178" t="n">
-        <v>0.4368233362002565</v>
+        <v>0.4355819894372172</v>
       </c>
       <c r="E178" t="n">
-        <v>9.999999999999811e-05</v>
+        <v>0.003491608615880625</v>
       </c>
     </row>
     <row r="179">
@@ -3469,16 +3469,16 @@
         <v>1.77</v>
       </c>
       <c r="B179" t="n">
-        <v>2.584804630853152</v>
+        <v>2.585015174081469</v>
       </c>
       <c r="C179" t="n">
-        <v>0.4238314762764228</v>
+        <v>0.4242891050624805</v>
       </c>
       <c r="D179" t="n">
-        <v>0.4378677097080441</v>
+        <v>0.4366190432567297</v>
       </c>
       <c r="E179" t="n">
-        <v>9.999999999999813e-05</v>
+        <v>0.003512239158477917</v>
       </c>
     </row>
     <row r="180">
@@ -3486,16 +3486,16 @@
         <v>1.78</v>
       </c>
       <c r="B180" t="n">
-        <v>2.578043646240141</v>
+        <v>2.578204671246665</v>
       </c>
       <c r="C180" t="n">
-        <v>0.4236996929590001</v>
+        <v>0.4241640236039705</v>
       </c>
       <c r="D180" t="n">
-        <v>0.4389582553108428</v>
+        <v>0.4376969214092156</v>
       </c>
       <c r="E180" t="n">
-        <v>9.999999999999815e-05</v>
+        <v>0.003534665913778626</v>
       </c>
     </row>
     <row r="181">
@@ -3503,16 +3503,16 @@
         <v>1.79</v>
       </c>
       <c r="B181" t="n">
-        <v>2.570951854490499</v>
+        <v>2.57106165414289</v>
       </c>
       <c r="C181" t="n">
-        <v>0.4235578300097082</v>
+        <v>0.4240294515073614</v>
       </c>
       <c r="D181" t="n">
-        <v>0.4400944515958505</v>
+        <v>0.4388152062322013</v>
       </c>
       <c r="E181" t="n">
-        <v>9.999999999999816e-05</v>
+        <v>0.003558951285711221</v>
       </c>
     </row>
     <row r="182">
@@ -3520,16 +3520,16 @@
         <v>1.8</v>
       </c>
       <c r="B182" t="n">
-        <v>2.563536000030446</v>
+        <v>2.563592993751272</v>
       </c>
       <c r="C182" t="n">
-        <v>0.4234056117730973</v>
+        <v>0.423885135396495</v>
       </c>
       <c r="D182" t="n">
-        <v>0.4412757827184555</v>
+        <v>0.4399734841369374</v>
       </c>
       <c r="E182" t="n">
-        <v>9.999999999999818e-05</v>
+        <v>0.003585157678204173</v>
       </c>
     </row>
     <row r="183">
@@ -3537,16 +3537,16 @@
         <v>1.81</v>
       </c>
       <c r="B183" t="n">
-        <v>2.55580290520303</v>
+        <v>2.555805638803895</v>
       </c>
       <c r="C183" t="n">
-        <v>0.4232427625937175</v>
+        <v>0.4237308218952136</v>
       </c>
       <c r="D183" t="n">
-        <v>0.4425017376879995</v>
+        <v>0.441171345088168</v>
       </c>
       <c r="E183" t="n">
-        <v>9.99999999999982e-05</v>
+        <v>0.003613347495185949</v>
       </c>
     </row>
     <row r="184">
@@ -3554,16 +3554,16 @@
         <v>1.82</v>
       </c>
       <c r="B184" t="n">
-        <v>2.547759463479478</v>
+        <v>2.547706608825214</v>
       </c>
       <c r="C184" t="n">
-        <v>0.4230690068161191</v>
+        <v>0.4235662576273592</v>
       </c>
       <c r="D184" t="n">
-        <v>0.4437718096639605</v>
+        <v>0.4424083820907005</v>
       </c>
       <c r="E184" t="n">
-        <v>9.999999999999822e-05</v>
+        <v>0.00364358314058502</v>
       </c>
     </row>
     <row r="185">
@@ -3571,16 +3571,16 @@
         <v>1.83</v>
       </c>
       <c r="B185" t="n">
-        <v>2.539412632748059</v>
+        <v>2.539302987256001</v>
       </c>
       <c r="C185" t="n">
-        <v>0.4228840687848524</v>
+        <v>0.4233911892167737</v>
       </c>
       <c r="D185" t="n">
-        <v>0.445085495262048</v>
+        <v>0.4436841906824603</v>
       </c>
       <c r="E185" t="n">
-        <v>9.999999999999824e-05</v>
+        <v>0.003675927018329855</v>
       </c>
     </row>
     <row r="186">
@@ -3588,16 +3588,16 @@
         <v>1.84</v>
       </c>
       <c r="B186" t="n">
-        <v>2.530769428687081</v>
+        <v>2.530601914666592</v>
       </c>
       <c r="C186" t="n">
-        <v>0.4226876728444675</v>
+        <v>0.4232053632872995</v>
       </c>
       <c r="D186" t="n">
-        <v>0.4464422938697441</v>
+        <v>0.4449983684337264</v>
       </c>
       <c r="E186" t="n">
-        <v>9.999999999999827e-05</v>
+        <v>0.003710441532348924</v>
       </c>
     </row>
     <row r="187">
@@ -3605,16 +3605,16 @@
         <v>1.85</v>
       </c>
       <c r="B187" t="n">
-        <v>2.521836918228317</v>
+        <v>2.521610582065902</v>
       </c>
       <c r="C187" t="n">
-        <v>0.4224795433395147</v>
+        <v>0.4230085264627783</v>
       </c>
       <c r="D187" t="n">
-        <v>0.4478417069708521</v>
+        <v>0.4463505144522723</v>
       </c>
       <c r="E187" t="n">
-        <v>9.99999999999983e-05</v>
+        <v>0.003747189086570696</v>
       </c>
     </row>
     <row r="188">
@@ -3622,16 +3622,16 @@
         <v>1.86</v>
       </c>
       <c r="B188" t="n">
-        <v>2.512622213116861</v>
+        <v>2.512336224312322</v>
       </c>
       <c r="C188" t="n">
-        <v>0.4222594046145441</v>
+        <v>0.4228004253670524</v>
       </c>
       <c r="D188" t="n">
-        <v>0.4492832374786463</v>
+        <v>0.4477402288941469</v>
       </c>
       <c r="E188" t="n">
-        <v>9.999999999999831e-05</v>
+        <v>0.00378623208492364</v>
       </c>
     </row>
     <row r="189">
@@ -3639,16 +3639,16 @@
         <v>1.87</v>
       </c>
       <c r="B189" t="n">
-        <v>2.503132463573067</v>
+        <v>2.50278611363229</v>
       </c>
       <c r="C189" t="n">
-        <v>0.4220269810141061</v>
+        <v>0.4225808066239637</v>
       </c>
       <c r="D189" t="n">
-        <v>0.4507663890772525</v>
+        <v>0.4491671124798596</v>
       </c>
       <c r="E189" t="n">
-        <v>9.999999999999835e-05</v>
+        <v>0.003827632931336227</v>
       </c>
     </row>
     <row r="190">
@@ -3656,16 +3656,16 @@
         <v>1.88</v>
       </c>
       <c r="B190" t="n">
-        <v>2.493374852061952</v>
+        <v>2.49296755325201</v>
       </c>
       <c r="C190" t="n">
-        <v>0.4217819968827508</v>
+        <v>0.4223494168573544</v>
       </c>
       <c r="D190" t="n">
-        <v>0.4522906655709136</v>
+        <v>0.450630766015741</v>
       </c>
       <c r="E190" t="n">
-        <v>9.999999999999838e-05</v>
+        <v>0.003871454029736924</v>
       </c>
     </row>
     <row r="191">
@@ -3673,16 +3673,16 @@
         <v>1.89</v>
       </c>
       <c r="B191" t="n">
-        <v>2.483356587175094</v>
+        <v>2.482887871147441</v>
       </c>
       <c r="C191" t="n">
-        <v>0.4215241765650284</v>
+        <v>0.4221060026910665</v>
       </c>
       <c r="D191" t="n">
-        <v>0.4538555702408301</v>
+        <v>0.4521307899202794</v>
       </c>
       <c r="E191" t="n">
-        <v>9.999999999999841e-05</v>
+        <v>0.003917757784054202</v>
       </c>
     </row>
     <row r="192">
@@ -3690,16 +3690,16 @@
         <v>1.9</v>
       </c>
       <c r="B192" t="n">
-        <v>2.473084897629776</v>
+        <v>2.472554413917373</v>
       </c>
       <c r="C192" t="n">
-        <v>0.4212532444054891</v>
+        <v>0.421850310748942</v>
       </c>
       <c r="D192" t="n">
-        <v>0.4554606052092919</v>
+        <v>0.4536667837552445</v>
       </c>
       <c r="E192" t="n">
-        <v>9.999999999999845e-05</v>
+        <v>0.00396660659821653</v>
       </c>
     </row>
     <row r="193">
@@ -3707,16 +3707,16 @@
         <v>1.91</v>
       </c>
       <c r="B193" t="n">
-        <v>2.462567026389766</v>
+        <v>2.461974540784065</v>
       </c>
       <c r="C193" t="n">
-        <v>0.4209689247486832</v>
+        <v>0.4215820876548231</v>
       </c>
       <c r="D193" t="n">
-        <v>0.4571052708108482</v>
+        <v>0.4552383457614289</v>
       </c>
       <c r="E193" t="n">
-        <v>9.999999999999847e-05</v>
+        <v>0.004018062876152378</v>
       </c>
     </row>
     <row r="194">
@@ -3724,16 +3724,16 @@
         <v>1.92</v>
       </c>
       <c r="B194" t="n">
-        <v>2.451810224911882</v>
+        <v>2.451155617725605</v>
       </c>
       <c r="C194" t="n">
-        <v>0.420670941939161</v>
+        <v>0.4213010800325518</v>
       </c>
       <c r="D194" t="n">
-        <v>0.4587890649702912</v>
+        <v>0.4568450723988594</v>
       </c>
       <c r="E194" t="n">
-        <v>9.99999999999985e-05</v>
+        <v>0.004072189021790214</v>
       </c>
     </row>
     <row r="195">
@@ -3741,16 +3741,16 @@
         <v>1.93</v>
       </c>
       <c r="B195" t="n">
-        <v>2.440821747522116</v>
+        <v>2.440105011743828</v>
       </c>
       <c r="C195" t="n">
-        <v>0.4203590203214727</v>
+        <v>0.4210070345059702</v>
       </c>
       <c r="D195" t="n">
-        <v>0.460511482587257</v>
+        <v>0.4584865578913412</v>
       </c>
       <c r="E195" t="n">
-        <v>9.999999999999854e-05</v>
+        <v>0.004129047439058509</v>
       </c>
     </row>
     <row r="196">
@@ -3758,16 +3758,16 @@
         <v>1.94</v>
       </c>
       <c r="B196" t="n">
-        <v>2.429608845924835</v>
+        <v>2.4288300852713</v>
       </c>
       <c r="C196" t="n">
-        <v>0.4200328842401683</v>
+        <v>0.4206996976989202</v>
       </c>
       <c r="D196" t="n">
-        <v>0.4622720149272763</v>
+        <v>0.4601623937752198</v>
       </c>
       <c r="E196" t="n">
-        <v>9.999999999999857e-05</v>
+        <v>0.004188700531885733</v>
       </c>
     </row>
     <row r="197">
@@ -3775,16 +3775,16 @@
         <v>1.95</v>
       </c>
       <c r="B197" t="n">
-        <v>2.418178763848249</v>
+        <v>2.417338190720599</v>
       </c>
       <c r="C197" t="n">
-        <v>0.4196922580397981</v>
+        <v>0.420378816235244</v>
       </c>
       <c r="D197" t="n">
-        <v>0.4640701490191339</v>
+        <v>0.4618721684522606</v>
       </c>
       <c r="E197" t="n">
-        <v>9.999999999999861e-05</v>
+        <v>0.004251210704200353</v>
       </c>
     </row>
     <row r="198">
@@ -3792,16 +3792,16 @@
         <v>1.96</v>
       </c>
       <c r="B198" t="n">
-        <v>2.406538731829055</v>
+        <v>2.405636665178756</v>
       </c>
       <c r="C198" t="n">
-        <v>0.4193368660649125</v>
+        <v>0.4200441367387837</v>
       </c>
       <c r="D198" t="n">
-        <v>0.465905367058423</v>
+        <v>0.4636154667465639</v>
       </c>
       <c r="E198" t="n">
-        <v>9.999999999999865e-05</v>
+        <v>0.00431664035993084</v>
       </c>
     </row>
     <row r="199">
@@ -3809,16 +3809,16 @@
         <v>1.97</v>
       </c>
       <c r="B199" t="n">
-        <v>2.394695962138862</v>
+        <v>2.393732825249473</v>
       </c>
       <c r="C199" t="n">
-        <v>0.4189664326600616</v>
+        <v>0.4196954058333813</v>
       </c>
       <c r="D199" t="n">
-        <v>0.4677771458172101</v>
+        <v>0.4653918694654467</v>
       </c>
       <c r="E199" t="n">
-        <v>9.999999999999869e-05</v>
+        <v>0.004385051903005663</v>
       </c>
     </row>
     <row r="200">
@@ -3826,16 +3826,16 @@
         <v>1.98</v>
       </c>
       <c r="B200" t="n">
-        <v>2.382657643854737</v>
+        <v>2.381633962045411</v>
       </c>
       <c r="C200" t="n">
-        <v>0.4185806821697956</v>
+        <v>0.4193323701428788</v>
       </c>
       <c r="D200" t="n">
-        <v>0.4696849560597493</v>
+        <v>0.4672009529642441</v>
       </c>
       <c r="E200" t="n">
-        <v>9.999999999999873e-05</v>
+        <v>0.004456507737353293</v>
       </c>
     </row>
     <row r="201">
@@ -3843,16 +3843,16 @@
         <v>1.99</v>
       </c>
       <c r="B201" t="n">
-        <v>2.37043093807589</v>
+        <v>2.369347336332535</v>
       </c>
       <c r="C201" t="n">
-        <v>0.4181793389386647</v>
+        <v>0.4189547762911184</v>
       </c>
       <c r="D201" t="n">
-        <v>0.4716282619642142</v>
+        <v>0.4690422887149937</v>
       </c>
       <c r="E201" t="n">
-        <v>9.999999999999877e-05</v>
+        <v>0.004531070266902196</v>
       </c>
     </row>
     <row r="202">
@@ -3860,16 +3860,16 @@
         <v>2</v>
       </c>
       <c r="B202" t="n">
-        <v>2.358022973288299</v>
+        <v>2.356880173828251</v>
       </c>
       <c r="C202" t="n">
-        <v>0.4177621273112193</v>
+        <v>0.4185623709019421</v>
       </c>
       <c r="D202" t="n">
-        <v>0.4736065205504393</v>
+        <v>0.4709154428789876</v>
       </c>
       <c r="E202" t="n">
-        <v>9.999999999999883e-05</v>
+        <v>0.004608801895580846</v>
       </c>
     </row>
     <row r="203">
@@ -3877,16 +3877,16 @@
         <v>2.01</v>
       </c>
       <c r="B203" t="n">
-        <v>2.345440840878745</v>
+        <v>2.344239660654758</v>
       </c>
       <c r="C203" t="n">
-        <v>0.4173287716320093</v>
+        <v>0.4181549005991919</v>
       </c>
       <c r="D203" t="n">
-        <v>0.4756191811136922</v>
+        <v>0.4728199758831882</v>
       </c>
       <c r="E203" t="n">
-        <v>9.999999999999885e-05</v>
+        <v>0.004689765027317709</v>
       </c>
     </row>
     <row r="204">
@@ -3894,16 +3894,16 @@
         <v>2.02</v>
       </c>
       <c r="B204" t="n">
-        <v>2.332691590799507</v>
+        <v>2.331432938948793</v>
       </c>
       <c r="C204" t="n">
-        <v>0.4168789962455852</v>
+        <v>0.41773211200671</v>
       </c>
       <c r="D204" t="n">
-        <v>0.4776656846645195</v>
+        <v>0.4747554420005235</v>
       </c>
       <c r="E204" t="n">
-        <v>9.999999999999891e-05</v>
+        <v>0.004774022066041253</v>
       </c>
     </row>
     <row r="205">
@@ -3911,16 +3911,16 @@
         <v>2.03</v>
       </c>
       <c r="B205" t="n">
-        <v>2.319782227384694</v>
+        <v>2.318467102628645</v>
       </c>
       <c r="C205" t="n">
-        <v>0.4164125254964971</v>
+        <v>0.4172937517483382</v>
       </c>
       <c r="D205" t="n">
-        <v>0.4797454633747401</v>
+        <v>0.4767213889340917</v>
       </c>
       <c r="E205" t="n">
-        <v>9.999999999999896e-05</v>
+        <v>0.004861635415679954</v>
       </c>
     </row>
     <row r="206">
@@ -3928,16 +3928,16 @@
         <v>2.04</v>
       </c>
       <c r="B206" t="n">
-        <v>2.306719705318948</v>
+        <v>2.30534919331912</v>
       </c>
       <c r="C206" t="n">
-        <v>0.4159290837292953</v>
+        <v>0.4168395664479189</v>
       </c>
       <c r="D206" t="n">
-        <v>0.481857940029677</v>
+        <v>0.4787173574053193</v>
       </c>
       <c r="E206" t="n">
-        <v>9.999999999999902e-05</v>
+        <v>0.004952667480162273</v>
       </c>
     </row>
     <row r="207">
@@ -3945,16 +3945,16 @@
         <v>2.05</v>
       </c>
       <c r="B207" t="n">
-        <v>2.293510925758998</v>
+        <v>2.292086196434801</v>
       </c>
       <c r="C207" t="n">
-        <v>0.4154283952885299</v>
+        <v>0.4163693027292939</v>
       </c>
       <c r="D207" t="n">
-        <v>0.4840025274867557</v>
+        <v>0.480742880746136</v>
       </c>
       <c r="E207" t="n">
-        <v>9.999999999999906e-05</v>
+        <v>0.005047180663416684</v>
       </c>
     </row>
     <row r="208">
@@ -3962,16 +3962,16 @@
         <v>2.06</v>
       </c>
       <c r="B208" t="n">
-        <v>2.280162732608322</v>
+        <v>2.278685037421783</v>
       </c>
       <c r="C208" t="n">
-        <v>0.4149101845187512</v>
+        <v>0.4158827072163054</v>
       </c>
       <c r="D208" t="n">
-        <v>0.4861786281406096</v>
+        <v>0.4827974844952421</v>
       </c>
       <c r="E208" t="n">
-        <v>9.999999999999911e-05</v>
+        <v>0.005145237369371659</v>
       </c>
     </row>
     <row r="209">
@@ -3979,16 +3979,16 @@
         <v>2.07</v>
       </c>
       <c r="B209" t="n">
-        <v>2.266681908944949</v>
+        <v>2.265152578157803</v>
       </c>
       <c r="C209" t="n">
-        <v>0.4143741757645094</v>
+        <v>0.4153795265327954</v>
       </c>
       <c r="D209" t="n">
-        <v>0.4883856333948666</v>
+        <v>0.4848806859985591</v>
       </c>
       <c r="E209" t="n">
-        <v>9.999999999999916e-05</v>
+        <v>0.00524690000195566</v>
       </c>
     </row>
     <row r="210">
@@ -3996,16 +3996,16 @@
         <v>2.08</v>
       </c>
       <c r="B210" t="n">
-        <v>2.253075173602201</v>
+        <v>2.251495613510418</v>
       </c>
       <c r="C210" t="n">
-        <v>0.4138200933703547</v>
+        <v>0.414859507302606</v>
       </c>
       <c r="D210" t="n">
-        <v>0.4906229231408125</v>
+        <v>0.4869919940139747</v>
       </c>
       <c r="E210" t="n">
-        <v>9.999999999999922e-05</v>
+        <v>0.005352230965097167</v>
       </c>
     </row>
     <row r="211">
@@ -4013,16 +4013,16 @@
         <v>2.09</v>
       </c>
       <c r="B211" t="n">
-        <v>2.239349177901977</v>
+        <v>2.237720868052756</v>
       </c>
       <c r="C211" t="n">
-        <v>0.4132476616808374</v>
+        <v>0.4143223961495793</v>
       </c>
       <c r="D211" t="n">
-        <v>0.492889865243151</v>
+        <v>0.4891309083205002</v>
       </c>
       <c r="E211" t="n">
-        <v>9.999999999999927e-05</v>
+        <v>0.005461292662724639</v>
       </c>
     </row>
     <row r="212">
@@ -4030,16 +4030,16 @@
         <v>2.1</v>
       </c>
       <c r="B212" t="n">
-        <v>2.225510502539959</v>
+        <v>2.223834992936054</v>
       </c>
       <c r="C212" t="n">
-        <v>0.4126566050405077</v>
+        <v>0.4137679396975572</v>
       </c>
       <c r="D212" t="n">
-        <v>0.4951858150331054</v>
+        <v>0.4912969193319821</v>
       </c>
       <c r="E212" t="n">
-        <v>9.999999999999933e-05</v>
+        <v>0.005574147498766553</v>
       </c>
     </row>
     <row r="213">
@@ -4047,16 +4047,16 @@
         <v>2.11</v>
       </c>
       <c r="B213" t="n">
-        <v>2.211565654621959</v>
+        <v>2.20984456291809</v>
       </c>
       <c r="C213" t="n">
-        <v>0.4120466477939157</v>
+        <v>0.413195884570382</v>
       </c>
       <c r="D213" t="n">
-        <v>0.4975101148091303</v>
+        <v>0.4934895077155174</v>
       </c>
       <c r="E213" t="n">
-        <v>9.999999999999939e-05</v>
+        <v>0.005690857877151369</v>
       </c>
     </row>
     <row r="214">
@@ -4064,16 +4064,16 @@
         <v>2.12</v>
       </c>
       <c r="B214" t="n">
-        <v>2.197521064850397</v>
+        <v>2.19575607354634</v>
       </c>
       <c r="C214" t="n">
-        <v>0.4114175142856117</v>
+        <v>0.4126059773918955</v>
       </c>
       <c r="D214" t="n">
-        <v>0.499862093345527</v>
+        <v>0.4957081440147442</v>
       </c>
       <c r="E214" t="n">
-        <v>9.999999999999945e-05</v>
+        <v>0.005811486201807571</v>
       </c>
     </row>
     <row r="215">
@@ -4081,16 +4081,16 @@
         <v>2.13</v>
       </c>
       <c r="B215" t="n">
-        <v>2.183383084859756</v>
+        <v>2.181575938494595</v>
       </c>
       <c r="C215" t="n">
-        <v>0.4107689288601459</v>
+        <v>0.41199796478594</v>
       </c>
       <c r="D215" t="n">
-        <v>0.5022410654092768</v>
+        <v>0.4979522882781849</v>
       </c>
       <c r="E215" t="n">
-        <v>9.99999999999995e-05</v>
+        <v>0.005936094876663613</v>
       </c>
     </row>
     <row r="216">
@@ -4098,16 +4098,16 @@
         <v>2.14</v>
       </c>
       <c r="B216" t="n">
-        <v>2.169157984699665</v>
+        <v>2.167310487051509</v>
       </c>
       <c r="C216" t="n">
-        <v>0.4101006158620686</v>
+        <v>0.4113715933763574</v>
       </c>
       <c r="D216" t="n">
-        <v>0.504646331285435</v>
+        <v>0.5002213896928458</v>
       </c>
       <c r="E216" t="n">
-        <v>9.999999999999958e-05</v>
+        <v>0.006064746305647978</v>
       </c>
     </row>
     <row r="217">
@@ -4115,16 +4115,16 @@
         <v>2.15</v>
       </c>
       <c r="B217" t="n">
-        <v>2.154851950464115</v>
+        <v>2.152965961759473</v>
       </c>
       <c r="C217" t="n">
-        <v>0.40941229963593</v>
+        <v>0.4107266097869898</v>
       </c>
       <c r="D217" t="n">
-        <v>0.5070771763114448</v>
+        <v>0.5025148862232783</v>
       </c>
       <c r="E217" t="n">
-        <v>9.999999999999964e-05</v>
+        <v>0.006197502892689123</v>
       </c>
     </row>
     <row r="218">
@@ -4132,16 +4132,16 @@
         <v>2.16</v>
       </c>
       <c r="B218" t="n">
-        <v>2.140471082065161</v>
+        <v>2.138548516201967</v>
       </c>
       <c r="C218" t="n">
-        <v>0.4087037045262802</v>
+        <v>0.4100627606416793</v>
       </c>
       <c r="D218" t="n">
-        <v>0.5095328704207606</v>
+        <v>0.5048322042563342</v>
       </c>
       <c r="E218" t="n">
-        <v>9.999999999999972e-05</v>
+        <v>0.00633442704171553</v>
       </c>
     </row>
     <row r="219">
@@ -4149,16 +4149,16 @@
         <v>2.17</v>
       </c>
       <c r="B219" t="n">
-        <v>2.12602139114929</v>
+        <v>2.124064212937479</v>
       </c>
       <c r="C219" t="n">
-        <v>0.4079745548776696</v>
+        <v>0.409379792564268</v>
       </c>
       <c r="D219" t="n">
-        <v>0.5120126676961854</v>
+        <v>0.5071727582518513</v>
       </c>
       <c r="E219" t="n">
-        <v>9.999999999999977e-05</v>
+        <v>0.006475581156655653</v>
       </c>
     </row>
     <row r="220">
@@ -4166,16 +4166,16 @@
         <v>2.18</v>
       </c>
       <c r="B220" t="n">
-        <v>2.111508799154536</v>
+        <v>2.109519021577861</v>
       </c>
       <c r="C220" t="n">
-        <v>0.4072245750346482</v>
+        <v>0.4086774521785979</v>
       </c>
       <c r="D220" t="n">
-        <v>0.5145158059333569</v>
+        <v>0.5095359503995271</v>
       </c>
       <c r="E220" t="n">
-        <v>9.999999999999986e-05</v>
+        <v>0.006621027641437979</v>
       </c>
     </row>
     <row r="221">
@@ -4183,16 +4183,16 @@
         <v>2.19</v>
       </c>
       <c r="B221" t="n">
-        <v>2.096939135506279</v>
+        <v>2.094918817008932</v>
       </c>
       <c r="C221" t="n">
-        <v>0.4064534893417664</v>
+        <v>0.4079554861085111</v>
       </c>
       <c r="D221" t="n">
-        <v>0.5170415062148308</v>
+        <v>0.5119211702822486</v>
       </c>
       <c r="E221" t="n">
-        <v>9.999999999999991e-05</v>
+        <v>0.006770828899990962</v>
       </c>
     </row>
     <row r="222">
@@ -4200,16 +4200,16 @@
         <v>2.2</v>
       </c>
       <c r="B222" t="n">
-        <v>2.082318135949508</v>
+        <v>2.080269377750964</v>
       </c>
       <c r="C222" t="n">
-        <v>0.4056610221435744</v>
+        <v>0.4072136409778495</v>
       </c>
       <c r="D222" t="n">
-        <v>0.5195889724952394</v>
+        <v>0.514327794546161</v>
       </c>
       <c r="E222" t="n">
-        <v>9.999999999999999e-05</v>
+        <v>0.006925047336243084</v>
       </c>
     </row>
     <row r="223">
@@ -4217,16 +4217,16 @@
         <v>2.21</v>
       </c>
       <c r="B223" t="n">
-        <v>2.0676514410153</v>
+        <v>2.065576384456598</v>
       </c>
       <c r="C223" t="n">
-        <v>0.4048468977846224</v>
+        <v>0.4064516634104554</v>
       </c>
       <c r="D223" t="n">
-        <v>0.522157391198017</v>
+        <v>0.5167551865777725</v>
       </c>
       <c r="E223" t="n">
-        <v>0.0001000000000000001</v>
+        <v>0.007083745354122801</v>
       </c>
     </row>
     <row r="224">
@@ -4234,16 +4234,16 @@
         <v>2.22</v>
       </c>
       <c r="B224" t="n">
-        <v>2.05294459461906</v>
+        <v>2.050845418543633</v>
       </c>
       <c r="C224" t="n">
-        <v>0.4040108406094606</v>
+        <v>0.4056693000301707</v>
       </c>
       <c r="D224" t="n">
-        <v>0.5247459308242119</v>
+        <v>0.5192026961884062</v>
       </c>
       <c r="E224" t="n">
-        <v>0.0001000000000000002</v>
+        <v>0.007246985357558598</v>
       </c>
     </row>
     <row r="225">
@@ -4251,16 +4251,16 @@
         <v>2.23</v>
       </c>
       <c r="B225" t="n">
-        <v>2.038203042788051</v>
+        <v>2.036081960960025</v>
       </c>
       <c r="C225" t="n">
-        <v>0.4031525749626391</v>
+        <v>0.4048662974608375</v>
       </c>
       <c r="D225" t="n">
-        <v>0.5273537415739187</v>
+        <v>0.5216696593063198</v>
       </c>
       <c r="E225" t="n">
-        <v>0.0001000000000000002</v>
+        <v>0.007414829750478929</v>
       </c>
     </row>
     <row r="226">
@@ -4268,16 +4268,16 @@
         <v>2.24</v>
       </c>
       <c r="B226" t="n">
-        <v>2.023432132515604</v>
+        <v>2.02129139107834</v>
       </c>
       <c r="C226" t="n">
-        <v>0.4022718251887084</v>
+        <v>0.4040424023262979</v>
       </c>
       <c r="D226" t="n">
-        <v>0.5299799549808882</v>
+        <v>0.5241553976768334</v>
       </c>
       <c r="E226" t="n">
-        <v>0.0001000000000000003</v>
+        <v>0.00758734093681228</v>
       </c>
     </row>
     <row r="227">
@@ -4285,16 +4285,16 @@
         <v>2.25</v>
       </c>
       <c r="B227" t="n">
-        <v>2.008637110739356</v>
+        <v>2.00647898571685</v>
       </c>
       <c r="C227" t="n">
-        <v>0.4013683156322185</v>
+        <v>0.403197361250394</v>
       </c>
       <c r="D227" t="n">
-        <v>0.5326236835608905</v>
+        <v>0.5266592185708123</v>
       </c>
       <c r="E227" t="n">
-        <v>0.0001000000000000004</v>
+        <v>0.007764581320487102</v>
       </c>
     </row>
     <row r="228">
@@ -4302,16 +4302,16 @@
         <v>2.26</v>
       </c>
       <c r="B228" t="n">
-        <v>1.993823123440731</v>
+        <v>1.991649918284345</v>
       </c>
       <c r="C228" t="n">
-        <v>0.4004417706377196</v>
+        <v>0.4023309208569678</v>
       </c>
       <c r="D228" t="n">
-        <v>0.535284020474425</v>
+        <v>0.5291804145018678</v>
       </c>
       <c r="E228" t="n">
-        <v>0.0001000000000000005</v>
+        <v>0.007946613305431881</v>
       </c>
     </row>
     <row r="229">
@@ -4319,16 +4319,16 @@
         <v>2.27</v>
       </c>
       <c r="B229" t="n">
-        <v>1.978995214862892</v>
+        <v>1.976809258045709</v>
       </c>
       <c r="C229" t="n">
-        <v>0.3994919145497622</v>
+        <v>0.4014428277698613</v>
       </c>
       <c r="D229" t="n">
-        <v>0.5379600392043886</v>
+        <v>0.5317182629526508</v>
       </c>
       <c r="E229" t="n">
-        <v>0.0001000000000000005</v>
+        <v>0.008133499295575072</v>
       </c>
     </row>
     <row r="230">
@@ -4336,16 +4336,16 @@
         <v>2.28</v>
       </c>
       <c r="B230" t="n">
-        <v>1.964158326844242</v>
+        <v>1.961961969505227</v>
       </c>
       <c r="C230" t="n">
-        <v>0.3985184717128962</v>
+        <v>0.4005328286129166</v>
       </c>
       <c r="D230" t="n">
-        <v>0.5406507932493345</v>
+        <v>0.5342720261106222</v>
       </c>
       <c r="E230" t="n">
-        <v>0.0001000000000000006</v>
+        <v>0.008325301694845159</v>
       </c>
     </row>
     <row r="231">
@@ -4353,16 +4353,16 @@
         <v>2.29</v>
       </c>
       <c r="B231" t="n">
-        <v>1.949317298264592</v>
+        <v>1.947112911904542</v>
       </c>
       <c r="C231" t="n">
-        <v>0.397521166471672</v>
+        <v>0.3996006700099758</v>
       </c>
       <c r="D231" t="n">
-        <v>0.5433553158329631</v>
+        <v>0.5368409506137024</v>
       </c>
       <c r="E231" t="n">
-        <v>0.0001000000000000007</v>
+        <v>0.008522082907170596</v>
       </c>
     </row>
     <row r="232">
@@ -4370,16 +4370,16 @@
         <v>2.3</v>
       </c>
       <c r="B232" t="n">
-        <v>1.934476864600967</v>
+        <v>1.932266838832138</v>
       </c>
       <c r="C232" t="n">
-        <v>0.3964997231706396</v>
+        <v>0.398646098584881</v>
       </c>
       <c r="D232" t="n">
-        <v>0.5460726196305132</v>
+        <v>0.5394242673062049</v>
       </c>
       <c r="E232" t="n">
-        <v>0.0001000000000000008</v>
+        <v>0.008723905336479869</v>
       </c>
     </row>
     <row r="233">
@@ -4387,16 +4387,16 @@
         <v>2.31</v>
       </c>
       <c r="B233" t="n">
-        <v>1.919641657590087</v>
+        <v>1.917428397941195</v>
       </c>
       <c r="C233" t="n">
-        <v>0.3954538661543496</v>
+        <v>0.3976688609614742</v>
       </c>
       <c r="D233" t="n">
-        <v>0.5488016965127245</v>
+        <v>0.5420211910054749</v>
       </c>
       <c r="E233" t="n">
-        <v>0.0001000000000000009</v>
+        <v>0.008930831386701431</v>
       </c>
     </row>
     <row r="234">
@@ -4404,16 +4404,16 @@
         <v>2.32</v>
       </c>
       <c r="B234" t="n">
-        <v>1.90481620499442</v>
+        <v>1.902602130772607</v>
       </c>
       <c r="C234" t="n">
-        <v>0.3943833197673519</v>
+        <v>0.3966687037635975</v>
       </c>
       <c r="D234" t="n">
-        <v>0.5515415173080672</v>
+        <v>0.5446309202796678</v>
       </c>
       <c r="E234" t="n">
-        <v>0.000100000000000001</v>
+        <v>0.009142923461763758</v>
       </c>
     </row>
     <row r="235">
@@ -4421,16 +4421,16 @@
         <v>2.33</v>
       </c>
       <c r="B235" t="n">
-        <v>1.890004930468777</v>
+        <v>1.887792472679966</v>
       </c>
       <c r="C235" t="n">
-        <v>0.3932878083541968</v>
+        <v>0.3956453736150929</v>
       </c>
       <c r="D235" t="n">
-        <v>0.5542910315839435</v>
+        <v>0.5472526372371032</v>
       </c>
       <c r="E235" t="n">
-        <v>0.0001000000000000011</v>
+        <v>0.00936024396559533</v>
       </c>
     </row>
     <row r="236">
@@ -4438,16 +4438,16 @@
         <v>2.34</v>
       </c>
       <c r="B236" t="n">
-        <v>1.875212153524309</v>
+        <v>1.873003752853265</v>
       </c>
       <c r="C236" t="n">
-        <v>0.3921670562594347</v>
+        <v>0.3945986171398025</v>
       </c>
       <c r="D236" t="n">
-        <v>0.557049167447574</v>
+        <v>0.5498855073276456</v>
       </c>
       <c r="E236" t="n">
-        <v>0.0001000000000000012</v>
+        <v>0.009582855302124597</v>
       </c>
     </row>
     <row r="237">
@@ -4455,16 +4455,16 @@
         <v>2.35</v>
       </c>
       <c r="B237" t="n">
-        <v>1.860442089586817</v>
+        <v>1.858240194438061</v>
       </c>
       <c r="C237" t="n">
-        <v>0.3910207878276154</v>
+        <v>0.3935281809615684</v>
       </c>
       <c r="D237" t="n">
-        <v>0.5598148313673043</v>
+        <v>0.5525286791565762</v>
       </c>
       <c r="E237" t="n">
-        <v>0.0001000000000000013</v>
+        <v>0.009810819875280052</v>
       </c>
     </row>
     <row r="238">
@@ -4472,16 +4472,16 @@
         <v>2.36</v>
       </c>
       <c r="B238" t="n">
-        <v>1.845698850146237</v>
+        <v>1.843505914746874</v>
       </c>
       <c r="C238" t="n">
-        <v>0.3898487274032896</v>
+        <v>0.3924338117042326</v>
       </c>
       <c r="D238" t="n">
-        <v>0.5625869080150641</v>
+        <v>0.5551812843114179</v>
       </c>
       <c r="E238" t="n">
-        <v>0.0001000000000000014</v>
+        <v>0.01004420008899014</v>
       </c>
     </row>
     <row r="239">
@@ -4489,16 +4489,16 @@
         <v>2.37</v>
       </c>
       <c r="B239" t="n">
-        <v>1.830986442994163</v>
+        <v>1.82880492555952</v>
       </c>
       <c r="C239" t="n">
-        <v>0.3886505993310072</v>
+        <v>0.3913152559916371</v>
       </c>
       <c r="D239" t="n">
-        <v>0.5653642601307327</v>
+        <v>0.5578424372021935</v>
       </c>
       <c r="E239" t="n">
-        <v>0.0001000000000000015</v>
+        <v>0.01028305834718335</v>
       </c>
     </row>
     <row r="240">
@@ -4506,16 +4506,16 @@
         <v>2.38</v>
       </c>
       <c r="B240" t="n">
-        <v>1.816308772546299</v>
+        <v>1.814141133509166</v>
       </c>
       <c r="C240" t="n">
-        <v>0.3874261279553186</v>
+        <v>0.3901722604476242</v>
       </c>
       <c r="D240" t="n">
-        <v>0.5681457284091628</v>
+        <v>0.5605112349156003</v>
       </c>
       <c r="E240" t="n">
-        <v>0.0001000000000000016</v>
+        <v>0.01052745705378813</v>
       </c>
     </row>
     <row r="241">
@@ -4523,16 +4523,16 @@
         <v>2.39</v>
       </c>
       <c r="B241" t="n">
-        <v>1.801669640246678</v>
+        <v>1.799518340550839</v>
       </c>
       <c r="C241" t="n">
-        <v>0.3861750376207739</v>
+        <v>0.3890045716960357</v>
       </c>
       <c r="D241" t="n">
-        <v>0.570930131410628</v>
+        <v>0.5631867570835921</v>
       </c>
       <c r="E241" t="n">
-        <v>0.0001000000000000017</v>
+        <v>0.01077745861273298</v>
       </c>
     </row>
     <row r="242">
@@ -4540,16 +4540,16 @@
         <v>2.4</v>
       </c>
       <c r="B242" t="n">
-        <v>1.787072745050574</v>
+        <v>1.78494024450916</v>
       </c>
       <c r="C242" t="n">
-        <v>0.3848970526719234</v>
+        <v>0.3878119363607138</v>
       </c>
       <c r="D242" t="n">
-        <v>0.5737162654954608</v>
+        <v>0.5658680657668639</v>
       </c>
       <c r="E242" t="n">
-        <v>0.0001000000000000018</v>
+        <v>0.01103312542794633</v>
       </c>
     </row>
     <row r="243">
@@ -4557,16 +4557,16 @@
         <v>2.41</v>
       </c>
       <c r="B243" t="n">
-        <v>1.772521683982959</v>
+        <v>1.770410439702091</v>
       </c>
       <c r="C243" t="n">
-        <v>0.3835918974533173</v>
+        <v>0.3865941010655005</v>
       </c>
       <c r="D243" t="n">
-        <v>0.5765029047836564</v>
+        <v>0.568554205353746</v>
       </c>
       <c r="E243" t="n">
-        <v>0.0001000000000000019</v>
+        <v>0.01129451990335669</v>
       </c>
     </row>
     <row r="244">
@@ -4574,16 +4574,16 @@
         <v>2.42</v>
       </c>
       <c r="B244" t="n">
-        <v>1.758019952769464</v>
+        <v>1.755932417637514</v>
       </c>
       <c r="C244" t="n">
-        <v>0.3822592963095058</v>
+        <v>0.385350812434238</v>
       </c>
       <c r="D244" t="n">
-        <v>0.5792888011402118</v>
+        <v>0.5712442024750102</v>
       </c>
       <c r="E244" t="n">
-        <v>0.000100000000000002</v>
+        <v>0.0115617044428925</v>
       </c>
     </row>
     <row r="245">
@@ -4591,16 +4591,16 @@
         <v>2.43</v>
       </c>
       <c r="B245" t="n">
-        <v>1.743570946536746</v>
+        <v>1.741509567779455</v>
       </c>
       <c r="C245" t="n">
-        <v>0.380898973585039</v>
+        <v>0.3840818170907681</v>
       </c>
       <c r="D245" t="n">
-        <v>0.5820726841869832</v>
+        <v>0.5739370659351051</v>
       </c>
       <c r="E245" t="n">
-        <v>0.0001000000000000021</v>
+        <v>0.01183474145048225</v>
       </c>
     </row>
     <row r="246">
@@ -4608,16 +4608,16 @@
         <v>2.44</v>
       </c>
       <c r="B246" t="n">
-        <v>1.729177960579249</v>
+        <v>1.727145178380846</v>
       </c>
       <c r="C246" t="n">
-        <v>0.3795106536244674</v>
+        <v>0.3827868616589332</v>
       </c>
       <c r="D246" t="n">
-        <v>0.584853261341833</v>
+        <v>0.5766317866603312</v>
       </c>
       <c r="E246" t="n">
-        <v>0.0001000000000000022</v>
+        <v>0.01211369333005439</v>
       </c>
     </row>
     <row r="247">
@@ -4625,16 +4625,16 @@
         <v>2.45</v>
       </c>
       <c r="B247" t="n">
-        <v>1.714844191189341</v>
+        <v>1.712842437379695</v>
       </c>
       <c r="C247" t="n">
-        <v>0.378094060772341</v>
+        <v>0.381465692762575</v>
       </c>
       <c r="D247" t="n">
-        <v>0.5876292178858415</v>
+        <v>0.5793273376644779</v>
       </c>
       <c r="E247" t="n">
-        <v>0.0001000000000000023</v>
+        <v>0.0123986224855374</v>
       </c>
     </row>
     <row r="248">
@@ -4642,16 +4642,16 @@
         <v>2.46</v>
       </c>
       <c r="B248" t="n">
-        <v>1.700572736547869</v>
+        <v>1.698604433355636</v>
       </c>
       <c r="C248" t="n">
-        <v>0.3766489193732101</v>
+        <v>0.3801180570255359</v>
       </c>
       <c r="D248" t="n">
-        <v>0.5903992170593532</v>
+        <v>0.5820226740324381</v>
       </c>
       <c r="E248" t="n">
-        <v>0.0001000000000000025</v>
+        <v>0.01268959132085975</v>
       </c>
     </row>
     <row r="249">
@@ -4659,16 +4659,16 @@
         <v>2.47</v>
       </c>
       <c r="B249" t="n">
-        <v>1.686366597672169</v>
+        <v>1.684434156543801</v>
       </c>
       <c r="C249" t="n">
-        <v>0.3751749537716249</v>
+        <v>0.3787437010716577</v>
       </c>
       <c r="D249" t="n">
-        <v>0.5931619001876238</v>
+        <v>0.5847167329223258</v>
       </c>
       <c r="E249" t="n">
-        <v>0.0001000000000000026</v>
+        <v>0.01298666223994992</v>
       </c>
     </row>
     <row r="250">
@@ -4676,16 +4676,16 @@
         <v>2.48</v>
       </c>
       <c r="B250" t="n">
-        <v>1.672228679418675</v>
+        <v>1.67033449990307</v>
       </c>
       <c r="C250" t="n">
-        <v>0.3736718883121357</v>
+        <v>0.3773423715247827</v>
       </c>
       <c r="D250" t="n">
-        <v>0.5959158868368232</v>
+        <v>0.5874084335866122</v>
       </c>
       <c r="E250" t="n">
-        <v>0.0001000000000000027</v>
+        <v>0.01328989764673634</v>
       </c>
     </row>
     <row r="251">
@@ -4693,16 +4693,16 @@
         <v>2.49</v>
       </c>
       <c r="B251" t="n">
-        <v>1.658161791537234</v>
+        <v>1.65630826023574</v>
       </c>
       <c r="C251" t="n">
-        <v>0.3721394473392925</v>
+        <v>0.3759138150087526</v>
       </c>
       <c r="D251" t="n">
-        <v>0.5986597750011454</v>
+        <v>0.5900966774128048</v>
       </c>
       <c r="E251" t="n">
-        <v>0.0001000000000000028</v>
+        <v>0.01359935994514753</v>
       </c>
     </row>
     <row r="252">
@@ -4710,16 +4710,16 @@
         <v>2.5</v>
       </c>
       <c r="B252" t="n">
-        <v>1.644168649774348</v>
+        <v>1.642358139355749</v>
       </c>
       <c r="C252" t="n">
-        <v>0.3705773551976458</v>
+        <v>0.3744577781474099</v>
       </c>
       <c r="D252" t="n">
-        <v>0.6013921413217596</v>
+        <v>0.5927803479841843</v>
       </c>
       <c r="E252" t="n">
-        <v>0.0001000000000000029</v>
+        <v>0.01391511153911192</v>
       </c>
     </row>
     <row r="253">
@@ -4727,16 +4727,16 @@
         <v>2.51</v>
       </c>
       <c r="B253" t="n">
-        <v>1.630251877022562</v>
+        <v>1.628486745302617</v>
       </c>
       <c r="C253" t="n">
-        <v>0.3689853362317456</v>
+        <v>0.3729740075645963</v>
       </c>
       <c r="D253" t="n">
-        <v>0.6041115413383311</v>
+        <v>0.5954583111611167</v>
       </c>
       <c r="E253" t="n">
-        <v>0.0001000000000000031</v>
+        <v>0.01423721483255802</v>
       </c>
     </row>
     <row r="254">
@@ -4744,16 +4744,16 @@
         <v>2.52</v>
       </c>
       <c r="B254" t="n">
-        <v>1.616414004513313</v>
+        <v>1.614696593598336</v>
       </c>
       <c r="C254" t="n">
-        <v>0.3673631147861423</v>
+        <v>0.3714622498841542</v>
       </c>
       <c r="D254" t="n">
-        <v>0.6068165097738165</v>
+        <v>0.5981294151834485</v>
       </c>
       <c r="E254" t="n">
-        <v>0.0001000000000000032</v>
+        <v>0.01456573222941425</v>
       </c>
     </row>
     <row r="255">
@@ -4761,16 +4761,16 @@
         <v>2.53</v>
       </c>
       <c r="B255" t="n">
-        <v>1.602657473050543</v>
+        <v>1.600990108544477</v>
       </c>
       <c r="C255" t="n">
-        <v>0.3657104152053859</v>
+        <v>0.3699222517299253</v>
       </c>
       <c r="D255" t="n">
-        <v>0.6095055608532319</v>
+        <v>0.600792490794496</v>
       </c>
       <c r="E255" t="n">
-        <v>0.0001000000000000033</v>
+        <v>0.01490072613360912</v>
       </c>
     </row>
     <row r="256">
@@ -4778,16 +4778,16 @@
         <v>2.54</v>
       </c>
       <c r="B256" t="n">
-        <v>1.588984634282518</v>
+        <v>1.587369624556864</v>
       </c>
       <c r="C256" t="n">
-        <v>0.3640269618340268</v>
+        <v>0.3683537597257519</v>
       </c>
       <c r="D256" t="n">
-        <v>0.6121771886570595</v>
+        <v>0.6034463513871231</v>
       </c>
       <c r="E256" t="n">
-        <v>0.0001000000000000035</v>
+        <v>0.01524225894907107</v>
       </c>
     </row>
     <row r="257">
@@ -4795,16 +4795,16 @@
         <v>2.55</v>
       </c>
       <c r="B257" t="n">
-        <v>1.575397752009261</v>
+        <v>1.573837387535201</v>
       </c>
       <c r="C257" t="n">
-        <v>0.3623124790166151</v>
+        <v>0.366756520495476</v>
       </c>
       <c r="D257" t="n">
-        <v>0.6148298675099529</v>
+        <v>0.6060897931724053</v>
       </c>
       <c r="E257" t="n">
-        <v>0.0001000000000000036</v>
+        <v>0.01559039307972859</v>
       </c>
     </row>
     <row r="258">
@@ -4812,16 +4812,16 @@
         <v>2.56</v>
       </c>
       <c r="B258" t="n">
-        <v>1.561899003523138</v>
+        <v>1.560395556265133</v>
       </c>
       <c r="C258" t="n">
-        <v>0.3605666910977013</v>
+        <v>0.3651302806629398</v>
       </c>
       <c r="D258" t="n">
-        <v>0.6174620524053609</v>
+        <v>0.6087215953713609</v>
       </c>
       <c r="E258" t="n">
-        <v>0.0001000000000000037</v>
+        <v>0.01594519092951014</v>
       </c>
     </row>
     <row r="259">
@@ -4829,16 +4829,16 @@
         <v>2.57</v>
       </c>
       <c r="B259" t="n">
-        <v>1.548490480980149</v>
+        <v>1.547046203850225</v>
       </c>
       <c r="C259" t="n">
-        <v>0.3587893224218353</v>
+        <v>0.3634747868519851</v>
       </c>
       <c r="D259" t="n">
-        <v>0.6200721794666797</v>
+        <v>0.6113405204302268</v>
       </c>
       <c r="E259" t="n">
-        <v>0.0001000000000000039</v>
+        <v>0.01630671490234419</v>
       </c>
     </row>
     <row r="260">
@@ -4846,16 +4846,16 @@
         <v>2.58</v>
       </c>
       <c r="B260" t="n">
-        <v>1.53517419279955</v>
+        <v>1.533791319171489</v>
       </c>
       <c r="C260" t="n">
-        <v>0.3569800973335674</v>
+        <v>0.361789785686454</v>
       </c>
       <c r="D260" t="n">
-        <v>0.6226586664455019</v>
+        <v>0.613945314259739</v>
       </c>
       <c r="E260" t="n">
-        <v>0.000100000000000004</v>
+        <v>0.01667502740215922</v>
       </c>
     </row>
     <row r="261">
@@ -4863,16 +4863,16 @@
         <v>2.59</v>
       </c>
       <c r="B261" t="n">
-        <v>1.521952065089511</v>
+        <v>1.520632808372073</v>
       </c>
       <c r="C261" t="n">
-        <v>0.3551387401774478</v>
+        <v>0.3600750237901889</v>
       </c>
       <c r="D261" t="n">
-        <v>0.6252199132575074</v>
+        <v>0.6165347064988744</v>
       </c>
       <c r="E261" t="n">
-        <v>0.0001000000000000042</v>
+        <v>0.01705019083288368</v>
       </c>
     </row>
     <row r="262">
@@ -4880,16 +4880,16 @@
         <v>2.6</v>
       </c>
       <c r="B262" t="n">
-        <v>1.50882594309653</v>
+        <v>1.507572496364847</v>
       </c>
       <c r="C262" t="n">
-        <v>0.3532649752980268</v>
+        <v>0.3583302477870314</v>
       </c>
       <c r="D262" t="n">
-        <v>0.6277543025565089</v>
+        <v>0.6191074108034894</v>
       </c>
       <c r="E262" t="n">
-        <v>0.0001000000000000043</v>
+        <v>0.01743226759844607</v>
       </c>
     </row>
     <row r="263">
@@ -4897,16 +4897,16 @@
         <v>2.61</v>
       </c>
       <c r="B263" t="n">
-        <v>1.495797592676447</v>
+        <v>1.494612128360661</v>
       </c>
       <c r="C263" t="n">
-        <v>0.3513585270398547</v>
+        <v>0.3565552043008238</v>
       </c>
       <c r="D263" t="n">
-        <v>0.6302602003471226</v>
+        <v>0.6216621251602771</v>
       </c>
       <c r="E263" t="n">
-        <v>0.0001000000000000044</v>
+        <v>0.01782132010277481</v>
       </c>
     </row>
     <row r="264">
@@ -4914,16 +4914,16 @@
         <v>2.62</v>
       </c>
       <c r="B264" t="n">
-        <v>1.48286870178491</v>
+        <v>1.481753371415122</v>
       </c>
       <c r="C264" t="n">
-        <v>0.3494191197474814</v>
+        <v>0.3547496399554081</v>
       </c>
       <c r="D264" t="n">
-        <v>0.6327359566365064</v>
+        <v>0.6241975322264566</v>
       </c>
       <c r="E264" t="n">
-        <v>0.0001000000000000046</v>
+        <v>0.01821741074979843</v>
       </c>
     </row>
     <row r="265">
@@ -4931,16 +4931,16 @@
         <v>2.63</v>
       </c>
       <c r="B265" t="n">
-        <v>1.470040881985249</v>
+        <v>1.468997815991823</v>
       </c>
       <c r="C265" t="n">
-        <v>0.3474464777654575</v>
+        <v>0.3529133013746266</v>
       </c>
       <c r="D265" t="n">
-        <v>0.6351799061255567</v>
+        <v>0.6267122996955774</v>
       </c>
       <c r="E265" t="n">
-        <v>0.0001000000000000047</v>
+        <v>0.01862060194344535</v>
       </c>
     </row>
     <row r="266">
@@ -4948,16 +4948,16 @@
         <v>2.64</v>
       </c>
       <c r="B266" t="n">
-        <v>1.457315669971751</v>
+        <v>1.456346977539976</v>
       </c>
       <c r="C266" t="n">
-        <v>0.345440325438333</v>
+        <v>0.351045935182321</v>
       </c>
       <c r="D266" t="n">
-        <v>0.637590368939924</v>
+        <v>0.629205080689817</v>
       </c>
       <c r="E266" t="n">
-        <v>0.0001000000000000049</v>
+        <v>0.01903095608764407</v>
       </c>
     </row>
     <row r="267">
@@ -4965,16 +4965,16 @@
         <v>2.65</v>
       </c>
       <c r="B267" t="n">
-        <v>1.444694529106415</v>
+        <v>1.443802298084539</v>
       </c>
       <c r="C267" t="n">
-        <v>0.3434003871106581</v>
+        <v>0.3491472880023335</v>
       </c>
       <c r="D267" t="n">
-        <v>0.6399656514011489</v>
+        <v>0.6316745141791156</v>
       </c>
       <c r="E267" t="n">
-        <v>0.0001000000000000051</v>
+        <v>0.01944853558632303</v>
       </c>
     </row>
     <row r="268">
@@ -4982,16 +4982,16 @@
         <v>2.66</v>
       </c>
       <c r="B268" t="n">
-        <v>1.432178850967307</v>
+        <v>1.431365147826919</v>
       </c>
       <c r="C268" t="n">
-        <v>0.3413263871269831</v>
+        <v>0.3472171064585062</v>
       </c>
       <c r="D268" t="n">
-        <v>0.6423040468381873</v>
+        <v>0.6341192254274859</v>
       </c>
       <c r="E268" t="n">
-        <v>0.0001000000000000052</v>
+        <v>0.01987340284341075</v>
       </c>
     </row>
     <row r="269">
@@ -4999,16 +4999,16 @@
         <v>2.67</v>
       </c>
       <c r="B269" t="n">
-        <v>1.419769956906736</v>
+        <v>1.419036826754485</v>
       </c>
       <c r="C269" t="n">
-        <v>0.3392180498318583</v>
+        <v>0.3452551371746813</v>
       </c>
       <c r="D269" t="n">
-        <v>0.6446038364395263</v>
+        <v>0.6365378264667952</v>
       </c>
       <c r="E269" t="n">
-        <v>0.0001000000000000054</v>
+        <v>0.02030562026283563</v>
       </c>
     </row>
     <row r="270">
@@ -5016,16 +5016,16 @@
         <v>2.68</v>
       </c>
       <c r="B270" t="n">
-        <v>1.407469099617482</v>
+        <v>1.406818566257088</v>
       </c>
       <c r="C270" t="n">
-        <v>0.3370750995698338</v>
+        <v>0.3432611267747005</v>
       </c>
       <c r="D270" t="n">
-        <v>0.6468632901460577</v>
+        <v>0.6389289165983103</v>
       </c>
       <c r="E270" t="n">
-        <v>0.0001000000000000055</v>
+        <v>0.0207452502485262</v>
       </c>
     </row>
     <row r="271">
@@ -5033,16 +5033,16 @@
         <v>2.69</v>
       </c>
       <c r="B271" t="n">
-        <v>1.395277464705447</v>
+        <v>1.394711530748975</v>
       </c>
       <c r="C271" t="n">
-        <v>0.3348972606854598</v>
+        <v>0.3412348218824062</v>
       </c>
       <c r="D271" t="n">
-        <v>0.6490806675848021</v>
+        <v>0.6412910829222527</v>
       </c>
       <c r="E271" t="n">
-        <v>0.0001000000000000057</v>
+        <v>0.02119235520441089</v>
       </c>
     </row>
     <row r="272">
@@ -5050,16 +5050,16 @@
         <v>2.7</v>
       </c>
       <c r="B272" t="n">
-        <v>1.383196172267076</v>
+        <v>1.382716819294441</v>
       </c>
       <c r="C272" t="n">
-        <v>0.3326842575232866</v>
+        <v>0.3391759691216403</v>
       </c>
       <c r="D272" t="n">
-        <v>0.6512542190435355</v>
+        <v>0.6436229008956006</v>
       </c>
       <c r="E272" t="n">
-        <v>0.0001000000000000058</v>
+        <v>0.0216469975344182</v>
       </c>
     </row>
     <row r="273">
@@ -5067,16 +5067,16 @@
         <v>2.71</v>
       </c>
       <c r="B273" t="n">
-        <v>1.371226278470042</v>
+        <v>1.370835467235694</v>
       </c>
       <c r="C273" t="n">
-        <v>0.3304358144278644</v>
+        <v>0.3370843151162449</v>
       </c>
       <c r="D273" t="n">
-        <v>0.6533821864862978</v>
+        <v>0.6459229349183299</v>
       </c>
       <c r="E273" t="n">
-        <v>0.000100000000000006</v>
+        <v>0.02210923964247656</v>
       </c>
     </row>
     <row r="274">
@@ -5084,16 +5084,16 @@
         <v>2.72</v>
       </c>
       <c r="B274" t="n">
-        <v>1.359368777135697</v>
+        <v>1.359068447821468</v>
       </c>
       <c r="C274" t="n">
-        <v>0.3281516557437433</v>
+        <v>0.334959606490062</v>
       </c>
       <c r="D274" t="n">
-        <v>0.655462804609706</v>
+        <v>0.6481897389482677</v>
       </c>
       <c r="E274" t="n">
-        <v>0.0001000000000000062</v>
+        <v>0.02257914393251449</v>
       </c>
     </row>
     <row r="275">
@@ -5101,16 +5101,16 @@
         <v>2.73</v>
       </c>
       <c r="B275" t="n">
-        <v>1.347624601321876</v>
+        <v>1.347416673834952</v>
       </c>
       <c r="C275" t="n">
-        <v>0.3258315058154738</v>
+        <v>0.3328015898669338</v>
       </c>
       <c r="D275" t="n">
-        <v>0.6574943019399279</v>
+        <v>0.6504218571446938</v>
       </c>
       <c r="E275" t="n">
-        <v>0.0001000000000000064</v>
+        <v>0.02305677280846041</v>
       </c>
     </row>
     <row r="276">
@@ -5118,16 +5118,16 @@
         <v>2.74</v>
       </c>
       <c r="B276" t="n">
-        <v>1.335994624904707</v>
+        <v>1.33588099921971</v>
       </c>
       <c r="C276" t="n">
-        <v>0.3234750889876059</v>
+        <v>0.3306100118707022</v>
       </c>
       <c r="D276" t="n">
-        <v>0.6594749019701059</v>
+        <v>0.6526178245407931</v>
       </c>
       <c r="E276" t="n">
-        <v>0.0001000000000000065</v>
+        <v>0.02354218867424283</v>
       </c>
     </row>
     <row r="277">
@@ -5135,16 +5135,16 @@
         <v>2.75</v>
       </c>
       <c r="B277" t="n">
-        <v>1.324479664158128</v>
+        <v>1.324462220702308</v>
       </c>
       <c r="C277" t="n">
-        <v>0.3210821296046898</v>
+        <v>0.3283846191252094</v>
       </c>
       <c r="D277" t="n">
-        <v>0.6614028243379482</v>
+        <v>0.6547761677450279</v>
       </c>
       <c r="E277" t="n">
-        <v>0.0001000000000000067</v>
+        <v>0.02403545393379019</v>
       </c>
     </row>
     <row r="278">
@@ -5152,16 +5152,16 @@
         <v>2.76</v>
       </c>
       <c r="B278" t="n">
-        <v>1.313080479329892</v>
+        <v>1.313161079410421</v>
       </c>
       <c r="C278" t="n">
-        <v>0.3186523520112758</v>
+        <v>0.3261251582542974</v>
       </c>
       <c r="D278" t="n">
-        <v>0.6632762860431359</v>
+        <v>0.6568954056714639</v>
       </c>
       <c r="E278" t="n">
-        <v>0.0001000000000000069</v>
+        <v>0.02453663099103099</v>
       </c>
     </row>
     <row r="279">
@@ -5169,16 +5169,16 @@
         <v>2.77</v>
       </c>
       <c r="B279" t="n">
-        <v>1.301797776212877</v>
+        <v>1.301978262485279</v>
       </c>
       <c r="C279" t="n">
-        <v>0.3161854805519142</v>
+        <v>0.3238313758818083</v>
       </c>
       <c r="D279" t="n">
-        <v>0.6650935027041175</v>
+        <v>0.6589740502990419</v>
       </c>
       <c r="E279" t="n">
-        <v>0.0001000000000000071</v>
+        <v>0.02504578224989366</v>
       </c>
     </row>
     <row r="280">
@@ -5186,16 +5186,16 @@
         <v>2.78</v>
       </c>
       <c r="B280" t="n">
-        <v>1.29063220771061</v>
+        <v>1.290914404687361</v>
       </c>
       <c r="C280" t="n">
-        <v>0.313681239571155</v>
+        <v>0.321503018631584</v>
       </c>
       <c r="D280" t="n">
-        <v>0.6668526898537892</v>
+        <v>0.6610106074597522</v>
       </c>
       <c r="E280" t="n">
-        <v>0.0001000000000000072</v>
+        <v>0.0255629701143067</v>
       </c>
     </row>
     <row r="281">
@@ -5203,16 +5203,16 @@
         <v>2.79</v>
       </c>
       <c r="B281" t="n">
-        <v>1.27958437539594</v>
+        <v>1.279970089994305</v>
       </c>
       <c r="C281" t="n">
-        <v>0.3111393534135486</v>
+        <v>0.3191398331274669</v>
       </c>
       <c r="D281" t="n">
-        <v>0.6685520642734762</v>
+        <v>0.6630035776556256</v>
       </c>
       <c r="E281" t="n">
-        <v>0.0001000000000000074</v>
+        <v>0.02608825698819856</v>
       </c>
     </row>
     <row r="282">
@@ -5220,16 +5220,16 @@
         <v>2.8</v>
       </c>
       <c r="B282" t="n">
-        <v>1.268654831061879</v>
+        <v>1.26914585319005</v>
       </c>
       <c r="C282" t="n">
-        <v>0.3085595464236452</v>
+        <v>0.3167415659932986</v>
       </c>
       <c r="D282" t="n">
-        <v>0.6701898453645579</v>
+        <v>0.664951456904414</v>
       </c>
       <c r="E282" t="n">
-        <v>0.0001000000000000076</v>
+        <v>0.02662170527549774</v>
       </c>
     </row>
     <row r="283">
@@ -5237,16 +5237,16 @@
         <v>2.81</v>
       </c>
       <c r="B283" t="n">
-        <v>1.257844078263674</v>
+        <v>1.258442181444338</v>
       </c>
       <c r="C283" t="n">
-        <v>0.305941542945995</v>
+        <v>0.3143079638529216</v>
       </c>
       <c r="D283" t="n">
-        <v>0.6717642565569893</v>
+        <v>0.6668527376137898</v>
       </c>
       <c r="E283" t="n">
-        <v>0.0001000000000000078</v>
+        <v>0.02716337738013266</v>
       </c>
     </row>
     <row r="284">
@@ -5254,16 +5254,16 @@
         <v>2.82</v>
       </c>
       <c r="B284" t="n">
-        <v>1.247152573851227</v>
+        <v>1.247859515881671</v>
       </c>
       <c r="C284" t="n">
-        <v>0.3032850673251483</v>
+        <v>0.3118387733301778</v>
       </c>
       <c r="D284" t="n">
-        <v>0.6732735267538931</v>
+        <v>0.6687059094838467</v>
       </c>
       <c r="E284" t="n">
-        <v>0.000100000000000008</v>
+        <v>0.02771333570603183</v>
       </c>
     </row>
     <row r="285">
@@ -5271,16 +5271,16 @@
         <v>2.83</v>
       </c>
       <c r="B285" t="n">
-        <v>1.236580729491051</v>
+        <v>1.237398253138982</v>
       </c>
       <c r="C285" t="n">
-        <v>0.300589843905655</v>
+        <v>0.3093337410489091</v>
       </c>
       <c r="D285" t="n">
-        <v>0.6747158918113114</v>
+        <v>0.6705094604376439</v>
       </c>
       <c r="E285" t="n">
-        <v>0.0001000000000000082</v>
+        <v>0.02827164265712372</v>
       </c>
     </row>
     <row r="286">
@@ -5288,16 +5288,16 @@
         <v>2.84</v>
       </c>
       <c r="B286" t="n">
-        <v>1.226128913176991</v>
+        <v>1.227058746911233</v>
       </c>
       <c r="C286" t="n">
-        <v>0.2978555970320657</v>
+        <v>0.3067926136329578</v>
       </c>
       <c r="D286" t="n">
-        <v>0.6760895960521164</v>
+        <v>0.6722618775794817</v>
       </c>
       <c r="E286" t="n">
-        <v>0.0001000000000000084</v>
+        <v>0.02883836063733676</v>
       </c>
     </row>
     <row r="287">
@@ -5305,16 +5305,16 @@
         <v>2.85</v>
       </c>
       <c r="B287" t="n">
-        <v>1.215797450728982</v>
+        <v>1.216841309484297</v>
       </c>
       <c r="C287" t="n">
-        <v>0.2950820510489304</v>
+        <v>0.3042151377061659</v>
       </c>
       <c r="D287" t="n">
-        <v>0.6773928938129946</v>
+        <v>0.6739616481805533</v>
       </c>
       <c r="E287" t="n">
-        <v>0.0001000000000000086</v>
+        <v>0.02941355205059948</v>
       </c>
     </row>
     <row r="288">
@@ -5322,16 +5322,16 @@
         <v>2.86</v>
       </c>
       <c r="B288" t="n">
-        <v>1.205586627279206</v>
+        <v>1.20674621325446</v>
       </c>
       <c r="C288" t="n">
-        <v>0.2922689303007995</v>
+        <v>0.3016010598923754</v>
       </c>
       <c r="D288" t="n">
-        <v>0.6786240510233292</v>
+        <v>0.6756072606915627</v>
       </c>
       <c r="E288" t="n">
-        <v>0.0001000000000000088</v>
+        <v>0.02999727930084028</v>
       </c>
     </row>
     <row r="289">
@@ -5339,16 +5339,16 @@
         <v>2.87</v>
       </c>
       <c r="B289" t="n">
-        <v>1.195496688745013</v>
+        <v>1.196773692233986</v>
       </c>
       <c r="C289" t="n">
-        <v>0.2894159591322228</v>
+        <v>0.2989501268154283</v>
       </c>
       <c r="D289" t="n">
-        <v>0.6797813468147136</v>
+        <v>0.6771972057818575</v>
       </c>
       <c r="E289" t="n">
-        <v>0.000100000000000009</v>
+        <v>0.0305896047919877</v>
       </c>
     </row>
     <row r="290">
@@ -5356,16 +5356,16 @@
         <v>2.88</v>
       </c>
       <c r="B290" t="n">
-        <v>1.185527843288062</v>
+        <v>1.186923943542213</v>
       </c>
       <c r="C290" t="n">
-        <v>0.2865228618877512</v>
+        <v>0.2962620850991668</v>
       </c>
       <c r="D290" t="n">
-        <v>0.6808630751597446</v>
+        <v>0.678729977404559</v>
       </c>
       <c r="E290" t="n">
-        <v>0.0001000000000000092</v>
+        <v>0.03119059092797015</v>
       </c>
     </row>
     <row r="291">
@@ -5373,16 +5373,16 @@
         <v>2.89</v>
       </c>
       <c r="B291" t="n">
-        <v>1.175680262759158</v>
+        <v>1.177197128881693</v>
       </c>
       <c r="C291" t="n">
-        <v>0.2835893629119344</v>
+        <v>0.2935366813674329</v>
       </c>
       <c r="D291" t="n">
-        <v>0.681867546538641</v>
+        <v>0.680204073887135</v>
       </c>
       <c r="E291" t="n">
-        <v>0.0001000000000000094</v>
+        <v>0.03180030011271615</v>
       </c>
     </row>
     <row r="292">
@@ -5390,16 +5390,16 @@
         <v>2.9</v>
       </c>
       <c r="B292" t="n">
-        <v>1.165954084128323</v>
+        <v>1.167593375998973</v>
       </c>
       <c r="C292" t="n">
-        <v>0.2806151865493228</v>
+        <v>0.2907736622440687</v>
       </c>
       <c r="D292" t="n">
-        <v>0.6827930896321549</v>
+        <v>0.6816179990467949</v>
       </c>
       <c r="E292" t="n">
-        <v>0.0001000000000000096</v>
+        <v>0.03241879475015411</v>
       </c>
     </row>
     <row r="293">
@@ -5407,16 +5407,16 @@
         <v>2.91</v>
       </c>
       <c r="B293" t="n">
-        <v>1.156349410899688</v>
+        <v>1.158112780129607</v>
       </c>
       <c r="C293" t="n">
-        <v>0.2776000571444664</v>
+        <v>0.2879727743529161</v>
       </c>
       <c r="D293" t="n">
-        <v>0.6836380530391418</v>
+        <v>0.682970263330039</v>
       </c>
       <c r="E293" t="n">
-        <v>0.0001000000000000098</v>
+        <v>0.03304613724421256</v>
       </c>
     </row>
     <row r="294">
@@ -5424,16 +5424,16 @@
         <v>2.92</v>
       </c>
       <c r="B294" t="n">
-        <v>1.146866314510831</v>
+        <v>1.148755405427094</v>
       </c>
       <c r="C294" t="n">
-        <v>0.2745436990419159</v>
+        <v>0.2851337643178176</v>
       </c>
       <c r="D294" t="n">
-        <v>0.6844008070170664</v>
+        <v>0.6842593849756374</v>
       </c>
       <c r="E294" t="n">
-        <v>0.00010000000000001</v>
+        <v>0.03368238999881992</v>
       </c>
     </row>
     <row r="295">
@@ -5441,16 +5441,16 @@
         <v>2.93</v>
       </c>
       <c r="B295" t="n">
-        <v>1.13750483571622</v>
+        <v>1.139521286375434</v>
       </c>
       <c r="C295" t="n">
-        <v>0.2714458365862211</v>
+        <v>0.2822563787626147</v>
       </c>
       <c r="D295" t="n">
-        <v>0.685079745243629</v>
+        <v>0.6854838912002561</v>
       </c>
       <c r="E295" t="n">
-        <v>0.0001000000000000102</v>
+        <v>0.0343276154179047</v>
       </c>
     </row>
     <row r="296">
@@ -5458,16 +5458,16 @@
         <v>2.94</v>
       </c>
       <c r="B296" t="n">
-        <v>1.128264985954499</v>
+        <v>1.130410429185073</v>
       </c>
       <c r="C296" t="n">
-        <v>0.2683061941219324</v>
+        <v>0.2793403643111498</v>
       </c>
       <c r="D296" t="n">
-        <v>0.6856732865976096</v>
+        <v>0.6866423194058928</v>
       </c>
       <c r="E296" t="n">
-        <v>0.0001000000000000105</v>
+        <v>0.03498187590539533</v>
       </c>
     </row>
     <row r="297">
@@ -5475,16 +5475,16 @@
         <v>2.95</v>
       </c>
       <c r="B297" t="n">
-        <v>1.119146748699354</v>
+        <v>1.121422813172025</v>
       </c>
       <c r="C297" t="n">
-        <v>0.2651244959935998</v>
+        <v>0.2763854675872648</v>
       </c>
       <c r="D297" t="n">
-        <v>0.6861798769569274</v>
+        <v>0.6877332184082311</v>
       </c>
       <c r="E297" t="n">
-        <v>0.0001000000000000107</v>
+        <v>0.03564523386522033</v>
       </c>
     </row>
     <row r="298">
@@ -5492,16 +5492,16 @@
         <v>2.96</v>
       </c>
       <c r="B298" t="n">
-        <v>1.110150080793768</v>
+        <v>1.112558392120031</v>
       </c>
       <c r="C298" t="n">
-        <v>0.2619004665457739</v>
+        <v>0.273391435214802</v>
       </c>
       <c r="D298" t="n">
-        <v>0.6865979910118322</v>
+        <v>0.6887551496849571</v>
       </c>
       <c r="E298" t="n">
-        <v>0.0001000000000000109</v>
+        <v>0.03631775170130811</v>
       </c>
     </row>
     <row r="299">
@@ -5509,16 +5509,16 @@
         <v>2.97</v>
       </c>
       <c r="B299" t="n">
-        <v>1.101274913767498</v>
+        <v>1.103817095625613</v>
       </c>
       <c r="C299" t="n">
-        <v>0.2586338301230046</v>
+        <v>0.2703580138176032</v>
       </c>
       <c r="D299" t="n">
-        <v>0.6869261340910531</v>
+        <v>0.6897066886430332</v>
       </c>
       <c r="E299" t="n">
-        <v>0.0001000000000000111</v>
+        <v>0.0369994918175872</v>
       </c>
     </row>
     <row r="300">
@@ -5526,16 +5526,16 @@
         <v>2.98</v>
       </c>
       <c r="B300" t="n">
-        <v>1.092521155137647</v>
+        <v>1.095198830425974</v>
       </c>
       <c r="C300" t="n">
-        <v>0.2553243110698423</v>
+        <v>0.2672849500195107</v>
       </c>
       <c r="D300" t="n">
-        <v>0.6871628439986361</v>
+        <v>0.6905864259038603</v>
       </c>
       <c r="E300" t="n">
-        <v>0.0001000000000000113</v>
+        <v>0.03769051661798601</v>
       </c>
     </row>
     <row r="301">
@@ -5543,16 +5543,16 @@
         <v>2.99</v>
       </c>
       <c r="B301" t="n">
-        <v>1.083888689692258</v>
+        <v>1.08670348170968</v>
       </c>
       <c r="C301" t="n">
-        <v>0.251971633730837</v>
+        <v>0.2641719904443662</v>
       </c>
       <c r="D301" t="n">
-        <v>0.6873066928591287</v>
+        <v>0.6913929686052049</v>
       </c>
       <c r="E301" t="n">
-        <v>0.0001000000000000116</v>
+        <v>0.03839088850643307</v>
       </c>
     </row>
     <row r="302">
@@ -5560,16 +5560,16 @@
         <v>3</v>
       </c>
       <c r="B302" t="n">
-        <v>1.075377380756869</v>
+        <v>1.078330914410148</v>
       </c>
       <c r="C302" t="n">
-        <v>0.2485755224505393</v>
+        <v>0.2610188817160123</v>
       </c>
       <c r="D302" t="n">
-        <v>0.6873562889686722</v>
+        <v>0.6921249417187086</v>
       </c>
       <c r="E302" t="n">
-        <v>0.0001000000000000118</v>
+        <v>0.03910066988685677</v>
       </c>
     </row>
     <row r="303">
@@ -5577,16 +5577,16 @@
         <v>3.01</v>
       </c>
       <c r="B303" t="n">
-        <v>1.066987071444016</v>
+        <v>1.070080974481949</v>
       </c>
       <c r="C303" t="n">
-        <v>0.2451357015734989</v>
+        <v>0.2578253704582905</v>
       </c>
       <c r="D303" t="n">
-        <v>0.6873102786494907</v>
+        <v>0.692780989381741</v>
       </c>
       <c r="E303" t="n">
-        <v>0.0001000000000000121</v>
+        <v>0.03981992316318568</v>
       </c>
     </row>
     <row r="304">
@@ -5594,16 +5594,16 @@
         <v>3.02</v>
       </c>
       <c r="B304" t="n">
-        <v>1.058717585885712</v>
+        <v>1.061953490160026</v>
       </c>
       <c r="C304" t="n">
-        <v>0.2416518954442666</v>
+        <v>0.2545912032950433</v>
       </c>
       <c r="D304" t="n">
-        <v>0.6871673481051831</v>
+        <v>0.6933597762422987</v>
       </c>
       <c r="E304" t="n">
-        <v>0.0001000000000000123</v>
+        <v>0.04054871073934818</v>
       </c>
     </row>
     <row r="305">
@@ -5611,16 +5611,16 @@
         <v>3.03</v>
       </c>
       <c r="B305" t="n">
-        <v>1.050568730448955</v>
+        <v>1.053948273201907</v>
       </c>
       <c r="C305" t="n">
-        <v>0.2381238284073921</v>
+        <v>0.2513161268501124</v>
       </c>
       <c r="D305" t="n">
-        <v>0.6869262252741438</v>
+        <v>0.6938599888155955</v>
       </c>
       <c r="E305" t="n">
-        <v>0.0001000000000000125</v>
+        <v>0.0412870950192728</v>
       </c>
     </row>
     <row r="306">
@@ -5628,16 +5628,16 @@
         <v>3.04</v>
       </c>
       <c r="B306" t="n">
-        <v>1.042540294934344</v>
+        <v>1.046065120113076</v>
       </c>
       <c r="C306" t="n">
-        <v>0.2345512248074261</v>
+        <v>0.2479998877473402</v>
       </c>
       <c r="D306" t="n">
-        <v>0.6865856816783728</v>
+        <v>0.6942803368509388</v>
       </c>
       <c r="E306" t="n">
-        <v>0.0001000000000000128</v>
+        <v>0.04203513840688795</v>
       </c>
     </row>
     <row r="307">
@@ -5645,16 +5645,16 @@
         <v>3.05</v>
       </c>
       <c r="B307" t="n">
-        <v>1.03463205375794</v>
+        <v>1.038303813355655</v>
       </c>
       <c r="C307" t="n">
-        <v>0.2309338089889183</v>
+        <v>0.2446422326105685</v>
       </c>
       <c r="D307" t="n">
-        <v>0.6861445342648542</v>
+        <v>0.6946195547074203</v>
       </c>
       <c r="E307" t="n">
-        <v>0.000100000000000013</v>
+        <v>0.04279290330612218</v>
       </c>
     </row>
     <row r="308">
@@ -5662,16 +5662,16 @@
         <v>3.06</v>
       </c>
       <c r="B308" t="n">
-        <v>1.026843767116498</v>
+        <v>1.030664122540615</v>
       </c>
       <c r="C308" t="n">
-        <v>0.2272713052964195</v>
+        <v>0.2412429080636396</v>
       </c>
       <c r="D308" t="n">
-        <v>0.685601647236629</v>
+        <v>0.6948764027369081</v>
       </c>
       <c r="E308" t="n">
-        <v>0.0001000000000000133</v>
+        <v>0.04356045212090388</v>
       </c>
     </row>
     <row r="309">
@@ -5679,16 +5679,16 @@
         <v>3.07</v>
       </c>
       <c r="B309" t="n">
-        <v>1.019175182136272</v>
+        <v>1.023145805603741</v>
       </c>
       <c r="C309" t="n">
-        <v>0.2235634380744793</v>
+        <v>0.2378016607303952</v>
       </c>
       <c r="D309" t="n">
-        <v>0.6849559338706093</v>
+        <v>0.6950496686727613</v>
       </c>
       <c r="E309" t="n">
-        <v>0.0001000000000000135</v>
+        <v>0.04433784725516158</v>
       </c>
     </row>
     <row r="310">
@@ -5696,16 +5696,16 @@
         <v>3.08</v>
       </c>
       <c r="B310" t="n">
-        <v>1.011626034005591</v>
+        <v>1.015748609965631</v>
       </c>
       <c r="C310" t="n">
-        <v>0.2198099316676484</v>
+        <v>0.2343182372346778</v>
       </c>
       <c r="D310" t="n">
-        <v>0.6842063583191369</v>
+        <v>0.6951381690226446</v>
       </c>
       <c r="E310" t="n">
-        <v>0.0001000000000000138</v>
+        <v>0.04512515111282369</v>
       </c>
     </row>
     <row r="311">
@@ -5713,16 +5713,16 @@
         <v>3.09</v>
       </c>
       <c r="B311" t="n">
-        <v>1.004196047091442</v>
+        <v>1.008472273676003</v>
       </c>
       <c r="C311" t="n">
-        <v>0.2160105104204769</v>
+        <v>0.2307923842003292</v>
       </c>
       <c r="D311" t="n">
-        <v>0.6833519373922242</v>
+        <v>0.6951407504637642</v>
       </c>
       <c r="E311" t="n">
-        <v>0.000100000000000014</v>
+        <v>0.04592242609781873</v>
       </c>
     </row>
     <row r="312">
@@ -5730,16 +5730,16 @@
         <v>3.1</v>
       </c>
       <c r="B312" t="n">
-        <v>0.9968849360403325</v>
+        <v>1.00131652654265</v>
       </c>
       <c r="C312" t="n">
-        <v>0.2121648986775148</v>
+        <v>0.2272238482511915</v>
       </c>
       <c r="D312" t="n">
-        <v>0.6823917423173697</v>
+        <v>0.6950562912388005</v>
       </c>
       <c r="E312" t="n">
-        <v>0.0001000000000000143</v>
+        <v>0.04672973461407516</v>
       </c>
     </row>
     <row r="313">
@@ -5747,16 +5747,16 @@
         <v>3.11</v>
       </c>
       <c r="B313" t="n">
-        <v>0.9896924068637172</v>
+        <v>0.9942810912453899</v>
       </c>
       <c r="C313" t="n">
-        <v>0.2082728207833126</v>
+        <v>0.2236123760111068</v>
       </c>
       <c r="D313" t="n">
-        <v>0.6813249004737957</v>
+        <v>0.6948837025507585</v>
       </c>
       <c r="E313" t="n">
-        <v>0.0001000000000000145</v>
+        <v>0.04754713906552142</v>
       </c>
     </row>
     <row r="314">
@@ -5764,16 +5764,16 @@
         <v>3.12</v>
       </c>
       <c r="B314" t="n">
-        <v>0.9826181580083067</v>
+        <v>0.9873656844353835</v>
       </c>
       <c r="C314" t="n">
-        <v>0.2043340010824204</v>
+        <v>0.219957714103917</v>
       </c>
       <c r="D314" t="n">
-        <v>0.6801505970979156</v>
+        <v>0.694621929954919</v>
       </c>
       <c r="E314" t="n">
-        <v>0.0001000000000000148</v>
+        <v>0.04837470185608604</v>
       </c>
     </row>
     <row r="315">
@@ -5781,16 +5781,16 @@
         <v>3.13</v>
       </c>
       <c r="B315" t="n">
-        <v>0.975661881411607</v>
+        <v>0.9805700178202293</v>
       </c>
       <c r="C315" t="n">
-        <v>0.2003481639193885</v>
+        <v>0.2162596091534646</v>
       </c>
       <c r="D315" t="n">
-        <v>0.6788680769568025</v>
+        <v>0.6942699547460223</v>
       </c>
       <c r="E315" t="n">
-        <v>0.0001000000000000151</v>
+        <v>0.0492124853896974</v>
       </c>
     </row>
     <row r="316">
@@ -5798,16 +5798,16 @@
         <v>3.14</v>
       </c>
       <c r="B316" t="n">
-        <v>0.968823263543049</v>
+        <v>0.9738937992352662</v>
       </c>
       <c r="C316" t="n">
-        <v>0.1963150336387669</v>
+        <v>0.2125178077835911</v>
       </c>
       <c r="D316" t="n">
-        <v>0.677476645986404</v>
+        <v>0.6938267953387757</v>
       </c>
       <c r="E316" t="n">
-        <v>0.0001000000000000153</v>
+        <v>0.05006055207028406</v>
       </c>
     </row>
     <row r="317">
@@ -5815,16 +5815,16 @@
         <v>3.15</v>
       </c>
       <c r="B317" t="n">
-        <v>0.9621019864311076</v>
+        <v>0.9673367337015396</v>
       </c>
       <c r="C317" t="n">
-        <v>0.1922343345851061</v>
+        <v>0.208732056618139</v>
       </c>
       <c r="D317" t="n">
-        <v>0.6759756728912255</v>
+        <v>0.693291508639739</v>
       </c>
       <c r="E317" t="n">
-        <v>0.0001000000000000156</v>
+        <v>0.05091896430177442</v>
       </c>
     </row>
     <row r="318">
@@ -5832,16 +5832,16 @@
         <v>3.16</v>
       </c>
       <c r="B318" t="n">
-        <v>0.9554977286768171</v>
+        <v>0.9608985244709077</v>
       </c>
       <c r="C318" t="n">
-        <v>0.188105791102956</v>
+        <v>0.2049021022809499</v>
       </c>
       <c r="D318" t="n">
-        <v>0.6743645907021864</v>
+        <v>0.6926631914085971</v>
       </c>
       <c r="E318" t="n">
-        <v>0.0001000000000000159</v>
+        <v>0.05178778448809701</v>
       </c>
     </row>
     <row r="319">
@@ -5849,16 +5849,16 @@
         <v>3.17</v>
       </c>
       <c r="B319" t="n">
-        <v>0.9490101664541309</v>
+        <v>0.954578874058802</v>
       </c>
       <c r="C319" t="n">
-        <v>0.1839291275368672</v>
+        <v>0.2010276913958665</v>
       </c>
       <c r="D319" t="n">
-        <v>0.672642898289348</v>
+        <v>0.691940981606803</v>
       </c>
       <c r="E319" t="n">
-        <v>0.0001000000000000162</v>
+        <v>0.05266707503318024</v>
       </c>
     </row>
     <row r="320">
@@ -5866,16 +5866,16 @@
         <v>3.18</v>
       </c>
       <c r="B320" t="n">
-        <v>0.9426389744975743</v>
+        <v>0.948377485265161</v>
       </c>
       <c r="C320" t="n">
-        <v>0.1797040682313897</v>
+        <v>0.1971085705867302</v>
       </c>
       <c r="D320" t="n">
-        <v>0.6708101618262041</v>
+        <v>0.6911240597315327</v>
       </c>
       <c r="E320" t="n">
-        <v>0.0001000000000000164</v>
+        <v>0.05355689834095264</v>
       </c>
     </row>
     <row r="321">
@@ -5883,16 +5883,16 @@
         <v>3.19</v>
       </c>
       <c r="B321" t="n">
-        <v>0.9363838270776844</v>
+        <v>0.9422940621840962</v>
       </c>
       <c r="C321" t="n">
-        <v>0.1754303375310738</v>
+        <v>0.1931444864773837</v>
       </c>
       <c r="D321" t="n">
-        <v>0.6688660162022307</v>
+        <v>0.6902116501328707</v>
       </c>
       <c r="E321" t="n">
-        <v>0.0001000000000000167</v>
+        <v>0.05445731681534259</v>
       </c>
     </row>
     <row r="322">
@@ -5900,16 +5900,16 @@
         <v>3.2</v>
       </c>
       <c r="B322" t="n">
-        <v>0.9302443989647331</v>
+        <v>0.9363283112028669</v>
       </c>
       <c r="C322" t="n">
-        <v>0.1711076597804694</v>
+        <v>0.1891351856916684</v>
       </c>
       <c r="D322" t="n">
-        <v>0.6668101663804055</v>
+        <v>0.6892030223121123</v>
       </c>
       <c r="E322" t="n">
-        <v>0.000100000000000017</v>
+        <v>0.0553683928602787</v>
       </c>
     </row>
     <row r="323">
@@ -5917,16 +5917,16 @@
         <v>3.21</v>
       </c>
       <c r="B323" t="n">
-        <v>0.9242203663812647</v>
+        <v>0.9304799419907611</v>
       </c>
       <c r="C323" t="n">
-        <v>0.1667357593241274</v>
+        <v>0.185080414853427</v>
       </c>
       <c r="D323" t="n">
-        <v>0.6646423886964239</v>
+        <v>0.6880974921990513</v>
       </c>
       <c r="E323" t="n">
-        <v>0.0001000000000000173</v>
+        <v>0.05629018887968927</v>
       </c>
     </row>
     <row r="324">
@@ -5934,16 +5934,16 @@
         <v>3.22</v>
       </c>
       <c r="B324" t="n">
-        <v>0.918311407943986</v>
+        <v>0.9247486684784997</v>
       </c>
       <c r="C324" t="n">
-        <v>0.1623143605065972</v>
+        <v>0.180979920586501</v>
       </c>
       <c r="D324" t="n">
-        <v>0.6623625320963619</v>
+        <v>0.6868944234060953</v>
       </c>
       <c r="E324" t="n">
-        <v>0.0001000000000000176</v>
+        <v>0.05722276727750293</v>
       </c>
     </row>
     <row r="325">
@@ -5951,16 +5951,16 @@
         <v>3.23</v>
       </c>
       <c r="B325" t="n">
-        <v>0.9125172055955918</v>
+        <v>0.9191342098288235</v>
       </c>
       <c r="C325" t="n">
-        <v>0.1578431876724298</v>
+        <v>0.1768334495147329</v>
       </c>
       <c r="D325" t="n">
-        <v>0.6599705193095763</v>
+        <v>0.6855932284570395</v>
       </c>
       <c r="E325" t="n">
-        <v>0.0001000000000000179</v>
+        <v>0.05816619045764801</v>
       </c>
     </row>
     <row r="326">
@@ -5968,16 +5968,16 @@
         <v>3.24</v>
       </c>
       <c r="B326" t="n">
-        <v>0.9068374455270947</v>
+        <v>0.9136362913989107</v>
       </c>
       <c r="C326" t="n">
-        <v>0.1533219651661748</v>
+        <v>0.1726407482619644</v>
       </c>
       <c r="D326" t="n">
-        <v>0.6574663479536681</v>
+        <v>0.6841933699883104</v>
       </c>
       <c r="E326" t="n">
-        <v>0.0001000000000000182</v>
+        <v>0.05912052082405309</v>
       </c>
     </row>
     <row r="327">
@@ -5985,16 +5985,16 @@
         <v>3.25</v>
       </c>
       <c r="B327" t="n">
-        <v>0.901271819091283</v>
+        <v>0.9082546456953322</v>
       </c>
       <c r="C327" t="n">
-        <v>0.1487504173323828</v>
+        <v>0.168401563452038</v>
       </c>
       <c r="D327" t="n">
-        <v>0.6548500915683888</v>
+        <v>0.6826943619204865</v>
       </c>
       <c r="E327" t="n">
-        <v>0.0001000000000000185</v>
+        <v>0.06008582078064657</v>
       </c>
     </row>
     <row r="328">
@@ -6002,16 +6002,16 @@
         <v>3.26</v>
       </c>
       <c r="B328" t="n">
-        <v>0.8958200237079258</v>
+        <v>0.9029890133222437</v>
       </c>
       <c r="C328" t="n">
-        <v>0.1441282685156038</v>
+        <v>0.1641156417087953</v>
       </c>
       <c r="D328" t="n">
-        <v>0.6521219005754261</v>
+        <v>0.6810957705978974</v>
       </c>
       <c r="E328" t="n">
-        <v>0.0001000000000000188</v>
+        <v>0.06106215273135696</v>
       </c>
     </row>
     <row r="329">
@@ -6019,16 +6019,16 @@
         <v>3.27</v>
       </c>
       <c r="B329" t="n">
-        <v>0.890481763761379</v>
+        <v>0.8978391439235601</v>
       </c>
       <c r="C329" t="n">
-        <v>0.1394552430603883</v>
+        <v>0.1597827296560787</v>
       </c>
       <c r="D329" t="n">
-        <v>0.6492820031610677</v>
+        <v>0.6793972158940961</v>
       </c>
       <c r="E329" t="n">
-        <v>0.0001000000000000191</v>
+        <v>0.06204957908011268</v>
       </c>
     </row>
     <row r="330">
@@ -6036,16 +6036,16 @@
         <v>3.28</v>
       </c>
       <c r="B330" t="n">
-        <v>0.8852567514912597</v>
+        <v>0.8928047971198632</v>
       </c>
       <c r="C330" t="n">
-        <v>0.1347310653112861</v>
+        <v>0.15540257391773</v>
       </c>
       <c r="D330" t="n">
-        <v>0.6463307060788244</v>
+        <v>0.6775983722810029</v>
       </c>
       <c r="E330" t="n">
-        <v>0.0001000000000000194</v>
+        <v>0.06304816223084227</v>
       </c>
     </row>
     <row r="331">
@@ -6053,16 +6053,16 @@
         <v>3.29</v>
       </c>
       <c r="B331" t="n">
-        <v>0.8801447078768763</v>
+        <v>0.887885743440823</v>
       </c>
       <c r="C331" t="n">
-        <v>0.1299554596128479</v>
+        <v>0.1509749211175916</v>
       </c>
       <c r="D331" t="n">
-        <v>0.6432683953691672</v>
+        <v>0.6756989698595358</v>
       </c>
       <c r="E331" t="n">
-        <v>0.0001000000000000197</v>
+        <v>0.06405796458747412</v>
       </c>
     </row>
     <row r="332">
@@ -6070,16 +6070,16 @@
         <v>3.3</v>
       </c>
       <c r="B332" t="n">
-        <v>0.8751453635161263</v>
+        <v>0.8830817652539442</v>
       </c>
       <c r="C332" t="n">
-        <v>0.1251281503096234</v>
+        <v>0.1464995178795052</v>
       </c>
       <c r="D332" t="n">
-        <v>0.6400955369936304</v>
+        <v>0.6736987953495338</v>
       </c>
       <c r="E332" t="n">
-        <v>0.00010000000000002</v>
+        <v>0.06507904855393679</v>
       </c>
     </row>
     <row r="333">
@@ -6087,16 +6087,16 @@
         <v>3.31</v>
       </c>
       <c r="B333" t="n">
-        <v>0.8702584594995924</v>
+        <v>0.878392657690453</v>
       </c>
       <c r="C333" t="n">
-        <v>0.1202488617461633</v>
+        <v>0.1419761108273131</v>
       </c>
       <c r="D333" t="n">
-        <v>0.6368126773806289</v>
+        <v>0.6715976930368152</v>
       </c>
       <c r="E333" t="n">
-        <v>0.0001000000000000203</v>
+        <v>0.06611147653415865</v>
       </c>
     </row>
     <row r="334">
@@ -6104,16 +6104,16 @@
         <v>3.32</v>
       </c>
       <c r="B334" t="n">
-        <v>0.8654837482805818</v>
+        <v>0.873818229569184</v>
       </c>
       <c r="C334" t="n">
-        <v>0.1153173182670174</v>
+        <v>0.1374044465848571</v>
       </c>
       <c r="D334" t="n">
-        <v>0.6334204438804443</v>
+        <v>0.6693955656752186</v>
       </c>
       <c r="E334" t="n">
-        <v>0.0001000000000000206</v>
+        <v>0.06715531093206828</v>
       </c>
     </row>
     <row r="335">
@@ -6121,16 +6121,16 @@
         <v>3.33</v>
       </c>
       <c r="B335" t="n">
-        <v>0.8608209945418894</v>
+        <v>0.869358304319342</v>
       </c>
       <c r="C335" t="n">
-        <v>0.1103332442167363</v>
+        <v>0.1327842717759797</v>
       </c>
       <c r="D335" t="n">
-        <v>0.6299195451269579</v>
+        <v>0.6670923753415068</v>
       </c>
       <c r="E335" t="n">
-        <v>0.0001000000000000209</v>
+        <v>0.06821061415159403</v>
       </c>
     </row>
     <row r="336">
@@ -6138,16 +6138,16 @@
         <v>3.34</v>
       </c>
       <c r="B336" t="n">
-        <v>0.8562699760600667</v>
+        <v>0.8650127209030318</v>
       </c>
       <c r="C336" t="n">
-        <v>0.1052963639398702</v>
+        <v>0.1281153330245227</v>
       </c>
       <c r="D336" t="n">
-        <v>0.6263107713038194</v>
+        <v>0.6646881442410364</v>
       </c>
       <c r="E336" t="n">
-        <v>0.0001000000000000213</v>
+        <v>0.06927744859666442</v>
       </c>
     </row>
     <row r="337">
@@ -6155,16 +6155,16 @@
         <v>3.35</v>
       </c>
       <c r="B337" t="n">
-        <v>0.8518304845680198</v>
+        <v>0.8607813347384879</v>
       </c>
       <c r="C337" t="n">
-        <v>0.1002064017809689</v>
+        <v>0.1233973769543279</v>
       </c>
       <c r="D337" t="n">
-        <v>0.6225949943128856</v>
+        <v>0.6621829554621382</v>
       </c>
       <c r="E337" t="n">
-        <v>0.0001000000000000216</v>
+        <v>0.07035587667120799</v>
       </c>
     </row>
     <row r="338">
@@ -6172,16 +6172,16 @@
         <v>3.36</v>
       </c>
       <c r="B338" t="n">
-        <v>0.8475023266167699</v>
+        <v>0.8566640186249559</v>
       </c>
       <c r="C338" t="n">
-        <v>0.09506308208458303</v>
+        <v>0.1186301501892379</v>
       </c>
       <c r="D338" t="n">
-        <v>0.618773167842897</v>
+        <v>0.6595769536771853</v>
       </c>
       <c r="E338" t="n">
-        <v>0.0001000000000000219</v>
+        <v>0.07144596077915309</v>
       </c>
     </row>
     <row r="339">
@@ -6189,16 +6189,16 @@
         <v>3.37</v>
       </c>
       <c r="B339" t="n">
-        <v>0.843285324437231</v>
+        <v>0.8526606636701937</v>
       </c>
       <c r="C339" t="n">
-        <v>0.08986612919526249</v>
+        <v>0.1138133993530942</v>
       </c>
       <c r="D339" t="n">
-        <v>0.6148463273365066</v>
+        <v>0.6568703457883672</v>
       </c>
       <c r="E339" t="n">
-        <v>0.0001000000000000222</v>
+        <v>0.0725477633244283</v>
       </c>
     </row>
     <row r="340">
@@ -6206,16 +6206,16 @@
         <v>3.38</v>
       </c>
       <c r="B340" t="n">
-        <v>0.8391793168028934</v>
+        <v>0.8487711802216099</v>
       </c>
       <c r="C340" t="n">
-        <v>0.08461526745755804</v>
+        <v>0.1089468710697395</v>
       </c>
       <c r="D340" t="n">
-        <v>0.6108155898539368</v>
+        <v>0.6540634015162531</v>
       </c>
       <c r="E340" t="n">
-        <v>0.0001000000000000226</v>
+        <v>0.07366134671096199</v>
       </c>
     </row>
     <row r="341">
@@ -6223,16 +6223,16 @@
         <v>3.39</v>
       </c>
       <c r="B341" t="n">
-        <v>0.8351841598943142</v>
+        <v>0.8449954988020669</v>
       </c>
       <c r="C341" t="n">
-        <v>0.07931022121601922</v>
+        <v>0.1040303119630152</v>
       </c>
       <c r="D341" t="n">
-        <v>0.6066821538316977</v>
+        <v>0.6511564539292529</v>
       </c>
       <c r="E341" t="n">
-        <v>0.0001000000000000229</v>
+        <v>0.0747867733426827</v>
       </c>
     </row>
     <row r="342">
@@ -6240,16 +6240,16 @@
         <v>3.4</v>
       </c>
       <c r="B342" t="n">
-        <v>0.8312997281663455</v>
+        <v>0.8413335710514097</v>
       </c>
       <c r="C342" t="n">
-        <v>0.07395071481519677</v>
+        <v>0.09906346865676391</v>
       </c>
       <c r="D342" t="n">
-        <v>0.6024472987349754</v>
+        <v>0.6481498999121745</v>
       </c>
       <c r="E342" t="n">
-        <v>0.0001000000000000233</v>
+        <v>0.07592410562351887</v>
       </c>
     </row>
     <row r="343">
@@ -6257,16 +6257,16 @@
         <v>3.41</v>
       </c>
       <c r="B343" t="n">
-        <v>0.8275259152190571</v>
+        <v>0.8377853706748198</v>
       </c>
       <c r="C343" t="n">
-        <v>0.06853647259964052</v>
+        <v>0.09404608777482726</v>
       </c>
       <c r="D343" t="n">
-        <v>0.5981123846024718</v>
+        <v>0.6450442005721102</v>
       </c>
       <c r="E343" t="n">
-        <v>0.0001000000000000236</v>
+        <v>0.07707340595739898</v>
       </c>
     </row>
     <row r="344">
@@ -6274,16 +6274,16 @@
         <v>3.42</v>
       </c>
       <c r="B344" t="n">
-        <v>0.8238626346733341</v>
+        <v>0.8343508943991117</v>
       </c>
       <c r="C344" t="n">
-        <v>0.0630672189139011</v>
+        <v>0.0889779159410477</v>
       </c>
       <c r="D344" t="n">
-        <v>0.5936788514826623</v>
+        <v>0.6418398815799784</v>
       </c>
       <c r="E344" t="n">
-        <v>0.0001000000000000239</v>
+        <v>0.07823473674825146</v>
       </c>
     </row>
     <row r="345">
@@ -6291,16 +6291,16 @@
         <v>3.43</v>
       </c>
       <c r="B345" t="n">
-        <v>0.8203098210521557</v>
+        <v>0.8310301629381347</v>
       </c>
       <c r="C345" t="n">
-        <v>0.05754267810252822</v>
+        <v>0.08385869977926691</v>
       </c>
       <c r="D345" t="n">
-        <v>0.5891482187606355</v>
+        <v>0.6385375334460962</v>
       </c>
       <c r="E345" t="n">
-        <v>0.0001000000000000243</v>
+        <v>0.07940816040000488</v>
       </c>
     </row>
     <row r="346">
@@ -6308,16 +6308,16 @@
         <v>3.44</v>
       </c>
       <c r="B346" t="n">
-        <v>0.8168674306685971</v>
+        <v>0.827823221968471</v>
       </c>
       <c r="C346" t="n">
-        <v>0.05196257451007269</v>
+        <v>0.07868818591332732</v>
       </c>
       <c r="D346" t="n">
-        <v>0.5845220843748622</v>
+        <v>0.6351378117282603</v>
       </c>
       <c r="E346" t="n">
-        <v>0.0001000000000000246</v>
+        <v>0.08059373931658759</v>
       </c>
     </row>
     <row r="347">
@@ -6325,16 +6325,16 @@
         <v>3.45</v>
       </c>
       <c r="B347" t="n">
-        <v>0.813535442521608</v>
+        <v>0.8247301431166494</v>
       </c>
       <c r="C347" t="n">
-        <v>0.04632663248108421</v>
+        <v>0.07346612096707067</v>
       </c>
       <c r="D347" t="n">
-        <v>0.5798021239234531</v>
+        <v>0.6316414371708722</v>
       </c>
       <c r="E347" t="n">
-        <v>0.000100000000000025</v>
+        <v>0.08179153590192814</v>
       </c>
     </row>
     <row r="348">
@@ -6342,16 +6342,16 @@
         <v>3.46</v>
       </c>
       <c r="B348" t="n">
-        <v>0.8103138592006807</v>
+        <v>0.8217510249591505</v>
       </c>
       <c r="C348" t="n">
-        <v>0.04063457636011342</v>
+        <v>0.06819225156433933</v>
       </c>
       <c r="D348" t="n">
-        <v>0.5749900896596708</v>
+        <v>0.6280491957737522</v>
       </c>
       <c r="E348" t="n">
-        <v>0.0001000000000000254</v>
+        <v>0.08300161255995495</v>
       </c>
     </row>
     <row r="349">
@@ -6359,16 +6359,16 @@
         <v>3.47</v>
       </c>
       <c r="B349" t="n">
-        <v>0.8072027078005147</v>
+        <v>0.8188859940364933</v>
       </c>
       <c r="C349" t="n">
-        <v>0.03488613049171013</v>
+        <v>0.06286632432897499</v>
       </c>
       <c r="D349" t="n">
-        <v>0.5700878093766677</v>
+        <v>0.6243619387893645</v>
       </c>
       <c r="E349" t="n">
-        <v>0.0001000000000000257</v>
+        <v>0.08422403169459652</v>
       </c>
     </row>
     <row r="350">
@@ -6376,16 +6376,16 @@
         <v>3.48</v>
       </c>
       <c r="B350" t="n">
-        <v>0.8042020408468542</v>
+        <v>0.816135205882754</v>
       </c>
       <c r="C350" t="n">
-        <v>0.029081019220425</v>
+        <v>0.05748808588482018</v>
       </c>
       <c r="D350" t="n">
-        <v>0.5650971851816492</v>
+        <v>0.6205805826472794</v>
       </c>
       <c r="E350" t="n">
-        <v>0.0001000000000000261</v>
+        <v>0.0854588557097813</v>
       </c>
     </row>
     <row r="351">
@@ -6393,16 +6393,16 @@
         <v>3.49</v>
       </c>
       <c r="B351" t="n">
-        <v>0.801311937234679</v>
+        <v>0.8134988460718932</v>
       </c>
       <c r="C351" t="n">
-        <v>0.02321896689080788</v>
+        <v>0.05205728285571648</v>
       </c>
       <c r="D351" t="n">
-        <v>0.560020192159864</v>
+        <v>0.6167061088047943</v>
       </c>
       <c r="E351" t="n">
-        <v>0.0001000000000000264</v>
+        <v>0.0867061470094378</v>
       </c>
     </row>
     <row r="352">
@@ -6410,16 +6410,16 @@
         <v>3.5</v>
       </c>
       <c r="B352" t="n">
-        <v>0.7985325031799861</v>
+        <v>0.810977131282329</v>
       </c>
       <c r="C352" t="n">
-        <v>0.01729969784740926</v>
+        <v>0.04657366186550638</v>
       </c>
       <c r="D352" t="n">
-        <v>0.5548588769290708</v>
+        <v>0.6127395635227495</v>
       </c>
       <c r="E352" t="n">
-        <v>0.0001000000000000268</v>
+        <v>0.08796596799749443</v>
       </c>
     </row>
   </sheetData>

--- a/01_Thermal/B_results/single_annular_var_params_pchip.xlsx
+++ b/01_Thermal/B_results/single_annular_var_params_pchip.xlsx
@@ -460,16 +460,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>0.01</v>
       </c>
       <c r="B3" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>0.02</v>
       </c>
       <c r="B4" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>0.03</v>
       </c>
       <c r="B5" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>0.04</v>
       </c>
       <c r="B6" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>0.05</v>
       </c>
       <c r="B7" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>0.06</v>
       </c>
       <c r="B8" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>0.08</v>
       </c>
       <c r="B10" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>0.09</v>
       </c>
       <c r="B11" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>0.11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>0.12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>0.13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>0.14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>0.15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>0.16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>0.17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>0.18</v>
       </c>
       <c r="B20" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>0.19</v>
       </c>
       <c r="B21" t="n">
-        <v>4.916295944828834</v>
+        <v>4.993168672000794</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="22">
@@ -800,16 +800,16 @@
         <v>0.2</v>
       </c>
       <c r="B22" t="n">
-        <v>4.916295944828835</v>
+        <v>4.993168672000795</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3066769217402805</v>
+        <v>0.3064636545788689</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2018969531010486</v>
+        <v>0.2076436482913198</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1193549673528184</v>
+        <v>0.04186236843006413</v>
       </c>
     </row>
     <row r="23">
@@ -817,16 +817,16 @@
         <v>0.21</v>
       </c>
       <c r="B23" t="n">
-        <v>4.878661060304989</v>
+        <v>4.974465549734321</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3067913214307943</v>
+        <v>0.3066462517610565</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2107387131634375</v>
+        <v>0.2123751448592523</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1081366855896947</v>
+        <v>0.03862874776558042</v>
       </c>
     </row>
     <row r="24">
@@ -834,16 +834,16 @@
         <v>0.22</v>
       </c>
       <c r="B24" t="n">
-        <v>4.842067008035257</v>
+        <v>4.955516466423386</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3071290049324162</v>
+        <v>0.3071820447064829</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2196210284283484</v>
+        <v>0.217147105498865</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09710616519411353</v>
+        <v>0.03550268756723568</v>
       </c>
     </row>
     <row r="25">
@@ -851,16 +851,16 @@
         <v>0.23</v>
       </c>
       <c r="B25" t="n">
-        <v>4.806615897947761</v>
+        <v>4.936330402872245</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3076816988902676</v>
+        <v>0.3080530355134432</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2284703290732541</v>
+        <v>0.2219165358904686</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08635024509555114</v>
+        <v>0.03250129850527321</v>
       </c>
     </row>
     <row r="26">
@@ -868,16 +868,16 @@
         <v>0.24</v>
       </c>
       <c r="B26" t="n">
-        <v>4.772406986792324</v>
+        <v>4.916916284708108</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3084411299494694</v>
+        <v>0.3092412262802323</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2372046692948225</v>
+        <v>0.2266368321116308</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0759557642234838</v>
+        <v>0.02964169124993631</v>
       </c>
     </row>
     <row r="27">
@@ -885,16 +885,16 @@
         <v>0.25</v>
       </c>
       <c r="B27" t="n">
-        <v>4.739536955272539</v>
+        <v>4.897282978794946</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3093990247551426</v>
+        <v>0.3107286191051455</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2457341139056164</v>
+        <v>0.2312578418113483</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06600956150738763</v>
+        <v>0.02694097647146824</v>
       </c>
     </row>
     <row r="28">
@@ -902,16 +902,16 @@
         <v>0.26</v>
       </c>
       <c r="B28" t="n">
-        <v>4.708100205181494</v>
+        <v>4.877439289780604</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3105471099524084</v>
+        <v>0.3124972160864778</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2539613991834851</v>
+        <v>0.2357260288824285</v>
       </c>
       <c r="E28" t="n">
-        <v>0.05659847587673891</v>
+        <v>0.02441626484011232</v>
       </c>
     </row>
     <row r="29">
@@ -919,16 +919,16 @@
         <v>0.27</v>
       </c>
       <c r="B29" t="n">
-        <v>4.678189175873423</v>
+        <v>4.857393956776929</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3118771121863879</v>
+        <v>0.3145290193225245</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2617828936830937</v>
+        <v>0.2399847526658876</v>
       </c>
       <c r="E29" t="n">
-        <v>0.04780934626101385</v>
+        <v>0.02208466702611182</v>
       </c>
     </row>
     <row r="30">
@@ -936,16 +936,16 @@
         <v>0.28</v>
       </c>
       <c r="B30" t="n">
-        <v>4.649894679601542</v>
+        <v>4.837155650172464</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3133807581022022</v>
+        <v>0.3168060309115806</v>
       </c>
       <c r="D30" t="n">
-        <v>0.269089877449682</v>
+        <v>0.2439746713770499</v>
       </c>
       <c r="E30" t="n">
-        <v>0.03972901158968865</v>
+        <v>0.01996329369971003</v>
       </c>
     </row>
     <row r="31">
@@ -953,16 +953,16 @@
         <v>0.29</v>
       </c>
       <c r="B31" t="n">
-        <v>4.623306255461236</v>
+        <v>4.816732968577167</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3150497743449722</v>
+        <v>0.3193102529519412</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2757701484183793</v>
+        <v>0.2476342773773474</v>
       </c>
       <c r="E31" t="n">
-        <v>0.03244431079223957</v>
+        <v>0.01806925553115027</v>
       </c>
     </row>
     <row r="32">
@@ -970,16 +970,16 @@
         <v>0.3</v>
       </c>
       <c r="B32" t="n">
-        <v>4.598512541898093</v>
+        <v>4.796134435898425</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3168758875598192</v>
+        <v>0.3220236875419015</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2817099527684763</v>
+        <v>0.2509005690770478</v>
       </c>
       <c r="E32" t="n">
-        <v>0.02604208279814274</v>
+        <v>0.01641966319067579</v>
       </c>
     </row>
     <row r="33">
@@ -987,16 +987,16 @@
         <v>0.31</v>
       </c>
       <c r="B33" t="n">
-        <v>4.575601667972243</v>
+        <v>4.775368498547622</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3188508243918641</v>
+        <v>0.3249283367797565</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2867962218223767</v>
+        <v>0.2537098606191439</v>
       </c>
       <c r="E33" t="n">
-        <v>0.02060916653687445</v>
+        <v>0.0150316273485299</v>
       </c>
     </row>
     <row r="34">
@@ -1004,16 +1004,16 @@
         <v>0.32</v>
       </c>
       <c r="B34" t="n">
-        <v>4.554661663814586</v>
+        <v>4.754443522776236</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3209663114862282</v>
+        <v>0.3280062027638015</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2909190821109755</v>
+        <v>0.2559987260775293</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01623240093791087</v>
+        <v>0.01392225867495589</v>
       </c>
     </row>
     <row r="35">
@@ -1021,16 +1021,16 @@
         <v>0.33</v>
       </c>
       <c r="B35" t="n">
-        <v>4.535780890968005</v>
+        <v>4.733367792140534</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3232140754880323</v>
+        <v>0.3312392875923315</v>
       </c>
       <c r="D35" t="n">
-        <v>0.29397458805018</v>
+        <v>0.257705069763072</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01299862493072824</v>
+        <v>0.01310866784019704</v>
       </c>
     </row>
     <row r="36">
@@ -1038,16 +1038,16 @@
         <v>0.34</v>
       </c>
       <c r="B36" t="n">
-        <v>4.519048493578473</v>
+        <v>4.712149505093636</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3255858430423978</v>
+        <v>0.3346095933636415</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2958676090706954</v>
+        <v>0.2587693084818135</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01099467744480279</v>
+        <v>0.01260796551449666</v>
       </c>
     </row>
     <row r="37">
@@ -1055,16 +1055,16 @@
         <v>0.35</v>
       </c>
       <c r="B37" t="n">
-        <v>4.504554871688979</v>
+        <v>4.690796772703752</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3280733407944455</v>
+        <v>0.3380991221760268</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2965147859884885</v>
+        <v>0.2591356454008263</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01030739740961069</v>
+        <v>0.01243726236809802</v>
       </c>
     </row>
     <row r="38">
@@ -1072,16 +1072,16 @@
         <v>0.36</v>
       </c>
       <c r="B38" t="n">
-        <v>4.492162571721678</v>
+        <v>4.669522448014706</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3325223279547383</v>
+        <v>0.3433015360046257</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2959319004499767</v>
+        <v>0.2590889323853326</v>
       </c>
       <c r="E38" t="n">
-        <v>0.01045205290417247</v>
+        <v>0.0125669070755485</v>
       </c>
     </row>
     <row r="39">
@@ -1089,16 +1089,16 @@
         <v>0.37</v>
       </c>
       <c r="B39" t="n">
-        <v>4.48148090417604</v>
+        <v>4.648462142639723</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3404136354718398</v>
+        <v>0.3514918205424901</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2942978290389194</v>
+        <v>0.2589575293142417</v>
       </c>
       <c r="E39" t="n">
-        <v>0.01085910673770678</v>
+        <v>0.01293172125232778</v>
       </c>
     </row>
     <row r="40">
@@ -1106,16 +1106,16 @@
         <v>0.38</v>
       </c>
       <c r="B40" t="n">
-        <v>4.472225077870323</v>
+        <v>4.62750948358536</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3511915975978725</v>
+        <v>0.362173963464786</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2917901758112764</v>
+        <v>0.2587545829138778</v>
       </c>
       <c r="E40" t="n">
-        <v>0.01148818993498708</v>
+        <v>0.01349552498007756</v>
       </c>
     </row>
     <row r="41">
@@ -1123,16 +1123,16 @@
         <v>0.39</v>
       </c>
       <c r="B41" t="n">
-        <v>4.464114112018759</v>
+        <v>4.606559998518676</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3643005485849587</v>
+        <v>0.3748519524466789</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2885898749584488</v>
+        <v>0.2584932662279519</v>
       </c>
       <c r="E41" t="n">
-        <v>0.01229893352078683</v>
+        <v>0.01422213834043957</v>
       </c>
     </row>
     <row r="42">
@@ -1140,16 +1140,16 @@
         <v>0.4</v>
       </c>
       <c r="B42" t="n">
-        <v>4.45687004061754</v>
+        <v>4.585511103211303</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3791848226852212</v>
+        <v>0.3890297751633348</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2848766256438352</v>
+        <v>0.2581867457541188</v>
       </c>
       <c r="E42" t="n">
-        <v>0.01325096851987948</v>
+        <v>0.01507538141505555</v>
       </c>
     </row>
     <row r="43">
@@ -1157,16 +1157,16 @@
         <v>0.41</v>
       </c>
       <c r="B43" t="n">
-        <v>4.450217292589179</v>
+        <v>4.56426211214447</v>
       </c>
       <c r="C43" t="n">
-        <v>0.3952887541507821</v>
+        <v>0.4042114192899193</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2808253638416682</v>
+        <v>0.2578481552350667</v>
       </c>
       <c r="E43" t="n">
-        <v>0.01430392595703849</v>
+        <v>0.01601907428556722</v>
       </c>
     </row>
     <row r="44">
@@ -1174,16 +1174,16 @@
         <v>0.42</v>
       </c>
       <c r="B44" t="n">
-        <v>4.443882244030197</v>
+        <v>4.542714271527228</v>
       </c>
       <c r="C44" t="n">
-        <v>0.412056677233764</v>
+        <v>0.4199008725015981</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2766037835406489</v>
+        <v>0.257490576115476</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0154174368570373</v>
+        <v>0.01701703703361629</v>
       </c>
     </row>
     <row r="45">
@@ -1191,16 +1191,16 @@
         <v>0.43</v>
       </c>
       <c r="B45" t="n">
-        <v>4.437592939827695</v>
+        <v>4.520770813966813</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4289329261862896</v>
+        <v>0.435602122473537</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2723708711641611</v>
+        <v>0.2571270246438136</v>
       </c>
       <c r="E45" t="n">
-        <v>0.01655113224464939</v>
+        <v>0.01803308974084451</v>
       </c>
     </row>
     <row r="46">
@@ -1208,16 +1208,16 @@
         <v>0.44</v>
       </c>
       <c r="B46" t="n">
-        <v>4.431078982534226</v>
+        <v>4.498337034002998</v>
       </c>
       <c r="C46" t="n">
-        <v>0.445361835260481</v>
+        <v>0.4508191568809021</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2682763852226191</v>
+        <v>0.2567704455749764</v>
       </c>
       <c r="E46" t="n">
-        <v>0.01766464314464822</v>
+        <v>0.01903105248889359</v>
       </c>
     </row>
     <row r="47">
@@ -1225,16 +1225,16 @@
         <v>0.45</v>
       </c>
       <c r="B47" t="n">
-        <v>4.424071586724375</v>
+        <v>4.475320383678668</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4607877387084607</v>
+        <v>0.4650559633988585</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2644611972639037</v>
+        <v>0.2564337124162292</v>
       </c>
       <c r="E47" t="n">
-        <v>0.01871760058180722</v>
+        <v>0.01997474535940525</v>
       </c>
     </row>
     <row r="48">
@@ -1242,16 +1242,16 @@
         <v>0.46</v>
       </c>
       <c r="B48" t="n">
-        <v>4.416303797105303</v>
+        <v>4.451630587267009</v>
       </c>
       <c r="C48" t="n">
-        <v>0.4746549707823515</v>
+        <v>0.4778165297025725</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2610584085845591</v>
+        <v>0.2561296341546033</v>
       </c>
       <c r="E48" t="n">
-        <v>0.01966963558089987</v>
+        <v>0.02082798843402123</v>
       </c>
     </row>
     <row r="49">
@@ -1259,16 +1259,16 @@
         <v>0.47</v>
       </c>
       <c r="B49" t="n">
-        <v>4.407510868421785</v>
+        <v>4.427179774212801</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4864078657342754</v>
+        <v>0.4886048434672097</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2581951680888568</v>
+        <v>0.2558709684088183</v>
       </c>
       <c r="E49" t="n">
-        <v>0.02048037916669961</v>
+        <v>0.02155460179438325</v>
       </c>
     </row>
     <row r="50">
@@ -1276,16 +1276,16 @@
         <v>0.48</v>
       </c>
       <c r="B50" t="n">
-        <v>4.397430804688746</v>
+        <v>4.401882629271871</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4954907578163553</v>
+        <v>0.4969248923679357</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2559951384497179</v>
+        <v>0.2556704409627398</v>
       </c>
       <c r="E50" t="n">
-        <v>0.02110946236397991</v>
+        <v>0.02211840552213303</v>
       </c>
     </row>
     <row r="51">
@@ -1293,16 +1293,16 @@
         <v>0.49</v>
       </c>
       <c r="B51" t="n">
-        <v>4.385805054506567</v>
+        <v>4.375656558750043</v>
       </c>
       <c r="C51" t="n">
-        <v>0.5013479812807133</v>
+        <v>0.5022806640799165</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2545815891281534</v>
+        <v>0.25554077166031</v>
       </c>
       <c r="E51" t="n">
-        <v>0.02151651619751422</v>
+        <v>0.02248321969891229</v>
       </c>
     </row>
     <row r="52">
@@ -1310,16 +1310,16 @@
         <v>0.5</v>
       </c>
       <c r="B52" t="n">
-        <v>4.372379358174996</v>
+        <v>4.348421871651814</v>
       </c>
       <c r="C52" t="n">
-        <v>0.5034238703794722</v>
+        <v>0.5041761462783177</v>
       </c>
       <c r="D52" t="n">
-        <v>0.2540811354115556</v>
+        <v>0.2554947066737376</v>
       </c>
       <c r="E52" t="n">
-        <v>0.02166117169207601</v>
+        <v>0.02261286440636278</v>
       </c>
     </row>
     <row r="53">
@@ -1327,16 +1327,16 @@
         <v>0.51</v>
       </c>
       <c r="B53" t="n">
-        <v>4.352971136117175</v>
+        <v>4.319788064759612</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5028084141744932</v>
+        <v>0.5039021255780184</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2546875768097981</v>
+        <v>0.2557111802770906</v>
       </c>
       <c r="E53" t="n">
-        <v>0.02164937158111585</v>
+        <v>0.02260417595106012</v>
       </c>
     </row>
     <row r="54">
@@ -1344,16 +1344,16 @@
         <v>0.52</v>
       </c>
       <c r="B54" t="n">
-        <v>4.324160039111483</v>
+        <v>4.289516896086689</v>
       </c>
       <c r="C54" t="n">
-        <v>0.5010294928148962</v>
+        <v>0.5031071824116145</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2564485921568287</v>
+        <v>0.2563424293900664</v>
       </c>
       <c r="E54" t="n">
-        <v>0.02161484361923466</v>
+        <v>0.02257867249586247</v>
       </c>
     </row>
     <row r="55">
@@ -1361,16 +1361,16 @@
         <v>0.53</v>
       </c>
       <c r="B55" t="n">
-        <v>4.286869636350116</v>
+        <v>4.257758326450918</v>
       </c>
       <c r="C55" t="n">
-        <v>0.4981882771836914</v>
+        <v>0.5018319951808476</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2592864980460822</v>
+        <v>0.2573625008736407</v>
       </c>
       <c r="E55" t="n">
-        <v>0.02155889636293135</v>
+        <v>0.02253719690683536</v>
       </c>
     </row>
     <row r="56">
@@ -1378,16 +1378,16 @@
         <v>0.54</v>
       </c>
       <c r="B56" t="n">
-        <v>4.242050824730428</v>
+        <v>4.22466055798709</v>
       </c>
       <c r="C56" t="n">
-        <v>0.4943859381638893</v>
+        <v>0.5001172422874595</v>
       </c>
       <c r="D56" t="n">
-        <v>0.2631336059083221</v>
+        <v>0.2587468417177509</v>
       </c>
       <c r="E56" t="n">
-        <v>0.02148283836870486</v>
+        <v>0.02248059205004431</v>
       </c>
     </row>
     <row r="57">
@@ -1395,16 +1395,16 @@
         <v>0.55</v>
       </c>
       <c r="B57" t="n">
-        <v>4.190666090973953</v>
+        <v>4.19036959549012</v>
       </c>
       <c r="C57" t="n">
-        <v>0.4897236466384999</v>
+        <v>0.4980036021331914</v>
       </c>
       <c r="D57" t="n">
-        <v>0.2679287831387771</v>
+        <v>0.2604719059951638</v>
       </c>
       <c r="E57" t="n">
-        <v>0.02138797819305412</v>
+        <v>0.02240970079155483</v>
       </c>
     </row>
     <row r="58">
@@ -1412,16 +1412,16 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58" t="n">
-        <v>4.133675441894602</v>
+        <v>4.155028853951166</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4843025734905336</v>
+        <v>0.495531753119785</v>
       </c>
       <c r="D58" t="n">
-        <v>0.2736143511629143</v>
+        <v>0.2625147943453541</v>
       </c>
       <c r="E58" t="n">
-        <v>0.02127562439247804</v>
+        <v>0.02232536599743245</v>
       </c>
     </row>
     <row r="59">
@@ -1429,16 +1429,16 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59" t="n">
-        <v>4.072024145871232</v>
+        <v>4.118778811827315</v>
       </c>
       <c r="C59" t="n">
-        <v>0.4782238896030007</v>
+        <v>0.492742373648982</v>
       </c>
       <c r="D59" t="n">
-        <v>0.2801332288520516</v>
+        <v>0.2648529218423381</v>
       </c>
       <c r="E59" t="n">
-        <v>0.02114708552347555</v>
+        <v>0.02222843053374267</v>
       </c>
     </row>
     <row r="60">
@@ -1446,16 +1446,16 @@
         <v>0.58</v>
       </c>
       <c r="B60" t="n">
-        <v>4.00663235889122</v>
+        <v>4.081756709274041</v>
       </c>
       <c r="C60" t="n">
-        <v>0.4715887658589115</v>
+        <v>0.4896761421225237</v>
       </c>
       <c r="D60" t="n">
-        <v>0.287426258950021</v>
+        <v>0.2674637111569573</v>
       </c>
       <c r="E60" t="n">
-        <v>0.02100367014254559</v>
+        <v>0.02211973726655103</v>
       </c>
     </row>
     <row r="61">
@@ -1463,16 +1463,16 @@
         <v>0.59</v>
       </c>
       <c r="B61" t="n">
-        <v>3.938386647495419</v>
+        <v>4.044096290296146</v>
       </c>
       <c r="C61" t="n">
-        <v>0.4644983731412759</v>
+        <v>0.4863737369421518</v>
       </c>
       <c r="D61" t="n">
-        <v>0.2954296809190959</v>
+        <v>0.2703243088713929</v>
       </c>
       <c r="E61" t="n">
-        <v>0.02084668680618706</v>
+        <v>0.02200012906192304</v>
       </c>
     </row>
     <row r="62">
@@ -1480,16 +1480,16 @@
         <v>0.6</v>
       </c>
       <c r="B62" t="n">
-        <v>3.868133369553209</v>
+        <v>4.005927587537109</v>
       </c>
       <c r="C62" t="n">
-        <v>0.4570538823331045</v>
+        <v>0.4828758365096077</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3040727371965491</v>
+        <v>0.2734113236617075</v>
       </c>
       <c r="E62" t="n">
-        <v>0.02067744407089891</v>
+        <v>0.02187044878592421</v>
       </c>
     </row>
     <row r="63">
@@ -1497,16 +1497,16 @@
         <v>0.61</v>
       </c>
       <c r="B63" t="n">
-        <v>3.796673832434567</v>
+        <v>3.967376748227751</v>
       </c>
       <c r="C63" t="n">
-        <v>0.4493564643174074</v>
+        <v>0.4792231192266331</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3132754221339709</v>
+        <v>0.2767005858474697</v>
       </c>
       <c r="E63" t="n">
-        <v>0.02049725049318005</v>
+        <v>0.02173153930462007</v>
       </c>
     </row>
     <row r="64">
@@ -1514,16 +1514,16 @@
         <v>0.62</v>
       </c>
       <c r="B64" t="n">
-        <v>3.724761116744197</v>
+        <v>3.928565899651808</v>
       </c>
       <c r="C64" t="n">
-        <v>0.441507289977195</v>
+        <v>0.4754562634949694</v>
       </c>
       <c r="D64" t="n">
-        <v>0.322946404307271</v>
+        <v>0.2801669285256989</v>
       </c>
       <c r="E64" t="n">
-        <v>0.02030741462952941</v>
+        <v>0.02158424348407614</v>
       </c>
     </row>
     <row r="65">
@@ -1531,16 +1531,16 @@
         <v>0.63</v>
       </c>
       <c r="B65" t="n">
-        <v>3.653098431878174</v>
+        <v>3.889613052356914</v>
       </c>
       <c r="C65" t="n">
-        <v>0.4336075301954774</v>
+        <v>0.4716159477163583</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3329811734751759</v>
+        <v>0.2837839911648566</v>
       </c>
       <c r="E65" t="n">
-        <v>0.02010924503644593</v>
+        <v>0.02142940419035793</v>
       </c>
     </row>
     <row r="66">
@@ -1548,16 +1548,16 @@
         <v>0.64</v>
       </c>
       <c r="B66" t="n">
-        <v>3.582338856511157</v>
+        <v>3.850632039242941</v>
       </c>
       <c r="C66" t="n">
-        <v>0.425758355855265</v>
+        <v>0.4677428502925412</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3432604828789818</v>
+        <v>0.2875240471348188</v>
       </c>
       <c r="E66" t="n">
-        <v>0.01990405027042851</v>
+        <v>0.02126786428953096</v>
       </c>
     </row>
     <row r="67">
@@ -1565,16 +1565,16 @@
         <v>0.65</v>
       </c>
       <c r="B67" t="n">
-        <v>3.513086311791973</v>
+        <v>3.811732488593744</v>
       </c>
       <c r="C67" t="n">
-        <v>0.4180609378395679</v>
+        <v>0.4638776496252597</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3536491750864014</v>
+        <v>0.2913578571885553</v>
       </c>
       <c r="E67" t="n">
-        <v>0.01969313888797609</v>
+        <v>0.02110046664766075</v>
       </c>
     </row>
     <row r="68">
@@ -1582,16 +1582,16 @@
         <v>0.66</v>
       </c>
       <c r="B68" t="n">
-        <v>3.445897616488558</v>
+        <v>3.773019829081196</v>
       </c>
       <c r="C68" t="n">
-        <v>0.4106164470313965</v>
+        <v>0.4600610241162554</v>
       </c>
       <c r="D68" t="n">
-        <v>0.363995494092797</v>
+        <v>0.2952545513851961</v>
       </c>
       <c r="E68" t="n">
-        <v>0.01947781944558759</v>
+        <v>0.02092805413081282</v>
       </c>
     </row>
     <row r="69">
@@ -1599,16 +1599,16 @@
         <v>0.67</v>
       </c>
       <c r="B69" t="n">
-        <v>3.381285480527907</v>
+        <v>3.734595324759705</v>
       </c>
       <c r="C69" t="n">
-        <v>0.403526054313761</v>
+        <v>0.4563336521672698</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3741309964811614</v>
+        <v>0.2991815423439111</v>
       </c>
       <c r="E69" t="n">
-        <v>0.01925940049976195</v>
+        <v>0.0207514696050527</v>
       </c>
     </row>
     <row r="70">
@@ -1616,16 +1616,16 @@
         <v>0.68</v>
       </c>
       <c r="B70" t="n">
-        <v>3.319722305310512</v>
+        <v>3.696556138083313</v>
       </c>
       <c r="C70" t="n">
-        <v>0.3968909305696717</v>
+        <v>0.4527362121800444</v>
       </c>
       <c r="D70" t="n">
-        <v>0.3838711784263797</v>
+        <v>0.3031044730326603</v>
       </c>
       <c r="E70" t="n">
-        <v>0.01903919060699808</v>
+        <v>0.02057155593644588</v>
       </c>
     </row>
     <row r="71">
@@ -1633,16 +1633,16 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71" t="n">
-        <v>3.261644674918248</v>
+        <v>3.658995419013588</v>
       </c>
       <c r="C71" t="n">
-        <v>0.3908122466821388</v>
+        <v>0.4493093825563207</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3930169313808969</v>
+        <v>0.3069872025122955</v>
       </c>
       <c r="E71" t="n">
-        <v>0.01881849832379491</v>
+        <v>0.02038915599105791</v>
       </c>
     </row>
     <row r="72">
@@ -1650,16 +1650,16 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72" t="n">
-        <v>3.207458441083491</v>
+        <v>3.622002418342992</v>
       </c>
       <c r="C72" t="n">
-        <v>0.3853911735341725</v>
+        <v>0.4460938416978404</v>
       </c>
       <c r="D72" t="n">
-        <v>0.401356925583186</v>
+        <v>0.3107918331600629</v>
       </c>
       <c r="E72" t="n">
-        <v>0.01859863220665136</v>
+        <v>0.02020511263495429</v>
       </c>
     </row>
     <row r="73">
@@ -1667,16 +1667,16 @@
         <v>0.71</v>
       </c>
       <c r="B73" t="n">
-        <v>3.157544325903925</v>
+        <v>3.585662623432996</v>
       </c>
       <c r="C73" t="n">
-        <v>0.3807288820087832</v>
+        <v>0.443130268006345</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4086709954991071</v>
+        <v>0.3144787828715873</v>
       </c>
       <c r="E73" t="n">
-        <v>0.01838090081206637</v>
+        <v>0.02002026873420054</v>
       </c>
     </row>
     <row r="74">
@@ -1684,16 +1684,16 @@
         <v>0.72</v>
       </c>
       <c r="B74" t="n">
-        <v>3.112263989305328</v>
+        <v>3.55005791465718</v>
       </c>
       <c r="C74" t="n">
-        <v>0.376926542988981</v>
+        <v>0.440459339883576</v>
       </c>
       <c r="D74" t="n">
-        <v>0.414734563836455</v>
+        <v>0.3180069055710505</v>
       </c>
       <c r="E74" t="n">
-        <v>0.01816661269653886</v>
+        <v>0.01983546715486219</v>
       </c>
     </row>
     <row r="75">
@@ -1701,16 +1701,16 @@
         <v>0.73</v>
       </c>
       <c r="B75" t="n">
-        <v>3.071966532895868</v>
+        <v>3.515266740944997</v>
       </c>
       <c r="C75" t="n">
-        <v>0.3740853273577763</v>
+        <v>0.438121735731275</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4193240905376529</v>
+        <v>0.3213336630302738</v>
       </c>
       <c r="E75" t="n">
-        <v>0.01795707641656775</v>
+        <v>0.01965155076300475</v>
       </c>
     </row>
     <row r="76">
@@ -1718,16 +1718,16 @@
         <v>0.74</v>
       </c>
       <c r="B76" t="n">
-        <v>3.036995438042817</v>
+        <v>3.481364312940068</v>
       </c>
       <c r="C76" t="n">
-        <v>0.3723064059981793</v>
+        <v>0.4361581339511834</v>
       </c>
       <c r="D76" t="n">
-        <v>0.4222234709003157</v>
+        <v>0.3244153504952167</v>
       </c>
       <c r="E76" t="n">
-        <v>0.01775360052865197</v>
+        <v>0.01946936242469374</v>
       </c>
     </row>
     <row r="77">
@@ -1735,16 +1735,16 @@
         <v>0.75</v>
       </c>
       <c r="B77" t="n">
-        <v>3.007695963869996</v>
+        <v>3.448422812416474</v>
       </c>
       <c r="C77" t="n">
-        <v>0.3716909497932002</v>
+        <v>0.4346092129450429</v>
       </c>
       <c r="D77" t="n">
-        <v>0.4232312347850639</v>
+        <v>0.3272073779322225</v>
       </c>
       <c r="E77" t="n">
-        <v>0.01755749358929044</v>
+        <v>0.01928974500599467</v>
       </c>
     </row>
     <row r="78">
@@ -1752,16 +1752,16 @@
         <v>0.76</v>
       </c>
       <c r="B78" t="n">
-        <v>2.981434996191224</v>
+        <v>3.415202228778989</v>
       </c>
       <c r="C78" t="n">
-        <v>0.3717383879665199</v>
+        <v>0.4332855121440255</v>
       </c>
       <c r="D78" t="n">
-        <v>0.4232147535870053</v>
+        <v>0.3298817189917871</v>
       </c>
       <c r="E78" t="n">
-        <v>0.01736086895025232</v>
+        <v>0.01910262865979081</v>
       </c>
     </row>
     <row r="79">
@@ -1769,16 +1769,16 @@
         <v>0.77</v>
       </c>
       <c r="B79" t="n">
-        <v>2.955375914873581</v>
+        <v>3.380557646522878</v>
       </c>
       <c r="C79" t="n">
-        <v>0.3718777227798674</v>
+        <v>0.4319715900160586</v>
       </c>
       <c r="D79" t="n">
-        <v>0.4231665937640576</v>
+        <v>0.3326362389239074</v>
       </c>
       <c r="E79" t="n">
-        <v>0.01715536234827001</v>
+        <v>0.01889808221416765</v>
       </c>
     </row>
     <row r="80">
@@ -1786,16 +1786,16 @@
         <v>0.78</v>
       </c>
       <c r="B80" t="n">
-        <v>2.929563519162011</v>
+        <v>3.344698084219473</v>
       </c>
       <c r="C80" t="n">
-        <v>0.372104484673326</v>
+        <v>0.430669153518017</v>
       </c>
       <c r="D80" t="n">
-        <v>0.4230886856567425</v>
+        <v>0.3354645625976997</v>
       </c>
       <c r="E80" t="n">
-        <v>0.01694156591728729</v>
+        <v>0.01867715654799406</v>
       </c>
     </row>
     <row r="81">
@@ -1803,16 +1803,16 @@
         <v>0.79</v>
       </c>
       <c r="B81" t="n">
-        <v>2.904041003759251</v>
+        <v>3.307827097795523</v>
       </c>
       <c r="C81" t="n">
-        <v>0.3724142040869786</v>
+        <v>0.4293799096067754</v>
       </c>
       <c r="D81" t="n">
-        <v>0.4229829647441813</v>
+        <v>0.3383600940712724</v>
       </c>
       <c r="E81" t="n">
-        <v>0.01672007179124794</v>
+        <v>0.01844090254013889</v>
       </c>
     </row>
     <row r="82">
@@ -1820,16 +1820,16 @@
         <v>0.8</v>
       </c>
       <c r="B82" t="n">
-        <v>2.87885000047398</v>
+        <v>3.270142162433982</v>
       </c>
       <c r="C82" t="n">
-        <v>0.3728024114609083</v>
+        <v>0.4281055652392085</v>
       </c>
       <c r="D82" t="n">
-        <v>0.4228513703330513</v>
+        <v>0.3413160008755732</v>
       </c>
       <c r="E82" t="n">
-        <v>0.01649147210409573</v>
+        <v>0.01819037106947101</v>
       </c>
     </row>
     <row r="83">
@@ -1837,16 +1837,16 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83" t="n">
-        <v>2.854030625977317</v>
+        <v>3.231834168588378</v>
       </c>
       <c r="C83" t="n">
-        <v>0.373264637235198</v>
+        <v>0.426847827372191</v>
       </c>
       <c r="D83" t="n">
-        <v>0.4226958443334353</v>
+        <v>0.3443251996240885</v>
       </c>
       <c r="E83" t="n">
-        <v>0.01625635898977445</v>
+        <v>0.01792661301485929</v>
       </c>
     </row>
     <row r="84">
@@ -1854,16 +1854,16 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84" t="n">
-        <v>2.829621535261811</v>
+        <v>3.193087027575822</v>
       </c>
       <c r="C84" t="n">
-        <v>0.373796411849931</v>
+        <v>0.4256084029625976</v>
       </c>
       <c r="D84" t="n">
-        <v>0.4225183301222321</v>
+        <v>0.3473803430374131</v>
       </c>
       <c r="E84" t="n">
-        <v>0.01601532458222789</v>
+        <v>0.01765067925517259</v>
       </c>
     </row>
     <row r="85">
@@ -1871,16 +1871,16 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85" t="n">
-        <v>2.80565998041874</v>
+        <v>3.154077381533269</v>
       </c>
       <c r="C85" t="n">
-        <v>0.3743932657451902</v>
+        <v>0.4243889989673031</v>
       </c>
       <c r="D85" t="n">
-        <v>0.4223207714946398</v>
+        <v>0.3504738084803976</v>
       </c>
       <c r="E85" t="n">
-        <v>0.01576896101539981</v>
+        <v>0.01736362066927978</v>
       </c>
     </row>
     <row r="86">
@@ -1888,16 +1888,16 @@
         <v>0.84</v>
       </c>
       <c r="B86" t="n">
-        <v>2.782181874373239</v>
+        <v>3.114974412004809</v>
       </c>
       <c r="C86" t="n">
-        <v>0.3750507293610588</v>
+        <v>0.4231913223431822</v>
       </c>
       <c r="D86" t="n">
-        <v>0.42210511170409</v>
+        <v>0.3535976881174381</v>
       </c>
       <c r="E86" t="n">
-        <v>0.01551786042323402</v>
+        <v>0.01706648813604972</v>
       </c>
     </row>
     <row r="87">
@@ -1905,16 +1905,16 @@
         <v>0.85</v>
       </c>
       <c r="B87" t="n">
-        <v>2.759221859242452</v>
+        <v>3.075939741064865</v>
       </c>
       <c r="C87" t="n">
-        <v>0.3757643331376195</v>
+        <v>0.4220170800471096</v>
       </c>
       <c r="D87" t="n">
-        <v>0.4218732925908795</v>
+        <v>0.356743780798393</v>
       </c>
       <c r="E87" t="n">
-        <v>0.01526261493967427</v>
+        <v>0.01676033253435127</v>
       </c>
     </row>
     <row r="88">
@@ -1922,16 +1922,16 @@
         <v>0.86</v>
       </c>
       <c r="B88" t="n">
-        <v>2.736813379009143</v>
+        <v>3.037127418662293</v>
       </c>
       <c r="C88" t="n">
-        <v>0.3765296075149557</v>
+        <v>0.42086797903596</v>
       </c>
       <c r="D88" t="n">
-        <v>0.4216272537996294</v>
+        <v>0.3599035857935203</v>
       </c>
       <c r="E88" t="n">
-        <v>0.01500381669866436</v>
+        <v>0.0164462047430533</v>
       </c>
     </row>
     <row r="89">
@@ -1939,16 +1939,16 @@
         <v>0.87</v>
       </c>
       <c r="B89" t="n">
-        <v>2.714988756232037</v>
+        <v>2.998683989781701</v>
       </c>
       <c r="C89" t="n">
-        <v>0.3773420829331504</v>
+        <v>0.419745726266608</v>
       </c>
       <c r="D89" t="n">
-        <v>0.4213689320855987</v>
+        <v>0.363068298500593</v>
       </c>
       <c r="E89" t="n">
-        <v>0.01474205783414806</v>
+        <v>0.01612515564102468</v>
       </c>
     </row>
     <row r="90">
@@ -1956,16 +1956,16 @@
         <v>0.88</v>
       </c>
       <c r="B90" t="n">
-        <v>2.693779272544309</v>
+        <v>2.960748635048674</v>
       </c>
       <c r="C90" t="n">
-        <v>0.3781972898322865</v>
+        <v>0.4186520286959285</v>
       </c>
       <c r="D90" t="n">
-        <v>0.4211002607097808</v>
+        <v>0.3662288082508829</v>
       </c>
       <c r="E90" t="n">
-        <v>0.01447793048006917</v>
+        <v>0.01579823610713426</v>
       </c>
     </row>
     <row r="91">
@@ -1973,16 +1973,16 @@
         <v>0.89</v>
       </c>
       <c r="B91" t="n">
-        <v>2.673215252723002</v>
+        <v>2.923453378542553</v>
       </c>
       <c r="C91" t="n">
-        <v>0.3790907586524471</v>
+        <v>0.4175885932807962</v>
       </c>
       <c r="D91" t="n">
-        <v>0.4208231689226325</v>
+        <v>0.3693756983428514</v>
       </c>
       <c r="E91" t="n">
-        <v>0.01421202677037145</v>
+        <v>0.01546649702025091</v>
       </c>
     </row>
     <row r="92">
@@ -1990,16 +1990,16 @@
         <v>0.9</v>
       </c>
       <c r="B92" t="n">
-        <v>2.653326152144673</v>
+        <v>2.886923356811947</v>
       </c>
       <c r="C92" t="n">
-        <v>0.3800180198337153</v>
+        <v>0.4165571269780857</v>
       </c>
       <c r="D92" t="n">
-        <v>0.4205395815362105</v>
+        <v>0.3724992484330709</v>
       </c>
       <c r="E92" t="n">
-        <v>0.01394493883899869</v>
+        <v>0.01513098925924351</v>
       </c>
     </row>
     <row r="93">
@@ -2007,16 +2007,16 @@
         <v>0.91</v>
       </c>
       <c r="B93" t="n">
-        <v>2.634140647476084</v>
+        <v>2.851277143402499</v>
       </c>
       <c r="C93" t="n">
-        <v>0.380974603816174</v>
+        <v>0.4155593367446718</v>
       </c>
       <c r="D93" t="n">
-        <v>0.4202514185844325</v>
+        <v>0.3755894394129469</v>
       </c>
       <c r="E93" t="n">
-        <v>0.01367725881989468</v>
+        <v>0.0147927637029809</v>
       </c>
     </row>
     <row r="94">
@@ -2024,16 +2024,16 @@
         <v>0.92</v>
       </c>
       <c r="B94" t="n">
-        <v>2.615686730483291</v>
+        <v>2.816627123592741</v>
       </c>
       <c r="C94" t="n">
-        <v>0.3819560410399065</v>
+        <v>0.4145969295374292</v>
       </c>
       <c r="D94" t="n">
-        <v>0.4199605950711288</v>
+        <v>0.3786359608971453</v>
       </c>
       <c r="E94" t="n">
-        <v>0.01340957884700318</v>
+        <v>0.01445287123033197</v>
       </c>
     </row>
     <row r="95">
@@ -2041,16 +2041,16 @@
         <v>0.93</v>
       </c>
       <c r="B95" t="n">
-        <v>2.597991804877974</v>
+        <v>2.783079914482029</v>
       </c>
       <c r="C95" t="n">
-        <v>0.3829578619449957</v>
+        <v>0.4136716123132325</v>
       </c>
       <c r="D95" t="n">
-        <v>0.4196690208055141</v>
+        <v>0.3816282214450794</v>
       </c>
       <c r="E95" t="n">
-        <v>0.01314249105426799</v>
+        <v>0.01411236272016556</v>
       </c>
     </row>
     <row r="96">
@@ -2058,16 +2058,16 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96" t="n">
-        <v>2.581082786156277</v>
+        <v>2.750736826075549</v>
       </c>
       <c r="C96" t="n">
-        <v>0.3839755969715247</v>
+        <v>0.4127850920289566</v>
       </c>
       <c r="D96" t="n">
-        <v>0.4193786003246827</v>
+        <v>0.3845553616303113</v>
       </c>
       <c r="E96" t="n">
-        <v>0.01287658757563288</v>
+        <v>0.01377228905135055</v>
       </c>
     </row>
     <row r="97">
@@ -2075,16 +2075,16 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97" t="n">
-        <v>2.564986204422877</v>
+        <v>2.719694359557613</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3850047765595764</v>
+        <v>0.4119390756414762</v>
       </c>
       <c r="D97" t="n">
-        <v>0.4190912329027134</v>
+        <v>0.387406270064113</v>
       </c>
       <c r="E97" t="n">
-        <v>0.01261246054504164</v>
+        <v>0.0134337011027558</v>
       </c>
     </row>
     <row r="98">
@@ -2092,16 +2092,16 @@
         <v>0.96</v>
       </c>
       <c r="B98" t="n">
-        <v>2.549728310231456</v>
+        <v>2.690044739529055</v>
       </c>
       <c r="C98" t="n">
-        <v>0.3860409311492339</v>
+        <v>0.4111352701076659</v>
       </c>
       <c r="D98" t="n">
-        <v>0.4188088126459688</v>
+        <v>0.3901696024686622</v>
       </c>
       <c r="E98" t="n">
-        <v>0.01235070209643804</v>
+        <v>0.01309764975325018</v>
       </c>
     </row>
     <row r="99">
@@ -2109,16 +2109,16 @@
         <v>0.97</v>
       </c>
       <c r="B99" t="n">
-        <v>2.535335183512356</v>
+        <v>2.66187647760272</v>
       </c>
       <c r="C99" t="n">
-        <v>0.3870795911805804</v>
+        <v>0.4103753823844005</v>
       </c>
       <c r="D99" t="n">
-        <v>0.4185332286741756</v>
+        <v>0.3928338038822944</v>
       </c>
       <c r="E99" t="n">
-        <v>0.01209190436376588</v>
+        <v>0.01276518588170255</v>
       </c>
     </row>
     <row r="100">
@@ -2126,16 +2126,16 @@
         <v>0.98</v>
       </c>
       <c r="B100" t="n">
-        <v>2.521832845699004</v>
+        <v>2.635274965398833</v>
       </c>
       <c r="C100" t="n">
-        <v>0.3881162870936989</v>
+        <v>0.4096611194285546</v>
       </c>
       <c r="D100" t="n">
-        <v>0.4182663653868972</v>
+        <v>0.395387134063858</v>
       </c>
       <c r="E100" t="n">
-        <v>0.01183665948096892</v>
+        <v>0.01243736036698176</v>
       </c>
     </row>
     <row r="101">
@@ -2143,16 +2143,16 @@
         <v>0.99</v>
       </c>
       <c r="B101" t="n">
-        <v>2.509247375206948</v>
+        <v>2.610323095657253</v>
       </c>
       <c r="C101" t="n">
-        <v>0.3891465493286724</v>
+        <v>0.4089941881970031</v>
       </c>
       <c r="D101" t="n">
-        <v>0.4180101028150296</v>
+        <v>0.3978176961454553</v>
       </c>
       <c r="E101" t="n">
-        <v>0.01158555958199094</v>
+        <v>0.0121152240879567</v>
       </c>
     </row>
     <row r="102">
@@ -2160,16 +2160,16 @@
         <v>1</v>
       </c>
       <c r="B102" t="n">
-        <v>2.497605026463053</v>
+        <v>2.587101910885646</v>
       </c>
       <c r="C102" t="n">
-        <v>0.3901659083255839</v>
+        <v>0.4083762956466205</v>
       </c>
       <c r="D102" t="n">
-        <v>0.4177663170569995</v>
+        <v>0.4001134685626957</v>
       </c>
       <c r="E102" t="n">
-        <v>0.01133919680077574</v>
+        <v>0.01179982792349622</v>
       </c>
     </row>
     <row r="103">
@@ -2177,16 +2177,16 @@
         <v>1.01</v>
       </c>
       <c r="B103" t="n">
-        <v>2.486932352728006</v>
+        <v>2.565691279692192</v>
       </c>
       <c r="C103" t="n">
-        <v>0.3911698945245164</v>
+        <v>0.4078091487342818</v>
       </c>
       <c r="D103" t="n">
-        <v>0.4175368807993848</v>
+        <v>0.4022623402690247</v>
       </c>
       <c r="E103" t="n">
-        <v>0.01109816327126709</v>
+        <v>0.01149222275246919</v>
       </c>
     </row>
     <row r="104">
@@ -2194,16 +2194,16 @@
         <v>1.02</v>
       </c>
       <c r="B104" t="n">
-        <v>2.477256333002776</v>
+        <v>2.54617060171118</v>
       </c>
       <c r="C104" t="n">
-        <v>0.3921540383655532</v>
+        <v>0.4072944544168614</v>
       </c>
       <c r="D104" t="n">
-        <v>0.4173236639217463</v>
+        <v>0.4042521492157747</v>
       </c>
       <c r="E104" t="n">
-        <v>0.01086305112740877</v>
+        <v>0.01119345945374448</v>
       </c>
     </row>
     <row r="105">
@@ -2211,16 +2211,16 @@
         <v>1.03</v>
       </c>
       <c r="B105" t="n">
-        <v>2.468604503359561</v>
+        <v>2.528619542823928</v>
       </c>
       <c r="C105" t="n">
-        <v>0.3931138702887772</v>
+        <v>0.4068339196512343</v>
       </c>
       <c r="D105" t="n">
-        <v>0.4171285341855232</v>
+        <v>0.406070724052371</v>
       </c>
       <c r="E105" t="n">
-        <v>0.01063445250314458</v>
+        <v>0.01090458890619093</v>
       </c>
     </row>
     <row r="106">
@@ -2228,16 +2228,16 @@
         <v>1.04</v>
       </c>
       <c r="B106" t="n">
-        <v>2.461005093090202</v>
+        <v>2.513118803211987</v>
       </c>
       <c r="C106" t="n">
-        <v>0.3940449207342714</v>
+        <v>0.4064292513942749</v>
       </c>
       <c r="D106" t="n">
-        <v>0.416953358006933</v>
+        <v>0.4077059289717277</v>
       </c>
       <c r="E106" t="n">
-        <v>0.01041295953241827</v>
+        <v>0.01062666198867744</v>
       </c>
     </row>
     <row r="107">
@@ -2245,16 +2245,16 @@
         <v>1.05</v>
       </c>
       <c r="B107" t="n">
-        <v>2.454487166120529</v>
+        <v>2.49975092166241</v>
       </c>
       <c r="C107" t="n">
-        <v>0.3949427201421188</v>
+        <v>0.4060821566028583</v>
       </c>
       <c r="D107" t="n">
-        <v>0.4168000013139035</v>
+        <v>0.4091457115944292</v>
       </c>
       <c r="E107" t="n">
-        <v>0.01019916434917363</v>
+        <v>0.01036072958007284</v>
       </c>
     </row>
     <row r="108">
@@ -2262,16 +2262,16 @@
         <v>1.06</v>
       </c>
       <c r="B108" t="n">
-        <v>2.449080768197968</v>
+        <v>2.488601120486183</v>
       </c>
       <c r="C108" t="n">
-        <v>0.3958027989524027</v>
+        <v>0.4057943422338589</v>
       </c>
       <c r="D108" t="n">
-        <v>0.4166703304871716</v>
+        <v>0.4103781537520029</v>
       </c>
       <c r="E108" t="n">
-        <v>0.009993659087354461</v>
+        <v>0.01010784255924602</v>
       </c>
     </row>
     <row r="109">
@@ -2279,16 +2279,16 @@
         <v>1.07</v>
       </c>
       <c r="B109" t="n">
-        <v>2.444817080422512</v>
+        <v>2.479758196422955</v>
       </c>
       <c r="C109" t="n">
-        <v>0.3966206876052059</v>
+        <v>0.4055675152441515</v>
       </c>
       <c r="D109" t="n">
-        <v>0.4165662133857939</v>
+        <v>0.4113915249946733</v>
       </c>
       <c r="E109" t="n">
-        <v>0.009797035880904522</v>
+        <v>0.009869051805065835</v>
       </c>
     </row>
     <row r="110">
@@ -2296,16 +2296,16 @@
         <v>1.08</v>
       </c>
       <c r="B110" t="n">
-        <v>2.441728579758304</v>
+        <v>2.473315464002805</v>
       </c>
       <c r="C110" t="n">
-        <v>0.3973919165406115</v>
+        <v>0.4054033825906109</v>
       </c>
       <c r="D110" t="n">
-        <v>0.4164895204574424</v>
+        <v>0.4121743386127331</v>
       </c>
       <c r="E110" t="n">
-        <v>0.009609886863767606</v>
+        <v>0.00964540819640115</v>
       </c>
     </row>
     <row r="111">
@@ -2313,16 +2313,16 @@
         <v>1.09</v>
       </c>
       <c r="B111" t="n">
-        <v>2.439849207235275</v>
+        <v>2.469371759036831</v>
       </c>
       <c r="C111" t="n">
-        <v>0.3981120161987026</v>
+        <v>0.4053036512301117</v>
       </c>
       <c r="D111" t="n">
-        <v>0.4164421259339888</v>
+        <v>0.4127154099233828</v>
       </c>
       <c r="E111" t="n">
-        <v>0.009432804169887489</v>
+        <v>0.009437962612120827</v>
       </c>
     </row>
     <row r="112">
@@ -2330,16 +2330,16 @@
         <v>1.1</v>
       </c>
       <c r="B112" t="n">
-        <v>2.439214544628072</v>
+        <v>2.468032511233544</v>
       </c>
       <c r="C112" t="n">
-        <v>0.3987765170195623</v>
+        <v>0.4052700281195287</v>
       </c>
       <c r="D112" t="n">
-        <v>0.4164259091130328</v>
+        <v>0.4130039165369583</v>
       </c>
       <c r="E112" t="n">
-        <v>0.009266379933207952</v>
+        <v>0.009247765931093733</v>
       </c>
     </row>
     <row r="113">
@@ -2347,16 +2347,16 @@
         <v>1.11</v>
       </c>
       <c r="B113" t="n">
-        <v>2.439447143223756</v>
+        <v>2.468256182231185</v>
       </c>
       <c r="C113" t="n">
-        <v>0.3994178701843819</v>
+        <v>0.4052966971208152</v>
       </c>
       <c r="D113" t="n">
-        <v>0.4164301412721976</v>
+        <v>0.4131581456763312</v>
       </c>
       <c r="E113" t="n">
-        <v>0.009104854637196456</v>
+        <v>0.009066135417943396</v>
       </c>
     </row>
     <row r="114">
@@ -2364,16 +2364,16 @@
         <v>1.12</v>
       </c>
       <c r="B114" t="n">
-        <v>2.440132495038688</v>
+        <v>2.46891522272558</v>
       </c>
       <c r="C114" t="n">
-        <v>0.4000708312441332</v>
+        <v>0.4053752625570375</v>
       </c>
       <c r="D114" t="n">
-        <v>0.4164427666543455</v>
+        <v>0.4133036227871111</v>
       </c>
       <c r="E114" t="n">
-        <v>0.008942194908937101</v>
+        <v>0.008883807794411612</v>
       </c>
     </row>
     <row r="115">
@@ -2381,16 +2381,16 @@
         <v>1.13</v>
       </c>
       <c r="B115" t="n">
-        <v>2.44125210739633</v>
+        <v>2.469991832327372</v>
       </c>
       <c r="C115" t="n">
-        <v>0.40073438719357</v>
+        <v>0.4055035620767399</v>
       </c>
       <c r="D115" t="n">
-        <v>0.4164636789873694</v>
+        <v>0.4134406923369435</v>
       </c>
       <c r="E115" t="n">
-        <v>0.008778582097798629</v>
+        <v>0.008700963125044639</v>
       </c>
     </row>
     <row r="116">
@@ -2398,16 +2398,16 @@
         <v>1.14</v>
       </c>
       <c r="B116" t="n">
-        <v>2.442787691713411</v>
+        <v>2.47146839715059</v>
       </c>
       <c r="C116" t="n">
-        <v>0.401407525027446</v>
+        <v>0.4056794333284668</v>
       </c>
       <c r="D116" t="n">
-        <v>0.416492772476669</v>
+        <v>0.4135696997903457</v>
       </c>
       <c r="E116" t="n">
-        <v>0.008614197553149782</v>
+        <v>0.008517781474388744</v>
       </c>
     </row>
     <row r="117">
@@ -2415,16 +2415,16 @@
         <v>1.15</v>
       </c>
       <c r="B117" t="n">
-        <v>2.444721131133204</v>
+        <v>2.473327460212266</v>
       </c>
       <c r="C117" t="n">
-        <v>0.4020892317405149</v>
+        <v>0.4059007139607626</v>
       </c>
       <c r="D117" t="n">
-        <v>0.4165299417841107</v>
+        <v>0.4136909915390724</v>
       </c>
       <c r="E117" t="n">
-        <v>0.008449222624359305</v>
+        <v>0.00833444290699019</v>
       </c>
     </row>
     <row r="118">
@@ -2432,16 +2432,16 @@
         <v>1.16</v>
       </c>
       <c r="B118" t="n">
-        <v>2.447034449695871</v>
+        <v>2.475551693233172</v>
       </c>
       <c r="C118" t="n">
-        <v>0.4027784943275304</v>
+        <v>0.4061652416221715</v>
       </c>
       <c r="D118" t="n">
-        <v>0.4165750820073011</v>
+        <v>0.4138049148353267</v>
       </c>
       <c r="E118" t="n">
-        <v>0.008283838660795939</v>
+        <v>0.008151127487395248</v>
       </c>
     </row>
     <row r="119">
@@ -2449,16 +2449,16 @@
         <v>1.17</v>
       </c>
       <c r="B119" t="n">
-        <v>2.449709782997879</v>
+        <v>2.478123869797975</v>
       </c>
       <c r="C119" t="n">
-        <v>0.4034742997832464</v>
+        <v>0.4064708539612381</v>
       </c>
       <c r="D119" t="n">
-        <v>0.4166280886591731</v>
+        <v>0.4139118177278397</v>
       </c>
       <c r="E119" t="n">
-        <v>0.008118227011828424</v>
+        <v>0.007968015280150171</v>
       </c>
     </row>
     <row r="120">
@@ -2466,16 +2466,16 @@
         <v>1.18</v>
       </c>
       <c r="B120" t="n">
-        <v>2.452729350299067</v>
+        <v>2.481026839838818</v>
       </c>
       <c r="C120" t="n">
-        <v>0.4041756351024165</v>
+        <v>0.4068153886265063</v>
       </c>
       <c r="D120" t="n">
-        <v>0.4166888576478776</v>
+        <v>0.4140120490008342</v>
       </c>
       <c r="E120" t="n">
-        <v>0.007952569026825503</v>
+        <v>0.007785286349801227</v>
       </c>
     </row>
     <row r="121">
@@ -2483,16 +2483,16 @@
         <v>1.19</v>
       </c>
       <c r="B121" t="n">
-        <v>2.45607542804211</v>
+        <v>2.484243505411715</v>
       </c>
       <c r="C121" t="n">
-        <v>0.4048814872797944</v>
+        <v>0.4071966832665209</v>
       </c>
       <c r="D121" t="n">
-        <v>0.4167572852569792</v>
+        <v>0.4141059581158912</v>
       </c>
       <c r="E121" t="n">
-        <v>0.007787046055155921</v>
+        <v>0.007603120760894679</v>
       </c>
     </row>
     <row r="122">
@@ -2500,16 +2500,16 @@
         <v>1.2</v>
       </c>
       <c r="B122" t="n">
-        <v>2.459730324754979</v>
+        <v>2.48775679774019</v>
       </c>
       <c r="C122" t="n">
-        <v>0.4055908433101339</v>
+        <v>0.407612575529826</v>
       </c>
       <c r="D122" t="n">
-        <v>0.4168332681259499</v>
+        <v>0.4141938951567351</v>
       </c>
       <c r="E122" t="n">
-        <v>0.007621839446188417</v>
+        <v>0.007421698577976794</v>
       </c>
     </row>
     <row r="123">
@@ -2517,16 +2517,16 @@
         <v>1.21</v>
       </c>
       <c r="B123" t="n">
-        <v>2.463676357312488</v>
+        <v>2.491549655505426</v>
       </c>
       <c r="C123" t="n">
-        <v>0.4063026901881888</v>
+        <v>0.408060903064966</v>
       </c>
       <c r="D123" t="n">
-        <v>0.4169167032309599</v>
+        <v>0.4142762107769498</v>
       </c>
       <c r="E123" t="n">
-        <v>0.007457130549291736</v>
+        <v>0.007241199865593833</v>
       </c>
     </row>
     <row r="124">
@@ -2534,16 +2534,16 @@
         <v>1.22</v>
       </c>
       <c r="B124" t="n">
-        <v>2.467895828538206</v>
+        <v>2.495605004366657</v>
       </c>
       <c r="C124" t="n">
-        <v>0.4070160149087126</v>
+        <v>0.4085395035204852</v>
       </c>
       <c r="D124" t="n">
-        <v>0.4170074878659596</v>
+        <v>0.4143532561506418</v>
       </c>
       <c r="E124" t="n">
-        <v>0.007293100713834622</v>
+        <v>0.007061804688292062</v>
       </c>
     </row>
     <row r="125">
@@ -2551,16 +2551,16 @@
         <v>1.23</v>
       </c>
       <c r="B125" t="n">
-        <v>2.47237100613291</v>
+        <v>2.499905737699838</v>
       </c>
       <c r="C125" t="n">
-        <v>0.4077298044664592</v>
+        <v>0.409046214544928</v>
       </c>
       <c r="D125" t="n">
-        <v>0.417105519624052</v>
+        <v>0.4144253829260592</v>
       </c>
       <c r="E125" t="n">
-        <v>0.007129931289185815</v>
+        <v>0.006883693110617743</v>
       </c>
     </row>
     <row r="126">
@@ -2568,16 +2568,16 @@
         <v>1.24</v>
       </c>
       <c r="B126" t="n">
-        <v>2.477084102920341</v>
+        <v>2.504434698546563</v>
       </c>
       <c r="C126" t="n">
-        <v>0.4084430458561823</v>
+        <v>0.4095788737868387</v>
       </c>
       <c r="D126" t="n">
-        <v>0.4172106963791502</v>
+        <v>0.4144929431821787</v>
       </c>
       <c r="E126" t="n">
-        <v>0.006967803624714058</v>
+        <v>0.006707045197117142</v>
       </c>
     </row>
     <row r="127">
@@ -2585,16 +2585,16 @@
         <v>1.25</v>
       </c>
       <c r="B127" t="n">
-        <v>2.482017258405299</v>
+        <v>2.509174662768994</v>
       </c>
       <c r="C127" t="n">
-        <v>0.4091547260726356</v>
+        <v>0.4101353188947615</v>
       </c>
       <c r="D127" t="n">
-        <v>0.4173229162679182</v>
+        <v>0.4145562893882703</v>
       </c>
       <c r="E127" t="n">
-        <v>0.006806899069788093</v>
+        <v>0.00653204101233652</v>
       </c>
     </row>
     <row r="128">
@@ -2602,16 +2602,16 @@
         <v>1.26</v>
       </c>
       <c r="B128" t="n">
-        <v>2.487152521643182</v>
+        <v>2.514108323410019</v>
       </c>
       <c r="C128" t="n">
-        <v>0.4098638321105729</v>
+        <v>0.4107133875172411</v>
       </c>
       <c r="D128" t="n">
-        <v>0.417442077671992</v>
+        <v>0.4146157743664479</v>
       </c>
       <c r="E128" t="n">
-        <v>0.006647398973776663</v>
+        <v>0.006358860620822145</v>
       </c>
     </row>
     <row r="129">
@@ -2619,16 +2619,16 @@
         <v>1.27</v>
       </c>
       <c r="B129" t="n">
-        <v>2.492471835423771</v>
+        <v>2.519218276261135</v>
       </c>
       <c r="C129" t="n">
-        <v>0.4105693509647479</v>
+        <v>0.4113109173028215</v>
       </c>
       <c r="D129" t="n">
-        <v>0.4175680792004783</v>
+        <v>0.414671751257213</v>
       </c>
       <c r="E129" t="n">
-        <v>0.00648948468604851</v>
+        <v>0.006187684087120278</v>
       </c>
     </row>
     <row r="130">
@@ -2636,16 +2636,16 @@
         <v>1.28</v>
       </c>
       <c r="B130" t="n">
-        <v>2.497957021775549</v>
+        <v>2.524487006643556</v>
       </c>
       <c r="C130" t="n">
-        <v>0.4112702696299142</v>
+        <v>0.4119257459000472</v>
       </c>
       <c r="D130" t="n">
-        <v>0.4177008196727281</v>
+        <v>0.4147245734879992</v>
       </c>
       <c r="E130" t="n">
-        <v>0.006333337555972377</v>
+        <v>0.006018691475777183</v>
       </c>
     </row>
     <row r="131">
@@ -2653,16 +2653,16 @@
         <v>1.29</v>
       </c>
       <c r="B131" t="n">
-        <v>2.503589768800044</v>
+        <v>2.529896877410807</v>
       </c>
       <c r="C131" t="n">
-        <v>0.4119655751008257</v>
+        <v>0.4125557109574626</v>
       </c>
       <c r="D131" t="n">
-        <v>0.417840198101382</v>
+        <v>0.4147745947447227</v>
       </c>
       <c r="E131" t="n">
-        <v>0.006179138932917007</v>
+        <v>0.005852062851339124</v>
       </c>
     </row>
     <row r="132">
@@ -2670,16 +2670,16 @@
         <v>1.3</v>
       </c>
       <c r="B132" t="n">
-        <v>2.50935161884857</v>
+        <v>2.535430118183611</v>
       </c>
       <c r="C132" t="n">
-        <v>0.4126542543722361</v>
+        <v>0.4131986501236118</v>
       </c>
       <c r="D132" t="n">
-        <v>0.4179861136756869</v>
+        <v>0.4148221689463451</v>
       </c>
       <c r="E132" t="n">
-        <v>0.006027070166251142</v>
+        <v>0.005687978278352367</v>
       </c>
     </row>
     <row r="133">
@@ -2687,16 +2687,16 @@
         <v>1.31</v>
       </c>
       <c r="B133" t="n">
-        <v>2.515223958056407</v>
+        <v>2.541068815830143</v>
       </c>
       <c r="C133" t="n">
-        <v>0.413335294438899</v>
+        <v>0.4138524010470394</v>
       </c>
       <c r="D133" t="n">
-        <v>0.4181384657450798</v>
+        <v>0.414867650222452</v>
       </c>
       <c r="E133" t="n">
-        <v>0.005877312605343525</v>
+        <v>0.005526617821363172</v>
       </c>
     </row>
     <row r="134">
@@ -2704,16 +2704,16 @@
         <v>1.32</v>
       </c>
       <c r="B134" t="n">
-        <v>2.521188007251826</v>
+        <v>2.546794906206799</v>
       </c>
       <c r="C134" t="n">
-        <v>0.4140076822955682</v>
+        <v>0.4145148013762897</v>
       </c>
       <c r="D134" t="n">
-        <v>0.4182971538030372</v>
+        <v>0.4149113928938518</v>
       </c>
       <c r="E134" t="n">
-        <v>0.005730047599562896</v>
+        <v>0.005368161544917808</v>
       </c>
     </row>
     <row r="135">
@@ -2721,16 +2721,16 @@
         <v>1.33</v>
       </c>
       <c r="B135" t="n">
-        <v>2.527224814259395</v>
+        <v>2.552590167176387</v>
       </c>
       <c r="C135" t="n">
-        <v>0.4146704049369976</v>
+        <v>0.4151836887599068</v>
       </c>
       <c r="D135" t="n">
-        <v>0.4184620774711889</v>
+        <v>0.4149537514561991</v>
       </c>
       <c r="E135" t="n">
-        <v>0.005585456498278</v>
+        <v>0.005212789513562533</v>
       </c>
     </row>
     <row r="136">
@@ -2738,16 +2738,16 @@
         <v>1.34</v>
       </c>
       <c r="B136" t="n">
-        <v>2.533315247618854</v>
+        <v>2.558436212922214</v>
       </c>
       <c r="C136" t="n">
-        <v>0.4153224493579407</v>
+        <v>0.4158569008464353</v>
       </c>
       <c r="D136" t="n">
-        <v>0.4186331364836932</v>
+        <v>0.4149950805666449</v>
       </c>
       <c r="E136" t="n">
-        <v>0.005443720650857579</v>
+        <v>0.005060681791843617</v>
       </c>
     </row>
     <row r="137">
@@ -2755,16 +2755,16 @@
         <v>1.35</v>
       </c>
       <c r="B137" t="n">
-        <v>2.539439991742278</v>
+        <v>2.564314489577821</v>
       </c>
       <c r="C137" t="n">
-        <v>0.4159628025531513</v>
+        <v>0.4165322752844196</v>
       </c>
       <c r="D137" t="n">
-        <v>0.4188102306718727</v>
+        <v>0.4150357350335163</v>
       </c>
       <c r="E137" t="n">
-        <v>0.005305021406670376</v>
+        <v>0.004912018444307319</v>
       </c>
     </row>
     <row r="138">
@@ -2772,16 +2772,16 @@
         <v>1.36</v>
       </c>
       <c r="B138" t="n">
-        <v>2.545579543533486</v>
+        <v>2.57020627219315</v>
       </c>
       <c r="C138" t="n">
-        <v>0.4165904515173831</v>
+        <v>0.4172076497224037</v>
       </c>
       <c r="D138" t="n">
-        <v>0.4189932599491082</v>
+        <v>0.4150760698090294</v>
       </c>
       <c r="E138" t="n">
-        <v>0.005169540115085132</v>
+        <v>0.004766979535499905</v>
       </c>
     </row>
     <row r="139">
@@ -2789,16 +2789,16 @@
         <v>1.37</v>
       </c>
       <c r="B139" t="n">
-        <v>2.551714210494501</v>
+        <v>2.576092663058657</v>
       </c>
       <c r="C139" t="n">
-        <v>0.4172043832453899</v>
+        <v>0.4178808618089322</v>
       </c>
       <c r="D139" t="n">
-        <v>0.4191821242959897</v>
+        <v>0.4151164399850362</v>
       </c>
       <c r="E139" t="n">
-        <v>0.005037458125470589</v>
+        <v>0.004625745129967639</v>
       </c>
     </row>
     <row r="140">
@@ -2806,16 +2806,16 @@
         <v>1.38</v>
       </c>
       <c r="B140" t="n">
-        <v>2.55782411034446</v>
+        <v>2.581954591409418</v>
       </c>
       <c r="C140" t="n">
-        <v>0.4178035847319254</v>
+        <v>0.4185497491925494</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4193767237457235</v>
+        <v>0.4151572007918087</v>
       </c>
       <c r="E140" t="n">
-        <v>0.004908956787195492</v>
+        <v>0.004488495292256784</v>
       </c>
     </row>
     <row r="141">
@@ -2823,16 +2823,16 @@
         <v>1.39</v>
       </c>
       <c r="B141" t="n">
-        <v>2.563889172176612</v>
+        <v>2.587772814531408</v>
       </c>
       <c r="C141" t="n">
-        <v>0.4183870429717432</v>
+        <v>0.4192121495217996</v>
       </c>
       <c r="D141" t="n">
-        <v>0.4195769583697921</v>
+        <v>0.4151987075998618</v>
       </c>
       <c r="E141" t="n">
-        <v>0.004784217449628582</v>
+        <v>0.004355410086913605</v>
       </c>
     </row>
     <row r="142">
@@ -2840,16 +2840,16 @@
         <v>1.4</v>
       </c>
       <c r="B142" t="n">
-        <v>2.569889139178938</v>
+        <v>2.593527920292127</v>
       </c>
       <c r="C142" t="n">
-        <v>0.4189537449595973</v>
+        <v>0.4198659004452272</v>
       </c>
       <c r="D142" t="n">
-        <v>0.4197827282638689</v>
+        <v>0.4152413159248175</v>
       </c>
       <c r="E142" t="n">
-        <v>0.004663421462138601</v>
+        <v>0.004226669578484366</v>
       </c>
     </row>
     <row r="143">
@@ -2857,16 +2857,16 @@
         <v>1.41</v>
       </c>
       <c r="B143" t="n">
-        <v>2.575803572943531</v>
+        <v>2.599200331117287</v>
       </c>
       <c r="C143" t="n">
-        <v>0.4195026776902412</v>
+        <v>0.4205088396113765</v>
       </c>
       <c r="D143" t="n">
-        <v>0.419993933533983</v>
+        <v>0.4152853814353121</v>
       </c>
       <c r="E143" t="n">
-        <v>0.004546750174094295</v>
+        <v>0.004102453831515332</v>
       </c>
     </row>
     <row r="144">
@@ -2874,16 +2874,16 @@
         <v>1.42</v>
       </c>
       <c r="B144" t="n">
-        <v>2.581611859389096</v>
+        <v>2.604770309434679</v>
       </c>
       <c r="C144" t="n">
-        <v>0.4200328281584288</v>
+        <v>0.4211388046687918</v>
       </c>
       <c r="D144" t="n">
-        <v>0.4202104742829361</v>
+        <v>0.4153312599639485</v>
       </c>
       <c r="E144" t="n">
-        <v>0.004434384934864401</v>
+        <v>0.003982942910552763</v>
       </c>
     </row>
     <row r="145">
@@ -2891,16 +2891,16 @@
         <v>1.43</v>
       </c>
       <c r="B145" t="n">
-        <v>2.587293216319776</v>
+        <v>2.610217964605279</v>
       </c>
       <c r="C145" t="n">
-        <v>0.4205431833589136</v>
+        <v>0.4217536332660176</v>
       </c>
       <c r="D145" t="n">
-        <v>0.4204322505969686</v>
+        <v>0.4153793075212979</v>
       </c>
       <c r="E145" t="n">
-        <v>0.004326507093817664</v>
+        <v>0.003868316880142925</v>
       </c>
     </row>
     <row r="146">
@@ -2908,16 +2908,16 @@
         <v>1.44</v>
       </c>
       <c r="B146" t="n">
-        <v>2.592826702642079</v>
+        <v>2.615523261360424</v>
       </c>
       <c r="C146" t="n">
-        <v>0.4210327302864496</v>
+        <v>0.422351163051598</v>
       </c>
       <c r="D146" t="n">
-        <v>0.4206591625326749</v>
+        <v>0.4154298803129514</v>
       </c>
       <c r="E146" t="n">
-        <v>0.004223298000322825</v>
+        <v>0.003758755804832082</v>
       </c>
     </row>
     <row r="147">
@@ -2925,16 +2925,16 @@
         <v>1.45</v>
       </c>
       <c r="B147" t="n">
-        <v>2.598191229259768</v>
+        <v>2.620666029762213</v>
       </c>
       <c r="C147" t="n">
-        <v>0.4215004559357903</v>
+        <v>0.4229292316740775</v>
       </c>
       <c r="D147" t="n">
-        <v>0.4208911101041667</v>
+        <v>0.4154833347596255</v>
       </c>
       <c r="E147" t="n">
-        <v>0.00412493900374863</v>
+        <v>0.003654439749166499</v>
       </c>
     </row>
     <row r="148">
@@ -2942,16 +2942,16 @@
         <v>1.46</v>
       </c>
       <c r="B148" t="n">
-        <v>2.603365571664405</v>
+        <v>2.625625976702424</v>
       </c>
       <c r="C148" t="n">
-        <v>0.4219453473016896</v>
+        <v>0.4234856767820004</v>
       </c>
       <c r="D148" t="n">
-        <v>0.4211279932704846</v>
+        <v>0.4155400275203268</v>
       </c>
       <c r="E148" t="n">
-        <v>0.004031611453463819</v>
+        <v>0.003555548777692439</v>
       </c>
     </row>
     <row r="149">
@@ -2959,16 +2959,16 @@
         <v>1.47</v>
       </c>
       <c r="B149" t="n">
-        <v>2.608328384236581</v>
+        <v>2.630382698952909</v>
       </c>
       <c r="C149" t="n">
-        <v>0.4223663913789011</v>
+        <v>0.4240183360239111</v>
       </c>
       <c r="D149" t="n">
-        <v>0.4213697119232559</v>
+        <v>0.4156003155185782</v>
       </c>
       <c r="E149" t="n">
-        <v>0.003943496698837133</v>
+        <v>0.003462262954956164</v>
       </c>
     </row>
     <row r="150">
@@ -2976,16 +2976,16 @@
         <v>1.48</v>
       </c>
       <c r="B150" t="n">
-        <v>2.613058216269922</v>
+        <v>2.634915697777889</v>
       </c>
       <c r="C150" t="n">
-        <v>0.4227625751621785</v>
+        <v>0.4245250470483539</v>
       </c>
       <c r="D150" t="n">
-        <v>0.4216161658745995</v>
+        <v>0.4156645559717109</v>
       </c>
       <c r="E150" t="n">
-        <v>0.003860776089237319</v>
+        <v>0.00337476234550394</v>
       </c>
     </row>
     <row r="151">
@@ -2993,16 +2993,16 @@
         <v>1.49</v>
       </c>
       <c r="B151" t="n">
-        <v>2.617533529726557</v>
+        <v>2.639204395115633</v>
       </c>
       <c r="C151" t="n">
-        <v>0.4231328856462757</v>
+        <v>0.4250036475038731</v>
       </c>
       <c r="D151" t="n">
-        <v>0.4218672548452772</v>
+        <v>0.4157331064232301</v>
       </c>
       <c r="E151" t="n">
-        <v>0.003783630974033116</v>
+        <v>0.003293227013882032</v>
       </c>
     </row>
     <row r="152">
@@ -3010,16 +3010,16 @@
         <v>1.5</v>
       </c>
       <c r="B152" t="n">
-        <v>2.621732718728994</v>
+        <v>2.643228151333745</v>
       </c>
       <c r="C152" t="n">
-        <v>0.4234763098259464</v>
+        <v>0.425451975039013</v>
       </c>
       <c r="D152" t="n">
-        <v>0.4221228784530897</v>
+        <v>0.4158063247782592</v>
       </c>
       <c r="E152" t="n">
-        <v>0.003712242702593266</v>
+        <v>0.003217837024636702</v>
       </c>
     </row>
     <row r="153">
@@ -3027,16 +3027,16 @@
         <v>1.51</v>
       </c>
       <c r="B153" t="n">
-        <v>2.625634130789186</v>
+        <v>2.646966284558714</v>
       </c>
       <c r="C153" t="n">
-        <v>0.4237918346959442</v>
+        <v>0.4258678673023181</v>
       </c>
       <c r="D153" t="n">
-        <v>0.4223829362015197</v>
+        <v>0.4158845693420681</v>
       </c>
       <c r="E153" t="n">
-        <v>0.003646792624286514</v>
+        <v>0.003148772442314213</v>
       </c>
     </row>
     <row r="154">
@@ -3044,16 +3044,16 @@
         <v>1.52</v>
       </c>
       <c r="B154" t="n">
-        <v>2.629216089771059</v>
+        <v>2.650398091576453</v>
       </c>
       <c r="C154" t="n">
-        <v>0.4240784472510228</v>
+        <v>0.4262491619423326</v>
       </c>
       <c r="D154" t="n">
-        <v>0.4226473274686193</v>
+        <v>0.4159681988616966</v>
       </c>
       <c r="E154" t="n">
-        <v>0.003587462088481601</v>
+        <v>0.003086213331460832</v>
       </c>
     </row>
     <row r="155">
@@ -3061,16 +3061,16 @@
         <v>1.53</v>
       </c>
       <c r="B155" t="n">
-        <v>2.632456920577848</v>
+        <v>2.653502870296325</v>
       </c>
       <c r="C155" t="n">
-        <v>0.4243351344859361</v>
+        <v>0.426593696607601</v>
       </c>
       <c r="D155" t="n">
-        <v>0.4229159514961437</v>
+        <v>0.4160575725706788</v>
       </c>
       <c r="E155" t="n">
-        <v>0.003534432444547269</v>
+        <v>0.00303033975662282</v>
       </c>
     </row>
     <row r="156">
@@ -3078,16 +3078,16 @@
         <v>1.54</v>
       </c>
       <c r="B156" t="n">
-        <v>2.635334975550306</v>
+        <v>2.65625994376656</v>
       </c>
       <c r="C156" t="n">
-        <v>0.4245608833954378</v>
+        <v>0.4268993089466675</v>
       </c>
       <c r="D156" t="n">
-        <v>0.4231887073789292</v>
+        <v>0.4161530502368807</v>
       </c>
       <c r="E156" t="n">
-        <v>0.003487885041852262</v>
+        <v>0.002981331782346444</v>
       </c>
     </row>
     <row r="157">
@@ -3095,16 +3095,16 @@
         <v>1.55</v>
       </c>
       <c r="B157" t="n">
-        <v>2.637828662556218</v>
+        <v>2.658648685724138</v>
       </c>
       <c r="C157" t="n">
-        <v>0.4247546809742815</v>
+        <v>0.4271638366080764</v>
       </c>
       <c r="D157" t="n">
-        <v>0.423465494054518</v>
+        <v>0.4162549922134602</v>
       </c>
       <c r="E157" t="n">
-        <v>0.003448001229765322</v>
+        <v>0.002939369473177965</v>
       </c>
     </row>
     <row r="158">
@@ -3112,16 +3112,16 @@
         <v>1.56</v>
       </c>
       <c r="B158" t="n">
-        <v>2.639916474745605</v>
+        <v>2.660648547656948</v>
       </c>
       <c r="C158" t="n">
-        <v>0.4249155142172211</v>
+        <v>0.4273851172403722</v>
       </c>
       <c r="D158" t="n">
-        <v>0.4237462102930274</v>
+        <v>0.4163637594929627</v>
       </c>
       <c r="E158" t="n">
-        <v>0.00341496235765519</v>
+        <v>0.002904632893663648</v>
       </c>
     </row>
     <row r="159">
@@ -3129,16 +3129,16 @@
         <v>1.57</v>
       </c>
       <c r="B159" t="n">
-        <v>2.641577021939703</v>
+        <v>2.662239087350642</v>
       </c>
       <c r="C159" t="n">
-        <v>0.4250423701190101</v>
+        <v>0.4275609884920991</v>
       </c>
       <c r="D159" t="n">
-        <v>0.4240307546872658</v>
+        <v>0.416479713764566</v>
       </c>
       <c r="E159" t="n">
-        <v>0.00338894977489061</v>
+        <v>0.002877302108349757</v>
       </c>
     </row>
     <row r="160">
@@ -3146,16 +3146,16 @@
         <v>1.58</v>
       </c>
       <c r="B160" t="n">
-        <v>2.64278906361508</v>
+        <v>2.663399998886739</v>
       </c>
       <c r="C160" t="n">
-        <v>0.4251342356744025</v>
+        <v>0.4276892880118016</v>
       </c>
       <c r="D160" t="n">
-        <v>0.4243190256430938</v>
+        <v>0.4166032174744884</v>
       </c>
       <c r="E160" t="n">
-        <v>0.003370144830840325</v>
+        <v>0.002857557181782555</v>
       </c>
     </row>
     <row r="161">
@@ -3163,16 +3163,16 @@
         <v>1.59</v>
       </c>
       <c r="B161" t="n">
-        <v>2.643531543437306</v>
+        <v>2.664111144052574</v>
       </c>
       <c r="C161" t="n">
-        <v>0.4251900978781518</v>
+        <v>0.4277678534480239</v>
       </c>
       <c r="D161" t="n">
-        <v>0.4246109213700334</v>
+        <v>0.4167346338895768</v>
       </c>
       <c r="E161" t="n">
-        <v>0.003358728874873075</v>
+        <v>0.002845578178508307</v>
       </c>
     </row>
     <row r="162">
@@ -3180,16 +3180,16 @@
         <v>1.6</v>
       </c>
       <c r="B162" t="n">
-        <v>2.64378362529128</v>
+        <v>2.664352585117351</v>
       </c>
       <c r="C162" t="n">
-        <v>0.4252089437250119</v>
+        <v>0.4277945224493103</v>
       </c>
       <c r="D162" t="n">
-        <v>0.4249063398721223</v>
+        <v>0.4168743271640927</v>
       </c>
       <c r="E162" t="n">
-        <v>0.003354883256357605</v>
+        <v>0.002841545163073277</v>
       </c>
     </row>
     <row r="163">
@@ -3197,16 +3197,16 @@
         <v>1.61</v>
       </c>
       <c r="B163" t="n">
-        <v>2.643566973760238</v>
+        <v>2.664117450000253</v>
       </c>
       <c r="C163" t="n">
-        <v>0.4252064365620241</v>
+        <v>0.4277880620542243</v>
       </c>
       <c r="D163" t="n">
-        <v>0.4252279351674651</v>
+        <v>0.4170504951552072</v>
       </c>
       <c r="E163" t="n">
-        <v>0.003355261329972068</v>
+        <v>0.002841915711667227</v>
       </c>
     </row>
     <row r="164">
@@ -3214,16 +3214,16 @@
         <v>1.62</v>
       </c>
       <c r="B164" t="n">
-        <v>2.64291987857634</v>
+        <v>2.663415384222296</v>
       </c>
       <c r="C164" t="n">
-        <v>0.425198746155622</v>
+        <v>0.4277686274783348</v>
       </c>
       <c r="D164" t="n">
-        <v>0.4255980484429554</v>
+        <v>0.4172905050771145</v>
       </c>
       <c r="E164" t="n">
-        <v>0.003356437153434438</v>
+        <v>0.002843073261945689</v>
       </c>
     </row>
     <row r="165">
@@ -3231,16 +3231,16 @@
         <v>1.63</v>
       </c>
       <c r="B165" t="n">
-        <v>2.641846783491508</v>
+        <v>2.662251577431058</v>
       </c>
       <c r="C165" t="n">
-        <v>0.4251856191296476</v>
+        <v>0.427736138635695</v>
       </c>
       <c r="D165" t="n">
-        <v>0.4260161189718851</v>
+        <v>0.4175934961541525</v>
       </c>
       <c r="E165" t="n">
-        <v>0.003358473130673182</v>
+        <v>0.002845086670653582</v>
       </c>
     </row>
     <row r="166">
@@ -3248,16 +3248,16 @@
         <v>1.64</v>
       </c>
       <c r="B166" t="n">
-        <v>2.64035233287378</v>
+        <v>2.660631452661776</v>
       </c>
       <c r="C166" t="n">
-        <v>0.4251668021079432</v>
+        <v>0.4276905154403577</v>
       </c>
       <c r="D166" t="n">
-        <v>0.4264815996980305</v>
+        <v>0.4179586336056962</v>
       </c>
       <c r="E166" t="n">
-        <v>0.003361431665616772</v>
+        <v>0.002848024794535826</v>
       </c>
     </row>
     <row r="167">
@@ -3265,16 +3265,16 @@
         <v>1.65</v>
       </c>
       <c r="B167" t="n">
-        <v>2.638441364674925</v>
+        <v>2.65856065750839</v>
       </c>
       <c r="C167" t="n">
-        <v>0.4251420417143507</v>
+        <v>0.427631677806376</v>
       </c>
       <c r="D167" t="n">
-        <v>0.4269939565443627</v>
+        <v>0.4183851072928564</v>
       </c>
       <c r="E167" t="n">
-        <v>0.003365375162193676</v>
+        <v>0.002851956490337339</v>
       </c>
     </row>
     <row r="168">
@@ -3282,16 +3282,16 @@
         <v>1.66</v>
       </c>
       <c r="B168" t="n">
-        <v>2.636118903320932</v>
+        <v>2.656045055206661</v>
       </c>
       <c r="C168" t="n">
-        <v>0.4251110845727122</v>
+        <v>0.427559545647803</v>
       </c>
       <c r="D168" t="n">
-        <v>0.4275526677369206</v>
+        <v>0.4188721304015016</v>
       </c>
       <c r="E168" t="n">
-        <v>0.003370366024332364</v>
+        <v>0.002856950614803041</v>
       </c>
     </row>
     <row r="169">
@@ -3299,16 +3299,16 @@
         <v>1.67</v>
       </c>
       <c r="B169" t="n">
-        <v>2.633390152536667</v>
+        <v>2.653090715644526</v>
       </c>
       <c r="C169" t="n">
-        <v>0.4250736773068696</v>
+        <v>0.4274740388786916</v>
       </c>
       <c r="D169" t="n">
-        <v>0.4281572231431161</v>
+        <v>0.419418938159636</v>
       </c>
       <c r="E169" t="n">
-        <v>0.003376466655961305</v>
+        <v>0.002863076024677851</v>
       </c>
     </row>
     <row r="170">
@@ -3316,16 +3316,16 @@
         <v>1.68</v>
       </c>
       <c r="B170" t="n">
-        <v>2.630260488115788</v>
+        <v>2.649703906314577</v>
       </c>
       <c r="C170" t="n">
-        <v>0.4250295665406653</v>
+        <v>0.4273750774130949</v>
       </c>
       <c r="D170" t="n">
-        <v>0.4288071236237685</v>
+        <v>0.420024786587262</v>
       </c>
       <c r="E170" t="n">
-        <v>0.003383739461008969</v>
+        <v>0.002870401576706688</v>
       </c>
     </row>
     <row r="171">
@@ -3333,16 +3333,16 @@
         <v>1.69</v>
       </c>
       <c r="B171" t="n">
-        <v>2.626735450646832</v>
+        <v>2.645891083223293</v>
       </c>
       <c r="C171" t="n">
-        <v>0.424978498897941</v>
+        <v>0.4272625811650658</v>
       </c>
       <c r="D171" t="n">
-        <v>0.4295018803982003</v>
+        <v>0.4206889512769491</v>
       </c>
       <c r="E171" t="n">
-        <v>0.003392246843403824</v>
+        <v>0.002878996127634471</v>
       </c>
     </row>
     <row r="172">
@@ -3350,16 +3350,16 @@
         <v>1.7</v>
       </c>
       <c r="B172" t="n">
-        <v>2.622820738206213</v>
+        <v>2.641658881771295</v>
       </c>
       <c r="C172" t="n">
-        <v>0.424920221002539</v>
+        <v>0.4271364700486573</v>
       </c>
       <c r="D172" t="n">
-        <v>0.4302410144217546</v>
+        <v>0.4214107262034188</v>
       </c>
       <c r="E172" t="n">
-        <v>0.003402051207074341</v>
+        <v>0.002888928534206119</v>
       </c>
     </row>
     <row r="173">
@@ -3367,16 +3367,16 @@
         <v>1.71</v>
       </c>
       <c r="B173" t="n">
-        <v>2.618522199028608</v>
+        <v>2.637014107618624</v>
       </c>
       <c r="C173" t="n">
-        <v>0.4248544794783013</v>
+        <v>0.4269966639779225</v>
       </c>
       <c r="D173" t="n">
-        <v>0.4310240557751259</v>
+        <v>0.4221894225605402</v>
       </c>
       <c r="E173" t="n">
-        <v>0.00341321495594899</v>
+        <v>0.002900267653166551</v>
       </c>
     </row>
     <row r="174">
@@ -3384,16 +3384,16 @@
         <v>1.72</v>
       </c>
       <c r="B174" t="n">
-        <v>2.613845824165028</v>
+        <v>2.631963727548644</v>
       </c>
       <c r="C174" t="n">
-        <v>0.4247810209490699</v>
+        <v>0.4268430828669145</v>
       </c>
       <c r="D174" t="n">
-        <v>0.4318505430649216</v>
+        <v>0.4230243676242135</v>
       </c>
       <c r="E174" t="n">
-        <v>0.003425800493956238</v>
+        <v>0.002913082341260687</v>
       </c>
     </row>
     <row r="175">
@@ -3401,16 +3401,16 @@
         <v>1.73</v>
       </c>
       <c r="B175" t="n">
-        <v>2.608797740138579</v>
+        <v>2.626514860343836</v>
       </c>
       <c r="C175" t="n">
-        <v>0.424699592038687</v>
+        <v>0.426675646629686</v>
       </c>
       <c r="D175" t="n">
-        <v>0.4327200228349037</v>
+        <v>0.4239149036396936</v>
       </c>
       <c r="E175" t="n">
-        <v>0.003439870225024557</v>
+        <v>0.002927441455233445</v>
       </c>
     </row>
     <row r="176">
@@ -3418,16 +3418,16 @@
         <v>1.74</v>
       </c>
       <c r="B176" t="n">
-        <v>2.603384201607726</v>
+        <v>2.620674767686341</v>
       </c>
       <c r="C176" t="n">
-        <v>0.4246099393709944</v>
+        <v>0.4264942751802903</v>
       </c>
       <c r="D176" t="n">
-        <v>0.4336320489873808</v>
+        <v>0.4248603867319851</v>
       </c>
       <c r="E176" t="n">
-        <v>0.003455486553082415</v>
+        <v>0.002943413851829745</v>
       </c>
     </row>
     <row r="177">
@@ -3435,16 +3435,16 @@
         <v>1.75</v>
       </c>
       <c r="B177" t="n">
-        <v>2.597611584046532</v>
+        <v>2.61445084509576</v>
       </c>
       <c r="C177" t="n">
-        <v>0.4245118095698345</v>
+        <v>0.4262988884327803</v>
       </c>
       <c r="D177" t="n">
-        <v>0.4345861822142507</v>
+        <v>0.4258601858380086</v>
       </c>
       <c r="E177" t="n">
-        <v>0.003472711882058281</v>
+        <v>0.002961068387794506</v>
       </c>
     </row>
     <row r="178">
@@ -3452,16 +3452,16 @@
         <v>1.76</v>
       </c>
       <c r="B178" t="n">
-        <v>2.591486376451147</v>
+        <v>2.607850612916231</v>
       </c>
       <c r="C178" t="n">
-        <v>0.4244049492590492</v>
+        <v>0.426089406301209</v>
       </c>
       <c r="D178" t="n">
-        <v>0.4355819894372172</v>
+        <v>0.4269136816593089</v>
       </c>
       <c r="E178" t="n">
-        <v>0.003491608615880625</v>
+        <v>0.002980473919872646</v>
       </c>
     </row>
     <row r="179">
@@ -3469,16 +3469,16 @@
         <v>1.77</v>
       </c>
       <c r="B179" t="n">
-        <v>2.585015174081469</v>
+        <v>2.600881707364475</v>
       </c>
       <c r="C179" t="n">
-        <v>0.4242891050624805</v>
+        <v>0.4258657486996295</v>
       </c>
       <c r="D179" t="n">
-        <v>0.4366190432567297</v>
+        <v>0.4280202656341454</v>
       </c>
       <c r="E179" t="n">
-        <v>0.003512239158477917</v>
+        <v>0.003001699304809085</v>
       </c>
     </row>
     <row r="180">
@@ -3486,16 +3486,16 @@
         <v>1.78</v>
       </c>
       <c r="B180" t="n">
-        <v>2.578204671246665</v>
+        <v>2.593551871649991</v>
       </c>
       <c r="C180" t="n">
-        <v>0.4241640236039705</v>
+        <v>0.4256278355420946</v>
       </c>
       <c r="D180" t="n">
-        <v>0.4376969214092156</v>
+        <v>0.4291793389278639</v>
       </c>
       <c r="E180" t="n">
-        <v>0.003534665913778626</v>
+        <v>0.003024813399348742</v>
       </c>
     </row>
     <row r="181">
@@ -3503,16 +3503,16 @@
         <v>1.79</v>
       </c>
       <c r="B181" t="n">
-        <v>2.57106165414289</v>
+        <v>2.585868947178182</v>
       </c>
       <c r="C181" t="n">
-        <v>0.4240294515073614</v>
+        <v>0.4253755867426575</v>
       </c>
       <c r="D181" t="n">
-        <v>0.4388152062322013</v>
+        <v>0.4303903114405173</v>
       </c>
       <c r="E181" t="n">
-        <v>0.003558951285711221</v>
+        <v>0.003049885060236537</v>
       </c>
     </row>
     <row r="182">
@@ -3520,16 +3520,16 @@
         <v>1.8</v>
       </c>
       <c r="B182" t="n">
-        <v>2.563592993751272</v>
+        <v>2.577840864846729</v>
       </c>
       <c r="C182" t="n">
-        <v>0.423885135396495</v>
+        <v>0.4251089222153712</v>
       </c>
       <c r="D182" t="n">
-        <v>0.4399734841369374</v>
+        <v>0.4316526008307612</v>
       </c>
       <c r="E182" t="n">
-        <v>0.003585157678204173</v>
+        <v>0.003076983144217387</v>
       </c>
     </row>
     <row r="183">
@@ -3537,16 +3537,16 @@
         <v>1.81</v>
       </c>
       <c r="B183" t="n">
-        <v>2.555805638803895</v>
+        <v>2.569475636445089</v>
       </c>
       <c r="C183" t="n">
-        <v>0.4237308218952136</v>
+        <v>0.4248277618742886</v>
       </c>
       <c r="D183" t="n">
-        <v>0.441171345088168</v>
+        <v>0.4329656315551064</v>
       </c>
       <c r="E183" t="n">
-        <v>0.003613347495185949</v>
+        <v>0.003106176508036214</v>
       </c>
     </row>
     <row r="184">
@@ -3554,16 +3554,16 @@
         <v>1.82</v>
       </c>
       <c r="B184" t="n">
-        <v>2.547706608825214</v>
+        <v>2.560781346166507</v>
       </c>
       <c r="C184" t="n">
-        <v>0.4235662576273592</v>
+        <v>0.4245320256334628</v>
       </c>
       <c r="D184" t="n">
-        <v>0.4424083820907005</v>
+        <v>0.4343288339216736</v>
       </c>
       <c r="E184" t="n">
-        <v>0.00364358314058502</v>
+        <v>0.003137534008437934</v>
       </c>
     </row>
     <row r="185">
@@ -3571,16 +3571,16 @@
         <v>1.83</v>
       </c>
       <c r="B185" t="n">
-        <v>2.539302987256001</v>
+        <v>2.551766142241485</v>
       </c>
       <c r="C185" t="n">
-        <v>0.4233911892167737</v>
+        <v>0.4242216334069468</v>
       </c>
       <c r="D185" t="n">
-        <v>0.4436841906824603</v>
+        <v>0.4357416431576434</v>
       </c>
       <c r="E185" t="n">
-        <v>0.003675927018329855</v>
+        <v>0.003171124502167469</v>
       </c>
     </row>
     <row r="186">
@@ -3588,16 +3588,16 @@
         <v>1.84</v>
       </c>
       <c r="B186" t="n">
-        <v>2.530601914666592</v>
+        <v>2.542438228701193</v>
       </c>
       <c r="C186" t="n">
-        <v>0.4232053632872995</v>
+        <v>0.4238965051087935</v>
       </c>
       <c r="D186" t="n">
-        <v>0.4449983684337264</v>
+        <v>0.437203498489656</v>
       </c>
       <c r="E186" t="n">
-        <v>0.003710441532348924</v>
+        <v>0.003207016845969736</v>
       </c>
     </row>
     <row r="187">
@@ -3605,16 +3605,16 @@
         <v>1.85</v>
       </c>
       <c r="B187" t="n">
-        <v>2.521610582065902</v>
+        <v>2.532805857278801</v>
       </c>
       <c r="C187" t="n">
-        <v>0.4230085264627783</v>
+        <v>0.4235565606530561</v>
       </c>
       <c r="D187" t="n">
-        <v>0.4463505144522723</v>
+        <v>0.4387138422364625</v>
       </c>
       <c r="E187" t="n">
-        <v>0.003747189086570696</v>
+        <v>0.003245279896589655</v>
       </c>
     </row>
     <row r="188">
@@ -3622,16 +3622,16 @@
         <v>1.86</v>
       </c>
       <c r="B188" t="n">
-        <v>2.512336224312322</v>
+        <v>2.522877319456286</v>
       </c>
       <c r="C188" t="n">
-        <v>0.4228004253670524</v>
+        <v>0.4232017199537875</v>
       </c>
       <c r="D188" t="n">
-        <v>0.4477402288941469</v>
+        <v>0.4402721189131824</v>
       </c>
       <c r="E188" t="n">
-        <v>0.00378623208492364</v>
+        <v>0.003285982510772144</v>
       </c>
     </row>
     <row r="189">
@@ -3639,16 +3639,16 @@
         <v>1.87</v>
       </c>
       <c r="B189" t="n">
-        <v>2.50278611363229</v>
+        <v>2.512660938663758</v>
       </c>
       <c r="C189" t="n">
-        <v>0.4225808066239637</v>
+        <v>0.4228319029250407</v>
       </c>
       <c r="D189" t="n">
-        <v>0.4491671124798596</v>
+        <v>0.4418777743465743</v>
       </c>
       <c r="E189" t="n">
-        <v>0.003827632931336227</v>
+        <v>0.003329193545262124</v>
       </c>
     </row>
     <row r="190">
@@ -3656,16 +3656,16 @@
         <v>1.88</v>
       </c>
       <c r="B190" t="n">
-        <v>2.49296755325201</v>
+        <v>2.502165062637923</v>
       </c>
       <c r="C190" t="n">
-        <v>0.4223494168573544</v>
+        <v>0.4224470294808687</v>
       </c>
       <c r="D190" t="n">
-        <v>0.450630766015741</v>
+        <v>0.4435302548007722</v>
       </c>
       <c r="E190" t="n">
-        <v>0.003871454029736924</v>
+        <v>0.003374981856804514</v>
       </c>
     </row>
     <row r="191">
@@ -3673,16 +3673,16 @@
         <v>1.89</v>
       </c>
       <c r="B191" t="n">
-        <v>2.482887871147441</v>
+        <v>2.491398055945786</v>
       </c>
       <c r="C191" t="n">
-        <v>0.4221060026910665</v>
+        <v>0.4220470195353246</v>
       </c>
       <c r="D191" t="n">
-        <v>0.4521307899202794</v>
+        <v>0.4452290061129927</v>
       </c>
       <c r="E191" t="n">
-        <v>0.003917757784054202</v>
+        <v>0.003423416302144231</v>
       </c>
     </row>
     <row r="192">
@@ -3690,16 +3690,16 @@
         <v>1.9</v>
       </c>
       <c r="B192" t="n">
-        <v>2.472554413917373</v>
+        <v>2.480368292679292</v>
       </c>
       <c r="C192" t="n">
-        <v>0.421850310748942</v>
+        <v>0.4216317930024613</v>
       </c>
       <c r="D192" t="n">
-        <v>0.4536667837552445</v>
+        <v>0.4469734728387599</v>
       </c>
       <c r="E192" t="n">
-        <v>0.00396660659821653</v>
+        <v>0.003474565738026195</v>
       </c>
     </row>
     <row r="193">
@@ -3707,16 +3707,16 @@
         <v>1.91</v>
       </c>
       <c r="B193" t="n">
-        <v>2.461974540784065</v>
+        <v>2.469084149326097</v>
       </c>
       <c r="C193" t="n">
-        <v>0.4215820876548231</v>
+        <v>0.4212012697963319</v>
       </c>
       <c r="D193" t="n">
-        <v>0.4552383457614289</v>
+        <v>0.4487630974062484</v>
       </c>
       <c r="E193" t="n">
-        <v>0.004018062876152378</v>
+        <v>0.003528499021195327</v>
       </c>
     </row>
     <row r="194">
@@ -3724,16 +3724,16 @@
         <v>1.92</v>
       </c>
       <c r="B194" t="n">
-        <v>2.451155617725605</v>
+        <v>2.457553997821232</v>
       </c>
       <c r="C194" t="n">
-        <v>0.4213010800325518</v>
+        <v>0.4207553698309893</v>
       </c>
       <c r="D194" t="n">
-        <v>0.4568450723988594</v>
+        <v>0.4505973192793828</v>
       </c>
       <c r="E194" t="n">
-        <v>0.004072189021790214</v>
+        <v>0.003585285008396543</v>
       </c>
     </row>
     <row r="195">
@@ -3741,16 +3741,16 @@
         <v>1.93</v>
       </c>
       <c r="B195" t="n">
-        <v>2.440105011743828</v>
+        <v>2.445786198783993</v>
       </c>
       <c r="C195" t="n">
-        <v>0.4210070345059702</v>
+        <v>0.4202940130204866</v>
       </c>
       <c r="D195" t="n">
-        <v>0.4584865578913412</v>
+        <v>0.4524755741293857</v>
       </c>
       <c r="E195" t="n">
-        <v>0.004129047439058509</v>
+        <v>0.003644992556374765</v>
       </c>
     </row>
     <row r="196">
@@ -3758,16 +3758,16 @@
         <v>1.94</v>
       </c>
       <c r="B196" t="n">
-        <v>2.4288300852713</v>
+        <v>2.433789094943917</v>
       </c>
       <c r="C196" t="n">
-        <v>0.4206996976989202</v>
+        <v>0.4198171192788768</v>
       </c>
       <c r="D196" t="n">
-        <v>0.4601623937752198</v>
+        <v>0.454397293014502</v>
       </c>
       <c r="E196" t="n">
-        <v>0.004188700531885733</v>
+        <v>0.00370769052187491</v>
       </c>
     </row>
     <row r="197">
@@ -3775,16 +3775,16 @@
         <v>1.95</v>
       </c>
       <c r="B197" t="n">
-        <v>2.417338190720599</v>
+        <v>2.421571004759291</v>
       </c>
       <c r="C197" t="n">
-        <v>0.420378816235244</v>
+        <v>0.4193246085202129</v>
       </c>
       <c r="D197" t="n">
-        <v>0.4618721684522606</v>
+        <v>0.4563619015676794</v>
       </c>
       <c r="E197" t="n">
-        <v>0.004251210704200353</v>
+        <v>0.003773447761641899</v>
       </c>
     </row>
     <row r="198">
@@ -3792,16 +3792,16 @@
         <v>1.96</v>
       </c>
       <c r="B198" t="n">
-        <v>2.405636665178756</v>
+        <v>2.40914021623124</v>
       </c>
       <c r="C198" t="n">
-        <v>0.4200441367387837</v>
+        <v>0.4188164006585479</v>
       </c>
       <c r="D198" t="n">
-        <v>0.4636154667465639</v>
+        <v>0.4583688191920229</v>
       </c>
       <c r="E198" t="n">
-        <v>0.00431664035993084</v>
+        <v>0.003842333132420649</v>
       </c>
     </row>
     <row r="199">
@@ -3809,16 +3809,16 @@
         <v>1.97</v>
       </c>
       <c r="B199" t="n">
-        <v>2.393732825249473</v>
+        <v>2.396504980915978</v>
       </c>
       <c r="C199" t="n">
-        <v>0.4196954058333813</v>
+        <v>0.4182924156079347</v>
       </c>
       <c r="D199" t="n">
-        <v>0.4653918694654467</v>
+        <v>0.4604174582638863</v>
       </c>
       <c r="E199" t="n">
-        <v>0.004385051903005663</v>
+        <v>0.003914415490956081</v>
       </c>
     </row>
     <row r="200">
@@ -3826,16 +3826,16 @@
         <v>1.98</v>
       </c>
       <c r="B200" t="n">
-        <v>2.381633962045411</v>
+        <v>2.383673508137449</v>
       </c>
       <c r="C200" t="n">
-        <v>0.4193323701428788</v>
+        <v>0.4177525732824266</v>
       </c>
       <c r="D200" t="n">
-        <v>0.4672009529642441</v>
+        <v>0.4625072233435069</v>
       </c>
       <c r="E200" t="n">
-        <v>0.004456507737353293</v>
+        <v>0.003989763693993113</v>
       </c>
     </row>
     <row r="201">
@@ -3843,16 +3843,16 @@
         <v>1.99</v>
       </c>
       <c r="B201" t="n">
-        <v>2.369347336332535</v>
+        <v>2.37065395940217</v>
       </c>
       <c r="C201" t="n">
-        <v>0.4189547762911184</v>
+        <v>0.4171967935960763</v>
       </c>
       <c r="D201" t="n">
-        <v>0.4690422887149937</v>
+        <v>0.4646375103931302</v>
       </c>
       <c r="E201" t="n">
-        <v>0.004531070266902196</v>
+        <v>0.004068446598276664</v>
       </c>
     </row>
     <row r="202">
@@ -3860,16 +3860,16 @@
         <v>2</v>
       </c>
       <c r="B202" t="n">
-        <v>2.356880173828251</v>
+        <v>2.357454443017703</v>
       </c>
       <c r="C202" t="n">
-        <v>0.4185623709019421</v>
+        <v>0.416624996462937</v>
       </c>
       <c r="D202" t="n">
-        <v>0.4709154428789876</v>
+        <v>0.4668077060026158</v>
       </c>
       <c r="E202" t="n">
-        <v>0.004608801895580846</v>
+        <v>0.004150533060551655</v>
       </c>
     </row>
     <row r="203">
@@ -3877,16 +3877,16 @@
         <v>2.01</v>
       </c>
       <c r="B203" t="n">
-        <v>2.344239660654758</v>
+        <v>2.344083008915811</v>
       </c>
       <c r="C203" t="n">
-        <v>0.4181549005991919</v>
+        <v>0.4160371017970617</v>
       </c>
       <c r="D203" t="n">
-        <v>0.4728199758831882</v>
+        <v>0.4690171866225544</v>
       </c>
       <c r="E203" t="n">
-        <v>0.004689765027317709</v>
+        <v>0.004236091937563005</v>
       </c>
     </row>
     <row r="204">
@@ -3894,16 +3894,16 @@
         <v>2.02</v>
       </c>
       <c r="B204" t="n">
-        <v>2.331432938948793</v>
+        <v>2.330547643681019</v>
       </c>
       <c r="C204" t="n">
-        <v>0.41773211200671</v>
+        <v>0.4154330295125033</v>
       </c>
       <c r="D204" t="n">
-        <v>0.4747554420005235</v>
+        <v>0.4712653178049699</v>
       </c>
       <c r="E204" t="n">
-        <v>0.004774022066041253</v>
+        <v>0.004325192086055627</v>
       </c>
     </row>
     <row r="205">
@@ -3911,16 +3911,16 @@
         <v>2.03</v>
       </c>
       <c r="B205" t="n">
-        <v>2.318467102628645</v>
+        <v>2.3168562657849</v>
       </c>
       <c r="C205" t="n">
-        <v>0.4172937517483382</v>
+        <v>0.4148126995233148</v>
       </c>
       <c r="D205" t="n">
-        <v>0.4767213889340917</v>
+        <v>0.4735514534517197</v>
       </c>
       <c r="E205" t="n">
-        <v>0.004861635415679954</v>
+        <v>0.00441790236277445</v>
       </c>
     </row>
     <row r="206">
@@ -3928,16 +3928,16 @@
         <v>2.04</v>
       </c>
       <c r="B206" t="n">
-        <v>2.30534919331912</v>
+        <v>2.303016721026124</v>
       </c>
       <c r="C206" t="n">
-        <v>0.4168395664479189</v>
+        <v>0.4141760317435494</v>
       </c>
       <c r="D206" t="n">
-        <v>0.4787173574053193</v>
+        <v>0.4758749350707486</v>
       </c>
       <c r="E206" t="n">
-        <v>0.004952667480162273</v>
+        <v>0.004514291624464383</v>
       </c>
     </row>
     <row r="207">
@@ -3945,16 +3945,16 @@
         <v>2.05</v>
       </c>
       <c r="B207" t="n">
-        <v>2.292086196434801</v>
+        <v>2.289036778175943</v>
       </c>
       <c r="C207" t="n">
-        <v>0.4163693027292939</v>
+        <v>0.4135229460872599</v>
       </c>
       <c r="D207" t="n">
-        <v>0.480742880746136</v>
+        <v>0.4782350910403916</v>
       </c>
       <c r="E207" t="n">
-        <v>0.005047180663416684</v>
+        <v>0.004614428727870351</v>
       </c>
     </row>
     <row r="208">
@@ -3962,16 +3962,16 @@
         <v>2.06</v>
       </c>
       <c r="B208" t="n">
-        <v>2.278685037421783</v>
+        <v>2.274924124828498</v>
       </c>
       <c r="C208" t="n">
-        <v>0.4158827072163054</v>
+        <v>0.4128533624684995</v>
       </c>
       <c r="D208" t="n">
-        <v>0.4827974844952421</v>
+        <v>0.4806312358819613</v>
       </c>
       <c r="E208" t="n">
-        <v>0.005145237369371659</v>
+        <v>0.004718382529737275</v>
       </c>
     </row>
     <row r="209">
@@ -3979,16 +3979,16 @@
         <v>2.07</v>
       </c>
       <c r="B209" t="n">
-        <v>2.265152578157803</v>
+        <v>2.260686363455022</v>
       </c>
       <c r="C209" t="n">
-        <v>0.4153795265327954</v>
+        <v>0.412167200801321</v>
       </c>
       <c r="D209" t="n">
-        <v>0.4848806859985591</v>
+        <v>0.4830626695408959</v>
       </c>
       <c r="E209" t="n">
-        <v>0.00524690000195566</v>
+        <v>0.004826221886810068</v>
       </c>
     </row>
     <row r="210">
@@ -3996,16 +3996,16 @@
         <v>2.08</v>
       </c>
       <c r="B210" t="n">
-        <v>2.251495613510418</v>
+        <v>2.246331007660728</v>
       </c>
       <c r="C210" t="n">
-        <v>0.414859507302606</v>
+        <v>0.4114643809997776</v>
       </c>
       <c r="D210" t="n">
-        <v>0.4869919940139747</v>
+        <v>0.4855286766767836</v>
       </c>
       <c r="E210" t="n">
-        <v>0.005352230965097167</v>
+        <v>0.004938015655833657</v>
       </c>
     </row>
     <row r="211">
@@ -4013,16 +4013,16 @@
         <v>2.09</v>
       </c>
       <c r="B211" t="n">
-        <v>2.237720868052756</v>
+        <v>2.231865478642903</v>
       </c>
       <c r="C211" t="n">
-        <v>0.4143223961495793</v>
+        <v>0.4107448229779221</v>
       </c>
       <c r="D211" t="n">
-        <v>0.4891309083205002</v>
+        <v>0.4880285259626194</v>
       </c>
       <c r="E211" t="n">
-        <v>0.005461292662724639</v>
+        <v>0.005053832693552951</v>
       </c>
     </row>
     <row r="212">
@@ -4030,16 +4030,16 @@
         <v>2.1</v>
       </c>
       <c r="B212" t="n">
-        <v>2.223834992936054</v>
+        <v>2.217297101848455</v>
       </c>
       <c r="C212" t="n">
-        <v>0.4137679396975572</v>
+        <v>0.4100084466498077</v>
       </c>
       <c r="D212" t="n">
-        <v>0.4912969193319821</v>
+        <v>0.4905614693936893</v>
       </c>
       <c r="E212" t="n">
-        <v>0.005574147498766553</v>
+        <v>0.00517374185671288</v>
       </c>
     </row>
     <row r="213">
@@ -4047,16 +4047,16 @@
         <v>2.11</v>
       </c>
       <c r="B213" t="n">
-        <v>2.20984456291809</v>
+        <v>2.202633103828946</v>
       </c>
       <c r="C213" t="n">
-        <v>0.413195884570382</v>
+        <v>0.4092551719294874</v>
       </c>
       <c r="D213" t="n">
-        <v>0.4934895077155174</v>
+        <v>0.4931267416065153</v>
       </c>
       <c r="E213" t="n">
-        <v>0.005690857877151369</v>
+        <v>0.005297812002058354</v>
       </c>
     </row>
     <row r="214">
@@ -4064,16 +4064,16 @@
         <v>2.12</v>
       </c>
       <c r="B214" t="n">
-        <v>2.19575607354634</v>
+        <v>2.187880609290847</v>
       </c>
       <c r="C214" t="n">
-        <v>0.4126059773918955</v>
+        <v>0.4084849187310141</v>
       </c>
       <c r="D214" t="n">
-        <v>0.4957081440147442</v>
+        <v>0.4957235592083356</v>
       </c>
       <c r="E214" t="n">
-        <v>0.005811486201807571</v>
+        <v>0.0054261119863343</v>
       </c>
     </row>
     <row r="215">
@@ -4081,16 +4081,16 @@
         <v>2.13</v>
       </c>
       <c r="B215" t="n">
-        <v>2.181575938494595</v>
+        <v>2.173046638338612</v>
       </c>
       <c r="C215" t="n">
-        <v>0.41199796478594</v>
+        <v>0.4076976069684409</v>
       </c>
       <c r="D215" t="n">
-        <v>0.4979522882781849</v>
+        <v>0.4983511201176304</v>
       </c>
       <c r="E215" t="n">
-        <v>0.005936094876663613</v>
+        <v>0.005558710666285628</v>
       </c>
     </row>
     <row r="216">
@@ -4098,16 +4098,16 @@
         <v>2.14</v>
       </c>
       <c r="B216" t="n">
-        <v>2.167310487051509</v>
+        <v>2.158138103907876</v>
       </c>
       <c r="C216" t="n">
-        <v>0.4113715933763574</v>
+        <v>0.4068931565558208</v>
       </c>
       <c r="D216" t="n">
-        <v>0.5002213896928458</v>
+        <v>0.5010086029162453</v>
       </c>
       <c r="E216" t="n">
-        <v>0.006064746305647978</v>
+        <v>0.005695676898657267</v>
       </c>
     </row>
     <row r="217">
@@ -4115,16 +4115,16 @@
         <v>2.15</v>
       </c>
       <c r="B217" t="n">
-        <v>2.152965961759473</v>
+        <v>2.143161809385958</v>
       </c>
       <c r="C217" t="n">
-        <v>0.4107266097869898</v>
+        <v>0.4060714874072067</v>
       </c>
       <c r="D217" t="n">
-        <v>0.5025148862232783</v>
+        <v>0.5036951662136953</v>
       </c>
       <c r="E217" t="n">
-        <v>0.006197502892689123</v>
+        <v>0.005837079540194127</v>
       </c>
     </row>
     <row r="218">
@@ -4132,16 +4132,16 @@
         <v>2.16</v>
       </c>
       <c r="B218" t="n">
-        <v>2.138548516201967</v>
+        <v>2.128124446416607</v>
       </c>
       <c r="C218" t="n">
-        <v>0.4100627606416793</v>
+        <v>0.4052325194366517</v>
       </c>
       <c r="D218" t="n">
-        <v>0.5048322042563342</v>
+        <v>0.5064099480242822</v>
       </c>
       <c r="E218" t="n">
-        <v>0.00633442704171553</v>
+        <v>0.005982987447641135</v>
       </c>
     </row>
     <row r="219">
@@ -4149,16 +4149,16 @@
         <v>2.17</v>
       </c>
       <c r="B219" t="n">
-        <v>2.124064212937479</v>
+        <v>2.113032592885814</v>
       </c>
       <c r="C219" t="n">
-        <v>0.409379792564268</v>
+        <v>0.4043761725582087</v>
       </c>
       <c r="D219" t="n">
-        <v>0.5071727582518513</v>
+        <v>0.5091520651576791</v>
       </c>
       <c r="E219" t="n">
-        <v>0.006475581156655653</v>
+        <v>0.006133469477743202</v>
       </c>
     </row>
     <row r="220">
@@ -4166,16 +4166,16 @@
         <v>2.18</v>
       </c>
       <c r="B220" t="n">
-        <v>2.109519021577861</v>
+        <v>2.097892711085305</v>
       </c>
       <c r="C220" t="n">
-        <v>0.4086774521785979</v>
+        <v>0.403502366685931</v>
       </c>
       <c r="D220" t="n">
-        <v>0.5095359503995271</v>
+        <v>0.5119206126236886</v>
       </c>
       <c r="E220" t="n">
-        <v>0.006621027641437979</v>
+        <v>0.006288594487245258</v>
       </c>
     </row>
     <row r="221">
@@ -4183,16 +4183,16 @@
         <v>2.19</v>
       </c>
       <c r="B221" t="n">
-        <v>2.094918817008932</v>
+        <v>2.082711146050219</v>
       </c>
       <c r="C221" t="n">
-        <v>0.4079554861085111</v>
+        <v>0.4026110217338713</v>
       </c>
       <c r="D221" t="n">
-        <v>0.5119211702822486</v>
+        <v>0.5147146630519022</v>
       </c>
       <c r="E221" t="n">
-        <v>0.006770828899990962</v>
+        <v>0.006448431332892208</v>
       </c>
     </row>
     <row r="222">
@@ -4200,16 +4200,16 @@
         <v>2.2</v>
       </c>
       <c r="B222" t="n">
-        <v>2.080269377750964</v>
+        <v>2.067494124067331</v>
       </c>
       <c r="C222" t="n">
-        <v>0.4072136409778495</v>
+        <v>0.4017020576160828</v>
       </c>
       <c r="D222" t="n">
-        <v>0.514327794546161</v>
+        <v>0.517533266127037</v>
       </c>
       <c r="E222" t="n">
-        <v>0.006925047336243084</v>
+        <v>0.006613048871428986</v>
       </c>
     </row>
     <row r="223">
@@ -4217,16 +4217,16 @@
         <v>2.21</v>
       </c>
       <c r="B223" t="n">
-        <v>2.065576384456598</v>
+        <v>2.052247751350049</v>
       </c>
       <c r="C223" t="n">
-        <v>0.4064516634104554</v>
+        <v>0.4007753942466184</v>
       </c>
       <c r="D223" t="n">
-        <v>0.5167551865777725</v>
+        <v>0.5203754480407499</v>
       </c>
       <c r="E223" t="n">
-        <v>0.007083745354122801</v>
+        <v>0.006782515959600497</v>
       </c>
     </row>
     <row r="224">
@@ -4234,16 +4234,16 @@
         <v>2.22</v>
       </c>
       <c r="B224" t="n">
-        <v>2.050845418543633</v>
+        <v>2.036978012876314</v>
       </c>
       <c r="C224" t="n">
-        <v>0.4056693000301707</v>
+        <v>0.3998309515395312</v>
       </c>
       <c r="D224" t="n">
-        <v>0.5192026961884062</v>
+        <v>0.523240210960771</v>
       </c>
       <c r="E224" t="n">
-        <v>0.007246985357558598</v>
+        <v>0.006956901454151674</v>
       </c>
     </row>
     <row r="225">
@@ -4251,16 +4251,16 @@
         <v>2.23</v>
       </c>
       <c r="B225" t="n">
-        <v>2.036081960960025</v>
+        <v>2.021690771385447</v>
       </c>
       <c r="C225" t="n">
-        <v>0.4048662974608375</v>
+        <v>0.3988686494088741</v>
       </c>
       <c r="D225" t="n">
-        <v>0.5216696593063198</v>
+        <v>0.5261265325182255</v>
       </c>
       <c r="E225" t="n">
-        <v>0.007414829750478929</v>
+        <v>0.007136274211827422</v>
       </c>
     </row>
     <row r="226">
@@ -4268,16 +4268,16 @@
         <v>2.24</v>
       </c>
       <c r="B226" t="n">
-        <v>2.02129139107834</v>
+        <v>2.006391766529845</v>
       </c>
       <c r="C226" t="n">
-        <v>0.4040424023262979</v>
+        <v>0.3978884077687002</v>
       </c>
       <c r="D226" t="n">
-        <v>0.5241553976768334</v>
+        <v>0.5290333653140512</v>
       </c>
       <c r="E226" t="n">
-        <v>0.00758734093681228</v>
+        <v>0.007320703089372676</v>
       </c>
     </row>
     <row r="227">
@@ -4285,16 +4285,16 @@
         <v>2.25</v>
       </c>
       <c r="B227" t="n">
-        <v>2.00647898571685</v>
+        <v>1.991086614177445</v>
       </c>
       <c r="C227" t="n">
-        <v>0.403197361250394</v>
+        <v>0.3968901465330624</v>
       </c>
       <c r="D227" t="n">
-        <v>0.5266592185708123</v>
+        <v>0.5319596364454426</v>
       </c>
       <c r="E227" t="n">
-        <v>0.007764581320487102</v>
+        <v>0.007510256943532336</v>
       </c>
     </row>
     <row r="228">
@@ -4302,16 +4302,16 @@
         <v>2.26</v>
       </c>
       <c r="B228" t="n">
-        <v>1.991649918284345</v>
+        <v>1.975780805860688</v>
       </c>
       <c r="C228" t="n">
-        <v>0.4023309208569678</v>
+        <v>0.3958737856160138</v>
       </c>
       <c r="D228" t="n">
-        <v>0.5291804145018678</v>
+        <v>0.5349042470532945</v>
       </c>
       <c r="E228" t="n">
-        <v>0.007946613305431881</v>
+        <v>0.007705004631051341</v>
       </c>
     </row>
     <row r="229">
@@ -4319,16 +4319,16 @@
         <v>2.27</v>
       </c>
       <c r="B229" t="n">
-        <v>1.976809258045709</v>
+        <v>1.960479708367788</v>
       </c>
       <c r="C229" t="n">
-        <v>0.4014428277698613</v>
+        <v>0.3948392449316074</v>
       </c>
       <c r="D229" t="n">
-        <v>0.5317182629526508</v>
+        <v>0.5378660718916314</v>
       </c>
       <c r="E229" t="n">
-        <v>0.008133499295575072</v>
+        <v>0.007905015008674594</v>
       </c>
     </row>
     <row r="230">
@@ -4336,16 +4336,16 @@
         <v>2.28</v>
       </c>
       <c r="B230" t="n">
-        <v>1.961961969505227</v>
+        <v>1.945188563471941</v>
       </c>
       <c r="C230" t="n">
-        <v>0.4005328286129166</v>
+        <v>0.3937864443938963</v>
       </c>
       <c r="D230" t="n">
-        <v>0.5342720261106222</v>
+        <v>0.5408439589200544</v>
       </c>
       <c r="E230" t="n">
-        <v>0.008325301694845159</v>
+        <v>0.008110356933147028</v>
       </c>
     </row>
     <row r="231">
@@ -4353,16 +4353,16 @@
         <v>2.29</v>
       </c>
       <c r="B231" t="n">
-        <v>1.947112911904542</v>
+        <v>1.929912487794182</v>
       </c>
       <c r="C231" t="n">
-        <v>0.3996006700099758</v>
+        <v>0.3927153039169333</v>
       </c>
       <c r="D231" t="n">
-        <v>0.5368409506137024</v>
+        <v>0.5438367289202491</v>
       </c>
       <c r="E231" t="n">
-        <v>0.008522082907170596</v>
+        <v>0.008321099261213544</v>
       </c>
     </row>
     <row r="232">
@@ -4370,16 +4370,16 @@
         <v>2.3</v>
       </c>
       <c r="B232" t="n">
-        <v>1.932266838832138</v>
+        <v>1.914656472795472</v>
       </c>
       <c r="C232" t="n">
-        <v>0.398646098584881</v>
+        <v>0.3916257434147716</v>
       </c>
       <c r="D232" t="n">
-        <v>0.5394242673062049</v>
+        <v>0.5468431751376356</v>
       </c>
       <c r="E232" t="n">
-        <v>0.008723905336479869</v>
+        <v>0.008537310849619083</v>
       </c>
     </row>
     <row r="233">
@@ -4387,16 +4387,16 @@
         <v>2.31</v>
       </c>
       <c r="B233" t="n">
-        <v>1.917428397941195</v>
+        <v>1.899425384893668</v>
       </c>
       <c r="C233" t="n">
-        <v>0.3976688609614742</v>
+        <v>0.3905176828014641</v>
       </c>
       <c r="D233" t="n">
-        <v>0.5420211910054749</v>
+        <v>0.5498620629492537</v>
       </c>
       <c r="E233" t="n">
-        <v>0.008930831386701431</v>
+        <v>0.008759060555108543</v>
       </c>
     </row>
     <row r="234">
@@ -4404,16 +4404,16 @@
         <v>2.32</v>
       </c>
       <c r="B234" t="n">
-        <v>1.902602130772607</v>
+        <v>1.884223965700937</v>
       </c>
       <c r="C234" t="n">
-        <v>0.3966687037635975</v>
+        <v>0.3893910419910639</v>
       </c>
       <c r="D234" t="n">
-        <v>0.5446309202796678</v>
+        <v>0.5528921295590123</v>
       </c>
       <c r="E234" t="n">
-        <v>0.009142923461763758</v>
+        <v>0.008986417234426853</v>
       </c>
     </row>
     <row r="235">
@@ -4421,16 +4421,16 @@
         <v>2.33</v>
       </c>
       <c r="B235" t="n">
-        <v>1.887792472679966</v>
+        <v>1.869056832377236</v>
       </c>
       <c r="C235" t="n">
-        <v>0.3956453736150929</v>
+        <v>0.3882457408976239</v>
       </c>
       <c r="D235" t="n">
-        <v>0.5472526372371032</v>
+        <v>0.5559320837214414</v>
       </c>
       <c r="E235" t="n">
-        <v>0.00936024396559533</v>
+        <v>0.009219449744318943</v>
       </c>
     </row>
     <row r="236">
@@ -4438,16 +4438,16 @@
         <v>2.34</v>
       </c>
       <c r="B236" t="n">
-        <v>1.873003752853265</v>
+        <v>1.853928478095453</v>
       </c>
       <c r="C236" t="n">
-        <v>0.3945986171398025</v>
+        <v>0.387081699435197</v>
       </c>
       <c r="D236" t="n">
-        <v>0.5498855073276456</v>
+        <v>0.558980605495107</v>
       </c>
       <c r="E236" t="n">
-        <v>0.009582855302124597</v>
+        <v>0.009458226941529708</v>
       </c>
     </row>
     <row r="237">
@@ -4455,16 +4455,16 @@
         <v>2.35</v>
       </c>
       <c r="B237" t="n">
-        <v>1.858240194438061</v>
+        <v>1.838843272613813</v>
       </c>
       <c r="C237" t="n">
-        <v>0.3935281809615684</v>
+        <v>0.3858988375178366</v>
       </c>
       <c r="D237" t="n">
-        <v>0.5525286791565762</v>
+        <v>0.5620363460268729</v>
       </c>
       <c r="E237" t="n">
-        <v>0.009810819875280052</v>
+        <v>0.009702817682804095</v>
       </c>
     </row>
     <row r="238">
@@ -4472,16 +4472,16 @@
         <v>2.36</v>
       </c>
       <c r="B238" t="n">
-        <v>1.843505914746874</v>
+        <v>1.823805462951203</v>
       </c>
       <c r="C238" t="n">
-        <v>0.3924338117042326</v>
+        <v>0.3846970750595954</v>
       </c>
       <c r="D238" t="n">
-        <v>0.5551812843114179</v>
+        <v>0.5650979273681994</v>
       </c>
       <c r="E238" t="n">
-        <v>0.01004420008899014</v>
+        <v>0.009953290824886997</v>
       </c>
     </row>
     <row r="239">
@@ -4489,16 +4489,16 @@
         <v>2.37</v>
       </c>
       <c r="B239" t="n">
-        <v>1.82880492555952</v>
+        <v>1.808819174161056</v>
       </c>
       <c r="C239" t="n">
-        <v>0.3913152559916371</v>
+        <v>0.3834763319745265</v>
       </c>
       <c r="D239" t="n">
-        <v>0.5578424372021935</v>
+        <v>0.5681639423246871</v>
       </c>
       <c r="E239" t="n">
-        <v>0.01028305834718335</v>
+        <v>0.01020971522452335</v>
       </c>
     </row>
     <row r="240">
@@ -4506,16 +4506,16 @@
         <v>2.38</v>
       </c>
       <c r="B240" t="n">
-        <v>1.814141133509166</v>
+        <v>1.793888410199506</v>
       </c>
       <c r="C240" t="n">
-        <v>0.3901722604476242</v>
+        <v>0.3822365281766828</v>
       </c>
       <c r="D240" t="n">
-        <v>0.5605112349156003</v>
+        <v>0.5712329543400838</v>
       </c>
       <c r="E240" t="n">
-        <v>0.01052745705378813</v>
+        <v>0.01047215973845807</v>
       </c>
     </row>
     <row r="241">
@@ -4523,16 +4523,16 @@
         <v>2.39</v>
       </c>
       <c r="B241" t="n">
-        <v>1.799518340550839</v>
+        <v>1.779017054883536</v>
       </c>
       <c r="C241" t="n">
-        <v>0.3890045716960357</v>
+        <v>0.3809775835801175</v>
       </c>
       <c r="D241" t="n">
-        <v>0.5631867570835921</v>
+        <v>0.57430349741598</v>
       </c>
       <c r="E241" t="n">
-        <v>0.01077745861273298</v>
+        <v>0.01074069322343607</v>
       </c>
     </row>
     <row r="242">
@@ -4540,16 +4540,16 @@
         <v>2.4</v>
       </c>
       <c r="B242" t="n">
-        <v>1.78494024450916</v>
+        <v>1.764208872934897</v>
       </c>
       <c r="C242" t="n">
-        <v>0.3878119363607138</v>
+        <v>0.3796994180988835</v>
       </c>
       <c r="D242" t="n">
-        <v>0.5658680657668639</v>
+        <v>0.5773740760684272</v>
       </c>
       <c r="E242" t="n">
-        <v>0.01103312542794633</v>
+        <v>0.01101538453620227</v>
       </c>
     </row>
     <row r="243">
@@ -4557,16 +4557,16 @@
         <v>2.41</v>
       </c>
       <c r="B243" t="n">
-        <v>1.770410439702091</v>
+        <v>1.749467511105634</v>
       </c>
       <c r="C243" t="n">
-        <v>0.3865941010655005</v>
+        <v>0.3784019516470338</v>
       </c>
       <c r="D243" t="n">
-        <v>0.568554205353746</v>
+        <v>0.5804431653227138</v>
       </c>
       <c r="E243" t="n">
-        <v>0.01129451990335669</v>
+        <v>0.01129630253350161</v>
       </c>
     </row>
     <row r="244">
@@ -4574,16 +4574,16 @@
         <v>2.42</v>
       </c>
       <c r="B244" t="n">
-        <v>1.755932417637514</v>
+        <v>1.734796499381096</v>
       </c>
       <c r="C244" t="n">
-        <v>0.385350812434238</v>
+        <v>0.3770851041386215</v>
       </c>
       <c r="D244" t="n">
-        <v>0.5712442024750102</v>
+        <v>0.583509210747534</v>
       </c>
       <c r="E244" t="n">
-        <v>0.0115617044428925</v>
+        <v>0.01158351607207897</v>
       </c>
     </row>
     <row r="245">
@@ -4591,16 +4591,16 @@
         <v>2.43</v>
       </c>
       <c r="B245" t="n">
-        <v>1.741509567779455</v>
+        <v>1.720199252256364</v>
       </c>
       <c r="C245" t="n">
-        <v>0.3840818170907681</v>
+        <v>0.3757487954876995</v>
       </c>
       <c r="D245" t="n">
-        <v>0.5739370659351051</v>
+        <v>0.5865706285297883</v>
       </c>
       <c r="E245" t="n">
-        <v>0.01183474145048225</v>
+        <v>0.0118770940086793</v>
       </c>
     </row>
     <row r="246">
@@ -4608,16 +4608,16 @@
         <v>2.44</v>
       </c>
       <c r="B246" t="n">
-        <v>1.727145178380846</v>
+        <v>1.705679070082134</v>
       </c>
       <c r="C246" t="n">
-        <v>0.3827868616589332</v>
+        <v>0.3743929456083208</v>
       </c>
       <c r="D246" t="n">
-        <v>0.5766317866603312</v>
+        <v>0.58962580559124</v>
       </c>
       <c r="E246" t="n">
-        <v>0.01211369333005439</v>
+        <v>0.0121771052000475</v>
       </c>
     </row>
     <row r="247">
@@ -4625,16 +4625,16 @@
         <v>2.45</v>
       </c>
       <c r="B247" t="n">
-        <v>1.712842437379695</v>
+        <v>1.691239140476084</v>
       </c>
       <c r="C247" t="n">
-        <v>0.381465692762575</v>
+        <v>0.3730174744145385</v>
       </c>
       <c r="D247" t="n">
-        <v>0.5793273376644779</v>
+        <v>0.5926730997482563</v>
       </c>
       <c r="E247" t="n">
-        <v>0.0123986224855374</v>
+        <v>0.01248361850292852</v>
       </c>
     </row>
     <row r="248">
@@ -4642,16 +4642,16 @@
         <v>2.46</v>
       </c>
       <c r="B248" t="n">
-        <v>1.698604433355636</v>
+        <v>1.676882539795924</v>
       </c>
       <c r="C248" t="n">
-        <v>0.3801180570255359</v>
+        <v>0.3716223018204056</v>
       </c>
       <c r="D248" t="n">
-        <v>0.5820226740324381</v>
+        <v>0.5957108399158382</v>
       </c>
       <c r="E248" t="n">
-        <v>0.01268959132085975</v>
+        <v>0.01279670277406723</v>
       </c>
     </row>
     <row r="249">
@@ -4659,16 +4659,16 @@
         <v>2.47</v>
       </c>
       <c r="B249" t="n">
-        <v>1.684434156543801</v>
+        <v>1.662612234670304</v>
       </c>
       <c r="C249" t="n">
-        <v>0.3787437010716577</v>
+        <v>0.370207347739975</v>
       </c>
       <c r="D249" t="n">
-        <v>0.5847167329223258</v>
+        <v>0.5987373263571406</v>
       </c>
       <c r="E249" t="n">
-        <v>0.01298666223994992</v>
+        <v>0.0131164268702086</v>
       </c>
     </row>
     <row r="250">
@@ -4676,16 +4676,16 @@
         <v>2.48</v>
       </c>
       <c r="B250" t="n">
-        <v>1.67033449990307</v>
+        <v>1.648431083583922</v>
       </c>
       <c r="C250" t="n">
-        <v>0.3773423715247827</v>
+        <v>0.3687725320873</v>
       </c>
       <c r="D250" t="n">
-        <v>0.5874084335866122</v>
+        <v>0.6017508309796593</v>
       </c>
       <c r="E250" t="n">
-        <v>0.01328989764673634</v>
+        <v>0.01344285964809751</v>
       </c>
     </row>
     <row r="251">
@@ -4693,16 +4693,16 @@
         <v>2.49</v>
       </c>
       <c r="B251" t="n">
-        <v>1.65630826023574</v>
+        <v>1.634341838513182</v>
       </c>
       <c r="C251" t="n">
-        <v>0.3759138150087526</v>
+        <v>0.3673177747764331</v>
       </c>
       <c r="D251" t="n">
-        <v>0.5900966774128048</v>
+        <v>0.6047495976792425</v>
       </c>
       <c r="E251" t="n">
-        <v>0.01359935994514753</v>
+        <v>0.01377606996447891</v>
       </c>
     </row>
     <row r="252">
@@ -4710,16 +4710,16 @@
         <v>2.5</v>
       </c>
       <c r="B252" t="n">
-        <v>1.642358139355749</v>
+        <v>1.620347146608901</v>
       </c>
       <c r="C252" t="n">
-        <v>0.3744577781474099</v>
+        <v>0.3658429957214279</v>
       </c>
       <c r="D252" t="n">
-        <v>0.5927803479841843</v>
+        <v>0.6077318427330602</v>
       </c>
       <c r="E252" t="n">
-        <v>0.01391511153911192</v>
+        <v>0.01411612667609769</v>
       </c>
     </row>
     <row r="253">
@@ -4727,16 +4727,16 @@
         <v>2.51</v>
       </c>
       <c r="B253" t="n">
-        <v>1.628486745302617</v>
+        <v>1.606449551922582</v>
       </c>
       <c r="C253" t="n">
-        <v>0.3729740075645963</v>
+        <v>0.3643481148363369</v>
       </c>
       <c r="D253" t="n">
-        <v>0.5954583111611167</v>
+        <v>0.610695755242636</v>
       </c>
       <c r="E253" t="n">
-        <v>0.01423721483255802</v>
+        <v>0.0144630986396988</v>
       </c>
     </row>
     <row r="254">
@@ -4744,16 +4744,16 @@
         <v>2.52</v>
       </c>
       <c r="B254" t="n">
-        <v>1.614696593598336</v>
+        <v>1.592651497172938</v>
       </c>
       <c r="C254" t="n">
-        <v>0.3714622498841542</v>
+        <v>0.3628330520352135</v>
       </c>
       <c r="D254" t="n">
-        <v>0.5981294151834485</v>
+        <v>0.6136394976280113</v>
       </c>
       <c r="E254" t="n">
-        <v>0.01456573222941425</v>
+        <v>0.01481705471202712</v>
       </c>
     </row>
     <row r="255">
@@ -4761,16 +4761,16 @@
         <v>2.53</v>
       </c>
       <c r="B255" t="n">
-        <v>1.600990108544477</v>
+        <v>1.578955325549352</v>
       </c>
       <c r="C255" t="n">
-        <v>0.3699222517299253</v>
+        <v>0.3612977272321103</v>
       </c>
       <c r="D255" t="n">
-        <v>0.600792490794496</v>
+        <v>0.6165612061740815</v>
       </c>
       <c r="E255" t="n">
-        <v>0.01490072613360912</v>
+        <v>0.01517806374982761</v>
       </c>
     </row>
     <row r="256">
@@ -4778,16 +4778,16 @@
         <v>2.54</v>
       </c>
       <c r="B256" t="n">
-        <v>1.587369624556864</v>
+        <v>1.565363282549152</v>
       </c>
       <c r="C256" t="n">
-        <v>0.3683537597257519</v>
+        <v>0.3597420603410807</v>
       </c>
       <c r="D256" t="n">
-        <v>0.6034463513871231</v>
+        <v>0.6194589916300949</v>
       </c>
       <c r="E256" t="n">
-        <v>0.01524225894907107</v>
+        <v>0.01554619460984516</v>
       </c>
     </row>
     <row r="257">
@@ -4795,16 +4795,16 @@
         <v>2.55</v>
       </c>
       <c r="B257" t="n">
-        <v>1.573837387535201</v>
+        <v>1.55187751784556</v>
       </c>
       <c r="C257" t="n">
-        <v>0.366756520495476</v>
+        <v>0.3581659712761776</v>
       </c>
       <c r="D257" t="n">
-        <v>0.6060897931724053</v>
+        <v>0.6223309398632707</v>
       </c>
       <c r="E257" t="n">
-        <v>0.01559039307972859</v>
+        <v>0.01592151614882471</v>
       </c>
     </row>
     <row r="258">
@@ -4812,16 +4812,16 @@
         <v>2.56</v>
       </c>
       <c r="B258" t="n">
-        <v>1.560395556265133</v>
+        <v>1.538500087183377</v>
       </c>
       <c r="C258" t="n">
-        <v>0.3651302806629398</v>
+        <v>0.3565693799514539</v>
       </c>
       <c r="D258" t="n">
-        <v>0.6087215953713609</v>
+        <v>0.6251751125674339</v>
       </c>
       <c r="E258" t="n">
-        <v>0.01594519092951014</v>
+        <v>0.01630409722351116</v>
       </c>
     </row>
     <row r="259">
@@ -4829,16 +4829,16 @@
         <v>2.57</v>
       </c>
       <c r="B259" t="n">
-        <v>1.547046203850225</v>
+        <v>1.525232954299485</v>
       </c>
       <c r="C259" t="n">
-        <v>0.3634747868519851</v>
+        <v>0.3549522062809627</v>
       </c>
       <c r="D259" t="n">
-        <v>0.6113405204302268</v>
+        <v>0.6279895480275216</v>
       </c>
       <c r="E259" t="n">
-        <v>0.01630671490234419</v>
+        <v>0.01669400669064943</v>
       </c>
     </row>
     <row r="260">
@@ -4846,16 +4846,16 @@
         <v>2.58</v>
       </c>
       <c r="B260" t="n">
-        <v>1.533791319171489</v>
+        <v>1.51207799286537</v>
       </c>
       <c r="C260" t="n">
-        <v>0.361789785686454</v>
+        <v>0.353314370178757</v>
       </c>
       <c r="D260" t="n">
-        <v>0.613945314259739</v>
+        <v>0.6307722619407524</v>
       </c>
       <c r="E260" t="n">
-        <v>0.01667502740215922</v>
+        <v>0.01709131340698446</v>
       </c>
     </row>
     <row r="261">
@@ -4863,16 +4863,16 @@
         <v>2.59</v>
       </c>
       <c r="B261" t="n">
-        <v>1.520632808372073</v>
+        <v>1.499036988448981</v>
       </c>
       <c r="C261" t="n">
-        <v>0.3600750237901889</v>
+        <v>0.3516557915588898</v>
       </c>
       <c r="D261" t="n">
-        <v>0.6165347064988744</v>
+        <v>0.6335212482951889</v>
       </c>
       <c r="E261" t="n">
-        <v>0.01705019083288368</v>
+        <v>0.01749608622926115</v>
       </c>
     </row>
     <row r="262">
@@ -4880,16 +4880,16 @@
         <v>2.6</v>
       </c>
       <c r="B262" t="n">
-        <v>1.507572496364847</v>
+        <v>1.486111640493301</v>
       </c>
       <c r="C262" t="n">
-        <v>0.3583302477870314</v>
+        <v>0.3499763903354141</v>
       </c>
       <c r="D262" t="n">
-        <v>0.6191074108034894</v>
+        <v>0.636234480306364</v>
       </c>
       <c r="E262" t="n">
-        <v>0.01743226759844607</v>
+        <v>0.01790839401422444</v>
       </c>
     </row>
     <row r="263">
@@ -4897,16 +4897,16 @@
         <v>2.61</v>
       </c>
       <c r="B263" t="n">
-        <v>1.494612128360661</v>
+        <v>1.473303564309145</v>
       </c>
       <c r="C263" t="n">
-        <v>0.3565552043008238</v>
+        <v>0.3482760864223828</v>
       </c>
       <c r="D263" t="n">
-        <v>0.6216621251602771</v>
+        <v>0.6389099114125623</v>
       </c>
       <c r="E263" t="n">
-        <v>0.01782132010277481</v>
+        <v>0.01832830561861921</v>
       </c>
     </row>
     <row r="264">
@@ -4914,16 +4914,16 @@
         <v>2.62</v>
       </c>
       <c r="B264" t="n">
-        <v>1.481753371415122</v>
+        <v>1.460614293079752</v>
       </c>
       <c r="C264" t="n">
-        <v>0.3547496399554081</v>
+        <v>0.3465547997338491</v>
       </c>
       <c r="D264" t="n">
-        <v>0.6241975322264566</v>
+        <v>0.6415454763292836</v>
       </c>
       <c r="E264" t="n">
-        <v>0.01821741074979843</v>
+        <v>0.01875588989919043</v>
       </c>
     </row>
     <row r="265">
@@ -4931,16 +4931,16 @@
         <v>2.63</v>
       </c>
       <c r="B265" t="n">
-        <v>1.468997815991823</v>
+        <v>1.448045279874879</v>
       </c>
       <c r="C265" t="n">
-        <v>0.3529133013746266</v>
+        <v>0.344812450183866</v>
       </c>
       <c r="D265" t="n">
-        <v>0.6267122996955774</v>
+        <v>0.6441390921633255</v>
       </c>
       <c r="E265" t="n">
-        <v>0.01862060194344535</v>
+        <v>0.01919121571268297</v>
       </c>
     </row>
     <row r="266">
@@ -4948,16 +4948,16 @@
         <v>2.64</v>
       </c>
       <c r="B266" t="n">
-        <v>1.456346977539976</v>
+        <v>1.435597899672166</v>
       </c>
       <c r="C266" t="n">
-        <v>0.351045935182321</v>
+        <v>0.3430489576864863</v>
       </c>
       <c r="D266" t="n">
-        <v>0.629205080689817</v>
+        <v>0.6466886595868495</v>
       </c>
       <c r="E266" t="n">
-        <v>0.01903095608764407</v>
+        <v>0.01963435191584179</v>
       </c>
     </row>
     <row r="267">
@@ -4965,16 +4965,16 @@
         <v>2.65</v>
       </c>
       <c r="B267" t="n">
-        <v>1.443802298084539</v>
+        <v>1.423273451383659</v>
       </c>
       <c r="C267" t="n">
-        <v>0.3491472880023335</v>
+        <v>0.3412642421557633</v>
       </c>
       <c r="D267" t="n">
-        <v>0.6316745141791156</v>
+        <v>0.6491920640716972</v>
       </c>
       <c r="E267" t="n">
-        <v>0.01944853558632303</v>
+        <v>0.02008536736541178</v>
       </c>
     </row>
     <row r="268">
@@ -4982,16 +4982,16 @@
         <v>2.66</v>
       </c>
       <c r="B268" t="n">
-        <v>1.431365147826919</v>
+        <v>1.411073159885457</v>
       </c>
       <c r="C268" t="n">
-        <v>0.3472171064585062</v>
+        <v>0.3394582235057497</v>
       </c>
       <c r="D268" t="n">
-        <v>0.6341192254274859</v>
+        <v>0.6516471771841391</v>
       </c>
       <c r="E268" t="n">
-        <v>0.01987340284341075</v>
+        <v>0.02054433091813788</v>
       </c>
     </row>
     <row r="269">
@@ -4999,16 +4999,16 @@
         <v>2.67</v>
       </c>
       <c r="B269" t="n">
-        <v>1.419036826754485</v>
+        <v>1.398998178048559</v>
       </c>
       <c r="C269" t="n">
-        <v>0.3452551371746813</v>
+        <v>0.3376308216504988</v>
       </c>
       <c r="D269" t="n">
-        <v>0.6365378264667952</v>
+        <v>0.6540518579401358</v>
       </c>
       <c r="E269" t="n">
-        <v>0.02030562026283563</v>
+        <v>0.02101131143076498</v>
       </c>
     </row>
     <row r="270">
@@ -5016,16 +5016,16 @@
         <v>2.68</v>
       </c>
       <c r="B270" t="n">
-        <v>1.406818566257088</v>
+        <v>1.387049588769064</v>
       </c>
       <c r="C270" t="n">
-        <v>0.3432611267747005</v>
+        <v>0.3357819565040634</v>
       </c>
       <c r="D270" t="n">
-        <v>0.6389289165983103</v>
+        <v>0.6564039542210911</v>
       </c>
       <c r="E270" t="n">
-        <v>0.0207452502485262</v>
+        <v>0.02148637776003804</v>
       </c>
     </row>
     <row r="271">
@@ -5033,16 +5033,16 @@
         <v>2.69</v>
       </c>
       <c r="B271" t="n">
-        <v>1.394711530748975</v>
+        <v>1.375228406995999</v>
       </c>
       <c r="C271" t="n">
-        <v>0.3412348218824062</v>
+        <v>0.3339115479804966</v>
       </c>
       <c r="D271" t="n">
-        <v>0.6412910829222527</v>
+        <v>0.6587013042499752</v>
       </c>
       <c r="E271" t="n">
-        <v>0.02119235520441089</v>
+        <v>0.02196959876270194</v>
       </c>
     </row>
     <row r="272">
@@ -5050,16 +5050,16 @@
         <v>2.7</v>
       </c>
       <c r="B272" t="n">
-        <v>1.382716819294441</v>
+        <v>1.363535581755081</v>
       </c>
       <c r="C272" t="n">
-        <v>0.3391759691216403</v>
+        <v>0.3320195159938514</v>
       </c>
       <c r="D272" t="n">
-        <v>0.6436229008956006</v>
+        <v>0.6609417381275806</v>
       </c>
       <c r="E272" t="n">
-        <v>0.0216469975344182</v>
+        <v>0.02246104329550163</v>
       </c>
     </row>
     <row r="273">
@@ -5067,16 +5067,16 @@
         <v>2.71</v>
       </c>
       <c r="B273" t="n">
-        <v>1.370835467235694</v>
+        <v>1.3519719981669</v>
       </c>
       <c r="C273" t="n">
-        <v>0.3370843151162449</v>
+        <v>0.3301057804581808</v>
       </c>
       <c r="D273" t="n">
-        <v>0.6459229349183299</v>
+        <v>0.6631230794285615</v>
       </c>
       <c r="E273" t="n">
-        <v>0.02210923964247656</v>
+        <v>0.022960780215182</v>
       </c>
     </row>
     <row r="274">
@@ -5084,16 +5084,16 @@
         <v>2.72</v>
       </c>
       <c r="B274" t="n">
-        <v>1.359068447821468</v>
+        <v>1.340538479458002</v>
       </c>
       <c r="C274" t="n">
-        <v>0.334959606490062</v>
+        <v>0.3281702612875378</v>
       </c>
       <c r="D274" t="n">
-        <v>0.6481897389482677</v>
+        <v>0.6652431468567926</v>
       </c>
       <c r="E274" t="n">
-        <v>0.02257914393251449</v>
+        <v>0.023468878378488</v>
       </c>
     </row>
     <row r="275">
@@ -5101,16 +5101,16 @@
         <v>2.73</v>
       </c>
       <c r="B275" t="n">
-        <v>1.347416673834952</v>
+        <v>1.329235788963521</v>
       </c>
       <c r="C275" t="n">
-        <v>0.3328015898669338</v>
+        <v>0.3262128783959755</v>
       </c>
       <c r="D275" t="n">
-        <v>0.6504218571446938</v>
+        <v>0.6672997559594549</v>
       </c>
       <c r="E275" t="n">
-        <v>0.02305677280846041</v>
+        <v>0.02398540664216452</v>
       </c>
     </row>
     <row r="276">
@@ -5118,16 +5118,16 @@
         <v>2.74</v>
       </c>
       <c r="B276" t="n">
-        <v>1.33588099921971</v>
+        <v>1.318064632120034</v>
       </c>
       <c r="C276" t="n">
-        <v>0.3306100118707022</v>
+        <v>0.3242335516975468</v>
       </c>
       <c r="D276" t="n">
-        <v>0.6526178245407931</v>
+        <v>0.669290720899136</v>
       </c>
       <c r="E276" t="n">
-        <v>0.02354218867424283</v>
+        <v>0.02451043386295652</v>
       </c>
     </row>
     <row r="277">
@@ -5135,16 +5135,16 @@
         <v>2.75</v>
       </c>
       <c r="B277" t="n">
-        <v>1.324462220702308</v>
+        <v>1.307025658447441</v>
       </c>
       <c r="C277" t="n">
-        <v>0.3283846191252094</v>
+        <v>0.3222322011063047</v>
       </c>
       <c r="D277" t="n">
-        <v>0.6547761677450279</v>
+        <v>0.671213856283102</v>
       </c>
       <c r="E277" t="n">
-        <v>0.02403545393379019</v>
+        <v>0.02504402889760885</v>
       </c>
     </row>
     <row r="278">
@@ -5152,16 +5152,16 @@
         <v>2.76</v>
       </c>
       <c r="B278" t="n">
-        <v>1.313161079410421</v>
+        <v>1.296119463518725</v>
       </c>
       <c r="C278" t="n">
-        <v>0.3261251582542974</v>
+        <v>0.3202087465363023</v>
       </c>
       <c r="D278" t="n">
-        <v>0.6568954056714639</v>
+        <v>0.6730669790487595</v>
       </c>
       <c r="E278" t="n">
-        <v>0.02453663099103099</v>
+        <v>0.02558626060286651</v>
       </c>
     </row>
     <row r="279">
@@ -5169,16 +5169,16 @@
         <v>2.77</v>
       </c>
       <c r="B279" t="n">
-        <v>1.301978262485279</v>
+        <v>1.285346590916556</v>
       </c>
       <c r="C279" t="n">
-        <v>0.3238313758818083</v>
+        <v>0.3181631079015926</v>
       </c>
       <c r="D279" t="n">
-        <v>0.6589740502990419</v>
+        <v>0.6748479104041999</v>
       </c>
       <c r="E279" t="n">
-        <v>0.02504578224989366</v>
+        <v>0.02613719783547435</v>
       </c>
     </row>
     <row r="280">
@@ -5186,16 +5186,16 @@
         <v>2.78</v>
       </c>
       <c r="B280" t="n">
-        <v>1.290914404687361</v>
+        <v>1.274707534175753</v>
       </c>
       <c r="C280" t="n">
-        <v>0.321503018631584</v>
+        <v>0.3160952051162285</v>
       </c>
       <c r="D280" t="n">
-        <v>0.6610106074597522</v>
+        <v>0.6765544778225709</v>
       </c>
       <c r="E280" t="n">
-        <v>0.0255629701143067</v>
+        <v>0.02669690945217735</v>
       </c>
     </row>
     <row r="281">
@@ -5203,16 +5203,16 @@
         <v>2.79</v>
       </c>
       <c r="B281" t="n">
-        <v>1.279970089994305</v>
+        <v>1.264202738710738</v>
       </c>
       <c r="C281" t="n">
-        <v>0.3191398331274669</v>
+        <v>0.3140049580942631</v>
       </c>
       <c r="D281" t="n">
-        <v>0.6630035776556256</v>
+        <v>0.6781845170888802</v>
       </c>
       <c r="E281" t="n">
-        <v>0.02608825698819856</v>
+        <v>0.02726546430972037</v>
       </c>
     </row>
     <row r="282">
@@ -5220,16 +5220,16 @@
         <v>2.8</v>
       </c>
       <c r="B282" t="n">
-        <v>1.26914585319005</v>
+        <v>1.253832603727134</v>
       </c>
       <c r="C282" t="n">
-        <v>0.3167415659932986</v>
+        <v>0.3118922867497493</v>
       </c>
       <c r="D282" t="n">
-        <v>0.664951456904414</v>
+        <v>0.679735874397696</v>
       </c>
       <c r="E282" t="n">
-        <v>0.02662170527549774</v>
+        <v>0.02784293126484838</v>
       </c>
     </row>
     <row r="283">
@@ -5237,16 +5237,16 @@
         <v>2.81</v>
       </c>
       <c r="B283" t="n">
-        <v>1.258442181444338</v>
+        <v>1.243597484116805</v>
       </c>
       <c r="C283" t="n">
-        <v>0.3143079638529216</v>
+        <v>0.3097571109967404</v>
       </c>
       <c r="D283" t="n">
-        <v>0.6668527376137898</v>
+        <v>0.6812064085000533</v>
       </c>
       <c r="E283" t="n">
-        <v>0.02716337738013266</v>
+        <v>0.02842937917430625</v>
       </c>
     </row>
     <row r="284">
@@ -5254,16 +5254,16 @@
         <v>2.82</v>
       </c>
       <c r="B284" t="n">
-        <v>1.247859515881671</v>
+        <v>1.233497692335652</v>
       </c>
       <c r="C284" t="n">
-        <v>0.3118387733301778</v>
+        <v>0.3075993507492891</v>
       </c>
       <c r="D284" t="n">
-        <v>0.6687059094838467</v>
+        <v>0.6825939928977366</v>
       </c>
       <c r="E284" t="n">
-        <v>0.02771333570603183</v>
+        <v>0.02902487689483894</v>
       </c>
     </row>
     <row r="285">
@@ -5271,16 +5271,16 @@
         <v>2.83</v>
       </c>
       <c r="B285" t="n">
-        <v>1.237398253138982</v>
+        <v>1.223533500263578</v>
       </c>
       <c r="C285" t="n">
-        <v>0.3093337410489091</v>
+        <v>0.3054189259214484</v>
       </c>
       <c r="D285" t="n">
-        <v>0.6705094604376439</v>
+        <v>0.6838965180829489</v>
       </c>
       <c r="E285" t="n">
-        <v>0.02827164265712372</v>
+        <v>0.02962949328319136</v>
       </c>
     </row>
     <row r="286">
@@ -5288,16 +5288,16 @@
         <v>2.84</v>
       </c>
       <c r="B286" t="n">
-        <v>1.227058746911233</v>
+        <v>1.213705141046111</v>
       </c>
       <c r="C286" t="n">
-        <v>0.3067926136329578</v>
+        <v>0.3032157564272717</v>
       </c>
       <c r="D286" t="n">
-        <v>0.6722618775794817</v>
+        <v>0.6851118938212328</v>
       </c>
       <c r="E286" t="n">
-        <v>0.02883836063733676</v>
+        <v>0.03024329719610841</v>
       </c>
     </row>
     <row r="287">
@@ -5305,16 +5305,16 @@
         <v>2.85</v>
       </c>
       <c r="B287" t="n">
-        <v>1.216841309484297</v>
+        <v>1.204012810917215</v>
       </c>
       <c r="C287" t="n">
-        <v>0.3042151377061659</v>
+        <v>0.3009897621808115</v>
       </c>
       <c r="D287" t="n">
-        <v>0.6739616481805533</v>
+        <v>0.68623805147535</v>
       </c>
       <c r="E287" t="n">
-        <v>0.02941355205059948</v>
+        <v>0.03086635749033505</v>
       </c>
     </row>
     <row r="288">
@@ -5322,16 +5322,16 @@
         <v>2.86</v>
       </c>
       <c r="B288" t="n">
-        <v>1.20674621325446</v>
+        <v>1.194456671002923</v>
       </c>
       <c r="C288" t="n">
-        <v>0.3016010598923754</v>
+        <v>0.2987408630961211</v>
       </c>
       <c r="D288" t="n">
-        <v>0.6756072606915627</v>
+        <v>0.6872729463676758</v>
       </c>
       <c r="E288" t="n">
-        <v>0.02999727930084028</v>
+        <v>0.03149874302261614</v>
       </c>
     </row>
     <row r="289">
@@ -5339,16 +5339,16 @@
         <v>2.87</v>
       </c>
       <c r="B289" t="n">
-        <v>1.196773692233986</v>
+        <v>1.185036849105459</v>
       </c>
       <c r="C289" t="n">
-        <v>0.2989501268154283</v>
+        <v>0.2964689790872534</v>
       </c>
       <c r="D289" t="n">
-        <v>0.6771972057818575</v>
+        <v>0.6882145601785101</v>
       </c>
       <c r="E289" t="n">
-        <v>0.0305896047919877</v>
+        <v>0.03214052264969666</v>
       </c>
     </row>
     <row r="290">
@@ -5356,16 +5356,16 @@
         <v>2.88</v>
       </c>
       <c r="B290" t="n">
-        <v>1.186923943542213</v>
+        <v>1.175753441467612</v>
       </c>
       <c r="C290" t="n">
-        <v>0.2962620850991668</v>
+        <v>0.2941740300682617</v>
       </c>
       <c r="D290" t="n">
-        <v>0.678729977404559</v>
+        <v>0.6890609033775509</v>
       </c>
       <c r="E290" t="n">
-        <v>0.03119059092797015</v>
+        <v>0.03279176522832148</v>
       </c>
     </row>
     <row r="291">
@@ -5373,16 +5373,16 @@
         <v>2.89</v>
       </c>
       <c r="B291" t="n">
-        <v>1.177197128881693</v>
+        <v>1.166606514517134</v>
       </c>
       <c r="C291" t="n">
-        <v>0.2935366813674329</v>
+        <v>0.2918559359531985</v>
       </c>
       <c r="D291" t="n">
-        <v>0.680204073887135</v>
+        <v>0.6898100176856222</v>
       </c>
       <c r="E291" t="n">
-        <v>0.03180030011271615</v>
+        <v>0.03345253961523556</v>
       </c>
     </row>
     <row r="292">
@@ -5390,16 +5390,16 @@
         <v>2.9</v>
       </c>
       <c r="B292" t="n">
-        <v>1.167593375998973</v>
+        <v>1.157596106591085</v>
       </c>
       <c r="C292" t="n">
-        <v>0.2907736622440687</v>
+        <v>0.2895146166561173</v>
       </c>
       <c r="D292" t="n">
-        <v>0.6816179990467949</v>
+        <v>0.6904599785635982</v>
       </c>
       <c r="E292" t="n">
-        <v>0.03241879475015411</v>
+        <v>0.03412291466718377</v>
       </c>
     </row>
     <row r="293">
@@ -5407,16 +5407,16 @@
         <v>2.91</v>
       </c>
       <c r="B293" t="n">
-        <v>1.158112780129607</v>
+        <v>1.148722229639997</v>
       </c>
       <c r="C293" t="n">
-        <v>0.2879727743529161</v>
+        <v>0.2871499920910707</v>
       </c>
       <c r="D293" t="n">
-        <v>0.682970263330039</v>
+        <v>0.6910088977253116</v>
       </c>
       <c r="E293" t="n">
-        <v>0.03304613724421256</v>
+        <v>0.03480295924091109</v>
       </c>
     </row>
     <row r="294">
@@ -5424,16 +5424,16 @@
         <v>2.92</v>
       </c>
       <c r="B294" t="n">
-        <v>1.148755405427094</v>
+        <v>1.139984870911879</v>
       </c>
       <c r="C294" t="n">
-        <v>0.2851337643178176</v>
+        <v>0.2847619821721121</v>
       </c>
       <c r="D294" t="n">
-        <v>0.6842593849756374</v>
+        <v>0.6914549256710851</v>
       </c>
       <c r="E294" t="n">
-        <v>0.03368238999881992</v>
+        <v>0.03549274219316238</v>
       </c>
     </row>
     <row r="295">
@@ -5441,16 +5441,16 @@
         <v>2.93</v>
       </c>
       <c r="B295" t="n">
-        <v>1.139521286375434</v>
+        <v>1.131383994616095</v>
       </c>
       <c r="C295" t="n">
-        <v>0.2822563787626147</v>
+        <v>0.2823505068132941</v>
       </c>
       <c r="D295" t="n">
-        <v>0.6854838912002561</v>
+        <v>0.6917962542383757</v>
       </c>
       <c r="E295" t="n">
-        <v>0.0343276154179047</v>
+        <v>0.03619233238068261</v>
       </c>
     </row>
     <row r="296">
@@ -5458,16 +5458,16 @@
         <v>2.94</v>
       </c>
       <c r="B296" t="n">
-        <v>1.130410429185073</v>
+        <v>1.122919543567205</v>
       </c>
       <c r="C296" t="n">
-        <v>0.2793403643111498</v>
+        <v>0.2799154859286701</v>
       </c>
       <c r="D296" t="n">
-        <v>0.6866423194058928</v>
+        <v>0.6920311191658813</v>
       </c>
       <c r="E296" t="n">
-        <v>0.03498187590539533</v>
+        <v>0.03690179866021664</v>
       </c>
     </row>
     <row r="297">
@@ -5475,16 +5475,16 @@
         <v>2.95</v>
       </c>
       <c r="B297" t="n">
-        <v>1.121422813172025</v>
+        <v>1.114591440808929</v>
       </c>
       <c r="C297" t="n">
-        <v>0.2763854675872648</v>
+        <v>0.2774568394322928</v>
       </c>
       <c r="D297" t="n">
-        <v>0.6877332184082311</v>
+        <v>0.6921578026673118</v>
       </c>
       <c r="E297" t="n">
-        <v>0.03564523386522033</v>
+        <v>0.03762120988850948</v>
       </c>
     </row>
     <row r="298">
@@ -5492,16 +5492,16 @@
         <v>2.96</v>
       </c>
       <c r="B298" t="n">
-        <v>1.112558392120031</v>
+        <v>1.106399591218431</v>
       </c>
       <c r="C298" t="n">
-        <v>0.273391435214802</v>
+        <v>0.2749744872382155</v>
       </c>
       <c r="D298" t="n">
-        <v>0.6887551496849571</v>
+        <v>0.6921746360108931</v>
       </c>
       <c r="E298" t="n">
-        <v>0.03631775170130811</v>
+        <v>0.03835063492230593</v>
       </c>
     </row>
     <row r="299">
@@ -5509,16 +5509,16 @@
         <v>2.97</v>
       </c>
       <c r="B299" t="n">
-        <v>1.103817095625613</v>
+        <v>1.098343883091177</v>
       </c>
       <c r="C299" t="n">
-        <v>0.2703580138176032</v>
+        <v>0.2724683492604908</v>
       </c>
       <c r="D299" t="n">
-        <v>0.6897066886430332</v>
+        <v>0.6920800021005385</v>
       </c>
       <c r="E299" t="n">
-        <v>0.0369994918175872</v>
+        <v>0.03909014261835102</v>
       </c>
     </row>
     <row r="300">
@@ -5526,16 +5526,16 @@
         <v>2.98</v>
       </c>
       <c r="B300" t="n">
-        <v>1.095198830425974</v>
+        <v>1.090424189706679</v>
       </c>
       <c r="C300" t="n">
-        <v>0.2672849500195107</v>
+        <v>0.2699383454131722</v>
       </c>
       <c r="D300" t="n">
-        <v>0.6905864259038603</v>
+        <v>0.6918723380544878</v>
       </c>
       <c r="E300" t="n">
-        <v>0.03769051661798601</v>
+        <v>0.03983980183338959</v>
       </c>
     </row>
     <row r="301">
@@ -5543,16 +5543,16 @@
         <v>2.99</v>
       </c>
       <c r="B301" t="n">
-        <v>1.08670348170968</v>
+        <v>1.082640370875453</v>
       </c>
       <c r="C301" t="n">
-        <v>0.2641719904443662</v>
+        <v>0.2673843956103124</v>
       </c>
       <c r="D301" t="n">
-        <v>0.6913929686052049</v>
+        <v>0.6915501377771027</v>
       </c>
       <c r="E301" t="n">
-        <v>0.03839088850643307</v>
+        <v>0.04059968142416662</v>
       </c>
     </row>
     <row r="302">
@@ -5560,16 +5560,16 @@
         <v>3</v>
       </c>
       <c r="B302" t="n">
-        <v>1.078330914410148</v>
+        <v>1.074992274467626</v>
       </c>
       <c r="C302" t="n">
-        <v>0.2610188817160123</v>
+        <v>0.2648064197659645</v>
       </c>
       <c r="D302" t="n">
-        <v>0.6921249417187086</v>
+        <v>0.6911119545193746</v>
       </c>
       <c r="E302" t="n">
-        <v>0.03910066988685677</v>
+        <v>0.04136985024742697</v>
       </c>
     </row>
     <row r="303">
@@ -5577,16 +5577,16 @@
         <v>3.01</v>
       </c>
       <c r="B303" t="n">
-        <v>1.070080974481949</v>
+        <v>1.067479737923596</v>
       </c>
       <c r="C303" t="n">
-        <v>0.2578253704582905</v>
+        <v>0.2622043377941813</v>
       </c>
       <c r="D303" t="n">
-        <v>0.692780989381741</v>
+        <v>0.6905564034236007</v>
       </c>
       <c r="E303" t="n">
-        <v>0.03981992316318568</v>
+        <v>0.04215037715991563</v>
       </c>
     </row>
     <row r="304">
@@ -5594,16 +5594,16 @@
         <v>3.02</v>
       </c>
       <c r="B304" t="n">
-        <v>1.061953490160026</v>
+        <v>1.060102589747276</v>
       </c>
       <c r="C304" t="n">
-        <v>0.2545912032950433</v>
+        <v>0.2595780696090162</v>
       </c>
       <c r="D304" t="n">
-        <v>0.6933597762422987</v>
+        <v>0.6898821640475783</v>
       </c>
       <c r="E304" t="n">
-        <v>0.04054871073934818</v>
+        <v>0.04294133101837744</v>
       </c>
     </row>
     <row r="305">
@@ -5611,16 +5611,16 @@
         <v>3.03</v>
       </c>
       <c r="B305" t="n">
-        <v>1.053948273201907</v>
+        <v>1.052860650982424</v>
       </c>
       <c r="C305" t="n">
-        <v>0.2513161268501124</v>
+        <v>0.2569275351245219</v>
       </c>
       <c r="D305" t="n">
-        <v>0.6938599888155955</v>
+        <v>0.6890879828635602</v>
       </c>
       <c r="E305" t="n">
-        <v>0.0412870950192728</v>
+        <v>0.04374278067955738</v>
       </c>
     </row>
     <row r="306">
@@ -5628,16 +5628,16 @@
         <v>3.04</v>
       </c>
       <c r="B306" t="n">
-        <v>1.046065120113076</v>
+        <v>1.045753736672653</v>
       </c>
       <c r="C306" t="n">
-        <v>0.2479998877473402</v>
+        <v>0.2542526542547517</v>
       </c>
       <c r="D306" t="n">
-        <v>0.6942803368509388</v>
+        <v>0.6881726757271439</v>
       </c>
       <c r="E306" t="n">
-        <v>0.04203513840688795</v>
+        <v>0.04455479500020032</v>
       </c>
     </row>
     <row r="307">
@@ -5645,16 +5645,16 @@
         <v>3.05</v>
       </c>
       <c r="B307" t="n">
-        <v>1.038303813355655</v>
+        <v>1.038781657305749</v>
       </c>
       <c r="C307" t="n">
-        <v>0.2446422326105685</v>
+        <v>0.2515533469137582</v>
       </c>
       <c r="D307" t="n">
-        <v>0.6946195547074203</v>
+        <v>0.6871351303111645</v>
       </c>
       <c r="E307" t="n">
-        <v>0.04279290330612218</v>
+        <v>0.04537744283705124</v>
       </c>
     </row>
     <row r="308">
@@ -5662,16 +5662,16 @@
         <v>3.06</v>
       </c>
       <c r="B308" t="n">
-        <v>1.030664122540615</v>
+        <v>1.031944220242936</v>
       </c>
       <c r="C308" t="n">
-        <v>0.2412429080636396</v>
+        <v>0.2488295330155948</v>
       </c>
       <c r="D308" t="n">
-        <v>0.6948764027369081</v>
+        <v>0.6859743084996101</v>
       </c>
       <c r="E308" t="n">
-        <v>0.04356045212090388</v>
+        <v>0.04621079304685498</v>
       </c>
     </row>
     <row r="309">
@@ -5679,16 +5679,16 @@
         <v>3.07</v>
       </c>
       <c r="B309" t="n">
-        <v>1.023145805603741</v>
+        <v>1.025241231133819</v>
       </c>
       <c r="C309" t="n">
-        <v>0.2378016607303952</v>
+        <v>0.2460811324743141</v>
       </c>
       <c r="D309" t="n">
-        <v>0.6950496686727613</v>
+        <v>0.6846892487365028</v>
       </c>
       <c r="E309" t="n">
-        <v>0.04433784725516158</v>
+        <v>0.04705491448635655</v>
       </c>
     </row>
     <row r="310">
@@ -5696,16 +5696,16 @@
         <v>3.08</v>
       </c>
       <c r="B310" t="n">
-        <v>1.015748609965631</v>
+        <v>1.018672495317739</v>
       </c>
       <c r="C310" t="n">
-        <v>0.2343182372346778</v>
+        <v>0.2433080652039696</v>
       </c>
       <c r="D310" t="n">
-        <v>0.6951381690226446</v>
+        <v>0.6832790683246415</v>
       </c>
       <c r="E310" t="n">
-        <v>0.04512515111282369</v>
+        <v>0.04790987601230078</v>
       </c>
     </row>
     <row r="311">
@@ -5713,16 +5713,16 @@
         <v>3.09</v>
       </c>
       <c r="B311" t="n">
-        <v>1.008472273676003</v>
+        <v>1.012237819212316</v>
       </c>
       <c r="C311" t="n">
-        <v>0.2307923842003292</v>
+        <v>0.240510251118614</v>
       </c>
       <c r="D311" t="n">
-        <v>0.6951407504637642</v>
+        <v>0.6817429656690634</v>
       </c>
       <c r="E311" t="n">
-        <v>0.04592242609781873</v>
+        <v>0.04877574648143265</v>
       </c>
     </row>
     <row r="312">
@@ -5730,16 +5730,16 @@
         <v>3.1</v>
       </c>
       <c r="B312" t="n">
-        <v>1.00131652654265</v>
+        <v>1.00593701169002</v>
       </c>
       <c r="C312" t="n">
-        <v>0.2272238482511915</v>
+        <v>0.2376876101323003</v>
       </c>
       <c r="D312" t="n">
-        <v>0.6950562912388005</v>
+        <v>0.6800802224600454</v>
       </c>
       <c r="E312" t="n">
-        <v>0.04672973461407516</v>
+        <v>0.04965259475049707</v>
       </c>
     </row>
     <row r="313">
@@ -5747,16 +5747,16 @@
         <v>3.11</v>
       </c>
       <c r="B313" t="n">
-        <v>0.9942810912453899</v>
+        <v>0.9997698854436379</v>
       </c>
       <c r="C313" t="n">
-        <v>0.2236123760111068</v>
+        <v>0.2348400621590817</v>
       </c>
       <c r="D313" t="n">
-        <v>0.6948837025507585</v>
+        <v>0.6782902057904533</v>
       </c>
       <c r="E313" t="n">
-        <v>0.04754713906552142</v>
+        <v>0.05054048967623893</v>
       </c>
     </row>
     <row r="314">
@@ -5764,16 +5764,16 @@
         <v>3.12</v>
       </c>
       <c r="B314" t="n">
-        <v>0.9873656844353835</v>
+        <v>0.9937362583415199</v>
       </c>
       <c r="C314" t="n">
-        <v>0.219957714103917</v>
+        <v>0.231967527113011</v>
       </c>
       <c r="D314" t="n">
-        <v>0.694621929954919</v>
+        <v>0.6763723702022363</v>
       </c>
       <c r="E314" t="n">
-        <v>0.04837470185608604</v>
+        <v>0.0514395001154032</v>
       </c>
     </row>
     <row r="315">
@@ -5781,16 +5781,16 @@
         <v>3.13</v>
       </c>
       <c r="B315" t="n">
-        <v>0.9805700178202293</v>
+        <v>0.9878359547735704</v>
       </c>
       <c r="C315" t="n">
-        <v>0.2162596091534646</v>
+        <v>0.2290699249081413</v>
       </c>
       <c r="D315" t="n">
-        <v>0.6942699547460223</v>
+        <v>0.6743262596568718</v>
       </c>
       <c r="E315" t="n">
-        <v>0.0492124853896974</v>
+        <v>0.05234969492473474</v>
       </c>
     </row>
     <row r="316">
@@ -5798,16 +5798,16 @@
         <v>3.14</v>
       </c>
       <c r="B316" t="n">
-        <v>0.9738937992352662</v>
+        <v>0.9820688069889605</v>
       </c>
       <c r="C316" t="n">
-        <v>0.2125178077835911</v>
+        <v>0.2261471754585256</v>
       </c>
       <c r="D316" t="n">
-        <v>0.6938267953387757</v>
+        <v>0.6721515094245809</v>
       </c>
       <c r="E316" t="n">
-        <v>0.05006055207028406</v>
+        <v>0.05327114296097851</v>
       </c>
     </row>
     <row r="317">
@@ -5815,16 +5815,16 @@
         <v>3.15</v>
       </c>
       <c r="B317" t="n">
-        <v>0.9673367337015396</v>
+        <v>0.9764346564265763</v>
       </c>
       <c r="C317" t="n">
-        <v>0.208732056618139</v>
+        <v>0.223199198678217</v>
       </c>
       <c r="D317" t="n">
-        <v>0.693291508639739</v>
+        <v>0.6698478478871709</v>
       </c>
       <c r="E317" t="n">
-        <v>0.05091896430177442</v>
+        <v>0.05420391308087941</v>
       </c>
     </row>
     <row r="318">
@@ -5832,16 +5832,16 @@
         <v>3.16</v>
       </c>
       <c r="B318" t="n">
-        <v>0.9608985244709077</v>
+        <v>0.9709333550392797</v>
       </c>
       <c r="C318" t="n">
-        <v>0.2049021022809499</v>
+        <v>0.2202259144812683</v>
       </c>
       <c r="D318" t="n">
-        <v>0.6926631914085971</v>
+        <v>0.6674150982494005</v>
       </c>
       <c r="E318" t="n">
-        <v>0.05178778448809701</v>
+        <v>0.05514807414118238</v>
       </c>
     </row>
     <row r="319">
@@ -5849,16 +5849,16 @@
         <v>3.17</v>
       </c>
       <c r="B319" t="n">
-        <v>0.954578874058802</v>
+        <v>0.9655647666130702</v>
       </c>
       <c r="C319" t="n">
-        <v>0.2010276913958665</v>
+        <v>0.2172272427817328</v>
       </c>
       <c r="D319" t="n">
-        <v>0.691940981606803</v>
+        <v>0.6648531801538269</v>
       </c>
       <c r="E319" t="n">
-        <v>0.05266707503318024</v>
+        <v>0.0561036949986323</v>
       </c>
     </row>
     <row r="320">
@@ -5866,16 +5866,16 @@
         <v>3.18</v>
       </c>
       <c r="B320" t="n">
-        <v>0.948377485265161</v>
+        <v>0.9603287680822973</v>
       </c>
       <c r="C320" t="n">
-        <v>0.1971085705867302</v>
+        <v>0.2142031034936631</v>
       </c>
       <c r="D320" t="n">
-        <v>0.6911240597315327</v>
+        <v>0.6621621111941638</v>
       </c>
       <c r="E320" t="n">
-        <v>0.05355689834095264</v>
+        <v>0.05707084450997416</v>
       </c>
     </row>
     <row r="321">
@@ -5883,16 +5883,16 @@
         <v>3.19</v>
       </c>
       <c r="B321" t="n">
-        <v>0.9422940621840962</v>
+        <v>0.9552252508421041</v>
       </c>
       <c r="C321" t="n">
-        <v>0.1931444864773837</v>
+        <v>0.2111534165311127</v>
       </c>
       <c r="D321" t="n">
-        <v>0.6902116501328707</v>
+        <v>0.6593420083222663</v>
       </c>
       <c r="E321" t="n">
-        <v>0.05445731681534259</v>
+        <v>0.05804959153195277</v>
       </c>
     </row>
     <row r="322">
@@ -5900,16 +5900,16 @@
         <v>3.2</v>
       </c>
       <c r="B322" t="n">
-        <v>0.9363283112028669</v>
+        <v>0.950254122059326</v>
       </c>
       <c r="C322" t="n">
-        <v>0.1891351856916684</v>
+        <v>0.2080781018081342</v>
       </c>
       <c r="D322" t="n">
-        <v>0.6892030223121123</v>
+        <v>0.6563930891439596</v>
       </c>
       <c r="E322" t="n">
-        <v>0.0553683928602787</v>
+        <v>0.05904000492131319</v>
       </c>
     </row>
     <row r="323">
@@ -5917,16 +5917,16 @@
         <v>3.21</v>
       </c>
       <c r="B323" t="n">
-        <v>0.9304799419907611</v>
+        <v>0.9454153059831096</v>
       </c>
       <c r="C323" t="n">
-        <v>0.185080414853427</v>
+        <v>0.2049770792387809</v>
       </c>
       <c r="D323" t="n">
-        <v>0.6880974921990513</v>
+        <v>0.6533156730990504</v>
       </c>
       <c r="E323" t="n">
-        <v>0.05629018887968927</v>
+        <v>0.06004215353480018</v>
       </c>
     </row>
     <row r="324">
@@ -5934,16 +5934,16 @@
         <v>3.22</v>
       </c>
       <c r="B324" t="n">
-        <v>0.9247486684784997</v>
+        <v>0.9407087452565596</v>
       </c>
       <c r="C324" t="n">
-        <v>0.180979920586501</v>
+        <v>0.2018502687371056</v>
       </c>
       <c r="D324" t="n">
-        <v>0.6868944234060953</v>
+        <v>0.650110182520976</v>
       </c>
       <c r="E324" t="n">
-        <v>0.05722276727750293</v>
+        <v>0.0610561062291588</v>
       </c>
     </row>
     <row r="325">
@@ -5951,16 +5951,16 @@
         <v>3.23</v>
       </c>
       <c r="B325" t="n">
-        <v>0.9191342098288235</v>
+        <v>0.9361344022307683</v>
       </c>
       <c r="C325" t="n">
-        <v>0.1768334495147329</v>
+        <v>0.1986975902171615</v>
       </c>
       <c r="D325" t="n">
-        <v>0.6855932284570395</v>
+        <v>0.6467771435717146</v>
       </c>
       <c r="E325" t="n">
-        <v>0.05816619045764801</v>
+        <v>0.06208193186113387</v>
       </c>
     </row>
     <row r="326">
@@ -5968,16 +5968,16 @@
         <v>3.24</v>
       </c>
       <c r="B326" t="n">
-        <v>0.9136362913989107</v>
+        <v>0.9316922602826229</v>
       </c>
       <c r="C326" t="n">
-        <v>0.1726407482619644</v>
+        <v>0.1955189635930014</v>
       </c>
       <c r="D326" t="n">
-        <v>0.6841933699883104</v>
+        <v>0.6433171870477128</v>
       </c>
       <c r="E326" t="n">
-        <v>0.05912052082405309</v>
+        <v>0.06311969928747038</v>
       </c>
     </row>
     <row r="327">
@@ -5985,16 +5985,16 @@
         <v>3.25</v>
       </c>
       <c r="B327" t="n">
-        <v>0.9082546456953322</v>
+        <v>0.9273823251378329</v>
       </c>
       <c r="C327" t="n">
-        <v>0.168401563452038</v>
+        <v>0.1923143087786784</v>
       </c>
       <c r="D327" t="n">
-        <v>0.6826943619204865</v>
+        <v>0.6397310490527893</v>
       </c>
       <c r="E327" t="n">
-        <v>0.06008582078064657</v>
+        <v>0.06416947736491319</v>
       </c>
     </row>
     <row r="328">
@@ -6002,16 +6002,16 @@
         <v>3.26</v>
       </c>
       <c r="B328" t="n">
-        <v>0.9029890133222437</v>
+        <v>0.9232046262006649</v>
       </c>
       <c r="C328" t="n">
-        <v>0.1641156417087953</v>
+        <v>0.1890835456882455</v>
       </c>
       <c r="D328" t="n">
-        <v>0.6810957705978974</v>
+        <v>0.6360195715341428</v>
       </c>
       <c r="E328" t="n">
-        <v>0.06106215273135696</v>
+        <v>0.06523133495020728</v>
       </c>
     </row>
     <row r="329">
@@ -6019,16 +6019,16 @@
         <v>3.27</v>
       </c>
       <c r="B329" t="n">
-        <v>0.8978391439235601</v>
+        <v>0.9191592178919328</v>
       </c>
       <c r="C329" t="n">
-        <v>0.1597827296560787</v>
+        <v>0.1858265942357558</v>
       </c>
       <c r="D329" t="n">
-        <v>0.6793972158940961</v>
+        <v>0.6321837026778079</v>
       </c>
       <c r="E329" t="n">
-        <v>0.06204957908011268</v>
+        <v>0.06630534090009749</v>
       </c>
     </row>
     <row r="330">
@@ -6036,16 +6036,16 @@
         <v>3.28</v>
       </c>
       <c r="B330" t="n">
-        <v>0.8928047971198632</v>
+        <v>0.9152461809968206</v>
       </c>
       <c r="C330" t="n">
-        <v>0.15540257391773</v>
+        <v>0.1825433743352622</v>
       </c>
       <c r="D330" t="n">
-        <v>0.6775983722810029</v>
+        <v>0.6282244971601179</v>
       </c>
       <c r="E330" t="n">
-        <v>0.06304816223084227</v>
+        <v>0.06739156407132882</v>
       </c>
     </row>
     <row r="331">
@@ -6053,16 +6053,16 @@
         <v>3.29</v>
       </c>
       <c r="B331" t="n">
-        <v>0.887885743440823</v>
+        <v>0.9114656240241866</v>
       </c>
       <c r="C331" t="n">
-        <v>0.1509749211175916</v>
+        <v>0.1792338059008179</v>
       </c>
       <c r="D331" t="n">
-        <v>0.6756989698595358</v>
+        <v>0.6241431162519698</v>
       </c>
       <c r="E331" t="n">
-        <v>0.06405796458747412</v>
+        <v>0.06849007332064613</v>
       </c>
     </row>
     <row r="332">
@@ -6070,16 +6070,16 @@
         <v>3.3</v>
       </c>
       <c r="B332" t="n">
-        <v>0.8830817652539442</v>
+        <v>0.9078176845790408</v>
       </c>
       <c r="C332" t="n">
-        <v>0.1464995178795052</v>
+        <v>0.1758978088464755</v>
       </c>
       <c r="D332" t="n">
-        <v>0.6736987953495338</v>
+        <v>0.61994082777293</v>
       </c>
       <c r="E332" t="n">
-        <v>0.06507904855393679</v>
+        <v>0.0696009375047944</v>
       </c>
     </row>
     <row r="333">
@@ -6087,16 +6087,16 @@
         <v>3.31</v>
       </c>
       <c r="B333" t="n">
-        <v>0.878392657690453</v>
+        <v>0.9043025307499476</v>
       </c>
       <c r="C333" t="n">
-        <v>0.1419761108273131</v>
+        <v>0.1725353030862885</v>
       </c>
       <c r="D333" t="n">
-        <v>0.6715976930368152</v>
+        <v>0.6156190058924832</v>
       </c>
       <c r="E333" t="n">
-        <v>0.06611147653415865</v>
+        <v>0.07072422548051846</v>
       </c>
     </row>
     <row r="334">
@@ -6104,16 +6104,16 @@
         <v>3.32</v>
       </c>
       <c r="B334" t="n">
-        <v>0.873818229569184</v>
+        <v>0.9009203625131635</v>
       </c>
       <c r="C334" t="n">
-        <v>0.1374044465848571</v>
+        <v>0.1691462085343095</v>
       </c>
       <c r="D334" t="n">
-        <v>0.6693955656752186</v>
+        <v>0.6111791307760023</v>
       </c>
       <c r="E334" t="n">
-        <v>0.06715531093206828</v>
+        <v>0.07186000610456335</v>
       </c>
     </row>
     <row r="335">
@@ -6121,16 +6121,16 @@
         <v>3.33</v>
       </c>
       <c r="B335" t="n">
-        <v>0.869358304319342</v>
+        <v>0.89767141315538</v>
       </c>
       <c r="C335" t="n">
-        <v>0.1327842717759797</v>
+        <v>0.1657304451045918</v>
       </c>
       <c r="D335" t="n">
-        <v>0.6670923753415068</v>
+        <v>0.6066227880733003</v>
       </c>
       <c r="E335" t="n">
-        <v>0.06821061415159403</v>
+        <v>0.07300834823367386</v>
       </c>
     </row>
     <row r="336">
@@ -6138,16 +6138,16 @@
         <v>3.34</v>
       </c>
       <c r="B336" t="n">
-        <v>0.8650127209030318</v>
+        <v>0.8945559507169998</v>
       </c>
       <c r="C336" t="n">
-        <v>0.1281153330245227</v>
+        <v>0.1622879327111884</v>
       </c>
       <c r="D336" t="n">
-        <v>0.6646881442410364</v>
+        <v>0.6019516682479266</v>
       </c>
       <c r="E336" t="n">
-        <v>0.06927744859666442</v>
+        <v>0.07416932072459496</v>
       </c>
     </row>
     <row r="337">
@@ -6155,16 +6155,16 @@
         <v>3.35</v>
       </c>
       <c r="B337" t="n">
-        <v>0.8607813347384879</v>
+        <v>0.8915742794579579</v>
       </c>
       <c r="C337" t="n">
-        <v>0.1233973769543279</v>
+        <v>0.158818591268152</v>
       </c>
       <c r="D337" t="n">
-        <v>0.6621829554621382</v>
+        <v>0.5971675657456817</v>
       </c>
       <c r="E337" t="n">
-        <v>0.07035587667120799</v>
+        <v>0.07534299243407164</v>
       </c>
     </row>
     <row r="338">
@@ -6172,16 +6172,16 @@
         <v>3.36</v>
       </c>
       <c r="B338" t="n">
-        <v>0.8566640186249559</v>
+        <v>0.8887267413481418</v>
       </c>
       <c r="C338" t="n">
-        <v>0.1186301501892379</v>
+        <v>0.1553223406895359</v>
       </c>
       <c r="D338" t="n">
-        <v>0.6595769536771853</v>
+        <v>0.5922723780011502</v>
       </c>
       <c r="E338" t="n">
-        <v>0.07144596077915309</v>
+        <v>0.0765294322188487</v>
       </c>
     </row>
     <row r="339">
@@ -6189,16 +6189,16 @@
         <v>3.37</v>
       </c>
       <c r="B339" t="n">
-        <v>0.8526606636701937</v>
+        <v>0.8860137175845617</v>
       </c>
       <c r="C339" t="n">
-        <v>0.1138133993530942</v>
+        <v>0.1517991008893929</v>
       </c>
       <c r="D339" t="n">
-        <v>0.6568703457883672</v>
+        <v>0.5872681042813668</v>
       </c>
       <c r="E339" t="n">
-        <v>0.0725477633244283</v>
+        <v>0.07772870893567117</v>
       </c>
     </row>
     <row r="340">
@@ -6206,16 +6206,16 @@
         <v>3.38</v>
       </c>
       <c r="B340" t="n">
-        <v>0.8487711802216099</v>
+        <v>0.8834356301374823</v>
       </c>
       <c r="C340" t="n">
-        <v>0.1089468710697395</v>
+        <v>0.1482487917817764</v>
       </c>
       <c r="D340" t="n">
-        <v>0.6540634015162531</v>
+        <v>0.5821568443661075</v>
       </c>
       <c r="E340" t="n">
-        <v>0.07366134671096199</v>
+        <v>0.07894089144128387</v>
       </c>
     </row>
     <row r="341">
@@ -6223,16 +6223,16 @@
         <v>3.39</v>
       </c>
       <c r="B341" t="n">
-        <v>0.8449954988020669</v>
+        <v>0.8809929433278132</v>
       </c>
       <c r="C341" t="n">
-        <v>0.1040303119630152</v>
+        <v>0.1446713332807389</v>
       </c>
       <c r="D341" t="n">
-        <v>0.6511564539292529</v>
+        <v>0.5769407970645988</v>
       </c>
       <c r="E341" t="n">
-        <v>0.0747867733426827</v>
+        <v>0.08016604859243182</v>
       </c>
     </row>
     <row r="342">
@@ -6240,16 +6240,16 @@
         <v>3.4</v>
       </c>
       <c r="B342" t="n">
-        <v>0.8413335710514097</v>
+        <v>0.8786861654381362</v>
       </c>
       <c r="C342" t="n">
-        <v>0.09906346865676391</v>
+        <v>0.1410666453003337</v>
       </c>
       <c r="D342" t="n">
-        <v>0.6481498999121745</v>
+        <v>0.5716222585688575</v>
       </c>
       <c r="E342" t="n">
-        <v>0.07592410562351887</v>
+        <v>0.08140424924585982</v>
       </c>
     </row>
     <row r="343">
@@ -6257,16 +6257,16 @@
         <v>3.41</v>
       </c>
       <c r="B343" t="n">
-        <v>0.8377853706748198</v>
+        <v>0.8765158503598348</v>
       </c>
       <c r="C343" t="n">
-        <v>0.09404608777482726</v>
+        <v>0.1374346477546138</v>
       </c>
       <c r="D343" t="n">
-        <v>0.6450442005721102</v>
+        <v>0.5662036206441777</v>
       </c>
       <c r="E343" t="n">
-        <v>0.07707340595739898</v>
+        <v>0.08265556225831289</v>
       </c>
     </row>
     <row r="344">
@@ -6274,16 +6274,16 @@
         <v>3.42</v>
       </c>
       <c r="B344" t="n">
-        <v>0.8343508943991117</v>
+        <v>0.8744825992788857</v>
       </c>
       <c r="C344" t="n">
-        <v>0.0889779159410477</v>
+        <v>0.1337752605576322</v>
       </c>
       <c r="D344" t="n">
-        <v>0.6418398815799784</v>
+        <v>0.5606873686577092</v>
       </c>
       <c r="E344" t="n">
-        <v>0.07823473674825146</v>
+        <v>0.0839200564865359</v>
       </c>
     </row>
     <row r="345">
@@ -6291,16 +6291,16 @@
         <v>3.43</v>
       </c>
       <c r="B345" t="n">
-        <v>0.8310301629381347</v>
+        <v>0.8725870624029601</v>
       </c>
       <c r="C345" t="n">
-        <v>0.08385869977926691</v>
+        <v>0.1300884036234418</v>
       </c>
       <c r="D345" t="n">
-        <v>0.6385375334460962</v>
+        <v>0.555076079446406</v>
       </c>
       <c r="E345" t="n">
-        <v>0.07940816040000488</v>
+        <v>0.08519780078727382</v>
       </c>
     </row>
     <row r="346">
@@ -6308,16 +6308,16 @@
         <v>3.44</v>
       </c>
       <c r="B346" t="n">
-        <v>0.827823221968471</v>
+        <v>0.8708299407325991</v>
       </c>
       <c r="C346" t="n">
-        <v>0.07868818591332732</v>
+        <v>0.1263739968660958</v>
       </c>
       <c r="D346" t="n">
-        <v>0.6351378117282603</v>
+        <v>0.5493724190260387</v>
       </c>
       <c r="E346" t="n">
-        <v>0.08059373931658759</v>
+        <v>0.08648886401727146</v>
       </c>
     </row>
     <row r="347">
@@ -6325,16 +6325,16 @@
         <v>3.45</v>
       </c>
       <c r="B347" t="n">
-        <v>0.8247301431166494</v>
+        <v>0.8692119878793114</v>
       </c>
       <c r="C347" t="n">
-        <v>0.07346612096707067</v>
+        <v>0.1226319601996469</v>
       </c>
       <c r="D347" t="n">
-        <v>0.6316414371708722</v>
+        <v>0.543579140143325</v>
       </c>
       <c r="E347" t="n">
-        <v>0.08179153590192814</v>
+        <v>0.08779331503327389</v>
       </c>
     </row>
     <row r="348">
@@ -6342,16 +6342,16 @@
         <v>3.46</v>
       </c>
       <c r="B348" t="n">
-        <v>0.8217510249591505</v>
+        <v>0.8677340119335791</v>
       </c>
       <c r="C348" t="n">
-        <v>0.06819225156433933</v>
+        <v>0.1188622135381485</v>
       </c>
       <c r="D348" t="n">
-        <v>0.6280491957737522</v>
+        <v>0.5376990796736387</v>
       </c>
       <c r="E348" t="n">
-        <v>0.08300161255995495</v>
+        <v>0.08911122269202587</v>
       </c>
     </row>
     <row r="349">
@@ -6359,16 +6359,16 @@
         <v>3.47</v>
       </c>
       <c r="B349" t="n">
-        <v>0.8188859940364933</v>
+        <v>0.8663968773858496</v>
       </c>
       <c r="C349" t="n">
-        <v>0.06286632432897499</v>
+        <v>0.1150646767956533</v>
       </c>
       <c r="D349" t="n">
-        <v>0.6243619387893645</v>
+        <v>0.531735155867132</v>
       </c>
       <c r="E349" t="n">
-        <v>0.08422403169459652</v>
+        <v>0.09044265585027247</v>
       </c>
     </row>
     <row r="350">
@@ -6376,16 +6376,16 @@
         <v>3.48</v>
       </c>
       <c r="B350" t="n">
-        <v>0.816135205882754</v>
+        <v>0.8652015071037404</v>
       </c>
       <c r="C350" t="n">
-        <v>0.05748808588482018</v>
+        <v>0.1112392698862146</v>
       </c>
       <c r="D350" t="n">
-        <v>0.6205805826472794</v>
+        <v>0.5256903654465056</v>
       </c>
       <c r="E350" t="n">
-        <v>0.0854588557097813</v>
+        <v>0.09178768336475848</v>
       </c>
     </row>
     <row r="351">
@@ -6393,16 +6393,16 @@
         <v>3.49</v>
       </c>
       <c r="B351" t="n">
-        <v>0.8134988460718932</v>
+        <v>0.8641488843687901</v>
       </c>
       <c r="C351" t="n">
-        <v>0.05205728285571648</v>
+        <v>0.107385912723885</v>
       </c>
       <c r="D351" t="n">
-        <v>0.6167061088047943</v>
+        <v>0.5195677805600338</v>
       </c>
       <c r="E351" t="n">
-        <v>0.0867061470094378</v>
+        <v>0.09314637409222892</v>
       </c>
     </row>
     <row r="352">
@@ -6410,16 +6410,16 @@
         <v>3.5</v>
       </c>
       <c r="B352" t="n">
-        <v>0.810977131282329</v>
+        <v>0.8632400549762426</v>
       </c>
       <c r="C352" t="n">
-        <v>0.04657366186550638</v>
+        <v>0.103504525222718</v>
       </c>
       <c r="D352" t="n">
-        <v>0.6127395635227495</v>
+        <v>0.5133705455938566</v>
       </c>
       <c r="E352" t="n">
-        <v>0.08796596799749443</v>
+        <v>0.09451879688942862</v>
       </c>
     </row>
   </sheetData>
